--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.87537282600714e-08</v>
+        <v>1.875372826007131e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.787358206402762e-08</v>
+        <v>1.787358206402765e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.915840950407171e-08</v>
+        <v>1.915840950407164e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.852473520843315e-08</v>
+        <v>1.852473520843311e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.890164316837448e-08</v>
+        <v>1.890164316837442e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.259635264125678e-08</v>
+        <v>2.259635264125674e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.889223508416999e-08</v>
+        <v>1.88922350841699e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.942698615937391e-08</v>
+        <v>1.942698615937393e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.994039153011346e-08</v>
+        <v>1.994039153011351e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.02185023956088e-08</v>
+        <v>2.021850239560876e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.890953719601147e-08</v>
+        <v>1.890953719601153e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.91833549354779e-08</v>
+        <v>1.918335493547792e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.965363908710751e-08</v>
+        <v>1.965363908710747e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.018420830157299e-08</v>
+        <v>3.018420830157302e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.877464029098459e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.871821338393782e-08</v>
+        <v>1.871821338393776e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.884672061805798e-08</v>
+        <v>1.88467206180579e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.870909479220332e-08</v>
+        <v>1.870909479220327e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.921882484786732e-08</v>
+        <v>1.92188248478673e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.638363472979502e-08</v>
+        <v>2.638363472979511e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.863391140788974e-08</v>
+        <v>1.863391140788973e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.70343184754331e-08</v>
+        <v>2.703431847543327e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.859500965113374e-08</v>
+        <v>1.859500965113381e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.860414830943414e-08</v>
+        <v>1.860414830943407e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.957157242845571e-08</v>
+        <v>2.957157242845569e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.947032856083525e-08</v>
+        <v>1.947032856083533e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.903560479260924e-08</v>
+        <v>1.903560479260926e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,82 +674,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.70012243967086e-08</v>
+        <v>1.700122439670869e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.442688638852427e-08</v>
+        <v>1.442688638852431e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.991909714548826e-08</v>
+        <v>1.991909714548827e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.537082685047671e-08</v>
+        <v>1.537082685047675e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.808727248919891e-08</v>
+        <v>1.808727248919896e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.436102485840622e-08</v>
+        <v>4.436102485840624e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.802455430988925e-08</v>
+        <v>1.802455430988939e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.18472855694264e-08</v>
+        <v>2.184728556942649e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.545998374083915e-08</v>
+        <v>2.545998374083921e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.750138518822899e-08</v>
+        <v>2.750138518822895e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.812345460935989e-08</v>
+        <v>1.812345460935986e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.03716517840945e-08</v>
+        <v>2.037165178409452e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.344778851594541e-08</v>
+        <v>2.344778851594538e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.679757315572765e-08</v>
+        <v>3.679757315572767e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.715133845650451e-08</v>
+        <v>1.715133845650454e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.676439793108966e-08</v>
+        <v>1.676439793108968e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.769357004957745e-08</v>
+        <v>1.769357004957752e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.668792281187171e-08</v>
+        <v>1.668792281187172e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.035312545901123e-08</v>
+        <v>2.035312545901126e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.126654789854675e-08</v>
+        <v>3.12665478985468e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.614613325967881e-08</v>
+        <v>1.614613325967894e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.139367590140072e-08</v>
+        <v>3.139367590140088e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.588463099214178e-08</v>
+        <v>1.588463099214177e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.594614557944453e-08</v>
+        <v>1.594614557944454e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.463056707387719e-08</v>
+        <v>3.463056707387723e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.213213942031628e-08</v>
+        <v>2.213213942031627e-08</v>
       </c>
       <c r="AB3" t="n">
         <v>1.917058411358372e-08</v>
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.196453320278621e-08</v>
+        <v>6.196453320278625e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.961286566424155e-08</v>
+        <v>5.961286566424164e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.65355940163393e-08</v>
+        <v>6.653559401633935e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.937795134252388e-08</v>
+        <v>5.937795134252391e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.363530013628919e-08</v>
+        <v>6.363530013628925e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.053687432828237e-07</v>
+        <v>1.053687432828238e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>6.352903149726682e-08</v>
+        <v>6.352903149726688e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.956929088934378e-08</v>
+        <v>6.956929088934379e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.529573591124599e-08</v>
+        <v>7.529573591124607e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.850983089307468e-08</v>
+        <v>7.850983089307472e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.372446680988233e-08</v>
+        <v>6.372446680988242e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.730985970516445e-08</v>
+        <v>6.73098597051645e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.212943997359248e-08</v>
+        <v>7.212943997359255e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.389378157314913e-08</v>
+        <v>6.389378157314912e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.220074421196109e-08</v>
+        <v>6.220074421196118e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.156337633920727e-08</v>
+        <v>6.156337633920724e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.301492466484274e-08</v>
+        <v>6.301492466484279e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.146037765080638e-08</v>
+        <v>6.14603776508064e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.721801311694217e-08</v>
+        <v>6.721801311694222e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.484494509661411e-08</v>
+        <v>6.484494509661408e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>6.011848204579111e-08</v>
+        <v>6.011848204579115e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.342944451975167e-08</v>
+        <v>6.342944451975174e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.017173350066927e-08</v>
+        <v>6.017173350066929e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.97496407503907e-08</v>
+        <v>5.974964075039072e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.14873445964021e-08</v>
+        <v>6.148734459640215e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.005886325234036e-08</v>
+        <v>7.005886325234043e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.536110219685732e-08</v>
+        <v>6.536110219685736e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,52 +850,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5113994012877e-07</v>
+        <v>1.511399401287702e-07</v>
       </c>
       <c r="C5" t="n">
         <v>1.129495879891756e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.608093055770977e-07</v>
+        <v>2.60809305577098e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.013918657364093e-07</v>
+        <v>1.013918657364089e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>2.02837192564528e-07</v>
+        <v>2.028371925645277e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.864549917212457e-07</v>
+        <v>9.864549917212451e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.033288244743565e-07</v>
+        <v>2.033288244743567e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.286434090931091e-07</v>
+        <v>3.28643409093109e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>4.147431748300306e-07</v>
+        <v>4.147431748300308e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.116636223448058e-07</v>
+        <v>5.116636223448062e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.926519466694341e-07</v>
+        <v>1.926519466694343e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.805232484147054e-07</v>
+        <v>2.805232484147056e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.295273662040351e-07</v>
+        <v>2.295273662040346e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.847518354694036e-07</v>
+        <v>1.847518354694034e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.564101523546081e-07</v>
+        <v>1.564101523546076e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.529544403175759e-07</v>
+        <v>1.529544403175755e-07</v>
       </c>
       <c r="R5" t="n">
         <v>1.893233931038871e-07</v>
@@ -904,31 +904,31 @@
         <v>1.441074896354104e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.762403017972604e-07</v>
+        <v>2.762403017972595e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.227681894268274e-07</v>
+        <v>2.227681894268265e-07</v>
       </c>
       <c r="V5" t="n">
         <v>1.234213399097192e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.879464498104565e-07</v>
+        <v>1.879464498104567e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.246588684686192e-07</v>
+        <v>1.246588684686185e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.245334753818375e-07</v>
+        <v>1.245334753818363e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.440788395148644e-07</v>
+        <v>1.440788395148643e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.239508622348084e-07</v>
+        <v>3.239508622348083e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.445373859696002e-07</v>
+        <v>2.445373859696001e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.024899786133326e-08</v>
+        <v>7.054810894410522e-08</v>
       </c>
       <c r="C6" t="n">
         <v>6.819644140556059e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.482005867488636e-08</v>
+        <v>6.482005867488628e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.796152708384286e-08</v>
+        <v>5.766241600107085e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.191976479483625e-08</v>
+        <v>7.221887587760821e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.036532079413709e-07</v>
+        <v>1.139523190241428e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>7.211260723858579e-08</v>
+        <v>7.211260723858582e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.815286663066271e-08</v>
+        <v>6.785375554789071e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.358020056979297e-08</v>
+        <v>8.387931165256503e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.679429555162165e-08</v>
+        <v>7.679429555162167e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.230804255120134e-08</v>
+        <v>6.200893146842936e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.559432436371148e-08</v>
+        <v>6.559432436371144e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.043341397742748e-08</v>
+        <v>7.043341397742756e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.274055203049507e-08</v>
+        <v>7.274055203049511e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.104760750458272e-08</v>
+        <v>7.104760750458277e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.984784099775428e-08</v>
+        <v>5.98478409977542e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.159850040616171e-08</v>
+        <v>6.12993893233897e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.004395339212529e-08</v>
+        <v>7.004395339212536e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.550247777548926e-08</v>
+        <v>6.550247777548919e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.365472785493191e-08</v>
+        <v>6.365472785493181e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.870205778711006e-08</v>
+        <v>6.87020577871101e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.193484352417754e-08</v>
+        <v>7.227627030898934e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.875530924198819e-08</v>
+        <v>6.875530924198828e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.866399422145292e-08</v>
+        <v>5.866399422145294e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.977180925494916e-08</v>
+        <v>5.97718092549491e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.864243899365939e-08</v>
+        <v>6.834332791088737e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.368372113352942e-08</v>
+        <v>6.368372113352943e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.949078086703709e-08</v>
+        <v>6.949078086703711e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.713911332849247e-08</v>
+        <v>6.71391133284925e-08</v>
       </c>
       <c r="D7" t="n">
         <v>7.40618416805902e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.690419900677475e-08</v>
+        <v>6.690419900677478e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.11615478005401e-08</v>
+        <v>7.116154780054013e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.128949909470746e-07</v>
+        <v>1.128949909470747e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>7.105527916151767e-08</v>
+        <v>7.105527916151774e-08</v>
       </c>
       <c r="I7" t="n">
         <v>7.709553855359464e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>8.282198357549687e-08</v>
+        <v>8.28219835754969e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.603607855732555e-08</v>
+        <v>8.603607855732557e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.125071447413322e-08</v>
+        <v>7.125071447413329e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>7.48361073694153e-08</v>
+        <v>7.483610736941533e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.965568763784338e-08</v>
+        <v>7.965568763784342e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>7.141856549346693e-08</v>
+        <v>7.141856549346691e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.972552813227898e-08</v>
+        <v>6.972552813227901e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.908962400345808e-08</v>
+        <v>6.90896240034581e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.054117232909362e-08</v>
+        <v>7.054117232909365e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.898662531505724e-08</v>
+        <v>6.898662531505725e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.474426078119309e-08</v>
+        <v>7.474426078119312e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>7.288484236648911e-08</v>
+        <v>7.28848423664891e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.7644729710042e-08</v>
+        <v>6.764472971004202e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.095569218400253e-08</v>
+        <v>7.095569218400255e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.769798116492015e-08</v>
+        <v>6.769798116492013e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.780120651441235e-08</v>
+        <v>6.780120651441234e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.901359226065299e-08</v>
+        <v>6.9013592260653e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>7.758511091659127e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.288734986110819e-08</v>
+        <v>7.28873498611082e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,79 +1114,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.039709058405817e-08</v>
+        <v>8.039709058405824e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>9.334160893742818e-08</v>
+        <v>9.334160893742834e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.002643372895259e-07</v>
+        <v>1.00264337289526e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>9.310669461571057e-08</v>
+        <v>8.496192683743625e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>8.445082450869124e-08</v>
+        <v>8.44508245086913e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.390974865560105e-07</v>
+        <v>1.422692503461324e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.725777477045345e-08</v>
+        <v>9.72577747704536e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.032980341625304e-07</v>
+        <v>1.032980341625305e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.090244791844327e-07</v>
+        <v>1.090244791844328e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.122385741662614e-07</v>
+        <v>1.122385741662615e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.745321008306904e-08</v>
+        <v>9.745321008306912e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>1.010386029783511e-07</v>
+        <v>1.010386029783497e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>9.400108018376845e-08</v>
+        <v>9.400108018376856e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>8.902385665807965e-08</v>
+        <v>8.902385665807971e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.653209817431142e-08</v>
+        <v>8.653209817431155e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.698988407398907e-08</v>
+        <v>7.698988407398911e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>9.674366793802938e-08</v>
+        <v>9.67436679380295e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>9.518912092399303e-08</v>
+        <v>9.518912092399319e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.009467563901288e-07</v>
+        <v>1.009467563901289e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>8.967910421078878e-08</v>
+        <v>9.162523385993417e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>9.384722531897772e-08</v>
+        <v>8.96578243076353e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>9.716119393051312e-08</v>
+        <v>9.716119393051321e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.700016706590873e-08</v>
+        <v>7.700016706590881e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.091988225679538e-07</v>
+        <v>1.091988225679539e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.521608786958875e-08</v>
+        <v>7.963576747123858e-08</v>
       </c>
       <c r="AA8" t="n">
         <v>1.037876065255271e-07</v>
@@ -1202,25 +1202,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.927225745771606e-08</v>
+        <v>9.927225745771611e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.087983177208172e-07</v>
+        <v>1.087983177208173e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.157210460729149e-07</v>
+        <v>1.15721046072915e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.085634033990995e-07</v>
+        <v>1.058220836117082e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>1.128207521928649e-07</v>
+        <v>8.543932862613288e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.545541953393994e-07</v>
+        <v>1.545542100830282e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.127144835538425e-07</v>
+        <v>1.127144835538426e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.187547429459194e-07</v>
@@ -1238,49 +1238,49 @@
         <v>1.164953117617401e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.213148920301681e-07</v>
+        <v>1.213148920301682e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.170155167002809e-07</v>
+        <v>1.170155167002808e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.161785501652086e-07</v>
+        <v>1.161785501652087e-07</v>
       </c>
       <c r="Q9" t="n">
         <v>1.107488431394116e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.122003767214183e-07</v>
+        <v>1.122003767214184e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.106458297073819e-07</v>
+        <v>1.10645829707382e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.164034651735178e-07</v>
+        <v>1.164034651735179e-07</v>
       </c>
       <c r="U9" t="n">
         <v>1.145557152529605e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>1.093039341023668e-07</v>
+        <v>1.230105951435379e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.126148965763273e-07</v>
+        <v>1.126148965763274e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.093571855572448e-07</v>
+        <v>1.093571855572449e-07</v>
       </c>
       <c r="Y9" t="n">
         <v>1.094604109067372e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.106727966529778e-07</v>
+        <v>1.035115888518834e-07</v>
       </c>
       <c r="AA9" t="n">
         <v>1.19244315308916e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.145465542534329e-07</v>
+        <v>1.14546554253433e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.462315401723618e-08</v>
+        <v>1.462315401723614e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.383510869874597e-08</v>
+        <v>1.383510869874595e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.465022438805023e-08</v>
+        <v>1.46502243880502e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.465098560936734e-08</v>
+        <v>1.465098560936731e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.477116876782966e-08</v>
+        <v>1.477116876782962e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.481932023560938e-08</v>
+        <v>1.481932023560932e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.466695482746204e-08</v>
+        <v>1.466695482746199e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.470084690476515e-08</v>
+        <v>1.470084690476511e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.477949815836981e-08</v>
+        <v>1.47794981583698e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.473271307134669e-08</v>
+        <v>1.473271307134665e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.484091213823365e-08</v>
+        <v>1.484091213823361e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.463063920305007e-08</v>
+        <v>1.463063920305006e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.466695164278903e-08</v>
+        <v>1.4666951642789e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.402842684901695e-08</v>
+        <v>2.402842684901694e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.474122961693018e-08</v>
+        <v>1.474122961693013e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.466551502402184e-08</v>
+        <v>1.466551502402181e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.496052582431779e-08</v>
+        <v>1.496052582431777e-08</v>
       </c>
       <c r="S2" t="n">
         <v>1.476603073311987e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.468171868425485e-08</v>
+        <v>1.468171868425481e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.103945404023683e-08</v>
+        <v>2.103945404023686e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.493776824071653e-08</v>
+        <v>1.493776824071651e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.230155987322169e-08</v>
+        <v>2.23015598732216e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.521041870622177e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.490973018787749e-08</v>
+        <v>1.490973018787746e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.532472195835266e-08</v>
+        <v>2.532472195835261e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.490155271509137e-08</v>
+        <v>1.490155271509133e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.460656406298657e-08</v>
+        <v>1.460656406298656e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1540,16 +1540,16 @@
         <v>1.075302120385976e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.190770633509049e-08</v>
+        <v>1.19077063350905e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.190244256910546e-08</v>
+        <v>1.190244256910544e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.277272784150323e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.310142325426564e-08</v>
+        <v>1.310142325426561e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.203105534184013e-08</v>
@@ -1558,13 +1558,13 @@
         <v>1.227086279039242e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.282331970091395e-08</v>
+        <v>1.282331970091389e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.249188133204733e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.325794356124219e-08</v>
+        <v>1.325794356124221e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.199891989560947e-08</v>
@@ -1573,46 +1573,46 @@
         <v>1.202692791368604e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.744803797793655e-08</v>
+        <v>2.744803797793657e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.254752320598796e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.201444720427597e-08</v>
+        <v>1.201444720427598e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.413263496828314e-08</v>
+        <v>1.413263496828315e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.272426212557865e-08</v>
+        <v>1.272426212557868e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.213414758824e-08</v>
+        <v>1.213414758823996e-08</v>
       </c>
       <c r="U3" t="n">
         <v>2.288856873309747e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.393776494815985e-08</v>
+        <v>1.393776494815986e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.76990989083468e-08</v>
+        <v>2.769909890834677e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.589910270387024e-08</v>
+        <v>1.589910270387016e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.376054218939367e-08</v>
+        <v>1.376054218939365e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.984049422416131e-08</v>
+        <v>2.984049422416133e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.370137123013724e-08</v>
+        <v>1.370137123013726e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.166280794670539e-08</v>
+        <v>1.16628079467054e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.24540227107663e-08</v>
+        <v>5.245402271076633e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.315836290183825e-08</v>
+        <v>5.315836290183824e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.275979500209693e-08</v>
+        <v>5.275979500209694e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.276839334705281e-08</v>
+        <v>5.276839334705285e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.412591740886897e-08</v>
+        <v>5.412591740886899e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.466981038821025e-08</v>
+        <v>5.46698103882103e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.294877301163544e-08</v>
+        <v>5.294877301163546e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.333159961589998e-08</v>
+        <v>5.333159961590001e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.417662551465194e-08</v>
+        <v>5.417662551465193e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.369154262659929e-08</v>
+        <v>5.369154262659933e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.491370086111743e-08</v>
+        <v>5.491370086111745e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.296142748917884e-08</v>
+        <v>5.296142748917887e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.289580223708985e-08</v>
+        <v>5.289580223708988e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.378774092676921e-08</v>
+        <v>5.378774092676923e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.293250976943635e-08</v>
+        <v>5.293250976943636e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.626479247045234e-08</v>
+        <v>5.626479247045236e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.40678809432092e-08</v>
+        <v>5.406788094320922e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.311553756581979e-08</v>
+        <v>5.311553756581981e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.377839173277482e-08</v>
+        <v>5.377839173277484e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.571246766055885e-08</v>
+        <v>5.57124676605589e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.927342693511102e-08</v>
+        <v>5.927342693511104e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.908744752796279e-08</v>
+        <v>5.908744752796284e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>5.582359346712614e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.342367793839148e-08</v>
+        <v>5.342367793839151e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.559866407276922e-08</v>
+        <v>5.559866407276925e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.238486439809061e-08</v>
+        <v>5.238486439809067e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.109616985486283e-08</v>
+        <v>7.109616985486287e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.526941524411493e-08</v>
+        <v>8.526941524411498e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.873495331780558e-08</v>
+        <v>7.873495331780562e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.33437661725639e-08</v>
+        <v>7.334376617256398e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.038482519460092e-07</v>
+        <v>1.038482519460091e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.057131758457072e-07</v>
+        <v>1.057131758457075e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.412071495636027e-08</v>
+        <v>8.412071495636031e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.981269307334811e-08</v>
+        <v>8.981269307334806e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.008798166510892e-07</v>
+        <v>1.00879816651089e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.285608584818827e-08</v>
+        <v>9.28560858481883e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.112797561034229e-07</v>
+        <v>1.112797561034228e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.294778358720933e-08</v>
+        <v>8.294778358720935e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.794351204774818e-08</v>
+        <v>7.79435120477482e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.18932477429156e-08</v>
+        <v>9.18932477429155e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.055157626596074e-08</v>
+        <v>8.055157626596078e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.460600889424608e-07</v>
+        <v>1.460600889424609e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.670916259941261e-08</v>
+        <v>9.670916259941255e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.588963522522025e-08</v>
+        <v>8.588963522522031e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.047874002925391e-08</v>
+        <v>9.047874002925392e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.244029775396929e-07</v>
+        <v>1.244029775396931e-07</v>
       </c>
       <c r="W5" t="n">
         <v>1.927464656810582e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.871579210005979e-07</v>
+        <v>1.871579210005983e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.309570399278663e-07</v>
+        <v>1.30957039927866e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>8.535572963513061e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.289046654300244e-07</v>
+        <v>1.289046654300245e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.338331290530098e-08</v>
+        <v>7.338331290530112e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.732967395011303e-08</v>
+        <v>5.111243365818451e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.803401414118495e-08</v>
+        <v>5.181677384925647e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.763544624144362e-08</v>
+        <v>5.763544624144368e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.764404458639953e-08</v>
+        <v>5.142680429447103e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.900156864821566e-08</v>
+        <v>5.278432835628717e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.332822133562848e-08</v>
+        <v>5.954546162755702e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.160718395905362e-08</v>
+        <v>5.782442425098216e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.199001056331817e-08</v>
+        <v>5.820725085524674e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.283503646207009e-08</v>
+        <v>5.905227675399867e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.856719386594603e-08</v>
+        <v>5.234995357401752e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.357211180853561e-08</v>
+        <v>5.978935210046417e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.161983843659702e-08</v>
+        <v>5.78370787285256e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.79161143156543e-08</v>
+        <v>5.791611431565434e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.230945686483245e-08</v>
+        <v>5.88048665167554e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.780816100878308e-08</v>
+        <v>5.78081610087831e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.492320341787053e-08</v>
+        <v>6.114044370979913e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.272629189062739e-08</v>
+        <v>5.894353218255594e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.799118880516653e-08</v>
+        <v>5.177394851323799e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.23042416027783e-08</v>
+        <v>5.852148189470686e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.437087860797705e-08</v>
+        <v>6.058811889990562e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.810642731076824e-08</v>
+        <v>5.810642731076825e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7745858475381e-08</v>
+        <v>5.774585847538104e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.448531306003928e-08</v>
+        <v>5.448531306003932e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.829932917773822e-08</v>
+        <v>5.20820888858097e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.42570750201874e-08</v>
+        <v>5.425707502018742e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.104107236836473e-08</v>
+        <v>5.104107236836476e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,25 +1886,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.71322966054621e-08</v>
+        <v>5.713229660546213e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.783663679653405e-08</v>
+        <v>5.783663679653404e-08</v>
       </c>
       <c r="D7" t="n">
         <v>5.743806889679272e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.744666724174858e-08</v>
+        <v>5.744666724174859e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.880419130356476e-08</v>
+        <v>5.880419130356477e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.934808428290609e-08</v>
+        <v>5.934808428290612e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.762704690633125e-08</v>
+        <v>5.762704690633126e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.80098735105958e-08</v>
@@ -1916,34 +1916,34 @@
         <v>5.836981652129512e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.95919747558132e-08</v>
+        <v>5.959197475581323e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.763970138387462e-08</v>
+        <v>5.763970138387464e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.75728139350418e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.846475262472112e-08</v>
+        <v>5.846475262472116e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.761078366413214e-08</v>
+        <v>5.761078366413212e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.094306636514813e-08</v>
+        <v>6.094306636514814e-08</v>
       </c>
       <c r="S7" t="n">
         <v>5.874615483790499e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.779381146051558e-08</v>
+        <v>5.779381146051559e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.832664356913207e-08</v>
+        <v>5.832664356913208e-08</v>
       </c>
       <c r="V7" t="n">
         <v>6.039074155525469e-08</v>
@@ -1952,19 +1952,19 @@
         <v>6.395170082980685e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.376572142265859e-08</v>
+        <v>6.376572142265861e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>6.036930628440723e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.810195183308727e-08</v>
+        <v>5.810195183308728e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.027693796746499e-08</v>
+        <v>6.027693796746502e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.706313829278643e-08</v>
+        <v>5.706313829278648e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.524814302831106e-08</v>
+        <v>6.524814302831117e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.669264887788744e-08</v>
+        <v>7.66926488778875e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.629408097814599e-08</v>
+        <v>7.629408097814614e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.63026793231019e-08</v>
+        <v>7.058385792482439e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.859323001264935e-08</v>
+        <v>6.85932300126494e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.820409636425937e-08</v>
+        <v>8.043113967931135e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.648305898768451e-08</v>
+        <v>7.648305898768462e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.68658855919491e-08</v>
+        <v>7.686588559194924e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.771091149070104e-08</v>
+        <v>7.771091149070111e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.72258286026484e-08</v>
+        <v>7.72258286026485e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.84479868371665e-08</v>
+        <v>7.844798683716659e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.649571346522795e-08</v>
+        <v>7.649571346522683e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.039256216364313e-08</v>
+        <v>7.039256216364317e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.07236814939577e-08</v>
+        <v>7.07236814939578e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.361594240232357e-08</v>
+        <v>6.361594240232365e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.979907844650144e-08</v>
+        <v>7.979907844650155e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.760216691925831e-08</v>
+        <v>7.760216691925836e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.664982354186882e-08</v>
+        <v>7.664982354186898e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.057394401308761e-08</v>
+        <v>7.194093096948863e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.92467536366079e-08</v>
+        <v>7.631455360497872e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.280982366096955e-08</v>
+        <v>8.280982366096962e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.075523768439921e-08</v>
+        <v>7.075523768439933e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.990906010895859e-08</v>
+        <v>8.990906010895873e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.695796391444059e-08</v>
+        <v>6.601829416440271e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.913295004881831e-08</v>
+        <v>7.913295004881839e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.71381514828458e-08</v>
+        <v>8.713815148284597e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2065,49 +2065,49 @@
         <v>6.578152379264271e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.130806072801291e-08</v>
+        <v>7.130806072801297e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.090949282827162e-08</v>
+        <v>7.090949282827167e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.091809117322754e-08</v>
+        <v>6.980515377438135e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.227561523504371e-08</v>
+        <v>6.115912555680718e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.281950821438503e-08</v>
+        <v>7.281951593711526e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.109847083781013e-08</v>
+        <v>7.109847083781015e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.148129744207476e-08</v>
+        <v>7.148129744207471e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.232632334082675e-08</v>
+        <v>7.232632334082666e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.184124045277404e-08</v>
+        <v>7.184124045277405e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.306339868729215e-08</v>
+        <v>7.306339868729218e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.111112531535362e-08</v>
+        <v>7.111112531535359e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199292241706507e-08</v>
+        <v>8.199292241706495e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.264358003223103e-08</v>
+        <v>7.264358003223107e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.388307201716403e-08</v>
+        <v>7.388307201716402e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.108221531834135e-08</v>
+        <v>7.10822153183414e-08</v>
       </c>
       <c r="R9" t="n">
         <v>7.441449029662708e-08</v>
@@ -2116,31 +2116,31 @@
         <v>7.221757876938395e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.126523539199449e-08</v>
+        <v>7.126523539199454e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.179552848153475e-08</v>
+        <v>7.179552848153481e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.386216548673357e-08</v>
+        <v>7.942688857941133e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.742312476128575e-08</v>
+        <v>7.742312476128579e-08</v>
       </c>
       <c r="X9" t="n">
         <v>7.723714535413757e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.384073021588607e-08</v>
+        <v>7.384073021588613e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.157337576456612e-08</v>
+        <v>6.866602300083038e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.374836189894396e-08</v>
+        <v>7.374836189894395e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.053456222426543e-08</v>
+        <v>7.053456222426538e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.770001217987784e-08</v>
+        <v>1.770001217987787e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.696261213101181e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.768371283071643e-08</v>
+        <v>1.768371283071647e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.751296338810174e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.763230586592755e-08</v>
+        <v>1.763230586592758e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.068766046364788e-08</v>
+        <v>2.068766046364792e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.762462227322787e-08</v>
+        <v>1.76246222732279e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79607991899253e-08</v>
+        <v>1.796079918992532e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.870338502036327e-08</v>
+        <v>1.870338502036329e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.890946352785774e-08</v>
+        <v>1.89094635278577e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.777298152285625e-08</v>
+        <v>1.777298152285628e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.778952945628476e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.800102047006483e-08</v>
+        <v>1.800102047006486e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.859013929196491e-08</v>
+        <v>2.859013929196488e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.789728398548534e-08</v>
+        <v>1.789728398548536e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.758235426712466e-08</v>
+        <v>1.758235426712473e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.76035118272166e-08</v>
+        <v>1.760351182721664e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.771140492201843e-08</v>
+        <v>1.771140492201846e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.774069678680362e-08</v>
+        <v>1.774069678680365e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.527891119631186e-08</v>
+        <v>2.527891119631185e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.757028452333083e-08</v>
+        <v>1.757028452333086e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.646684463875026e-08</v>
+        <v>2.646684463875025e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.770533108365986e-08</v>
+        <v>1.770533108365989e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.764695447553774e-08</v>
+        <v>1.764695447553783e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.846327575124287e-08</v>
+        <v>2.846327575124299e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.789873308761725e-08</v>
+        <v>1.789873308761738e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.781991437379196e-08</v>
+        <v>1.781991437379193e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.561069049304993e-08</v>
+        <v>1.561069049305001e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.388999940222155e-08</v>
+        <v>1.388999940222154e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.551098747587088e-08</v>
+        <v>1.551098747587096e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.427774899912612e-08</v>
+        <v>1.427774899912618e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.514438893364876e-08</v>
+        <v>1.514438893364879e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.687193054974788e-08</v>
+        <v>3.687193054974792e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.509317279375389e-08</v>
+        <v>1.509317279375395e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.749760959821455e-08</v>
+        <v>1.749760959821463e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.27578652019621e-08</v>
+        <v>2.275786520196214e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.42406194728001e-08</v>
+        <v>2.424061947280021e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.614005341344398e-08</v>
+        <v>1.614005341344406e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.654268083717057e-08</v>
+        <v>1.654268083717058e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.777445728675523e-08</v>
+        <v>1.777445728675531e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.397564973254556e-08</v>
+        <v>3.397564973254559e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.70153470601688e-08</v>
+        <v>1.701534706016889e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.478314802107109e-08</v>
+        <v>1.478314802107111e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.493963251106623e-08</v>
+        <v>1.493963251106628e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.569493550956555e-08</v>
+        <v>1.56949355095656e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.59189955519127e-08</v>
+        <v>1.591899555191277e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.899757105973834e-08</v>
+        <v>2.899757105973835e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.468438731077461e-08</v>
+        <v>1.468438731077468e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.279418068391014e-08</v>
+        <v>3.279418068391016e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.566349789879899e-08</v>
+        <v>1.566349789879906e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.524183617588614e-08</v>
+        <v>1.524183617588622e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.313954707009115e-08</v>
+        <v>3.313954707009118e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.703936569467524e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.660274220317994e-08</v>
+        <v>1.660274220317993e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2485,40 +2485,40 @@
         <v>5.942429967028818e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.83559313068121e-08</v>
+        <v>5.835593130681209e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.924019102343903e-08</v>
+        <v>5.924019102343905e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.731149752048192e-08</v>
+        <v>5.731149752048193e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.865952570777636e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.317116142158363e-08</v>
+        <v>9.317116142158351e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.85727359936062e-08</v>
+        <v>5.857273599360619e-08</v>
       </c>
       <c r="I4" t="n">
         <v>6.237000891672585e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.069162775885398e-08</v>
+        <v>7.0691627758854e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.308560902082942e-08</v>
+        <v>7.308560902082943e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.024852196678535e-08</v>
+        <v>6.024852196678536e-08</v>
       </c>
       <c r="M4" t="n">
         <v>6.093385802527747e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.282432677860523e-08</v>
+        <v>6.282432677860522e-08</v>
       </c>
       <c r="O4" t="n">
         <v>6.023481033372854e-08</v>
@@ -2530,37 +2530,37 @@
         <v>5.80952994204277e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.83342837946242e-08</v>
+        <v>5.833428379462423e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.955298593368651e-08</v>
+        <v>5.955298593368652e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.988385102135885e-08</v>
+        <v>5.988385102135883e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.07977504501508e-08</v>
+        <v>6.079775045015082e-08</v>
       </c>
       <c r="V4" t="n">
         <v>5.750982519117762e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.498584091976965e-08</v>
+        <v>6.498584091976964e-08</v>
       </c>
       <c r="X4" t="n">
         <v>5.948437913532266e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.842765478303553e-08</v>
+        <v>5.842765478303554e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.892739518395711e-08</v>
+        <v>5.892739518395712e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>6.16689437393398e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.097437024616642e-08</v>
+        <v>6.09743702461664e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.248643426487743e-07</v>
+        <v>1.248643426487742e-07</v>
       </c>
       <c r="C5" t="n">
         <v>1.116437138403796e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.306299605009833e-07</v>
+        <v>1.306299605009832e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.604748329778933e-08</v>
+        <v>8.604748329778936e-08</v>
       </c>
       <c r="F5" t="n">
         <v>1.198151548436821e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.286017751011261e-07</v>
+        <v>7.28601775101126e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.201885512789012e-07</v>
+        <v>1.201885512789013e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.948375227935961e-07</v>
+        <v>1.94837522793596e-07</v>
       </c>
       <c r="J5" t="n">
         <v>3.313351339853441e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.820667881075331e-07</v>
+        <v>3.820667881075329e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.452188225317587e-07</v>
+        <v>1.452188225317591e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.658089861633092e-07</v>
+        <v>1.658089861633094e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.627405876342404e-07</v>
+        <v>1.627405876342403e-07</v>
       </c>
       <c r="O5" t="n">
         <v>1.374832433022827e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.651709968600184e-07</v>
+        <v>1.651709968600186e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.065140702175695e-07</v>
+        <v>1.065140702175696e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.140815510306897e-07</v>
+        <v>1.140815510306898e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.289295300400663e-07</v>
+        <v>1.289295300400667e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.435291936603999e-07</v>
+        <v>1.435291936603998e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61111345014768e-07</v>
+        <v>1.611113450147678e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.646943021370063e-08</v>
+        <v>9.646943021370036e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>2.360879417330787e-07</v>
+        <v>2.360879417330788e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.342570248958213e-07</v>
+        <v>1.342570248958216e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.189946864502518e-07</v>
+        <v>1.18994686450252e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.174005762918285e-07</v>
+        <v>1.174005762918284e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.730866030032231e-07</v>
+        <v>1.730866030032232e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.708380872569761e-07</v>
+        <v>1.708380872569759e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.662924243729266e-08</v>
+        <v>5.771214147023831e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.556087407381655e-08</v>
+        <v>6.556087407381656e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.752803282338917e-08</v>
+        <v>6.644513379044349e-08</v>
       </c>
       <c r="E6" t="n">
         <v>5.559933932043205e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.586446847478083e-08</v>
+        <v>5.694736750772651e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.003761041885879e-07</v>
+        <v>9.145900322153364e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.686057779355633e-08</v>
+        <v>6.577767876061062e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.0657850716676e-08</v>
+        <v>6.065785071667599e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.789657052585842e-08</v>
+        <v>7.789657052585836e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.137345082077955e-08</v>
+        <v>8.029055178783387e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.853636376673549e-08</v>
+        <v>5.85363637667355e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.922169982522763e-08</v>
+        <v>5.922169982522762e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.112250450911697e-08</v>
+        <v>6.112250450911712e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765754699151063e-08</v>
+        <v>6.765754699151066e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.907538893027385e-08</v>
+        <v>6.90753889302739e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.638314122037785e-08</v>
+        <v>6.530024218743215e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.662212559457435e-08</v>
+        <v>6.553922656162864e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.784082773363667e-08</v>
+        <v>6.6757928700691e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.708879378836328e-08</v>
+        <v>5.817169282130897e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.840002692613724e-08</v>
+        <v>5.948292595908292e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.471476795818209e-08</v>
+        <v>6.471476795818208e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.240874390405316e-08</v>
+        <v>7.240874390405318e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.777222093527279e-08</v>
+        <v>6.668932190232706e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.721407539980005e-08</v>
+        <v>5.721407539980019e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.721523698390728e-08</v>
+        <v>6.613233795096159e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.887388650634422e-08</v>
+        <v>5.995678553928994e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.928412325912215e-08</v>
+        <v>5.928412325912214e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,52 +2746,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.567641942782842e-08</v>
+        <v>6.56764194278284e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.460805106435231e-08</v>
+        <v>6.46080510643523e-08</v>
       </c>
       <c r="D7" t="n">
         <v>6.549231078097925e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.356361727802213e-08</v>
+        <v>6.35636172780221e-08</v>
       </c>
       <c r="F7" t="n">
         <v>6.491164546531656e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.942328117912369e-08</v>
+        <v>9.942328117912362e-08</v>
       </c>
       <c r="H7" t="n">
         <v>6.482485575114641e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.862212867426606e-08</v>
+        <v>6.862212867426608e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.69437475163942e-08</v>
+        <v>7.694374751639418e-08</v>
       </c>
       <c r="K7" t="n">
         <v>7.933772877836962e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.650064172432558e-08</v>
+        <v>6.650064172432559e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.718597778281768e-08</v>
+        <v>6.718597778281767e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.907644653614544e-08</v>
+        <v>6.907644653614546e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.648557177493394e-08</v>
+        <v>6.648557177493392e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.790333690534435e-08</v>
+        <v>6.790333690534433e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.434741917796793e-08</v>
+        <v>6.434741917796791e-08</v>
       </c>
       <c r="R7" t="n">
         <v>6.458640355216443e-08</v>
@@ -2809,22 +2809,22 @@
         <v>6.37619449487178e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.123796067730986e-08</v>
+        <v>7.123796067730985e-08</v>
       </c>
       <c r="X7" t="n">
         <v>6.573649889286289e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.507710824955773e-08</v>
+        <v>6.507710824955772e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.517951494149735e-08</v>
+        <v>6.517951494149733e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.792106349688e-08</v>
+        <v>6.792106349687999e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.722649000370664e-08</v>
+        <v>6.722649000370662e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,82 +2834,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.568550058602506e-08</v>
+        <v>7.568550058602507e-08</v>
       </c>
       <c r="C8" t="n">
         <v>8.829152912484115e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.91757888414681e-08</v>
+        <v>8.917578884146812e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.724709533851092e-08</v>
+        <v>7.996588235739341e-08</v>
       </c>
       <c r="F8" t="n">
         <v>7.705103784436357e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.231067592396126e-07</v>
+        <v>1.259422345177735e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.850833381163523e-08</v>
+        <v>8.850833381163522e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.230560673475487e-08</v>
+        <v>9.230560673475485e-08</v>
       </c>
       <c r="J8" t="n">
         <v>1.00627225576883e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.030212068388584e-07</v>
+        <v>1.030212068388585e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.018411978481438e-08</v>
+        <v>9.018411978481436e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>9.086945584330649e-08</v>
+        <v>9.086945584330562e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.215997932005684e-08</v>
+        <v>8.21599793200568e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>8.248341987463212e-08</v>
+        <v>8.248341987463211e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.318714885760075e-08</v>
+        <v>8.318714885760077e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>7.166916924162884e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.826988161265327e-08</v>
+        <v>8.826988161265321e-08</v>
       </c>
       <c r="S8" t="n">
         <v>8.948858375171552e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.981944883938792e-08</v>
+        <v>8.981944883938788e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.271103475856983e-08</v>
+        <v>8.445092230426865e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.744542300920668e-08</v>
+        <v>8.370197194341238e-08</v>
       </c>
       <c r="W8" t="n">
         <v>9.49241261476379e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.431153460369e-08</v>
+        <v>7.431153460369002e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.023473719401095e-07</v>
+        <v>1.023473719401096e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.886299300198617e-08</v>
+        <v>7.493458715637699e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.16045415573688e-08</v>
+        <v>9.160454155736874e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>1.051940190630738e-07</v>
@@ -2922,28 +2922,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.69021829384504e-08</v>
+        <v>8.690218293845041e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.488766185204036e-08</v>
+        <v>9.488766185204035e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.577192156866728e-08</v>
+        <v>9.577192156866732e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.384322806571018e-08</v>
+        <v>9.175364709531944e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>9.519125625300464e-08</v>
+        <v>7.431965019401023e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.297028919668118e-07</v>
+        <v>1.297029050338067e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.510446653883448e-08</v>
+        <v>9.510446653883452e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.890173946195408e-08</v>
+        <v>9.89017394619541e-08</v>
       </c>
       <c r="J9" t="n">
         <v>1.072233583040822e-07</v>
@@ -2952,37 +2952,37 @@
         <v>1.096173395660577e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.678025251201361e-08</v>
+        <v>9.678025251201367e-08</v>
       </c>
       <c r="M9" t="n">
         <v>9.746558857050575e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.935605732383348e-08</v>
+        <v>9.935605732383346e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>9.976699140895538e-08</v>
+        <v>9.97669914089554e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.018373002087315e-07</v>
+        <v>1.018373002087316e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.462704303265086e-08</v>
+        <v>9.462704303265081e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.486601433985251e-08</v>
+        <v>9.486601433985248e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>9.608471647891478e-08</v>
+        <v>9.608471647891482e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>9.641558156658714e-08</v>
+        <v>9.641558156658711e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>9.772681470436102e-08</v>
+        <v>9.772681470436109e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.404155573640593e-08</v>
+        <v>1.044895181622628e-07</v>
       </c>
       <c r="W9" t="n">
         <v>1.015175714649979e-07</v>
@@ -2991,13 +2991,13 @@
         <v>9.60161096805509e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.53567190372458e-08</v>
+        <v>9.535671903724578e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.545912572918536e-08</v>
+        <v>9.000046610938616e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.820067428456809e-08</v>
+        <v>9.820067428456811e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>9.750610079139476e-08</v>
@@ -3169,13 +3169,13 @@
         <v>1.739780901677576e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.679456391888099e-08</v>
+        <v>1.679456391888101e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.757050137359638e-08</v>
+        <v>1.757050137359639e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.738475561554884e-08</v>
+        <v>1.738475561554883e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.733239774455585e-08</v>
@@ -3184,67 +3184,67 @@
         <v>2.003710606927371e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.728775807427355e-08</v>
+        <v>1.728775807427356e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.752062414769517e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.82730018611678e-08</v>
+        <v>1.827300186116778e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.748051120226482e-08</v>
+        <v>1.748051120226483e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.744651391331091e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.751595873121328e-08</v>
+        <v>1.75159587312133e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.74355057043339e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.812547268251189e-08</v>
+        <v>2.812547268251187e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.760682191673333e-08</v>
+        <v>1.760682191673336e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.735384317897652e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.723672425839181e-08</v>
+        <v>1.723672425839184e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.744633059559968e-08</v>
+        <v>1.74463305955997e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.735799970273107e-08</v>
+        <v>1.735799970273108e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.552000992242193e-08</v>
+        <v>2.552000992242196e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.735025707458043e-08</v>
+        <v>1.735025707458042e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.663361012847879e-08</v>
+        <v>2.663361012847881e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.782001205627122e-08</v>
+        <v>1.782001205627123e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.769983449278263e-08</v>
+        <v>1.769983449278266e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.830642081639577e-08</v>
+        <v>2.830642081639576e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.745480555818128e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75451045526224e-08</v>
+        <v>1.754510455262241e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3254,37 +3254,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.4890317423732e-08</v>
+        <v>1.489031742373199e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.360141999083865e-08</v>
+        <v>1.360141999083867e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.613714516540409e-08</v>
+        <v>1.61371451654041e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.479577993894709e-08</v>
+        <v>1.479577993894708e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.443443459924266e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3654405374354e-08</v>
+        <v>3.365440537435404e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.411775980948455e-08</v>
+        <v>1.411775980948458e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.578286839777174e-08</v>
+        <v>1.578286839777176e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.111752313840454e-08</v>
+        <v>2.111752313840459e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.548287594782389e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.524292608043576e-08</v>
+        <v>1.524292608043577e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.601972064201464e-08</v>
@@ -3293,25 +3293,25 @@
         <v>1.516845611214386e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.273051625030272e-08</v>
+        <v>3.273051625030284e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.637537939014723e-08</v>
+        <v>1.637537939014729e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.458402423620673e-08</v>
+        <v>1.458402423620675e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.375025890689288e-08</v>
+        <v>1.375025890689284e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.523628636918316e-08</v>
+        <v>1.523628636918324e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.461745137974997e-08</v>
+        <v>1.461745137975e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.917175330994623e-08</v>
+        <v>2.917175330994633e-08</v>
       </c>
       <c r="V3" t="n">
         <v>1.454634319871085e-08</v>
@@ -3320,19 +3320,19 @@
         <v>3.221834875919695e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.791849173330314e-08</v>
+        <v>1.791849173330318e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705204352888104e-08</v>
+        <v>1.705204352888109e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.304459152960646e-08</v>
+        <v>3.30445915296065e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.530404424945795e-08</v>
+        <v>1.530404424945793e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.606903014445471e-08</v>
+        <v>1.606903014445473e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,64 +3342,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.783402854603505e-08</v>
+        <v>5.783402854603507e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.72089835620633e-08</v>
+        <v>5.720898356206329e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.978466815873289e-08</v>
+        <v>5.978466815873293e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.768658437431563e-08</v>
+        <v>5.768658437431565e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.709517813563942e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.764610289062877e-08</v>
+        <v>8.764610289062878e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.659095252453805e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.922128194752118e-08</v>
+        <v>5.922128194752123e-08</v>
       </c>
       <c r="J4" t="n">
         <v>6.76616557603565e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.876818777601899e-08</v>
+        <v>5.876818777601904e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.838417275775905e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.966256868473879e-08</v>
+        <v>5.966256868473882e-08</v>
       </c>
       <c r="N4" t="n">
         <v>5.825982997333724e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.811412250494256e-08</v>
+        <v>5.811412250494268e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.019492540174031e-08</v>
+        <v>6.019492540174042e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.733741418280803e-08</v>
+        <v>5.733741418280807e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.601450209743852e-08</v>
+        <v>5.601450209743853e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.838210209988045e-08</v>
+        <v>5.838210209988046e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.738436403071123e-08</v>
+        <v>5.738436403071129e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.929449882671278e-08</v>
+        <v>5.929449882671295e-08</v>
       </c>
       <c r="V4" t="n">
         <v>5.690229937520265e-08</v>
@@ -3408,16 +3408,16 @@
         <v>6.210690525643844e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.260300610013018e-08</v>
+        <v>6.26030061001303e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.093173096238136e-08</v>
+        <v>6.09317309623814e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>5.814652150586867e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.847783070091464e-08</v>
+        <v>5.847783070091466e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>5.968656522721906e-08</v>
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.048940746447631e-07</v>
+        <v>1.048940746447632e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.786587707589065e-08</v>
+        <v>9.786587707589067e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.468121100676452e-07</v>
+        <v>1.46812110067646e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.015738727827154e-07</v>
+        <v>1.015738727827158e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.750638402533991e-08</v>
+        <v>9.750638402533995e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.94491403700247e-07</v>
+        <v>5.944914037002464e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.95837085421478e-08</v>
+        <v>8.958370854214777e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.377284077899635e-07</v>
+        <v>1.377284077899645e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.697884973330015e-07</v>
+        <v>2.697884973330016e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.226127528277139e-07</v>
+        <v>1.226127528277143e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.172150860163524e-07</v>
+        <v>1.172150860163525e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.464441913137629e-07</v>
+        <v>1.46444191313763e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.354463443443852e-07</v>
+        <v>1.354463443443871e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.078685790098676e-07</v>
+        <v>1.078685790098677e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.431920484263452e-07</v>
+        <v>1.431920484263463e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.999378541731195e-08</v>
+        <v>9.999378541731244e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.769362930517059e-08</v>
+        <v>7.769362930517066e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1441561882595e-07</v>
+        <v>1.144156188259515e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.027736421715053e-07</v>
+        <v>1.02773642171506e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.367948274714953e-07</v>
+        <v>1.367948274714975e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.261905530283903e-08</v>
+        <v>9.261905530283721e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.842258199792429e-07</v>
+        <v>1.842258199792427e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.96957765181753e-07</v>
+        <v>1.969577651817547e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.684221669376098e-07</v>
+        <v>1.684221669376121e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.082605406699695e-07</v>
+        <v>1.082605406699696e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.198770854943695e-07</v>
+        <v>1.198770854943698e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.505614158461239e-07</v>
+        <v>1.505614158461238e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.442701763967386e-08</v>
+        <v>5.625753459125039e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.56324896072786e-08</v>
+        <v>5.563248960727863e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.637765725237172e-08</v>
+        <v>6.637765725237184e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.611009041953095e-08</v>
+        <v>5.6110090419531e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.551868418085474e-08</v>
+        <v>6.368816722927827e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.423909198426754e-08</v>
+        <v>8.606960893584407e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.501445856975334e-08</v>
+        <v>5.501445856975338e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.581427104115999e-08</v>
+        <v>5.764478799273658e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.425464485399524e-08</v>
+        <v>7.425464485399531e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.719169382123427e-08</v>
+        <v>6.536117686965789e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.497716185139786e-08</v>
+        <v>5.680767880297437e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.625555777837762e-08</v>
+        <v>6.625555777837765e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.668571036551894e-08</v>
+        <v>5.668571036551893e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.489754228717288e-08</v>
+        <v>5.654000289712435e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.69784794632238e-08</v>
+        <v>6.6978479463224e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.393040327644683e-08</v>
+        <v>6.393040327644691e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.260749119107738e-08</v>
+        <v>6.260749119107739e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.680560814509567e-08</v>
+        <v>5.680560814509579e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.580787007592658e-08</v>
+        <v>5.580787007592663e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.620130219408658e-08</v>
+        <v>5.803181914566324e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.349528846884146e-08</v>
+        <v>6.349528846884148e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.889021916426496e-08</v>
+        <v>6.072978732563481e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.102651214534552e-08</v>
+        <v>6.102651214534565e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.977294762484923e-08</v>
+        <v>5.977294762484929e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.473951059950749e-08</v>
+        <v>5.657002755108398e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.690133674612996e-08</v>
+        <v>6.50708197945535e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.81213632386196e-08</v>
+        <v>5.812136323861964e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.31141392660836e-08</v>
+        <v>6.311413926608363e-08</v>
       </c>
       <c r="C7" t="n">
         <v>6.248909428211186e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.506477887878147e-08</v>
+        <v>6.506477887878152e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.296669509436417e-08</v>
+        <v>6.296669509436418e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.237528885568796e-08</v>
+        <v>6.237528885568798e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.292621361067723e-08</v>
+        <v>9.29262136106773e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.187106324458656e-08</v>
+        <v>6.187106324458659e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.45013926675697e-08</v>
+        <v>6.450139266756978e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.294176648040498e-08</v>
+        <v>7.294176648040501e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.404829849606751e-08</v>
+        <v>6.404829849606759e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.366428347780757e-08</v>
+        <v>6.366428347780759e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.494267940478733e-08</v>
+        <v>6.494267940478735e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.353994069338578e-08</v>
+        <v>6.353994069338581e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.339296170136251e-08</v>
+        <v>6.339296170136257e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.547376459816004e-08</v>
+        <v>6.547376459816027e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.261752490285657e-08</v>
+        <v>6.261752490285662e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.129461281748705e-08</v>
+        <v>6.129461281748708e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.366221281992892e-08</v>
+        <v>6.366221281992902e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.266447475075977e-08</v>
+        <v>6.266447475075983e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.488168967444299e-08</v>
+        <v>6.488168967444314e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.218241009525118e-08</v>
+        <v>6.21824100952512e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.738701597648696e-08</v>
+        <v>6.738701597648697e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.788311682017874e-08</v>
+        <v>6.78831168201788e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.652565595616489e-08</v>
+        <v>6.652565595616495e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.342663222591719e-08</v>
+        <v>6.342663222591722e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.375794142096318e-08</v>
+        <v>6.375794142096322e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.49666759472676e-08</v>
+        <v>6.496667594726762e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,25 +3694,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.250679125699523e-08</v>
+        <v>7.250679125699525e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.444493581499106e-08</v>
+        <v>8.444493581499107e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.702062041166068e-08</v>
+        <v>8.702062041166072e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.492253662724338e-08</v>
+        <v>7.823300878692886e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.37251389477063e-08</v>
+        <v>7.372513894770631e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.148820551435565e-07</v>
+        <v>1.174871143367153e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.382690477746582e-08</v>
+        <v>8.382690477746585e-08</v>
       </c>
       <c r="I8" t="n">
         <v>8.645723420044899e-08</v>
@@ -3721,55 +3721,55 @@
         <v>9.489760801328419e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.600414002894677e-08</v>
+        <v>8.600414002894683e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.562012501068672e-08</v>
+        <v>8.562012501068676e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.689852093766653e-08</v>
+        <v>8.689852093766497e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.575720855493217e-08</v>
+        <v>7.57572085549322e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.828774568976435e-08</v>
+        <v>7.828774568976444e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.971253636720443e-08</v>
+        <v>7.971253636720459e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.954122340761462e-08</v>
+        <v>6.954122340761468e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.325045435036626e-08</v>
+        <v>8.32504543503663e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.561805435280806e-08</v>
+        <v>8.561805435280824e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.462031628363896e-08</v>
+        <v>8.462031628363906e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.910955754921446e-08</v>
+        <v>8.070810681812763e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.413825162813035e-08</v>
+        <v>8.069987318148843e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.934532653525255e-08</v>
+        <v>8.934532653525259e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.595825660959323e-08</v>
+        <v>7.595825660959331e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.009655487815295e-07</v>
+        <v>1.009655487815296e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.538247375879644e-08</v>
+        <v>7.258591652074719e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.571378295384237e-08</v>
+        <v>8.571378295384245e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>1.000458194735827e-07</v>
@@ -3782,37 +3782,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.991727981536348e-08</v>
+        <v>7.991727981536349e-08</v>
       </c>
       <c r="C9" t="n">
         <v>8.680980428995028e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.938548888661984e-08</v>
+        <v>8.938548888661989e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.728740510220259e-08</v>
+        <v>8.555238974393201e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.66959988635264e-08</v>
+        <v>6.936593423442079e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.172469236185157e-07</v>
+        <v>1.172469353308266e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.619177325242508e-08</v>
+        <v>8.619177325242505e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.882210267540812e-08</v>
+        <v>8.88221026754082e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.726247648824348e-08</v>
+        <v>9.726247648824346e-08</v>
       </c>
       <c r="K9" t="n">
         <v>8.836900850390602e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.798499348564605e-08</v>
+        <v>8.798499348564604e-08</v>
       </c>
       <c r="M9" t="n">
         <v>8.926338941262579e-08</v>
@@ -3824,7 +3824,7 @@
         <v>9.020627150173488e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.28288930057977e-08</v>
+        <v>9.282889300579778e-08</v>
       </c>
       <c r="Q9" t="n">
         <v>8.693824662300601e-08</v>
@@ -3833,34 +3833,34 @@
         <v>8.561532282532551e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.798292282776739e-08</v>
+        <v>8.798292282776746e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.698518475859821e-08</v>
+        <v>8.698518475859826e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.920913382833468e-08</v>
+        <v>8.920913382833486e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.650312010308964e-08</v>
+        <v>9.51782491431801e-08</v>
       </c>
       <c r="W9" t="n">
         <v>9.170772598432538e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.220382682801715e-08</v>
+        <v>9.220382682801722e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.084636596400336e-08</v>
+        <v>9.084636596400337e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.774734223375558e-08</v>
+        <v>8.321492098943263e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.807865142880164e-08</v>
+        <v>8.807865142880161e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.928738595510603e-08</v>
+        <v>8.928738595510604e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.697083615828397e-08</v>
+        <v>1.697083615828395e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.623461188983173e-08</v>
+        <v>1.623461188983171e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.69577259931329e-08</v>
+        <v>1.695772599313293e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.692028086586408e-08</v>
+        <v>1.692028086586413e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.696207589275666e-08</v>
+        <v>1.696207589275671e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.92305874227161e-08</v>
+        <v>1.923058742271615e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.689753906497045e-08</v>
+        <v>1.689753906497043e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.70351264226941e-08</v>
+        <v>1.703512642269413e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.765638754870453e-08</v>
+        <v>1.76563875487045e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.709164035971107e-08</v>
+        <v>1.709164035971103e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.70316882179058e-08</v>
+        <v>1.703168821790585e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.706182173986766e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.684901035703324e-08</v>
+        <v>1.684901035703327e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.762306963609469e-08</v>
+        <v>2.76230696360946e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.710547033538026e-08</v>
+        <v>1.710547033538029e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.690511854340953e-08</v>
+        <v>1.690511854340957e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.691763397027846e-08</v>
+        <v>1.69176339702785e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.705963412263536e-08</v>
+        <v>1.705963412263541e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.700021914368535e-08</v>
+        <v>1.70002191436854e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.531075568753633e-08</v>
+        <v>2.531075568753639e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.699616923308409e-08</v>
+        <v>1.699616923308413e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6157232363607e-08</v>
+        <v>2.615723236360703e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.756916772683358e-08</v>
+        <v>1.756916772683359e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.748142047581208e-08</v>
+        <v>1.748142047581211e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.801712500647833e-08</v>
+        <v>2.801712500647837e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.706522293529117e-08</v>
+        <v>1.706522293529122e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.712935411328725e-08</v>
+        <v>1.712935411328723e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,49 +4114,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.434997059748566e-08</v>
+        <v>1.43499705974857e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.273384745329343e-08</v>
+        <v>1.273384745329342e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426597787228475e-08</v>
+        <v>1.42659778722848e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.398694816143714e-08</v>
+        <v>1.398694816143711e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.42990599877221e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.038801448940871e-08</v>
+        <v>3.038801448940868e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.384092340334113e-08</v>
+        <v>1.38409234033411e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.482208880587705e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.922067214663787e-08</v>
+        <v>1.922067214663788e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.521484980693286e-08</v>
+        <v>1.521484980693283e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.478754628081225e-08</v>
+        <v>1.478754628081224e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5275067356295e-08</v>
+        <v>1.527506735629499e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.348863762468506e-08</v>
+        <v>1.348863762468501e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.210518429832204e-08</v>
+        <v>3.210518429832203e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.530468542353385e-08</v>
+        <v>1.530468542353386e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.388819926745019e-08</v>
@@ -4165,34 +4165,34 @@
         <v>1.398325253398526e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.498277333906364e-08</v>
+        <v>1.498277333906363e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.457273978133166e-08</v>
+        <v>1.457273978133165e-08</v>
       </c>
       <c r="U3" t="n">
         <v>2.937835560225949e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.452440886745518e-08</v>
+        <v>1.452440886745516e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.025762608962877e-08</v>
+        <v>3.025762608962872e-08</v>
       </c>
       <c r="X3" t="n">
         <v>1.862844063328785e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.800574470635068e-08</v>
+        <v>1.800574470635067e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.266884738348536e-08</v>
+        <v>3.266884738348533e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.503192824401006e-08</v>
+        <v>1.503192824401007e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.559655138224313e-08</v>
+        <v>1.559655138224312e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4208,22 +4208,22 @@
         <v>5.622581925817075e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.692529320085052e-08</v>
+        <v>5.692529320085051e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.650233326273966e-08</v>
+        <v>5.650233326273964e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.697442731815359e-08</v>
+        <v>5.697442731815357e-08</v>
       </c>
       <c r="G4" t="n">
         <v>8.25983086159072e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.624545415990013e-08</v>
+        <v>5.624545415990012e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.77995666587012e-08</v>
+        <v>5.779956665870121e-08</v>
       </c>
       <c r="J4" t="n">
         <v>6.476412155710945e-08</v>
@@ -4232,55 +4232,55 @@
         <v>5.843791757500228e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.776073055396498e-08</v>
+        <v>5.776073055396496e-08</v>
       </c>
       <c r="M4" t="n">
         <v>5.858525964033816e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.569730007944134e-08</v>
+        <v>5.569730007944132e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.743118095092375e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.859413351228985e-08</v>
+        <v>5.859413351228982e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.633106785560248e-08</v>
+        <v>5.633106785560247e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.647243535946779e-08</v>
+        <v>5.647243535946778e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.807639240363685e-08</v>
+        <v>5.807639240363682e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.740527288415561e-08</v>
+        <v>5.740527288415559e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.93902612784605e-08</v>
+        <v>5.939026127846053e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.699985575629411e-08</v>
+        <v>5.69998557562941e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.858881543421652e-08</v>
+        <v>5.858881543421651e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.383180886009362e-08</v>
+        <v>6.38318088600936e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>6.257623608576406e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.72580013877451e-08</v>
+        <v>5.725800138774509e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.81395206135647e-08</v>
+        <v>5.813952061356472e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.903407982793147e-08</v>
+        <v>5.903407982793146e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,25 +4290,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.778814605136835e-08</v>
+        <v>9.778814605136841e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.729871313619503e-08</v>
+        <v>8.729871313619506e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.001311053831699e-07</v>
+        <v>1.001311053831698e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.654465290661485e-08</v>
+        <v>8.654465290661493e-08</v>
       </c>
       <c r="F5" t="n">
         <v>1.020555733742636e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.026432408871867e-07</v>
+        <v>5.026432408871875e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.044040813830863e-08</v>
+        <v>9.044040813830869e-08</v>
       </c>
       <c r="I5" t="n">
         <v>1.1751161389793e-07</v>
@@ -4317,7 +4317,7 @@
         <v>2.232344881136629e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.233181612140704e-07</v>
+        <v>1.233181612140707e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.116404726544712e-07</v>
@@ -4326,40 +4326,40 @@
         <v>1.310972082491887e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.377125452583961e-07</v>
+        <v>1.37712545258397e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.030605824204889e-07</v>
+        <v>1.030605824204888e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.214846474698534e-07</v>
+        <v>1.214846474698538e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.842072327951528e-08</v>
+        <v>8.842072327951534e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>9.38904895393206e-08</v>
+        <v>9.389048953932074e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.150343591458556e-07</v>
+        <v>1.150343591458555e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.104269601251164e-07</v>
+        <v>1.104269601251166e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.416699336657279e-07</v>
+        <v>1.416699336657277e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.919091063532765e-08</v>
+        <v>9.919091063532758e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.286112197315408e-07</v>
+        <v>1.286112197315406e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.215445310459021e-07</v>
+        <v>2.215445310459016e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.058596655656811e-07</v>
+        <v>2.058596655656821e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>9.86079198504484e-08</v>
@@ -4368,7 +4368,7 @@
         <v>1.209534139309753e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.442687024055193e-07</v>
+        <v>1.442687024055194e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,49 +4378,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.505015745809126e-08</v>
+        <v>6.30072413598795e-08</v>
       </c>
       <c r="C6" t="n">
         <v>5.420259816905697e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.490207211173674e-08</v>
+        <v>5.490207211173672e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.447911217362588e-08</v>
+        <v>6.24361960754141e-08</v>
       </c>
       <c r="F6" t="n">
         <v>5.495120622903978e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.057508752679343e-08</v>
+        <v>8.853217142858166e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.217931697257458e-08</v>
+        <v>5.422223307078634e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.577634556958743e-08</v>
+        <v>5.577634556958741e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.274090046799567e-08</v>
+        <v>7.06979843697839e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.437178038767664e-08</v>
+        <v>6.437178038767666e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.57375094648512e-08</v>
+        <v>6.369459336663942e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.656203855122438e-08</v>
+        <v>5.656203855122436e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.368259040370505e-08</v>
+        <v>5.368259040370503e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.541647127518744e-08</v>
+        <v>6.354512198925444e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.470817737227216e-08</v>
+        <v>5.640204418409174e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>6.226493066827691e-08</v>
@@ -4429,22 +4429,22 @@
         <v>6.240629817214223e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.401025521631133e-08</v>
+        <v>6.401025521631132e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.53820517950418e-08</v>
+        <v>6.333913569683007e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.558855129944702e-08</v>
+        <v>5.763146739765886e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.293371856896854e-08</v>
+        <v>5.49766346671803e-08</v>
       </c>
       <c r="W6" t="n">
         <v>6.470271545822225e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.180858777097974e-08</v>
+        <v>6.180858777097977e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>6.092030415825691e-08</v>
@@ -4456,7 +4456,7 @@
         <v>6.407338342623915e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.702505440973559e-08</v>
+        <v>5.702505440973557e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.208871989809553e-08</v>
+        <v>6.208871989809552e-08</v>
       </c>
       <c r="C7" t="n">
         <v>6.124116060906125e-08</v>
@@ -4475,73 +4475,73 @@
         <v>6.1940634551741e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.151767461363015e-08</v>
+        <v>6.151767461363014e-08</v>
       </c>
       <c r="F7" t="n">
         <v>6.198976866904405e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.76136499667976e-08</v>
+        <v>8.761364996679763e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.126079551079063e-08</v>
+        <v>6.12607955107906e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.281490800959169e-08</v>
+        <v>6.28149080095917e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.977946290799996e-08</v>
+        <v>6.977946290799994e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.345325892589275e-08</v>
+        <v>6.345325892589272e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.277607190485549e-08</v>
+        <v>6.27760719048555e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.360060099122865e-08</v>
+        <v>6.360060099122863e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.071264143033185e-08</v>
+        <v>6.071264143033184e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.244525001634437e-08</v>
+        <v>6.244525001634436e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.360820257771048e-08</v>
+        <v>6.360820257771047e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.134640920649293e-08</v>
+        <v>6.134640920649292e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.148777671035829e-08</v>
+        <v>6.148777671035827e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.309173375452735e-08</v>
+        <v>6.309173375452736e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.24206142350461e-08</v>
+        <v>6.242061423504609e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.466493936614294e-08</v>
+        <v>6.466493936614298e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.201519710718458e-08</v>
+        <v>6.201519710718457e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.360415678510701e-08</v>
+        <v>6.360415678510699e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.88471502109841e-08</v>
+        <v>6.884715021098406e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.785600464496663e-08</v>
+        <v>6.785600464496662e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>6.227334273863559e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.315486196445518e-08</v>
+        <v>6.315486196445519e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>6.404942117882194e-08</v>
@@ -4557,46 +4557,46 @@
         <v>7.143425791060033e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.300042324399503e-08</v>
+        <v>8.300042324399498e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.36998971866748e-08</v>
+        <v>8.369989718667474e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.327693724856388e-08</v>
+        <v>7.66669950689411e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.326921989503181e-08</v>
+        <v>7.326921989503178e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.093729126017315e-07</v>
+        <v>1.119469792701595e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.302005814572442e-08</v>
+        <v>8.302005814572435e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.457417064452547e-08</v>
+        <v>8.457417064452546e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.15387255429337e-08</v>
+        <v>9.153872554293367e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.521252156082654e-08</v>
+        <v>8.52125215608265e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.453533453978923e-08</v>
+        <v>8.453533453978921e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.535986362616241e-08</v>
+        <v>8.535986362616148e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.284919071153196e-08</v>
+        <v>7.284919071153194e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.722747676501933e-08</v>
+        <v>7.722747676501931e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.77422217185119e-08</v>
+        <v>7.774222171851183e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>6.825236700086963e-08</v>
@@ -4605,31 +4605,31 @@
         <v>8.324703934529205e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.485099638946115e-08</v>
+        <v>8.485099638946111e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.417987686997984e-08</v>
+        <v>8.417987686997983e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.878775423868009e-08</v>
+        <v>8.03673601675684e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.377445974211836e-08</v>
+        <v>8.037833793520279e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.536585907188584e-08</v>
+        <v>8.536585907188581e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.689085053321232e-08</v>
+        <v>7.689085053321228e-08</v>
       </c>
       <c r="Y8" t="n">
         <v>1.019528891288593e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.403260537356938e-08</v>
+        <v>7.138828944265991e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.491412459938897e-08</v>
+        <v>8.491412459938893e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>9.877585720078215e-08</v>
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.668403015420906e-08</v>
+        <v>7.668403015420905e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.269142879384566e-08</v>
+        <v>8.269142879384563e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.339090273652541e-08</v>
+        <v>8.33909027365254e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.296794279841455e-08</v>
+        <v>8.138585495988852e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.344003685382845e-08</v>
+        <v>6.763747352499488e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.090639181515821e-07</v>
+        <v>1.090639291896763e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.271106369557506e-08</v>
+        <v>8.271106369557501e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.426517619437614e-08</v>
+        <v>8.426517619437606e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.122973109278435e-08</v>
+        <v>9.122973109278431e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.490352711067716e-08</v>
+        <v>8.490352711067713e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.422634008963991e-08</v>
+        <v>8.422634008963986e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.505086917601308e-08</v>
+        <v>8.505086917601306e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.216290961511625e-08</v>
+        <v>8.216290961511622e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.61685292644637e-08</v>
+        <v>8.616852926446369e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.782554363294543e-08</v>
+        <v>8.78255436329454e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.279668842937158e-08</v>
+        <v>8.279668842937157e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.293804489514268e-08</v>
+        <v>8.293804489514264e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.454200193931178e-08</v>
+        <v>8.454200193931179e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.387088241983046e-08</v>
+        <v>8.387088241983047e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.612029802244749e-08</v>
+        <v>8.612029802244751e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.346546529196899e-08</v>
+        <v>9.137595415470342e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.505442496989139e-08</v>
+        <v>8.505442496989135e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.029741839576844e-08</v>
+        <v>9.029741839576845e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>8.930627282975099e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.372361092341996e-08</v>
+        <v>7.959068524217913e-08</v>
       </c>
       <c r="AA9" t="n">
         <v>8.460513014923957e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.549968936360632e-08</v>
+        <v>8.549968936360631e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,79 +4886,79 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.56185639044198e-08</v>
+        <v>1.56185639044199e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.484211719824067e-08</v>
+        <v>1.484211719824066e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.599679740768793e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.569736051414048e-08</v>
+        <v>1.569736051414052e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.565506702039165e-08</v>
+        <v>1.565506702039164e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.635617942584399e-08</v>
+        <v>1.635617942584401e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.573400284857639e-08</v>
+        <v>1.573400284857644e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.580690265678221e-08</v>
+        <v>1.580690265678224e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.594925496754746e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.628935419972187e-08</v>
+        <v>1.628935419972188e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.585611575672558e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.56740632638057e-08</v>
+        <v>1.567406326380569e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.605388807780245e-08</v>
+        <v>1.605388807780244e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.568577565954861e-08</v>
+        <v>2.568577565954864e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.587205967914802e-08</v>
+        <v>1.587205967914801e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.578877432188915e-08</v>
+        <v>1.578877432188919e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.576290694519247e-08</v>
+        <v>1.576290694519248e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.575235120974724e-08</v>
+        <v>1.575235120974726e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.568582606975059e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.282118551732549e-08</v>
+        <v>2.282118551732556e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.560669523291589e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.366611888505182e-08</v>
+        <v>2.366611888505191e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5765899897518e-08</v>
+        <v>1.576589989751811e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.561462475715144e-08</v>
+        <v>1.561462475715145e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.656413949006929e-08</v>
+        <v>2.656413949006925e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.57698995226155e-08</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.293645477424375e-08</v>
+        <v>1.293645477424377e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.123867608880284e-08</v>
+        <v>1.123867608880283e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.564936391227542e-08</v>
+        <v>1.564936391227545e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.34959680467715e-08</v>
+        <v>1.349596804677152e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.320589363323256e-08</v>
+        <v>1.320589363323259e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81588322011481e-08</v>
+        <v>1.815883220114818e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.377597962277643e-08</v>
+        <v>1.377597962277641e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.42933896812022e-08</v>
+        <v>1.429338968120218e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.528401905604021e-08</v>
+        <v>1.52840190560403e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.771386434718812e-08</v>
+        <v>1.771386434718828e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.462213925477464e-08</v>
+        <v>1.462213925477468e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.358213936639461e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.604666980984133e-08</v>
+        <v>1.604666980984137e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.966120722927234e-08</v>
+        <v>2.966120722927237e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.473901323816868e-08</v>
+        <v>1.473901323816873e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.415435447308113e-08</v>
+        <v>1.415435447308114e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.398136991892434e-08</v>
+        <v>1.398136991892438e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.387983613430827e-08</v>
+        <v>1.387983613430831e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.342355519412322e-08</v>
+        <v>1.342355519412327e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.524365445886112e-08</v>
+        <v>2.524365445886115e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.284797054663863e-08</v>
+        <v>1.284797054663879e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.699964009396578e-08</v>
+        <v>2.699964009396594e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.399629250629567e-08</v>
+        <v>1.399629250629568e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.291327723869942e-08</v>
+        <v>1.291327723869951e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.168055418235586e-08</v>
+        <v>3.168055418235594e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.402155187688799e-08</v>
+        <v>1.402155187688803e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.996701180915237e-08</v>
+        <v>2.996701180915236e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5068,10 +5068,10 @@
         <v>5.376494029930353e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.890846934516137e-08</v>
+        <v>5.890846934516135e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.552619188476645e-08</v>
+        <v>5.552619188476646e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.504846741690481e-08</v>
@@ -5080,7 +5080,7 @@
         <v>6.296785456413048e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.59400839085271e-08</v>
+        <v>5.594008390852709e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.676352077778056e-08</v>
@@ -5089,25 +5089,25 @@
         <v>5.831451441534333e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.221303289395815e-08</v>
+        <v>6.221303289395812e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.731940538078477e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.571211874417389e-08</v>
+        <v>5.571211874417391e-08</v>
       </c>
       <c r="N4" t="n">
         <v>5.955333472711064e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.485919259665076e-08</v>
+        <v>5.485919259665075e-08</v>
       </c>
       <c r="P4" t="n">
         <v>5.749949931911284e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.65587528957171e-08</v>
+        <v>5.655875289571709e-08</v>
       </c>
       <c r="R4" t="n">
         <v>5.626656897634665e-08</v>
@@ -5116,28 +5116,28 @@
         <v>5.614733708861481e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.539590502927595e-08</v>
+        <v>5.539590502927593e-08</v>
       </c>
       <c r="U4" t="n">
         <v>5.528086155440005e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.411589143004343e-08</v>
+        <v>5.411589143004341e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.623025016943003e-08</v>
+        <v>5.623025016943004e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.630037574968977e-08</v>
+        <v>5.630037574968976e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>5.440195040093695e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.604153203633651e-08</v>
+        <v>5.604153203633649e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.634555335508426e-08</v>
+        <v>5.634555335508427e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>8.145395680769285e-08</v>
@@ -5150,22 +5150,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.679285923541893e-08</v>
+        <v>8.679285923541901e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.397995756576431e-08</v>
+        <v>7.397995756576427e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.750469503620589e-07</v>
+        <v>1.750469503620588e-07</v>
       </c>
       <c r="E5" t="n">
         <v>1.020299846674031e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>9.954666504704152e-08</v>
+        <v>9.954666504704174e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.209577203165918e-07</v>
+        <v>2.209577203165921e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.20140966277996e-07</v>
@@ -5174,25 +5174,25 @@
         <v>1.341089877019754e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.503583988452415e-07</v>
+        <v>1.503583988452416e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.244642079387792e-07</v>
+        <v>2.24464207938779e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.321135306453163e-07</v>
+        <v>1.321135306453164e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.102453924470403e-07</v>
+        <v>1.102453924470402e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.073180003337825e-07</v>
+        <v>1.073180003337824e-07</v>
       </c>
       <c r="O5" t="n">
         <v>9.025405415013984e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.372324650958704e-07</v>
+        <v>1.372324650958706e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.248690642395242e-07</v>
@@ -5201,34 +5201,34 @@
         <v>1.258137544114474e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.089898228947527e-07</v>
+        <v>1.089898228947526e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0507747481552e-07</v>
+        <v>1.050774748155199e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.032352302093813e-07</v>
+        <v>1.032352302093811e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.177128491416585e-08</v>
+        <v>8.177128491416536e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.196837529606412e-07</v>
+        <v>1.196837529606413e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.228723154215901e-07</v>
+        <v>1.228723154215902e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.869692673179242e-08</v>
+        <v>8.869692673179246e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>1.099219770948107e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.218989278142244e-07</v>
+        <v>1.218989278142243e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.29915159999243e-07</v>
+        <v>6.299151599992423e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5238,82 +5238,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.29147094847995e-08</v>
+        <v>5.291470948479946e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.960393801969132e-08</v>
+        <v>5.960393801969133e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.474746706554913e-08</v>
+        <v>5.718703090022042e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.136518960515426e-08</v>
+        <v>5.380475343982554e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.088746513729257e-08</v>
+        <v>6.088746513729258e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.12464161191896e-08</v>
+        <v>6.880685228451826e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.421864546358619e-08</v>
+        <v>5.421864546358617e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.260251849816835e-08</v>
+        <v>5.504208233283965e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.659307597040244e-08</v>
+        <v>5.659307597040241e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.805203061434593e-08</v>
+        <v>6.049159444901719e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.315840310117256e-08</v>
+        <v>5.559796693584385e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.399068029923302e-08</v>
+        <v>6.155111646456171e-08</v>
       </c>
       <c r="N6" t="n">
         <v>5.782977219760066e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.088211878257765e-08</v>
+        <v>6.088211878257769e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.352250152501557e-08</v>
+        <v>5.560015923365441e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.239775061610489e-08</v>
+        <v>6.239775061610488e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.210556669673442e-08</v>
+        <v>5.454513053140573e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.198633480900259e-08</v>
+        <v>5.442589864367388e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.367446658433505e-08</v>
+        <v>6.123490274966372e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.130956232309743e-08</v>
+        <v>5.374912615776874e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.239445298510255e-08</v>
+        <v>5.995488915043123e-08</v>
       </c>
       <c r="W6" t="n">
         <v>5.466806448312379e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.45789373047489e-08</v>
+        <v>5.457893730474885e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.298358461355633e-08</v>
+        <v>5.298358461355632e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.43200935913956e-08</v>
+        <v>6.188052975672429e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.462411491014338e-08</v>
+        <v>6.218455107547207e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>7.988657851058659e-08</v>
@@ -5326,37 +5326,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.002226561620926e-08</v>
+        <v>6.002226561620927e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.915105798577242e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.429458703163024e-08</v>
+        <v>6.429458703163025e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.091230957123535e-08</v>
+        <v>6.091230957123533e-08</v>
       </c>
       <c r="F7" t="n">
         <v>6.043458510337369e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.835397225059936e-08</v>
+        <v>6.835397225059935e-08</v>
       </c>
       <c r="H7" t="n">
         <v>6.132620159499598e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.214963846424948e-08</v>
+        <v>6.214963846424946e-08</v>
       </c>
       <c r="J7" t="n">
         <v>6.370063210181222e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.759915058042698e-08</v>
+        <v>6.759915058042697e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.270552306725363e-08</v>
+        <v>6.270552306725364e-08</v>
       </c>
       <c r="M7" t="n">
         <v>6.109823643064279e-08</v>
@@ -5365,46 +5365,46 @@
         <v>6.493945241357952e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.024396294229268e-08</v>
+        <v>6.024396294229267e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.288426966475477e-08</v>
+        <v>6.288426966475478e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>6.194487058218599e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.165268666281554e-08</v>
+        <v>6.165268666281553e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.153345477508368e-08</v>
+        <v>6.153345477508367e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.078202271574482e-08</v>
+        <v>6.078202271574483e-08</v>
       </c>
       <c r="U7" t="n">
         <v>6.085533873467848e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.950200911651231e-08</v>
+        <v>5.95020091165123e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.16163678558989e-08</v>
+        <v>6.161636785589892e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.168649343615865e-08</v>
+        <v>6.168649343615864e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.997777113571544e-08</v>
+        <v>5.997777113571546e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.142764972280537e-08</v>
+        <v>6.142764972280538e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.173167104155317e-08</v>
+        <v>6.173167104155316e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.684007449416167e-08</v>
+        <v>8.684007449416163e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5417,82 +5417,82 @@
         <v>6.929612316231184e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.082101523669787e-08</v>
+        <v>8.082101523669789e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.596454428255575e-08</v>
+        <v>8.596454428255574e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.258226682216081e-08</v>
+        <v>7.598170939120239e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.163961010677712e-08</v>
+        <v>7.163961010677715e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.002392950152485e-08</v>
+        <v>9.259434152848875e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.299615884592147e-08</v>
+        <v>8.299615884592144e-08</v>
       </c>
       <c r="I8" t="n">
         <v>8.38195957151749e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.537058935273775e-08</v>
+        <v>8.537058935273773e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.926910783135247e-08</v>
+        <v>8.926910783135243e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.437548031817912e-08</v>
+        <v>8.437548031817915e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.276819368156823e-08</v>
+        <v>8.276819368156753e-08</v>
       </c>
       <c r="N8" t="n">
         <v>7.700035857052643e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.494686711455682e-08</v>
+        <v>7.494686711455684e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.693988654964648e-08</v>
+        <v>7.693988654964645e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.878261160864867e-08</v>
+        <v>6.878261160864866e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.332264391374099e-08</v>
+        <v>8.3322643913741e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.32034120260092e-08</v>
+        <v>8.320341202600916e-08</v>
       </c>
       <c r="T8" t="n">
         <v>8.245197996667028e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.489872797661281e-08</v>
+        <v>7.647627165698456e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.117196636743781e-08</v>
+        <v>7.778392864372085e-08</v>
       </c>
       <c r="W8" t="n">
         <v>8.328876129503382e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.966036163187139e-08</v>
+        <v>6.966036163187135e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.397289318991093e-08</v>
+        <v>9.397289318991089e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.309760697373086e-08</v>
+        <v>7.047124335227133e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.340162829247863e-08</v>
+        <v>8.340162829247861e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.214587944321188e-07</v>
+        <v>1.214587944321187e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5502,37 +5502,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.582137604919286e-08</v>
+        <v>7.58213760491929e-08</v>
       </c>
       <c r="C9" t="n">
         <v>8.215019730683463e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.729372635269245e-08</v>
+        <v>8.72937263526925e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.391144889229753e-08</v>
+        <v>8.224971883751944e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.34337244244359e-08</v>
+        <v>6.683568047029832e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.135311157166151e-08</v>
+        <v>9.135312098945825e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.432534091605816e-08</v>
+        <v>8.43253409160582e-08</v>
       </c>
       <c r="I9" t="n">
         <v>8.514877778531166e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.669977142287443e-08</v>
+        <v>8.669977142287439e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.059828990148919e-08</v>
+        <v>9.05982899014892e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.570466238831589e-08</v>
+        <v>8.570466238831592e-08</v>
       </c>
       <c r="M9" t="n">
         <v>8.409737575170499e-08</v>
@@ -5541,43 +5541,43 @@
         <v>8.793859173464175e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.563054228890032e-08</v>
+        <v>8.563054228890043e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.878978118362315e-08</v>
+        <v>8.878978118362319e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.494401932104478e-08</v>
+        <v>8.494401932104481e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.465182598387776e-08</v>
+        <v>8.465182598387777e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.453259409614588e-08</v>
+        <v>8.453259409614591e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.378116203680703e-08</v>
+        <v>8.378116203680704e-08</v>
       </c>
       <c r="U9" t="n">
         <v>8.385582161024078e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.250114843757453e-08</v>
+        <v>9.080983978217734e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.461550717696112e-08</v>
+        <v>8.461550717696114e-08</v>
       </c>
       <c r="X9" t="n">
         <v>8.468563275722088e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.297691045677768e-08</v>
+        <v>8.297691045677769e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.442678904386759e-08</v>
+        <v>8.008581561560851e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.473081036261539e-08</v>
+        <v>8.473081036261542e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>1.098392138152239e-07</v>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.533959664825784e-08</v>
+        <v>1.533959664825775e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.470506660055387e-08</v>
+        <v>1.470506660055386e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.538231710238088e-08</v>
+        <v>1.538231710238076e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.537737225725164e-08</v>
+        <v>1.537737225725153e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.548393813816251e-08</v>
+        <v>1.54839381381624e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.544425289595098e-08</v>
+        <v>1.544425289595087e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.536397798134737e-08</v>
+        <v>1.536397798134726e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.540413500123145e-08</v>
+        <v>1.540413500123142e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.54285399845466e-08</v>
+        <v>1.542853998454659e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.534166092576893e-08</v>
+        <v>1.534166092576885e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.542406319244773e-08</v>
+        <v>1.54240631924476e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.524466004628385e-08</v>
+        <v>1.524466004628386e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.550605236334691e-08</v>
+        <v>1.550605236334681e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.574064820723685e-08</v>
+        <v>2.574064820723677e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.535912138985219e-08</v>
+        <v>1.535912138985207e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.529804844932549e-08</v>
+        <v>1.529804844932538e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.562283647651852e-08</v>
+        <v>1.562283647651841e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.539884088723252e-08</v>
+        <v>1.539884088723242e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.528543317608948e-08</v>
+        <v>1.528543317608936e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.270638809570543e-08</v>
+        <v>2.27063880957054e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.537218800119564e-08</v>
+        <v>1.537218800119553e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.391488315478325e-08</v>
+        <v>2.391488315478313e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.558872529589869e-08</v>
+        <v>1.55887252958986e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.534191974096439e-08</v>
+        <v>1.53419197409643e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.647427252969602e-08</v>
+        <v>2.64742725296959e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.539583141706134e-08</v>
+        <v>1.539583141706123e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.521395730439968e-08</v>
+        <v>1.521395730439967e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.291115494218179e-08</v>
+        <v>1.291115494218169e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.186359250151751e-08</v>
+        <v>1.186359250151749e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.322179225625886e-08</v>
+        <v>1.322179225625879e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.317815756564442e-08</v>
+        <v>1.317815756564433e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.394938942757829e-08</v>
+        <v>1.394938942757825e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.364821528105691e-08</v>
+        <v>1.364821528105686e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.309834650908407e-08</v>
+        <v>1.309834650908404e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.338099864513086e-08</v>
+        <v>1.338099864513073e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.35422971029514e-08</v>
+        <v>1.354229710295137e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.292950562066951e-08</v>
+        <v>1.292950562066947e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.350402162624366e-08</v>
+        <v>1.350402162624351e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.248859154913912e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.410131149123323e-08</v>
+        <v>1.410131149123319e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14469678985556e-08</v>
+        <v>3.144696789855551e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.304910255448285e-08</v>
+        <v>1.304910255448284e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.261671258655165e-08</v>
+        <v>1.261671258655159e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.494812290971223e-08</v>
+        <v>1.494812290971218e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.332631509556738e-08</v>
+        <v>1.332631509556731e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.25315297202544e-08</v>
+        <v>1.253152972025433e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.454643413419507e-08</v>
+        <v>2.454643413419498e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.313594993446165e-08</v>
+        <v>1.313594993446153e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.868525116260809e-08</v>
+        <v>2.868525116260796e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.469048202076732e-08</v>
+        <v>1.469048202076729e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.293347186918577e-08</v>
+        <v>1.293347186918573e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.233456217007887e-08</v>
+        <v>3.233456217007881e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.331796547172798e-08</v>
+        <v>1.33179654717279e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.210579389133023e-08</v>
+        <v>1.21057938913302e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.418270463450717e-08</v>
+        <v>5.418270463450718e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.417109488116188e-08</v>
+        <v>5.417109488116184e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.466525181620679e-08</v>
+        <v>5.466525181620677e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.460939751573108e-08</v>
+        <v>5.460939751573105e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.581310816334656e-08</v>
+        <v>5.581310816334661e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.536484509645392e-08</v>
+        <v>5.536484509645388e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4458103007721e-08</v>
+        <v>5.445810300772097e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.49116950204536e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.51394586506913e-08</v>
+        <v>5.513945865069129e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.420602159861016e-08</v>
+        <v>5.420602159861009e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.513679310766211e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.356787804703441e-08</v>
+        <v>5.356787804703438e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.606289850985048e-08</v>
+        <v>5.606289850985051e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.702585855861051e-08</v>
+        <v>5.702585855861056e-08</v>
       </c>
       <c r="P4" t="n">
         <v>5.440324557264037e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.371339861445071e-08</v>
+        <v>5.371339861445072e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.738202879147007e-08</v>
+        <v>5.738202879147005e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.485189556742278e-08</v>
+        <v>5.485189556742273e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.357090329993761e-08</v>
+        <v>5.357090329993759e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.295976970251177e-08</v>
+        <v>5.295976970251176e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.422520475521941e-08</v>
+        <v>5.422520475521944e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.752323146091694e-08</v>
+        <v>5.75232314609169e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.699672731445088e-08</v>
+        <v>5.699672731445097e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.410012867300102e-08</v>
+        <v>5.410012867300104e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.635534913103783e-08</v>
+        <v>5.635534913103778e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.481790221741469e-08</v>
+        <v>5.481790221741465e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.291600443764365e-08</v>
+        <v>5.291600443764369e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,25 +6010,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.929133281539285e-08</v>
+        <v>8.929133281539291e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.213003536149583e-08</v>
+        <v>9.213003536149585e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.008002245950789e-07</v>
+        <v>1.008002245950788e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.548875688951098e-08</v>
+        <v>9.54887568895111e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.223056764649503e-07</v>
+        <v>1.223056764649501e-07</v>
       </c>
       <c r="G5" t="n">
         <v>1.050811820926391e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.009928115002576e-07</v>
+        <v>1.009928115002575e-07</v>
       </c>
       <c r="I5" t="n">
         <v>1.069680794497644e-07</v>
@@ -6037,58 +6037,58 @@
         <v>1.05120460337632e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.157857902429501e-08</v>
+        <v>9.157857902429495e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.009965397452705e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.174453658175703e-08</v>
+        <v>8.174453658175698e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.502027108246499e-08</v>
+        <v>7.502027108246494e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.323286054393162e-07</v>
+        <v>1.323286054393161e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>9.246570149992954e-08</v>
+        <v>9.246570149992956e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207356234392539e-08</v>
+        <v>8.207356234392534e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.538942139335763e-07</v>
+        <v>1.538942139335765e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.715284806232569e-08</v>
+        <v>9.715284806232565e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.20682251859272e-08</v>
+        <v>8.206822518592715e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.202595863742839e-08</v>
+        <v>7.20259586374284e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>9.142884749546914e-08</v>
+        <v>9.142884749546973e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.465469151884451e-07</v>
+        <v>1.46546915188445e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.397271092152221e-07</v>
+        <v>1.397271092152229e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.272844000504095e-08</v>
+        <v>9.272844000504103e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>1.216557867373133e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.033554508625549e-07</v>
+        <v>1.033554508625547e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.12935447428365e-08</v>
+        <v>7.129354474283644e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.265821709142197e-08</v>
+        <v>5.265821709142201e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.925566879611261e-08</v>
+        <v>5.264660733807666e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.314076427312163e-08</v>
+        <v>5.314076427312158e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.969397143068182e-08</v>
+        <v>5.96939714306818e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.089768207829734e-08</v>
+        <v>6.089768207829732e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.044941901140465e-08</v>
+        <v>5.384035755336872e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.954267692267171e-08</v>
+        <v>5.29336154646358e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.338720747736844e-08</v>
+        <v>5.338720747736843e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.022403256564207e-08</v>
+        <v>5.361497110760613e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.26815340555249e-08</v>
+        <v>5.268153405552493e-08</v>
       </c>
       <c r="L6" t="n">
         <v>6.022136702261282e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.204339050394922e-08</v>
+        <v>5.865245196198511e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.453686001095103e-08</v>
+        <v>5.453686001095111e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.54998200597111e-08</v>
+        <v>5.549982005971113e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.965201221832392e-08</v>
+        <v>5.270416379597965e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.87979725294015e-08</v>
+        <v>5.218891107136556e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.246660270642084e-08</v>
+        <v>6.246660270642079e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.993646948237351e-08</v>
+        <v>5.332740802433758e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.865547721488836e-08</v>
+        <v>5.865547721488832e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.154409852172877e-08</v>
+        <v>5.154409852172875e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.270071721213428e-08</v>
+        <v>5.930977867017017e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.616733578429067e-08</v>
+        <v>5.616733578429055e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.547223977136576e-08</v>
+        <v>5.547223977136579e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.280956392618686e-08</v>
+        <v>5.28095639261869e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.143992304598851e-08</v>
+        <v>6.14399230459885e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.329341467432952e-08</v>
+        <v>5.990247613236536e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.138237313576783e-08</v>
+        <v>5.138237313576781e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.88275181749456e-08</v>
+        <v>5.882751817494558e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.881590842160025e-08</v>
+        <v>5.881590842160024e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.931006535664518e-08</v>
+        <v>5.931006535664515e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.925421105616949e-08</v>
+        <v>5.925421105616947e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.045792170378499e-08</v>
+        <v>6.0457921703785e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.00096586368923e-08</v>
+        <v>6.000965863689226e-08</v>
       </c>
       <c r="H7" t="n">
         <v>5.910291654815936e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.955650856089199e-08</v>
+        <v>5.955650856089198e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.978427219112972e-08</v>
+        <v>5.978427219112971e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.88508351390485e-08</v>
+        <v>5.885083513904848e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.978160664810051e-08</v>
+        <v>5.978160664810048e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.821269158747279e-08</v>
+        <v>5.821269158747277e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.070771205028891e-08</v>
+        <v>6.070771205028887e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.166941188992839e-08</v>
+        <v>6.166941188992834e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.904679890395818e-08</v>
+        <v>5.904679890395812e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.835821215488917e-08</v>
+        <v>5.835821215488912e-08</v>
       </c>
       <c r="R7" t="n">
         <v>6.202684233190847e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.949670910786116e-08</v>
+        <v>5.949670910786113e-08</v>
       </c>
       <c r="T7" t="n">
         <v>5.8215716840376e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.771433962841056e-08</v>
+        <v>5.77143396284105e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.887001829565787e-08</v>
+        <v>5.887001829565783e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.216804500135538e-08</v>
+        <v>6.216804500135531e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.164154085488934e-08</v>
+        <v>6.164154085488937e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.885375857574158e-08</v>
+        <v>5.88537585757416e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.100016267147621e-08</v>
+        <v>6.100016267147618e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.946271575785307e-08</v>
+        <v>5.946271575785305e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.756081797808209e-08</v>
+        <v>5.756081797808208e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,22 +6274,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.739581185205975e-08</v>
+        <v>6.739581185205979e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.870222051671509e-08</v>
+        <v>7.870222051671507e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.919637745176005e-08</v>
+        <v>7.919637745176001e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.914052315128434e-08</v>
+        <v>7.311401220415056e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.078943037355619e-08</v>
+        <v>7.078943037355622e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.989597073200722e-08</v>
+        <v>8.224283558110488e-08</v>
       </c>
       <c r="H8" t="n">
         <v>7.898922864327427e-08</v>
@@ -6298,61 +6298,61 @@
         <v>7.944282065600685e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.967058428624462e-08</v>
+        <v>7.967058428624459e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.873714723416341e-08</v>
+        <v>7.873714723416336e-08</v>
       </c>
       <c r="L8" t="n">
         <v>7.966791874321539e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.809900368258763e-08</v>
+        <v>7.809900368258657e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.182066640783285e-08</v>
+        <v>7.182066640783282e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.519462134059287e-08</v>
+        <v>7.519462134059291e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.198101525075808e-08</v>
+        <v>7.198101525075806e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.470225689124277e-08</v>
+        <v>6.470225689124278e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.191315442702331e-08</v>
+        <v>8.191315442702334e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.938302120297599e-08</v>
+        <v>7.938302120297603e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.810202893549085e-08</v>
+        <v>7.810202893549086e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.063679356063402e-08</v>
+        <v>7.207724309612867e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.875633039077271e-08</v>
+        <v>7.566482600593438e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.205658141093888e-08</v>
+        <v>8.205658141093885e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.902290446843457e-08</v>
+        <v>6.902290446843465e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.999623574408496e-08</v>
+        <v>8.999623574408495e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.088647476659109e-08</v>
+        <v>6.935821834537039e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.934902785296793e-08</v>
+        <v>7.934902785296792e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.926974670850174e-08</v>
+        <v>8.926974670850171e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.093777920759105e-08</v>
+        <v>7.0937779207591e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.683191725073402e-08</v>
+        <v>7.683191725073398e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.732607418577895e-08</v>
+        <v>7.732607418577892e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.727021988530324e-08</v>
+        <v>7.590720433293201e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.847393053291878e-08</v>
+        <v>6.48595582370472e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.802566746602609e-08</v>
+        <v>7.802567650127692e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.711892537729314e-08</v>
+        <v>7.71189253772931e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.757251739002585e-08</v>
+        <v>7.757251739002577e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.780028102026346e-08</v>
+        <v>7.780028102026342e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.686684396818233e-08</v>
+        <v>7.686684396818223e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.77976154772343e-08</v>
+        <v>7.779761547723427e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.622870041660655e-08</v>
+        <v>7.62287004166065e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.872372087942264e-08</v>
+        <v>7.872372087942256e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.164385004454401e-08</v>
+        <v>8.164385004454397e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.944688579700294e-08</v>
+        <v>7.944688579700291e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.637423001927384e-08</v>
+        <v>7.637423001927376e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.004285116104223e-08</v>
+        <v>8.004285116104219e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.751271793699488e-08</v>
+        <v>7.751271793699485e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.623172566950973e-08</v>
+        <v>7.62317256695097e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.57294084343861e-08</v>
+        <v>7.572940843438605e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.68860271247916e-08</v>
+        <v>8.370114611348556e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.01840538304891e-08</v>
+        <v>8.018405383048904e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.965754968402309e-08</v>
+        <v>7.965754968402306e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.686976740487534e-08</v>
+        <v>7.686976740487532e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.901617150060997e-08</v>
+        <v>7.545553432670989e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.747872458698682e-08</v>
+        <v>7.747872458698678e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.557682680721585e-08</v>
+        <v>7.557682680721577e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.558700804967519e-08</v>
+        <v>1.558700804967521e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.480581964516213e-08</v>
+        <v>1.480581964516212e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.552704834105675e-08</v>
+        <v>1.552704834105677e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.56487837919117e-08</v>
+        <v>1.564878379191172e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.556907200372283e-08</v>
+        <v>1.556907200372285e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.549440891144525e-08</v>
+        <v>1.549440891144527e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.545233237718721e-08</v>
+        <v>1.545233237718722e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.546473815058546e-08</v>
+        <v>1.546473815058549e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.554601814379325e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.543639701422435e-08</v>
+        <v>1.543639701422438e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.557539454858037e-08</v>
+        <v>1.557539454858039e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.53767676280898e-08</v>
+        <v>1.537676762808978e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.548878413501644e-08</v>
+        <v>1.548878413501647e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.607112678083022e-08</v>
+        <v>2.607112678083021e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.556132453804325e-08</v>
+        <v>1.556132453804327e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.541963760227614e-08</v>
+        <v>1.541963760227615e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.583121815337237e-08</v>
+        <v>1.583121815337238e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.553095465210987e-08</v>
+        <v>1.55309546521099e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.541364088304283e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.336280330205204e-08</v>
+        <v>2.336280330205201e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.575201486098141e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.474561615843919e-08</v>
+        <v>2.474561615843916e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.580620418398107e-08</v>
+        <v>1.580620418398106e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.550091881941876e-08</v>
+        <v>1.550091881941878e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.671093233756933e-08</v>
+        <v>2.671093233756936e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.554445453001551e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.540230081696344e-08</v>
+        <v>1.540230081696343e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6694,37 +6694,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377710279918534e-08</v>
+        <v>1.377710279918533e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.203462926091043e-08</v>
+        <v>1.203462926091042e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.335996970880925e-08</v>
+        <v>1.335996970880922e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.421216465910874e-08</v>
+        <v>1.421216465910873e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.366324382287752e-08</v>
+        <v>1.366324382287751e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.311817770482904e-08</v>
+        <v>1.311817770482905e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.283103991837469e-08</v>
+        <v>1.283103991837468e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.291724785864601e-08</v>
+        <v>1.2917247858646e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.348795194244846e-08</v>
+        <v>1.348795194244843e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.271202539269069e-08</v>
+        <v>1.271202539269068e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.369168153389749e-08</v>
+        <v>1.36916815338975e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.25351055640371e-08</v>
@@ -6733,46 +6733,46 @@
         <v>1.308525156221954e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.199490087820386e-08</v>
+        <v>3.199490087820383e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.359246129327768e-08</v>
+        <v>1.359246129327769e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.259098477326595e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.554290170818362e-08</v>
+        <v>1.554290170818361e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33775898636392e-08</v>
+        <v>1.337758986363921e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.255118499145611e-08</v>
+        <v>1.255118499145609e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.573557530797334e-08</v>
+        <v>2.573557530797331e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.494205856752119e-08</v>
+        <v>1.494205856752124e-08</v>
       </c>
       <c r="W3" t="n">
         <v>3.053645464056313e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.534304330361367e-08</v>
+        <v>1.534304330361366e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.317293492935864e-08</v>
+        <v>1.317293492935863e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.213605042979432e-08</v>
+        <v>3.213605042979434e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.348298886843952e-08</v>
+        <v>1.348298886843951e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.254709301277033e-08</v>
+        <v>1.254709301277032e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6785,82 +6785,82 @@
         <v>5.585852804059554e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.490722354580632e-08</v>
+        <v>5.490722354580634e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.518125554892164e-08</v>
+        <v>5.518125554892165e-08</v>
       </c>
       <c r="E4" t="n">
         <v>5.655631346740261e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.565593215057495e-08</v>
+        <v>5.565593215057498e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.481257817658023e-08</v>
+        <v>5.481257817658028e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.433730436597361e-08</v>
+        <v>5.433730436597362e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.447743328344456e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.535281244824665e-08</v>
+        <v>5.535281244824667e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.415730711067891e-08</v>
+        <v>5.415730711067892e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.572734820325519e-08</v>
+        <v>5.57273482032552e-08</v>
       </c>
       <c r="M4" t="n">
         <v>5.393771353597004e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.474904373929203e-08</v>
+        <v>5.474904373929206e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.77572069560074e-08</v>
+        <v>5.775720695600741e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.556842096171374e-08</v>
+        <v>5.556842096171375e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.396800184301342e-08</v>
+        <v>5.396800184301343e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.861699350405318e-08</v>
+        <v>5.86169935040532e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.522537912925863e-08</v>
+        <v>5.522537912925864e-08</v>
       </c>
       <c r="T4" t="n">
         <v>5.390026614064595e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.393272168741535e-08</v>
+        <v>5.393272168741534e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.743158945062282e-08</v>
+        <v>5.743158945062283e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.923455756065443e-08</v>
+        <v>5.923455756065444e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.833444921278362e-08</v>
+        <v>5.833444921278363e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.480250023116482e-08</v>
+        <v>5.480250023116483e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.586297576297388e-08</v>
+        <v>5.58629757629739e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.53778664604532e-08</v>
+        <v>5.537786646045319e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.390924644230236e-08</v>
+        <v>5.390924644230238e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6873,31 +6873,31 @@
         <v>1.083474290557292e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.671516095060386e-08</v>
+        <v>9.671516095060389e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.019667861751849e-07</v>
+        <v>1.019667861751848e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.176652343522341e-07</v>
+        <v>1.176652343522342e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.120978314564592e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.086357803455519e-08</v>
+        <v>9.086357803455515e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.927976393258242e-08</v>
+        <v>8.927976393258236e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.054932121207724e-08</v>
+        <v>9.05493212120771e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.018757632019962e-07</v>
+        <v>1.018757632019963e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.335841074096787e-08</v>
+        <v>8.335841074096782e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.047135307494743e-07</v>
@@ -6906,7 +6906,7 @@
         <v>8.052090857109367e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.981706964249464e-08</v>
+        <v>7.981706964249459e-08</v>
       </c>
       <c r="O5" t="n">
         <v>1.365522373071307e-07</v>
@@ -6915,40 +6915,40 @@
         <v>1.025235386931852e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.927028196917096e-08</v>
+        <v>7.927028196917099e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.689816568901374e-07</v>
+        <v>1.689816568901375e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.74305196258248e-08</v>
+        <v>9.743051962582477e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.962647312686827e-08</v>
+        <v>7.962647312686829e-08</v>
       </c>
       <c r="U5" t="n">
         <v>7.908435794129987e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.344369347705125e-07</v>
+        <v>1.344369347705127e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.688906511488143e-07</v>
+        <v>1.688906511488139e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.529293886731354e-07</v>
+        <v>1.529293886731352e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.646314957503805e-08</v>
+        <v>9.646314957503815e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.05686662346341e-07</v>
+        <v>1.056866623463409e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.048172892241729e-07</v>
+        <v>1.048172892241728e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.101293193791492e-08</v>
+        <v>8.101293193791494e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,37 +6958,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.072428818798805e-08</v>
+        <v>6.072428818798806e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.977298369319884e-08</v>
+        <v>5.977298369319881e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.004701569631418e-08</v>
+        <v>6.004701569631416e-08</v>
       </c>
       <c r="E6" t="n">
         <v>6.142207361479513e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.381841657459658e-08</v>
+        <v>6.052169229796749e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.297506260060185e-08</v>
+        <v>5.967833832397281e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.24997887899952e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.93431934308371e-08</v>
+        <v>5.263991770746617e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.021857259563921e-08</v>
+        <v>5.351529687226825e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.231979153470053e-08</v>
+        <v>5.902306725807142e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.059310835064771e-08</v>
+        <v>6.05931083506477e-08</v>
       </c>
       <c r="M6" t="n">
         <v>5.880347368336257e-08</v>
@@ -6997,43 +6997,43 @@
         <v>5.290910710817063e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.591727032488593e-08</v>
+        <v>6.280856925726995e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.061989436293069e-08</v>
+        <v>6.061989436293066e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>5.883376199040594e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.34827536514457e-08</v>
+        <v>5.677947792807477e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.338786355328021e-08</v>
+        <v>5.33878635532802e-08</v>
       </c>
       <c r="T6" t="n">
         <v>5.876602628803848e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.888209218548981e-08</v>
+        <v>5.88820921854898e-08</v>
       </c>
       <c r="V6" t="n">
         <v>5.559407387464443e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.428585399077061e-08</v>
+        <v>6.428585399077059e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.320020936017613e-08</v>
+        <v>5.64969336368052e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.31805788413755e-08</v>
+        <v>5.318057884137551e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.072873591036639e-08</v>
+        <v>5.402546018699547e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.024362660784567e-08</v>
+        <v>5.354035088447478e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>5.205737709716227e-08</v>
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.035046748078119e-08</v>
+        <v>6.035046748078116e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.939916298599196e-08</v>
+        <v>5.939916298599194e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.96731949891073e-08</v>
+        <v>5.967319498910726e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.104825290758828e-08</v>
+        <v>6.104825290758827e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.014787159076061e-08</v>
+        <v>6.01478715907606e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.930451761676587e-08</v>
+        <v>5.930451761676591e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.882924380615926e-08</v>
+        <v>5.882924380615924e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.896937272363022e-08</v>
+        <v>5.89693727236302e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.984475188843232e-08</v>
+        <v>5.984475188843228e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.864924655086458e-08</v>
+        <v>5.864924655086455e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.021928764344085e-08</v>
+        <v>6.021928764344081e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.842965297615568e-08</v>
+        <v>5.842965297615566e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.92409831794777e-08</v>
+        <v>5.924098317947767e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.22478817795241e-08</v>
+        <v>6.224788177952408e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.005909578523043e-08</v>
+        <v>6.005909578523041e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.845994128319905e-08</v>
+        <v>5.845994128319903e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.310893294423881e-08</v>
+        <v>6.310893294423878e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.971731856944427e-08</v>
+        <v>5.971731856944423e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.83922055808316e-08</v>
+        <v>5.839220558083157e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.851173625922032e-08</v>
+        <v>5.851173625922031e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.192352889080846e-08</v>
+        <v>6.192352889080844e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.372649700084009e-08</v>
+        <v>6.372649700084005e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.282638865296919e-08</v>
+        <v>6.28263886529692e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>5.937805002203242e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.035491520315955e-08</v>
+        <v>6.035491520315953e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.986980590063884e-08</v>
+        <v>5.986980590063882e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.8401185882488e-08</v>
+        <v>5.840118588248798e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.91524855397587e-08</v>
+        <v>6.915248553975865e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.975631422951721e-08</v>
+        <v>7.975631422951711e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.00303462326325e-08</v>
+        <v>8.003034623263246e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.140540415111349e-08</v>
+        <v>7.525263658523751e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.075004435179879e-08</v>
+        <v>7.075004435179869e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.966166886029109e-08</v>
+        <v>8.205770100089398e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.918639504968451e-08</v>
+        <v>7.918639504968441e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.932652396715545e-08</v>
+        <v>7.932652396715536e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.020190313195767e-08</v>
+        <v>8.020190313195749e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.900639779438981e-08</v>
+        <v>7.900639779438973e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.057643888696607e-08</v>
+        <v>8.057643888696602e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.878680421968095e-08</v>
+        <v>7.878680421968097e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.064097307291589e-08</v>
+        <v>7.064097307291581e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.611064200229305e-08</v>
+        <v>7.611064200229298e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.331848147951677e-08</v>
+        <v>7.331848147951669e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.499111193789987e-08</v>
+        <v>6.499111193789984e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.346608418776406e-08</v>
+        <v>8.346608418776401e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.007446981296949e-08</v>
+        <v>8.007446981296942e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.874935682435685e-08</v>
+        <v>7.87493568243568e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.175843695094489e-08</v>
+        <v>7.322918160579284e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.228068013433371e-08</v>
+        <v>7.912653057644635e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.40859191586788e-08</v>
+        <v>8.408591915867865e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.041661022437203e-08</v>
+        <v>7.0416610224372e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.123047721405085e-08</v>
+        <v>9.123047721405069e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.071206644668479e-08</v>
+        <v>6.894229073038591e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.022695714416404e-08</v>
+        <v>8.022695714416396e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.082863996220275e-08</v>
+        <v>9.082863996220264e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.139303611333472e-08</v>
+        <v>7.139303611333471e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.609077142407939e-08</v>
+        <v>7.609077142407935e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.636480342719475e-08</v>
+        <v>7.636480342719471e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.773986134567567e-08</v>
+        <v>7.643609265715062e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.683948002884802e-08</v>
+        <v>6.381689021221335e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.599612605485333e-08</v>
+        <v>7.599613470870567e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.552085224424669e-08</v>
+        <v>7.552085224424667e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.56609811617176e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.653636032651978e-08</v>
+        <v>7.653636032651973e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.534085498895198e-08</v>
+        <v>7.534085498895197e-08</v>
       </c>
       <c r="L9" t="n">
         <v>7.691089608152824e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.512126141424311e-08</v>
+        <v>7.512126141424309e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.593259161756515e-08</v>
+        <v>7.59325916175651e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.081285075077656e-08</v>
+        <v>8.081285075077652e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.903121161649921e-08</v>
+        <v>7.903121161649919e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.515155837513894e-08</v>
+        <v>7.515155837513891e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.980054138232628e-08</v>
+        <v>7.980054138232622e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.640892700753166e-08</v>
+        <v>7.640892700753164e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.508381401891905e-08</v>
+        <v>7.508381401891898e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.519987991637039e-08</v>
+        <v>7.519987991637036e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.861513732889591e-08</v>
+        <v>8.513402080985264e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.041810543892751e-08</v>
+        <v>8.041810543892747e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.951799709105674e-08</v>
+        <v>7.951799709105672e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.606965846011982e-08</v>
+        <v>7.606965846011983e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.704652364124693e-08</v>
+        <v>7.364065840707809e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.656141433872626e-08</v>
+        <v>7.656141433872625e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.509279432057541e-08</v>
+        <v>7.509279432057545e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,16 +7466,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.740945176652064e-08</v>
+        <v>1.74094517665206e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.66229308583242e-08</v>
+        <v>1.662293085832421e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.762518394367865e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.728663577011294e-08</v>
+        <v>1.728663577011296e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.743048275835095e-08</v>
@@ -7484,19 +7484,19 @@
         <v>2.030953211259075e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.741121289173131e-08</v>
+        <v>1.741121289173132e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.784585578292441e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.841492916776874e-08</v>
+        <v>1.841492916776871e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.832895206829813e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.754151595645079e-08</v>
+        <v>1.754151595645075e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.759214078490443e-08</v>
@@ -7505,7 +7505,7 @@
         <v>1.818863115974924e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.813282877141949e-08</v>
+        <v>2.813282877141947e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.768044828437293e-08</v>
@@ -7517,28 +7517,28 @@
         <v>1.748971709645149e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.746318305068615e-08</v>
+        <v>1.746318305068613e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.764678894707517e-08</v>
+        <v>1.764678894707516e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.483685786745037e-08</v>
+        <v>2.48368578674504e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.732531980243142e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.554843826963379e-08</v>
+        <v>2.554843826963376e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.776128440517373e-08</v>
+        <v>1.776128440517372e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.741354246348521e-08</v>
+        <v>1.741354246348522e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.82292710876852e-08</v>
+        <v>2.822927108768518e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.761776683790447e-08</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.499124711450521e-08</v>
+        <v>1.499124711450516e-08</v>
       </c>
       <c r="C3" t="n">
         <v>1.305069666532737e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.654962149070563e-08</v>
+        <v>1.654962149070558e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.411520249418771e-08</v>
+        <v>1.411520249418772e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.515604740306521e-08</v>
+        <v>1.515604740306519e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.557913622000457e-08</v>
+        <v>3.557913622000464e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.502314425330801e-08</v>
+        <v>1.502314425330803e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.812990736945022e-08</v>
+        <v>1.81299073694502e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.213574432267429e-08</v>
+        <v>2.213574432267428e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.153838669106837e-08</v>
+        <v>2.153838669106836e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.593691766787086e-08</v>
+        <v>1.593691766787088e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.65718094043221e-08</v>
+        <v>1.657180940432212e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.056956025340993e-08</v>
+        <v>2.056956025340991e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.319485605105433e-08</v>
+        <v>3.319485605105425e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.692011023817018e-08</v>
+        <v>1.692011023817016e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.512905048904484e-08</v>
+        <v>1.512905048904483e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.558381372692184e-08</v>
+        <v>1.558381372692183e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5371015912575e-08</v>
+        <v>1.537101591257499e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.670408723898737e-08</v>
+        <v>1.670408723898735e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.81424327071909e-08</v>
+        <v>2.814243270719088e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.438939978401907e-08</v>
+        <v>1.438939978401908e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.875281072777259e-08</v>
+        <v>2.875281072777261e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.751925105778107e-08</v>
+        <v>1.751925105778111e-08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.502850669723294e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.311684934851879e-08</v>
+        <v>3.311684934851876e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.648656006837412e-08</v>
+        <v>1.648656006837411e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.601549865721289e-08</v>
+        <v>1.60154986572129e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.834338432158989e-08</v>
+        <v>5.834338432159001e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.699219360702894e-08</v>
+        <v>5.6992193607029e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.078017850429486e-08</v>
+        <v>6.07801785042949e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.695612114401592e-08</v>
+        <v>5.695612114401604e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.858093904904793e-08</v>
+        <v>5.8580939049048e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.110112593332344e-08</v>
+        <v>9.110112593332356e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.836327704100259e-08</v>
+        <v>5.836327704100264e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.327276844263683e-08</v>
+        <v>6.32727684426369e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.96349219887982e-08</v>
+        <v>6.963492198879828e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.872956322120397e-08</v>
+        <v>6.872956322120404e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.98351100993799e-08</v>
+        <v>5.983511009938e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0899668615553e-08</v>
+        <v>6.089966861555305e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.71445740083372e-08</v>
+        <v>6.714457400833724e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.938937195870316e-08</v>
+        <v>5.93893719587032e-08</v>
       </c>
       <c r="P4" t="n">
         <v>6.140441465528955e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.854692797021161e-08</v>
+        <v>5.854692797021168e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.925001814703541e-08</v>
+        <v>5.925001814703551e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.895030389385141e-08</v>
+        <v>5.895030389385159e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.1024216956451e-08</v>
+        <v>6.10242169564511e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.975770122014512e-08</v>
+        <v>5.975770122014521e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.694687907953354e-08</v>
+        <v>5.694687907953355e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.899871060981594e-08</v>
+        <v>5.899871060981599e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.231749582618696e-08</v>
+        <v>6.231749582618705e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.799990589939847e-08</v>
+        <v>5.799990589939853e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.889163098502932e-08</v>
+        <v>5.889163098502941e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.069639888253795e-08</v>
+        <v>6.069639888253808e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.995269526396505e-08</v>
+        <v>5.995269526396513e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,82 +7730,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.116461330523645e-07</v>
+        <v>1.116461330523646e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.194759135095415e-08</v>
+        <v>9.19475913509542e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.681114379656687e-07</v>
+        <v>1.681114379656683e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.569356275541954e-08</v>
+        <v>8.56935627554199e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.243138180112502e-07</v>
+        <v>1.243138180112501e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.697779480920218e-07</v>
+        <v>6.697779480920216e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.227715180093639e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.182109218984872e-07</v>
+        <v>2.182109218984874e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.087241379828175e-07</v>
+        <v>3.087241379828179e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.994734368983657e-07</v>
+        <v>2.994734368983653e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.415877633896032e-07</v>
+        <v>1.415877633896033e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.649814632583392e-07</v>
+        <v>1.649814632583393e-07</v>
       </c>
       <c r="N5" t="n">
         <v>1.545370726977418e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.284542028463351e-07</v>
+        <v>1.284542028463348e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.666025937082349e-07</v>
+        <v>1.666025937082342e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.206080241237208e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.397498565014752e-07</v>
+        <v>1.397498565014753e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.210561299665204e-07</v>
+        <v>1.210561299665202e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.728757224527457e-07</v>
+        <v>1.728757224527456e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.475398846357697e-07</v>
+        <v>1.475398846357701e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.245668927166147e-08</v>
+        <v>9.245668927166141e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.286947647194899e-07</v>
+        <v>1.2869476471949e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.962188506779365e-07</v>
+        <v>1.962188506779376e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.170046506628984e-07</v>
+        <v>1.170046506628982e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.215776399760218e-07</v>
+        <v>1.215776399760219e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.608962055257216e-07</v>
+        <v>1.608962055257221e-07</v>
       </c>
       <c r="AB5" t="n">
         <v>1.562162519996154e-07</v>
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.540068473143885e-08</v>
+        <v>6.54006847314389e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.523696527507182e-08</v>
+        <v>5.523696527507192e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.783747891414378e-08</v>
+        <v>6.783747891414382e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.401342155386486e-08</v>
+        <v>6.401342155386494e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.563823945889691e-08</v>
+        <v>6.563823945889692e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.934589760136631e-08</v>
+        <v>8.934589760136639e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.542057745085149e-08</v>
+        <v>6.542057745085155e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.151754011067974e-08</v>
+        <v>6.151754011067978e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.669222239864706e-08</v>
+        <v>6.787969365684117e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.697433488924688e-08</v>
+        <v>6.697433488924697e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.807988176742283e-08</v>
+        <v>6.689241050922891e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.795696902540187e-08</v>
+        <v>6.795696902540192e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.539864768169454e-08</v>
+        <v>6.539864768169469e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.764344563206047e-08</v>
+        <v>5.764344563206067e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.869198471313232e-08</v>
+        <v>6.869198471313239e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.679169963825454e-08</v>
+        <v>6.560422838006055e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.630731855688433e-08</v>
+        <v>6.630731855688443e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.600760430370031e-08</v>
+        <v>6.600760430370043e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.808151736629994e-08</v>
+        <v>5.926898862449404e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.720468635621433e-08</v>
+        <v>6.720468635621442e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.519165074757648e-08</v>
+        <v>6.400417948938245e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.742648521354722e-08</v>
+        <v>5.742648521354731e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.937479623603589e-08</v>
+        <v>6.056226749422999e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.673145193376861e-08</v>
+        <v>5.673145193376881e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.713640265307225e-08</v>
+        <v>5.713640265307234e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.775369929238691e-08</v>
+        <v>6.775369929238694e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.821545522684529e-08</v>
+        <v>5.821545522684534e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.440852564255177e-08</v>
+        <v>6.44085256425518e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.305733492799074e-08</v>
+        <v>6.30573349279908e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.684531982525672e-08</v>
+        <v>6.68453198252567e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.302126246497779e-08</v>
+        <v>6.302126246497784e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.464608037000981e-08</v>
+        <v>6.464608037000982e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.716626725428523e-08</v>
+        <v>9.716626725428529e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442841836196438e-08</v>
+        <v>6.442841836196445e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.933790976359868e-08</v>
+        <v>6.933790976359865e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.570006330976008e-08</v>
+        <v>7.570006330976009e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.479470454216581e-08</v>
+        <v>7.479470454216585e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.590025142034175e-08</v>
+        <v>6.590025142034185e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.696480993651484e-08</v>
+        <v>6.696480993651482e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.320971532929904e-08</v>
+        <v>7.320971532929907e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.545315777898708e-08</v>
+        <v>6.545315777898715e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.746820047557339e-08</v>
+        <v>6.746820047557343e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.461206929117345e-08</v>
+        <v>6.461206929117346e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.531515946799728e-08</v>
+        <v>6.531515946799732e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.50154452148133e-08</v>
+        <v>6.501544521481338e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.70893582774129e-08</v>
+        <v>6.708935827741291e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.620442461016678e-08</v>
+        <v>6.620442461016681e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.301202040049531e-08</v>
+        <v>6.301202040049532e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.506385193077771e-08</v>
+        <v>6.506385193077778e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.838263714714884e-08</v>
+        <v>6.838263714714891e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.445473194658063e-08</v>
+        <v>6.445473194658067e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.495677230599118e-08</v>
+        <v>6.495677230599122e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.676154020349984e-08</v>
+        <v>6.67615402034999e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.601783658492693e-08</v>
+        <v>6.601783658492694e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.427600181004512e-08</v>
+        <v>7.42760018100452e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.634651551492071e-08</v>
+        <v>8.634651551492086e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.013450041218675e-08</v>
+        <v>9.013450041218679e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.631044305190777e-08</v>
+        <v>7.916378136395204e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.66045012228023e-08</v>
+        <v>7.660450122280239e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.204554478412153e-07</v>
+        <v>1.232385256869174e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.771759894889438e-08</v>
+        <v>8.771759894889446e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.262709035052859e-08</v>
+        <v>9.262709035052875e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.898924389668998e-08</v>
+        <v>9.898924389669014e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.808388512909579e-08</v>
+        <v>9.808388512909591e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.918943200727176e-08</v>
+        <v>8.918943200727191e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>9.025399052344477e-08</v>
+        <v>9.025399052344413e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.609482958839236e-08</v>
+        <v>8.609482958839242e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>8.119875530230023e-08</v>
+        <v>8.11987553023003e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.251295669786386e-08</v>
+        <v>8.251295669786398e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.184187420444029e-08</v>
+        <v>7.184187420444038e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.860434005492727e-08</v>
+        <v>8.860434005492738e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.830462580174323e-08</v>
+        <v>8.830462580174331e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>9.037853886434279e-08</v>
+        <v>9.03785388643429e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.123777995208395e-08</v>
+        <v>8.294552418333085e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.630120098742529e-08</v>
+        <v>8.262707949193738e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.835567026621917e-08</v>
+        <v>8.835567026621925e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.684256793941178e-08</v>
+        <v>7.684256793941188e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.010798626469148e-07</v>
+        <v>1.010798626469149e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.824595289292112e-08</v>
+        <v>7.457493342277029e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.005072079042982e-08</v>
+        <v>9.005072079042992e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.033271097425775e-07</v>
+        <v>1.033271097425776e-07</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.534121671395446e-08</v>
+        <v>8.534121671395453e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.28919991155241e-08</v>
+        <v>9.28919991155242e-08</v>
       </c>
       <c r="D9" t="n">
         <v>9.667998401279013e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.285592665251115e-08</v>
+        <v>9.080139743977888e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>9.448074455754313e-08</v>
+        <v>7.395925019398637e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.270009314418187e-07</v>
+        <v>1.270009442758429e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.426308254949782e-08</v>
+        <v>9.426308254949788e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.917257395113204e-08</v>
+        <v>9.917257395113213e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.055347274972934e-07</v>
+        <v>1.055347274972935e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.046293687296991e-07</v>
+        <v>1.046293687296992e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.573491560787514e-08</v>
+        <v>9.573491560787526e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>9.679947412404812e-08</v>
+        <v>9.679947412404824e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.030443795168324e-07</v>
+        <v>1.030443795168325e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.823929678894823e-08</v>
+        <v>9.82392967889484e-08</v>
       </c>
       <c r="P9" t="n">
         <v>1.008959370313115e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.444674631273081e-08</v>
+        <v>9.444674631273093e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.514982365553062e-08</v>
+        <v>9.514982365553073e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>9.485010940234669e-08</v>
+        <v>9.485010940234677e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>9.692402246494622e-08</v>
+        <v>9.692402246494637e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>9.604719145486065e-08</v>
+        <v>9.604719145486073e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.284668458802875e-08</v>
+        <v>1.03119387081186e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>9.489851611831114e-08</v>
+        <v>9.489851611831122e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.82173013346821e-08</v>
+        <v>9.821730133468227e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.428939613411403e-08</v>
+        <v>9.428939613411418e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.479143649352458e-08</v>
+        <v>8.942434339508193e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.659620439103326e-08</v>
+        <v>9.65962043910333e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.585250077246029e-08</v>
+        <v>9.585250077246037e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,55 +8326,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.696391800713369e-08</v>
+        <v>1.696391800713371e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.644016874511645e-08</v>
+        <v>1.644016874511644e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.704334495154305e-08</v>
+        <v>1.704334495154306e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7045151039208e-08</v>
+        <v>1.704515103920801e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.709825202529625e-08</v>
+        <v>1.709825202529627e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.923716950217094e-08</v>
+        <v>1.923716950217093e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.699598753492084e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.707016967344463e-08</v>
+        <v>1.707016967344464e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.784127299293754e-08</v>
+        <v>1.784127299293753e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.716335425945792e-08</v>
+        <v>1.716335425945793e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.729049315149968e-08</v>
+        <v>1.729049315149969e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.700520809336844e-08</v>
+        <v>1.700520809336845e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.705109056867022e-08</v>
+        <v>1.705109056867023e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.743067112575617e-08</v>
+        <v>2.743067112575615e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74005291676546e-08</v>
+        <v>1.740052916765458e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.711220846246808e-08</v>
+        <v>1.71122084624681e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.726908945904207e-08</v>
+        <v>1.726908945904208e-08</v>
       </c>
       <c r="S2" t="n">
         <v>1.715797151921982e-08</v>
@@ -8383,28 +8383,28 @@
         <v>1.703634831969776e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.47863676779309e-08</v>
+        <v>2.478636767793089e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.705387937671693e-08</v>
+        <v>1.705387937671694e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.592013513544177e-08</v>
+        <v>2.592013513544176e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.752375331177885e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.737826917510043e-08</v>
+        <v>1.737826917510044e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.780568805277026e-08</v>
+        <v>2.780568805277027e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.706087587711317e-08</v>
+        <v>1.706087587711319e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.382425573479451e-08</v>
+        <v>3.382425573479436e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8414,70 +8414,70 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.374409452483316e-08</v>
+        <v>1.374409452483313e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.324303735646191e-08</v>
+        <v>1.32430373564619e-08</v>
       </c>
       <c r="D3" t="n">
         <v>1.431680733800617e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.431898070279485e-08</v>
+        <v>1.431898070279486e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.47096244961905e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.984967474181467e-08</v>
+        <v>2.984967474181458e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.398228916377298e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.451074016004113e-08</v>
+        <v>1.451074016004115e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.997519101639426e-08</v>
+        <v>1.997519101639423e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.516555781916943e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6064724562676e-08</v>
+        <v>1.606472456267603e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.431180075668847e-08</v>
+        <v>1.431180075668845e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.437088613999422e-08</v>
+        <v>1.437088613999421e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.126023038603201e-08</v>
+        <v>3.126023038603199e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68453853860962e-08</v>
+        <v>1.684538538609616e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.480093466916208e-08</v>
+        <v>1.480093466916211e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5937930694334e-08</v>
+        <v>1.593793069433401e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.512000840849835e-08</v>
+        <v>1.512000840849836e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.426763712622113e-08</v>
+        <v>1.426763712622109e-08</v>
       </c>
       <c r="U3" t="n">
         <v>2.700540341687153e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.437812795500122e-08</v>
+        <v>1.437812795500121e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.032184751892924e-08</v>
+        <v>3.032184751892929e-08</v>
       </c>
       <c r="X3" t="n">
         <v>1.774410436797513e-08</v>
@@ -8486,13 +8486,13 @@
         <v>1.670346739700929e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.199790210687322e-08</v>
+        <v>3.19979021068732e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.443926270882924e-08</v>
+        <v>1.443926270882925e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.331970737115237e-07</v>
+        <v>1.331970737115234e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.593783223175501e-08</v>
+        <v>5.593783223175504e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.667460236739856e-08</v>
+        <v>5.667460236739851e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.683499610705831e-08</v>
+        <v>5.683499610705827e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.685539669807546e-08</v>
+        <v>5.685539669807541e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.745519676360278e-08</v>
+        <v>5.74551967636027e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.161525361555421e-08</v>
+        <v>8.161525361555401e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.630007230082262e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.713799368091835e-08</v>
+        <v>5.713799368091838e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.579194971062199e-08</v>
+        <v>6.579194971062197e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.81905564469662e-08</v>
+        <v>5.819055644696612e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.962664871935785e-08</v>
+        <v>5.962664871935773e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.689708953460921e-08</v>
+        <v>5.689708953460915e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.692248641566975e-08</v>
+        <v>5.692248641566978e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.643350578388536e-08</v>
+        <v>5.643350578388527e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.086955614089564e-08</v>
+        <v>6.08695561408957e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.761284114173674e-08</v>
+        <v>5.76128411417367e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.938488416686384e-08</v>
+        <v>5.93848841668638e-08</v>
       </c>
       <c r="S4" t="n">
         <v>5.81297559197937e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.675596593175626e-08</v>
+        <v>5.675596593175625e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.634962624158248e-08</v>
+        <v>5.63496262415825e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.657346260290649e-08</v>
+        <v>5.657346260290648e-08</v>
       </c>
       <c r="W4" t="n">
         <v>5.962419743996524e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.226142953468607e-08</v>
+        <v>6.2261429534686e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.033509366833824e-08</v>
+        <v>6.033509366833823e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.668096808476764e-08</v>
+        <v>5.668096808476758e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.703301597599722e-08</v>
+        <v>5.703301597599723e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.438774848146162e-07</v>
+        <v>2.438774848146163e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.773437254157379e-08</v>
+        <v>7.773437254157375e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.297823222684757e-08</v>
+        <v>9.297823222684744e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.662798114379922e-08</v>
+        <v>9.662798114379918e-08</v>
       </c>
       <c r="E5" t="n">
         <v>9.143510306841598e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.080857501880179e-07</v>
+        <v>1.08085750188018e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.703536279312083e-07</v>
+        <v>4.703536279312058e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.896731925566405e-08</v>
+        <v>8.896731925566402e-08</v>
       </c>
       <c r="I5" t="n">
         <v>1.032739754795073e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.370822236409474e-07</v>
+        <v>2.370822236409467e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.165808778316938e-07</v>
+        <v>1.165808778316939e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.377156191722461e-07</v>
+        <v>1.37715619172246e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>9.741199224928223e-08</v>
+        <v>9.741199224928216e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>9.030141093091372e-08</v>
+        <v>9.030141093091364e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>8.551030248556096e-08</v>
+        <v>8.551030248556092e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.572774927887943e-07</v>
+        <v>1.572774927887946e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.065739223508305e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46895500162685e-07</v>
+        <v>1.468955001626848e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.118092695787017e-07</v>
+        <v>1.118092695787018e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.562669500226177e-08</v>
+        <v>9.562669500226154e-08</v>
       </c>
       <c r="U5" t="n">
         <v>9.001157637338195e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>9.116729294834048e-08</v>
+        <v>9.116729294834051e-08</v>
       </c>
       <c r="W5" t="n">
         <v>1.446733006803639e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.918771776553587e-07</v>
+        <v>1.918771776553586e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.616157180939124e-07</v>
+        <v>1.61615718093912e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.907950262355758e-08</v>
+        <v>8.90795026235575e-08</v>
       </c>
       <c r="AA5" t="n">
         <v>9.874988440425052e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.651158524187256e-06</v>
+        <v>3.651158524187251e-06</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.327071576430187e-08</v>
+        <v>5.432361701938147e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.400748589994533e-08</v>
+        <v>6.400748589994528e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.522078089468482e-08</v>
+        <v>5.52207808946847e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.524118148570193e-08</v>
+        <v>6.418828023062218e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.584098155122904e-08</v>
+        <v>6.478808029614946e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.894813714810084e-08</v>
+        <v>8.00010384031804e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.468585708844906e-08</v>
+        <v>6.363295583336939e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.552377846854483e-08</v>
+        <v>6.447087721346518e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.312483324316882e-08</v>
+        <v>6.417773449824839e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.657634123459239e-08</v>
+        <v>6.552343997951286e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.695953225190463e-08</v>
+        <v>5.801243350698416e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.52828743222357e-08</v>
+        <v>6.422997306715592e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.530960379066459e-08</v>
+        <v>5.530960379066441e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.392454753403885e-08</v>
+        <v>5.482062315887999e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.906604060910499e-08</v>
+        <v>5.906604060910479e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.599862592936324e-08</v>
+        <v>6.494572467428349e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.671776769941073e-08</v>
+        <v>6.671776769941059e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.651554070742016e-08</v>
+        <v>5.651554070742012e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.514175071938278e-08</v>
+        <v>5.514175071938268e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.396553539068489e-08</v>
+        <v>5.501843664576452e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.390634613545331e-08</v>
+        <v>6.390634613545326e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.819335584412814e-08</v>
+        <v>5.819335584412821e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.959431306723289e-08</v>
+        <v>6.064721432231242e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.911030555878515e-08</v>
+        <v>5.91103055587851e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.506675287239413e-08</v>
+        <v>5.506675287239403e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.4365899508544e-08</v>
+        <v>6.436589950854394e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.432972092625519e-07</v>
+        <v>2.432972092625521e-07</v>
       </c>
     </row>
     <row r="7">
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.102123346938153e-08</v>
+        <v>6.102123346938156e-08</v>
       </c>
       <c r="C7" t="n">
         <v>6.175800360502502e-08</v>
@@ -8775,28 +8775,28 @@
         <v>6.191839734468478e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.193879793570195e-08</v>
+        <v>6.193879793570193e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.253859800122924e-08</v>
+        <v>6.25385980012292e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.669865485318065e-08</v>
+        <v>8.669865485318041e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.13834735384491e-08</v>
+        <v>6.138347353844911e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.222139491854485e-08</v>
+        <v>6.222139491854491e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.087535094824853e-08</v>
+        <v>7.087535094824844e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.327395768459256e-08</v>
+        <v>6.327395768459259e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.471004995698426e-08</v>
+        <v>6.471004995698424e-08</v>
       </c>
       <c r="M7" t="n">
         <v>6.198049077223564e-08</v>
@@ -8805,46 +8805,46 @@
         <v>6.200588765329627e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.151564046600134e-08</v>
+        <v>6.151564046600131e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.595169082301178e-08</v>
+        <v>6.595169082301176e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.269624237936333e-08</v>
+        <v>6.269624237936323e-08</v>
       </c>
       <c r="R7" t="n">
         <v>6.446828540449031e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.321315715742016e-08</v>
+        <v>6.321315715742019e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.183936716938272e-08</v>
+        <v>6.183936716938275e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.17103818719198e-08</v>
+        <v>6.171038187191984e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.165686384053296e-08</v>
+        <v>6.165686384053298e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.470759867759179e-08</v>
+        <v>6.470759867759173e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.734483077231265e-08</v>
+        <v>6.734483077231251e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.570152052252039e-08</v>
+        <v>6.570152052252031e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>6.176436932239409e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.211641721362362e-08</v>
+        <v>6.21164172136237e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.48960886052243e-07</v>
+        <v>2.489608860522428e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8857,82 +8857,82 @@
         <v>7.032866306221902e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.338351440395049e-08</v>
+        <v>8.338351440395043e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.354390814361029e-08</v>
+        <v>8.354390814361022e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.356430873462745e-08</v>
+        <v>7.700529385292144e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.376504068108571e-08</v>
+        <v>7.376504068108565e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.08324165652106e-07</v>
+        <v>1.108784000350891e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.300898433737457e-08</v>
+        <v>8.300898433737458e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.384690571747044e-08</v>
+        <v>8.384690571747032e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.250086174717392e-08</v>
+        <v>9.250086174717388e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.489946848351803e-08</v>
+        <v>8.489946848351801e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.633556075590973e-08</v>
+        <v>8.633556075590966e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.360600157116115e-08</v>
+        <v>8.360600157115936e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.408282474692984e-08</v>
+        <v>7.408282474692981e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.621787507796935e-08</v>
+        <v>7.621787507796938e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.001071204054285e-08</v>
+        <v>8.001071204054262e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>6.958288786836674e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.609379620341588e-08</v>
+        <v>8.609379620341575e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.483866795634574e-08</v>
+        <v>8.483866795634563e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.346487796830826e-08</v>
+        <v>8.34648779683082e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.575845286150029e-08</v>
+        <v>7.732585935521751e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.328237463945844e-08</v>
+        <v>7.991189230977115e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.633553033160627e-08</v>
+        <v>8.633553033160628e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.536045287996067e-08</v>
+        <v>7.536045287996062e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.956877956519084e-08</v>
+        <v>9.956877956519093e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.338988012131962e-08</v>
+        <v>7.084298423232514e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.374192801254914e-08</v>
+        <v>8.374192801254912e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.834536626921692e-07</v>
+        <v>2.83453662692169e-07</v>
       </c>
     </row>
     <row r="9">
@@ -8945,82 +8945,82 @@
         <v>7.682314791817425e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.471748243948093e-08</v>
+        <v>8.471748243948079e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.487787617914063e-08</v>
+        <v>8.487787617914049e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.48982767701578e-08</v>
+        <v>8.324634551716405e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.5498076835685e-08</v>
+        <v>6.899792825830062e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.096581336876363e-07</v>
+        <v>1.096581407235376e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.434295237290493e-08</v>
+        <v>8.434295237290488e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.518087375300071e-08</v>
+        <v>8.518087375300061e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.383482978270426e-08</v>
+        <v>9.383482978270419e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.623343651904844e-08</v>
+        <v>8.623343651904839e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.766952879144015e-08</v>
+        <v>8.766952879144002e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.493996960669161e-08</v>
+        <v>8.493996960669146e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.496536648775213e-08</v>
+        <v>8.496536648775201e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.684840268893601e-08</v>
+        <v>8.684840268893602e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.180032447997392e-08</v>
+        <v>9.180032447997384e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.565572824972046e-08</v>
+        <v>8.56557282497204e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.742776423894623e-08</v>
+        <v>8.742776423894606e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.617263599187608e-08</v>
+        <v>8.617263599187599e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.479884600383858e-08</v>
+        <v>8.479884600383852e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.467553193022048e-08</v>
+        <v>8.467553193022037e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.461634267498877e-08</v>
+        <v>9.287602471671907e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.766707751204762e-08</v>
+        <v>8.766707751204754e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.030430960676833e-08</v>
+        <v>9.030430960676825e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>8.866099935697614e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.472384815684996e-08</v>
+        <v>8.040847610163227e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.507589604807967e-08</v>
+        <v>8.507589604807952e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.719203648866987e-07</v>
+        <v>2.719203648866982e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.875372826007131e-08</v>
+        <v>1.777760292998748e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.787358206402765e-08</v>
+        <v>1.697928116501753e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.915840950407164e-08</v>
+        <v>1.833291740186988e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.852473520843311e-08</v>
+        <v>1.76258558591763e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.890164316837442e-08</v>
+        <v>1.825087085375678e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.259635264125674e-08</v>
+        <v>2.062882993288248e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88922350841699e-08</v>
+        <v>1.807066051816932e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.942698615937393e-08</v>
+        <v>1.860127654901627e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.994039153011351e-08</v>
+        <v>1.886405297174167e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.021850239560876e-08</v>
+        <v>1.939486335819077e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.890953719601153e-08</v>
+        <v>2.174876416612552e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.918335493547792e-08</v>
+        <v>1.854622780514137e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.965363908710747e-08</v>
+        <v>1.881467392046555e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.018420830157302e-08</v>
+        <v>2.881425703101803e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.877464029098459e-08</v>
+        <v>1.786640433414131e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.871821338393776e-08</v>
+        <v>1.796795360197904e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.88467206180579e-08</v>
+        <v>1.802113209117414e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.870909479220327e-08</v>
+        <v>1.78887123427196e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92188248478673e-08</v>
+        <v>1.840996789987221e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.638363472979511e-08</v>
+        <v>2.52647126076956e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.863391140788973e-08</v>
+        <v>1.776481011466894e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.703431847543327e-08</v>
+        <v>2.588180570904055e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.859500965113381e-08</v>
+        <v>1.84598823396305e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.860414830943407e-08</v>
+        <v>1.786389546733571e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.957157242845569e-08</v>
+        <v>2.887489450297037e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.947032856083533e-08</v>
+        <v>1.863663995279268e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.903560479260926e-08</v>
+        <v>1.829684955710514e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.700122439670869e-08</v>
+        <v>1.540744814826009e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.442688638852431e-08</v>
+        <v>1.368118818925492e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.991909714548827e-08</v>
+        <v>1.939673325727312e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.537082685047675e-08</v>
+        <v>1.432447919144536e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.808727248919896e-08</v>
+        <v>1.881751721686176e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.436102485840624e-08</v>
+        <v>3.570781563268802e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.802455430988939e-08</v>
+        <v>1.753057170874663e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.184728556942649e-08</v>
+        <v>2.132343384213253e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.545998374083921e-08</v>
+        <v>2.315334367893462e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.750138518822895e-08</v>
+        <v>2.699223122181022e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.812345460935986e-08</v>
+        <v>4.375099463345161e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.037165178409452e-08</v>
+        <v>2.11747969770157e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.344778851594538e-08</v>
+        <v>2.282897198213923e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.679757315572767e-08</v>
+        <v>3.492915835980493e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.715133845650454e-08</v>
+        <v>1.603963590011563e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.676439793108968e-08</v>
+        <v>1.677979781139349e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.769357004957752e-08</v>
+        <v>1.717066522852699e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.668792281187172e-08</v>
+        <v>1.620142767456693e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.035312545901126e-08</v>
+        <v>1.99498988858574e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.12665478985468e-08</v>
+        <v>3.013619581359911e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.614613325967894e-08</v>
+        <v>1.53129735401997e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.139367590140088e-08</v>
+        <v>3.021408252663519e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.588463099214177e-08</v>
+        <v>2.030032706986299e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.594614557944454e-08</v>
+        <v>1.603204412566962e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.463056707387723e-08</v>
+        <v>3.495554372161095e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.213213942031627e-08</v>
+        <v>2.155099524754312e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.917058411358372e-08</v>
+        <v>1.924813081417069e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.196453320278625e-08</v>
+        <v>5.369943634765697e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.961286566424164e-08</v>
+        <v>5.28252315329121e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.653559401633935e-08</v>
+        <v>5.997196876484644e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.937795134252391e-08</v>
+        <v>5.19853833757429e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>6.363530013628925e-08</v>
+        <v>5.904521526063211e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.053687432828238e-07</v>
+        <v>8.590535697457851e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>6.352903149726688e-08</v>
+        <v>5.700965661932165e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.956929088934379e-08</v>
+        <v>6.300320878317177e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.529573591124607e-08</v>
+        <v>6.590248385873116e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.850983089307472e-08</v>
+        <v>7.196713686076625e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.372446680988242e-08</v>
+        <v>9.855552933425913e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.73098597051645e-08</v>
+        <v>6.282999258150731e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.212943997359255e-08</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>6.389378157314912e-08</v>
+        <v>5.640446452723438e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.220074421196118e-08</v>
+        <v>5.470248905823833e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.156337633920724e-08</v>
+        <v>5.584953475343639e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>6.301492466484279e-08</v>
+        <v>5.64502102522089e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.14603776508064e-08</v>
+        <v>5.495446827732106e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.721801311694222e-08</v>
+        <v>6.084228958476292e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.484494509661408e-08</v>
+        <v>5.815354941798632e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>6.011848204579115e-08</v>
+        <v>5.308805384887102e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.342944451975174e-08</v>
+        <v>5.662472008028071e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.017173350066929e-08</v>
+        <v>6.140609614360958e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.974964075039072e-08</v>
+        <v>5.427519412268541e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.148734459640215e-08</v>
+        <v>5.623587115837466e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.005886325234043e-08</v>
+        <v>6.340265469679574e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.536110219685736e-08</v>
+        <v>5.973538256917886e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.511399401287702e-07</v>
+        <v>1.160248879449678e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.129495879891756e-07</v>
+        <v>1.051893901112536e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.60809305577098e-07</v>
+        <v>2.57780239267764e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.013918657364089e-07</v>
+        <v>8.154169478027623e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.028371925645277e-07</v>
+        <v>2.428940718496277e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.864549917212451e-07</v>
+        <v>7.354705526349978e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.033288244743567e-07</v>
+        <v>2.014414646874756e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.28643409093109e-07</v>
+        <v>3.256032188998217e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>4.147431748300308e-07</v>
+        <v>3.582412368316834e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.116636223448062e-07</v>
+        <v>5.090468569466533e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.926519466694343e-07</v>
+        <v>1.020025965946092e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>2.805232484147056e-07</v>
+        <v>3.224262860278252e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.295273662040346e-07</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.847518354694034e-07</v>
+        <v>1.644485650237887e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.564101523546076e-07</v>
+        <v>1.352778310500248e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.529544403175755e-07</v>
+        <v>1.675296857752115e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.893233931038871e-07</v>
+        <v>1.863599143551124e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.441074896354104e-07</v>
+        <v>1.418846248683629e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.762403017972595e-07</v>
+        <v>2.772396815897163e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.227681894268265e-07</v>
+        <v>2.145031807900991e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.234213399097192e-07</v>
+        <v>1.107630047960236e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.879464498104567e-07</v>
+        <v>1.798739443571468e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.246588684686185e-07</v>
+        <v>2.851381853084972e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.245334753818363e-07</v>
+        <v>1.408373504428537e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.440788395148643e-07</v>
+        <v>1.659154330319847e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.239508622348083e-07</v>
+        <v>3.188901091374535e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.445373859696001e-07</v>
+        <v>2.62529910112338e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.054810894410522e-08</v>
+        <v>5.21129887882083e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.819644140556059e-08</v>
+        <v>6.076702147383658e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.482005867488628e-08</v>
+        <v>6.791375870577096e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.766241600107085e-08</v>
+        <v>5.992717331666737e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.221887587760821e-08</v>
+        <v>5.745876770118342e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.139523190241428e-07</v>
+        <v>9.384714691550311e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.211260723858582e-08</v>
+        <v>6.495144656024619e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.785375554789071e-08</v>
+        <v>6.141676122372315e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.387931165256503e-08</v>
+        <v>6.43160362992825e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.679429555162167e-08</v>
+        <v>7.990892680169072e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.200893146842936e-08</v>
+        <v>1.064973192751837e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>6.559432436371144e-08</v>
+        <v>7.077178252243185e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.043341397742756e-08</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>7.274055203049511e-08</v>
+        <v>5.484046460676524e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.104760750458277e-08</v>
+        <v>6.285680318539479e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.98478409977542e-08</v>
+        <v>6.379132469436091e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.12993893233897e-08</v>
+        <v>6.439200019313338e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.004395339212536e-08</v>
+        <v>5.336802071787241e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.550247777548919e-08</v>
+        <v>5.925584202531426e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.365472785493181e-08</v>
+        <v>5.696605798938567e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.87020577871101e-08</v>
+        <v>6.102984378979551e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.227627030898934e-08</v>
+        <v>6.477899757290672e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.875530924198828e-08</v>
+        <v>6.934788608453416e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.866399422145294e-08</v>
+        <v>5.320839124417301e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.97718092549491e-08</v>
+        <v>5.464942359892601e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.834332791088737e-08</v>
+        <v>7.134444463772024e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.368372113352943e-08</v>
+        <v>5.819793101106311e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.949078086703711e-08</v>
+        <v>6.063743997872017e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.71391133284925e-08</v>
+        <v>5.976323516397532e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>7.40618416805902e-08</v>
+        <v>6.690997239590968e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.690419900677478e-08</v>
+        <v>5.892338700680611e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>7.116154780054013e-08</v>
+        <v>6.598321889169527e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.128949909470747e-07</v>
+        <v>9.284336060564187e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>7.105527916151774e-08</v>
+        <v>6.394766025038485e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>7.709553855359464e-08</v>
+        <v>6.994121241423496e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>8.28219835754969e-08</v>
+        <v>7.284048748979437e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>8.603607855732557e-08</v>
+        <v>7.890514049182944e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.125071447413329e-08</v>
+        <v>1.054935329653224e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>7.483610736941533e-08</v>
+        <v>6.976799621257051e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.965568763784342e-08</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>7.141856549346691e-08</v>
+        <v>6.334101238576154e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.972552813227901e-08</v>
+        <v>6.163903691676546e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.90896240034581e-08</v>
+        <v>6.278753838449954e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.054117232909365e-08</v>
+        <v>6.338821388327214e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.898662531505725e-08</v>
+        <v>6.189247190838424e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>7.474426078119312e-08</v>
+        <v>6.778029321582616e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>7.28848423664891e-08</v>
+        <v>6.548037540003444e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.764472971004202e-08</v>
+        <v>6.002605747993423e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.095569218400255e-08</v>
+        <v>6.356272371134389e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.769798116492013e-08</v>
+        <v>6.834409977467284e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.780120651441234e-08</v>
+        <v>6.161215388459663e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.9013592260653e-08</v>
+        <v>6.317387478943787e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.758511091659127e-08</v>
+        <v>7.034065832785894e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.28873498611082e-08</v>
+        <v>6.667338620024202e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.039709058405824e-08</v>
+        <v>7.128365034792817e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>9.334160893742834e-08</v>
+        <v>8.498373179626769e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.00264337289526e-07</v>
+        <v>9.213046902820201e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>8.496192683743625e-08</v>
+        <v>7.638350611844546e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>8.44508245086913e-08</v>
+        <v>7.889993272689207e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.422692503461324e-07</v>
+        <v>1.210859304372871e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>9.72577747704536e-08</v>
+        <v>8.916815688267722e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>1.032980341625305e-07</v>
+        <v>9.516170904652739e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.090244791844328e-07</v>
+        <v>9.806098412208674e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.122385741662615e-07</v>
+        <v>1.041256371241219e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>9.745321008306912e-08</v>
+        <v>1.307140295976147e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.010386029783497e-07</v>
+        <v>9.498849284486121e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>9.400108018376856e-08</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>8.902385665807971e-08</v>
+        <v>8.037010857519501e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.653209817431155e-08</v>
+        <v>7.790710742520204e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.698988407398911e-08</v>
+        <v>7.056956886080485e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>9.67436679380295e-08</v>
+        <v>8.860871051556451e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>9.518912092399319e-08</v>
+        <v>8.71129685406767e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>1.009467563901289e-07</v>
+        <v>9.300078984811854e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>9.162523385993417e-08</v>
+        <v>8.359076596462163e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.96578243076353e-08</v>
+        <v>8.125576417645823e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>9.716119393051321e-08</v>
+        <v>8.878608460735931e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.700016706590881e-08</v>
+        <v>7.74618925460859e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.091988225679539e-07</v>
+        <v>1.013120266829454e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.963576747123858e-08</v>
+        <v>7.354936030842796e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.037876065255271e-07</v>
+        <v>9.556115496015132e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.150679906801763e-07</v>
+        <v>1.071179435161942e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.927225745771611e-08</v>
+        <v>8.760503920236649e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>1.087983177208173e-07</v>
+        <v>9.75880944918477e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.15721046072915e-07</v>
+        <v>1.04734831723782e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.058220836117082e-07</v>
+        <v>9.4242444821764e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>8.543932862613288e-08</v>
+        <v>7.877911376584233e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.545542100830282e-07</v>
+        <v>1.306682327170964e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.127144835538426e-07</v>
+        <v>1.017725195782572e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.187547429459194e-07</v>
+        <v>1.077660717421073e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.244811879678216e-07</v>
+        <v>1.106653468176667e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.276952829496504e-07</v>
+        <v>1.167299998197018e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.12909918866458e-07</v>
+        <v>1.433183922931947e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.164953117617401e-07</v>
+        <v>1.075928555404428e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.213148920301682e-07</v>
+        <v>3.637490207634528e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.170155167002808e-07</v>
+        <v>1.047654262883863e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.161785501652087e-07</v>
+        <v>1.038459727956834e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.107488431394116e-07</v>
+        <v>1.006124104959541e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.122003767214184e-07</v>
+        <v>1.012130732111445e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.10645829707382e-07</v>
+        <v>9.971733123625662e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>1.164034651735179e-07</v>
+        <v>1.056051525436986e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.145557152529605e-07</v>
+        <v>1.033153685077699e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>1.230105951435379e-07</v>
+        <v>1.103799767304189e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.126148965763274e-07</v>
+        <v>1.013875830392163e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.093571855572449e-07</v>
+        <v>1.061689591025452e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.094604109067372e-07</v>
+        <v>9.943701321246898e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.035115888518834e-07</v>
+        <v>9.445277681591905e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.19244315308916e-07</v>
+        <v>1.081655176557312e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14546554253433e-07</v>
+        <v>1.044982455281144e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.462315401723614e-08</v>
+        <v>1.480204094928746e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.383510869874595e-08</v>
+        <v>1.401762742297641e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.46502243880502e-08</v>
+        <v>1.482808175944911e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.465098560936731e-08</v>
+        <v>1.482723712584341e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.477116876782962e-08</v>
+        <v>1.494878295140336e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.481932023560932e-08</v>
+        <v>1.49792717670154e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.466695482746199e-08</v>
+        <v>1.484517774452389e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.470084690476511e-08</v>
+        <v>1.488649669047692e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.47794981583698e-08</v>
+        <v>1.495483647480489e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.473271307134665e-08</v>
+        <v>1.491892222730485e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.484091213823361e-08</v>
+        <v>1.505079718821335e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.463063920305006e-08</v>
+        <v>1.481386156400576e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.4666951642789e-08</v>
+        <v>1.484536233614822e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.402842684901694e-08</v>
+        <v>2.424826369928913e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.474122961693013e-08</v>
+        <v>1.491635003420392e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.466551502402181e-08</v>
+        <v>1.484392303820307e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.496052582431777e-08</v>
+        <v>1.51416318926115e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.476603073311987e-08</v>
+        <v>1.494249700607935e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.468171868425481e-08</v>
+        <v>1.48698469243444e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.103945404023686e-08</v>
+        <v>2.123743756496554e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.493776824071651e-08</v>
+        <v>1.511497477602927e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.23015598732216e-08</v>
+        <v>2.250259035524714e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.521041870622177e-08</v>
+        <v>1.538341873353302e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.490973018787746e-08</v>
+        <v>1.508823900029773e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.532472195835261e-08</v>
+        <v>2.551278824734141e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.490155271509133e-08</v>
+        <v>1.507908871130573e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.460656406298656e-08</v>
+        <v>1.479063966899347e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.171019925332394e-08</v>
+        <v>1.190370028386849e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.075302120385976e-08</v>
+        <v>1.094462304375464e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.19077063350905e-08</v>
+        <v>1.209401814914238e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.190244256910544e-08</v>
+        <v>1.20777965994397e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.277272784150323e-08</v>
+        <v>1.295724833077349e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.310142325426561e-08</v>
+        <v>1.316081028466353e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.203105534184013e-08</v>
+        <v>1.221992046390603e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.227086279039242e-08</v>
+        <v>1.251280762509685e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.282331970091389e-08</v>
+        <v>1.299182833521149e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.249188133204733e-08</v>
+        <v>1.273769869778459e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.325794356124221e-08</v>
+        <v>1.367168832468179e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.199891989560947e-08</v>
+        <v>1.222324388072823e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.202692791368604e-08</v>
+        <v>1.22169944487842e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.744803797793657e-08</v>
+        <v>2.770368670888216e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.254752320598796e-08</v>
+        <v>1.271431923488172e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.201444720427598e-08</v>
+        <v>1.220461601585518e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.413263496828315e-08</v>
+        <v>1.434209159879455e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.272426212557868e-08</v>
+        <v>1.290064090795443e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.213414758823996e-08</v>
+        <v>1.239379979371334e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.288856873309747e-08</v>
+        <v>2.310811973804398e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.393776494815986e-08</v>
+        <v>1.41194696407566e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.769909890834677e-08</v>
+        <v>2.792630078116228e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.589910270387016e-08</v>
+        <v>1.605075257081359e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.376054218939365e-08</v>
+        <v>1.395129887298218e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.984049422416133e-08</v>
+        <v>3.005704295094464e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.370137123013726e-08</v>
+        <v>1.388517620250221e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16628079467054e-08</v>
+        <v>1.189300051498642e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.245402271076633e-08</v>
+        <v>4.890939920001639e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.315836290183824e-08</v>
+        <v>4.959714427934369e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.275979500209694e-08</v>
+        <v>4.920354213015663e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.276839334705285e-08</v>
+        <v>4.919400160502973e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.412591740886899e-08</v>
+        <v>5.056691761857146e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.46698103882103e-08</v>
+        <v>5.091130281645769e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.294877301163546e-08</v>
+        <v>4.939664914611803e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.333159961590001e-08</v>
+        <v>4.986336564831164e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.417662551465193e-08</v>
+        <v>5.059197888746107e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.369154262659933e-08</v>
+        <v>5.02296270032661e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.491370086111745e-08</v>
+        <v>5.171921535220791e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.296142748917887e-08</v>
+        <v>4.946517340225624e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.289580223708988e-08</v>
+        <v>4.933965035594227e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.378774092676923e-08</v>
+        <v>5.020057289892466e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.293250976943636e-08</v>
+        <v>4.938247666103092e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.626479247045236e-08</v>
+        <v>5.274523512441343e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.406788094320922e-08</v>
+        <v>5.049591497445873e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.311553756581981e-08</v>
+        <v>4.967529888057373e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.377839173277484e-08</v>
+        <v>5.021633115729994e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.57124676605589e-08</v>
+        <v>5.214928007862405e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.927342693511104e-08</v>
+        <v>5.572299196362781e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.908744752796284e-08</v>
+        <v>5.547632872006398e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.582359346712614e-08</v>
+        <v>5.226904407606544e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.342367793839151e-08</v>
+        <v>4.989529631620938e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.559866407276925e-08</v>
+        <v>5.203878112027981e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.238486439809067e-08</v>
+        <v>4.889773938388498e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.109616985486287e-08</v>
+        <v>6.806281490216041e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.526941524411498e-08</v>
+        <v>8.204038034524045e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.873495331780562e-08</v>
+        <v>7.557821277381631e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.334376617256398e-08</v>
+        <v>7.012702340948527e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.038482519460091e-07</v>
+        <v>1.006140722720556e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.057131758457075e-07</v>
+        <v>9.943012878891758e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.412071495636031e-08</v>
+        <v>8.100818443422179e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.981269307334806e-08</v>
+        <v>8.822212887752999e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.00879816651089e-07</v>
+        <v>9.73108002427181e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.28560858481883e-08</v>
+        <v>9.131522894582286e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.112797561034228e-07</v>
+        <v>1.139254118656209e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.294778358720935e-08</v>
+        <v>8.087742644684281e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.79435120477482e-08</v>
+        <v>7.478495559301024e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.18932477429155e-08</v>
+        <v>8.819904600473023e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.055157626596078e-08</v>
+        <v>7.74670289645539e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.460600889424609e-07</v>
+        <v>1.435309691177882e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.670916259941255e-08</v>
+        <v>9.327207810304661e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.588963522522031e-08</v>
+        <v>8.480381044337956e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.047874002925392e-08</v>
+        <v>8.73671300211027e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.244029775396931e-07</v>
+        <v>1.211362857910052e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.927464656810582e-07</v>
+        <v>1.895955917928828e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.871579210005983e-07</v>
+        <v>1.830334597753328e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.30957039927866e-07</v>
+        <v>1.278244678661054e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.535572963513061e-08</v>
+        <v>8.261304357683895e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.289046654300245e-07</v>
+        <v>1.255732504622025e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.338331290530112e-08</v>
+        <v>7.150309180398992e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.111243365818451e-08</v>
+        <v>4.759073546030051e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.181677384925647e-08</v>
+        <v>5.453010628128906e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.763544624144368e-08</v>
+        <v>4.788487839044075e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.142680429447103e-08</v>
+        <v>5.412696360697511e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.278432835628717e-08</v>
+        <v>5.549987962051685e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.954546162755702e-08</v>
+        <v>4.959263907674184e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.782442425098216e-08</v>
+        <v>4.807798540640215e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.820725085524674e-08</v>
+        <v>4.854470190859578e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.905227675399867e-08</v>
+        <v>5.552494088940646e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.234995357401752e-08</v>
+        <v>4.891096326355023e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.978935210046417e-08</v>
+        <v>5.665217735415326e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.78370787285256e-08</v>
+        <v>4.814650966254036e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.791611431565434e-08</v>
+        <v>5.442041871330687e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.88048665167554e-08</v>
+        <v>4.874324468964625e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.78081610087831e-08</v>
+        <v>4.806381292131505e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.114044370979913e-08</v>
+        <v>5.142657138469757e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.894353218255594e-08</v>
+        <v>5.542887697640411e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.177394851323799e-08</v>
+        <v>4.835663514085787e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.852148189470686e-08</v>
+        <v>5.502238692696527e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.058811889990562e-08</v>
+        <v>5.08306163389082e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.810642731076825e-08</v>
+        <v>5.458040865431952e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.774585847538104e-08</v>
+        <v>6.040929072200938e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.448531306003932e-08</v>
+        <v>5.09607852649851e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.20820888858097e-08</v>
+        <v>4.857663257649352e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.425707502018742e-08</v>
+        <v>5.69717431222252e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.104107236836476e-08</v>
+        <v>4.757707332856786e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.713229660546213e-08</v>
+        <v>5.361992067874849e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.783663679653404e-08</v>
+        <v>5.430766575807578e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.743806889679272e-08</v>
+        <v>5.391406360888871e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.744666724174859e-08</v>
+        <v>5.390452308376184e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.880419130356477e-08</v>
+        <v>5.527743909730356e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.934808428290612e-08</v>
+        <v>5.562182429518979e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.762704690633126e-08</v>
+        <v>5.41071706248501e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.80098735105958e-08</v>
+        <v>5.457388712704373e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.885489940934773e-08</v>
+        <v>5.530250036619315e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.836981652129512e-08</v>
+        <v>5.49401484819982e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.959197475581323e-08</v>
+        <v>5.642973683093998e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.763970138387464e-08</v>
+        <v>5.417569488098834e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.75728139350418e-08</v>
+        <v>5.404890987952628e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.846475262472116e-08</v>
+        <v>5.490983242250868e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.761078366413212e-08</v>
+        <v>5.4092998139763e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.094306636514814e-08</v>
+        <v>5.74557566031455e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.874615483790499e-08</v>
+        <v>5.520643645319084e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.779381146051559e-08</v>
+        <v>5.438582035930581e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.832664356913208e-08</v>
+        <v>5.480046326043861e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.039074155525469e-08</v>
+        <v>5.685980155735615e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.395170082980685e-08</v>
+        <v>6.04335134423599e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.376572142265861e-08</v>
+        <v>6.018685019879609e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.036930628440723e-08</v>
+        <v>5.685265932251748e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.810195183308728e-08</v>
+        <v>5.460581779494147e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.027693796746502e-08</v>
+        <v>5.674930259901192e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.706313829278648e-08</v>
+        <v>5.360826086261708e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.524814302831117e-08</v>
+        <v>6.175275159466828e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.66926488778875e-08</v>
+        <v>7.321795866629966e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.629408097814614e-08</v>
+        <v>7.282435651711257e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.058385792482439e-08</v>
+        <v>6.707613539615674e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.85932300126494e-08</v>
+        <v>6.508927263235975e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.043113967931135e-08</v>
+        <v>7.676689415623254e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.648305898768462e-08</v>
+        <v>7.301746353307395e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.686588559194924e-08</v>
+        <v>7.34841800352676e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.771091149070111e-08</v>
+        <v>7.421279327441704e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.72258286026485e-08</v>
+        <v>7.385044139022202e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.844798683716659e-08</v>
+        <v>7.534002973916385e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.649571346522683e-08</v>
+        <v>7.308598778921058e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.039256216364317e-08</v>
+        <v>6.690197276094768e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.07236814939578e-08</v>
+        <v>6.720012844147423e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.361594240232365e-08</v>
+        <v>6.010781179021827e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.979907844650155e-08</v>
+        <v>7.636604951136937e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.760216691925836e-08</v>
+        <v>7.411672936141468e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.664982354186898e-08</v>
+        <v>7.329611326752966e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.194093096948863e-08</v>
+        <v>6.845128249380358e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.631455360497872e-08</v>
+        <v>7.282597208263561e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.280982366096962e-08</v>
+        <v>7.93459244300726e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.075523768439933e-08</v>
+        <v>6.718943965582978e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.990906010895873e-08</v>
+        <v>8.648109565238667e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.601829416440271e-08</v>
+        <v>6.25384518207896e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.913295004881839e-08</v>
+        <v>7.565959550723572e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.713815148284597e-08</v>
+        <v>8.377651401875791e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.578152379264271e-08</v>
+        <v>6.452226214971618e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.130806072801297e-08</v>
+        <v>7.066685039552426e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.090949282827167e-08</v>
+        <v>7.027324824633719e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.980515377438135e-08</v>
+        <v>6.900429650571989e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.115912555680718e-08</v>
+        <v>5.905710086074497e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.281951593711526e-08</v>
+        <v>7.198101664096391e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.109847083781015e-08</v>
+        <v>7.046635526229858e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.148129744207471e-08</v>
+        <v>7.093307176449218e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.232632334082666e-08</v>
+        <v>7.166168500364166e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.184124045277405e-08</v>
+        <v>7.129933311944664e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.306339868729218e-08</v>
+        <v>7.278892146838849e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.111112531535359e-08</v>
+        <v>7.053487951843683e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199292241706495e-08</v>
+        <v>7.884599896713189e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.264358003223107e-08</v>
+        <v>7.221775741522345e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.388307201716402e-08</v>
+        <v>7.347197445996628e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.10822153183414e-08</v>
+        <v>7.045219048553715e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.441449029662708e-08</v>
+        <v>7.381494124059398e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.221757876938395e-08</v>
+        <v>7.15656210906393e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.126523539199454e-08</v>
+        <v>7.07450049967543e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.179552848153481e-08</v>
+        <v>7.115913104120046e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.942688857941133e-08</v>
+        <v>7.951607776292936e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.742312476128579e-08</v>
+        <v>7.679269807980837e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.723714535413757e-08</v>
+        <v>7.654603483624455e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.384073021588613e-08</v>
+        <v>7.321184395996592e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.866602300083038e-08</v>
+        <v>6.767501430531992e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.374836189894395e-08</v>
+        <v>7.310848723646038e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.053456222426538e-08</v>
+        <v>6.996744550006556e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.770001217987787e-08</v>
+        <v>1.67285640506783e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.696261213101181e-08</v>
+        <v>1.59986827971712e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.768371283071647e-08</v>
+        <v>1.685574968338418e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.751296338810174e-08</v>
+        <v>1.663933761591123e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.763230586592758e-08</v>
+        <v>1.696305838283366e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.068766046364792e-08</v>
+        <v>1.892572948801746e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76246222732279e-08</v>
+        <v>1.676800804309926e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.796079918992532e-08</v>
+        <v>1.71298241673665e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.870338502036329e-08</v>
+        <v>1.765741915790367e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.89094635278577e-08</v>
+        <v>1.807580877165371e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.777298152285628e-08</v>
+        <v>1.996484493613665e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.778952945628476e-08</v>
+        <v>1.718352166149429e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.800102047006486e-08</v>
+        <v>1.715077858893748e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.859013929196488e-08</v>
+        <v>2.704931374130809e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.789728398548536e-08</v>
+        <v>1.697209691635239e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.758235426712473e-08</v>
+        <v>1.680833780614653e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.760351182721664e-08</v>
+        <v>1.678755119554106e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.771140492201846e-08</v>
+        <v>1.686154425047875e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.774069678680365e-08</v>
+        <v>1.693234907412786e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.527891119631185e-08</v>
+        <v>2.376214547269443e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.757028452333086e-08</v>
+        <v>1.669939448760116e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.646684463875025e-08</v>
+        <v>2.488355441969427e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.770533108365989e-08</v>
+        <v>1.759540640434003e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.764695447553783e-08</v>
+        <v>1.687232647697351e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.846327575124299e-08</v>
+        <v>2.762891484315836e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.789873308761738e-08</v>
+        <v>1.708744056830628e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.781991437379193e-08</v>
+        <v>1.728316344829476e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.561069049305001e-08</v>
+        <v>1.411693328641942e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.388999940222154e-08</v>
+        <v>1.302654315138086e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.551098747587096e-08</v>
+        <v>1.50381474329409e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.427774899912618e-08</v>
+        <v>1.347853482953636e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.514438893364879e-08</v>
+        <v>1.580781777322252e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.687193054974792e-08</v>
+        <v>2.975233929864184e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.509317279375395e-08</v>
+        <v>1.441519981534203e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.749760959821463e-08</v>
+        <v>1.700331994731703e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.275786520196214e-08</v>
+        <v>2.07356606563419e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.424061947280021e-08</v>
+        <v>2.372651455478557e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.614005341344406e-08</v>
+        <v>3.721511363509726e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.654268083717058e-08</v>
+        <v>1.763301798618321e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.777445728675531e-08</v>
+        <v>1.714209220064743e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.397564973254559e-08</v>
+        <v>3.180056559309551e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.701534706016889e-08</v>
+        <v>1.58497171487286e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.478314802107111e-08</v>
+        <v>1.469560392583968e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.493963251106628e-08</v>
+        <v>1.455311048870567e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.56949355095656e-08</v>
+        <v>1.506520812087209e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.591899555191277e-08</v>
+        <v>1.558655270083782e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.899757105973835e-08</v>
+        <v>2.720131644774254e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.468438731077468e-08</v>
+        <v>1.390531734649605e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.279418068391016e-08</v>
+        <v>3.089105161896663e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.566349789879906e-08</v>
+        <v>2.032506408223762e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.524183617588622e-08</v>
+        <v>1.51489290263491e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.313954707009118e-08</v>
+        <v>3.315675324152522e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.703936569467524e-08</v>
+        <v>1.66850133907854e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.660274220317993e-08</v>
+        <v>1.818089626624777e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.942429967028818e-08</v>
+        <v>5.16301059579572e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.835593130681209e-08</v>
+        <v>5.184238652270357e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.924019102343905e-08</v>
+        <v>5.306672618765165e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.731149752048193e-08</v>
+        <v>5.062225233107532e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.865952570777636e-08</v>
+        <v>5.427882731237424e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.317116142158351e-08</v>
+        <v>7.644810031874042e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.857273599360619e-08</v>
+        <v>5.207564399748479e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.237000891672585e-08</v>
+        <v>5.616252356472366e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0691627758854e-08</v>
+        <v>6.205849488424779e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.308560902082943e-08</v>
+        <v>6.684785484456561e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.024852196678536e-08</v>
+        <v>8.818538732196937e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.093385802527747e-08</v>
+        <v>5.721906738353241e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.282432677860522e-08</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>6.023481033372854e-08</v>
+        <v>5.297450085628684e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.165257546413894e-08</v>
+        <v>5.438092170639904e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.80952994204277e-08</v>
+        <v>5.253118722371135e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.833428379462423e-08</v>
+        <v>5.229639289460944e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.955298593368652e-08</v>
+        <v>5.313217848861751e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.988385102135883e-08</v>
+        <v>5.393195154356235e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>6.079775045015082e-08</v>
+        <v>5.420347695056531e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.750982519117762e-08</v>
+        <v>5.08703354920552e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.498584091976964e-08</v>
+        <v>5.843578407554172e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.948437913532266e-08</v>
+        <v>6.142148910975021e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.842765478303554e-08</v>
+        <v>5.281872165789357e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.892739518395712e-08</v>
+        <v>5.379071958955029e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.16689437393398e-08</v>
+        <v>5.568378131591958e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.09743702461664e-08</v>
+        <v>5.801791186181804e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.248643426487742e-07</v>
+        <v>9.572859236471485e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.116437138403796e-07</v>
+        <v>1.046857424696307e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.306299605009832e-07</v>
+        <v>1.303911971037391e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.604748329778936e-08</v>
+        <v>7.579072214624724e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.198151548436821e-07</v>
+        <v>1.554244267417669e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.28601775101126e-07</v>
+        <v>5.394723501368017e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.201885512789013e-07</v>
+        <v>1.134698842040725e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.94837522793596e-07</v>
+        <v>1.939812501667982e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.313351339853441e-07</v>
+        <v>2.881721886967512e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.820667881075329e-07</v>
+        <v>3.802545201849811e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.452188225317591e-07</v>
+        <v>7.872918433308304e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.658089861633094e-07</v>
+        <v>2.150478427787266e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.627405876342403e-07</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.374832433022827e-07</v>
+        <v>1.180080563747316e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.651709968600186e-07</v>
+        <v>1.447807221443927e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.065140702175696e-07</v>
+        <v>1.179502516754856e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.140815510306898e-07</v>
+        <v>1.167707466569024e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.289295300400667e-07</v>
+        <v>1.236783294367385e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.435291936603998e-07</v>
+        <v>1.477027043304359e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.611113450147678e-07</v>
+        <v>1.533821331850621e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.646943021370036e-08</v>
+        <v>8.716012765342338e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>2.360879417330788e-07</v>
+        <v>2.284131197551736e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.342570248958216e-07</v>
+        <v>2.927835327026079e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18994686450252e-07</v>
+        <v>1.297449527602629e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.174005762918284e-07</v>
+        <v>1.35109937339441e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.730866030032232e-07</v>
+        <v>1.761349703253029e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.708380872569759e-07</v>
+        <v>2.380542820714801e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.771214147023831e-08</v>
+        <v>5.00898941793932e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.556087407381656e-08</v>
+        <v>5.85052778822203e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.644513379044349e-08</v>
+        <v>5.152651440908772e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.559933932043205e-08</v>
+        <v>5.728514369059206e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.694736750772651e-08</v>
+        <v>5.273861553381031e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.145900322153364e-08</v>
+        <v>8.311099167825715e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.577767876061062e-08</v>
+        <v>5.873853535700153e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.065785071667599e-08</v>
+        <v>6.282541492424037e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.789657052585836e-08</v>
+        <v>6.872138624376451e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.029055178783387e-08</v>
+        <v>6.530764306600169e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.85363637667355e-08</v>
+        <v>9.484827868148599e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.922169982522762e-08</v>
+        <v>6.388195874304915e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.112250450911712e-08</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>6.765754699151066e-08</v>
+        <v>5.144506733686679e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.90753889302739e-08</v>
+        <v>6.124730315133143e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.530024218743215e-08</v>
+        <v>5.099097544514741e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.553922656162864e-08</v>
+        <v>5.895928425412618e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.6757928700691e-08</v>
+        <v>5.159196671005357e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.817169282130897e-08</v>
+        <v>5.23917397649984e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.948292595908292e-08</v>
+        <v>5.309851221105274e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.471476795818208e-08</v>
+        <v>4.933012371349126e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.240874390405318e-08</v>
+        <v>5.71039454026264e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.668932190232706e-08</v>
+        <v>6.808438046926692e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.721407539980019e-08</v>
+        <v>5.181779736136816e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.613233795096159e-08</v>
+        <v>5.225050781098636e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.995678553928994e-08</v>
+        <v>6.234667267543632e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.928412325912214e-08</v>
+        <v>5.653021217379349e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.56764194278284e-08</v>
+        <v>5.754539506516854e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.46080510643523e-08</v>
+        <v>5.775767562991495e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.549231078097925e-08</v>
+        <v>5.898201529486305e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.35636172780221e-08</v>
+        <v>5.653754143828668e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.491164546531656e-08</v>
+        <v>6.019411641958563e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.942328117912362e-08</v>
+        <v>8.236338942595175e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.482485575114641e-08</v>
+        <v>5.799093310469617e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.862212867426608e-08</v>
+        <v>6.207781267193499e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.694374751639418e-08</v>
+        <v>6.797378399145918e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.933772877836962e-08</v>
+        <v>7.276314395177703e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.650064172432559e-08</v>
+        <v>9.410067642918095e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.718597778281767e-08</v>
+        <v>6.313435649074377e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.907644653614546e-08</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>6.648557177493392e-08</v>
+        <v>5.888844474752959e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.790333690534433e-08</v>
+        <v>6.029486559764176e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.434741917796791e-08</v>
+        <v>5.844647633092272e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.458640355216443e-08</v>
+        <v>5.821168200182081e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.580510569122673e-08</v>
+        <v>5.904746759582888e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.613597077889906e-08</v>
+        <v>5.984724065077371e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.743878853243597e-08</v>
+        <v>6.05454228901423e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.37619449487178e-08</v>
+        <v>5.678562459926656e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>7.123796067730985e-08</v>
+        <v>6.435107318275308e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.573649889286289e-08</v>
+        <v>6.733677821696158e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.507710824955772e-08</v>
+        <v>5.916925780415632e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.517951494149733e-08</v>
+        <v>5.970600869676166e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.792106349687999e-08</v>
+        <v>6.159907042313098e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.722649000370662e-08</v>
+        <v>6.393320096902939e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.568550058602507e-08</v>
+        <v>6.713603951865725e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.829152912484115e-08</v>
+        <v>8.025002292707442e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.917578884146812e-08</v>
+        <v>8.147436259202253e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.996588235739341e-08</v>
+        <v>7.216011254750743e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.705103784436357e-08</v>
+        <v>7.179469539025723e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.259422345177735e-07</v>
+        <v>1.07530988854592e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.850833381163522e-08</v>
+        <v>8.048328040185561e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.230560673475485e-08</v>
+        <v>8.457015996909445e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>1.00627225576883e-07</v>
+        <v>9.046613128861857e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.030212068388585e-07</v>
+        <v>9.525549124893644e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.018411978481436e-08</v>
+        <v>1.165930237263403e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.086945584330562e-08</v>
+        <v>8.562670378790184e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.21599793200568e-08</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>8.248341987463211e-08</v>
+        <v>7.412951477033949e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.318714885760077e-08</v>
+        <v>7.48622472479693e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.166916924162884e-08</v>
+        <v>6.550164170828902e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.826988161265321e-08</v>
+        <v>8.070402929898031e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.948858375171552e-08</v>
+        <v>8.153981489298835e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.981944883938788e-08</v>
+        <v>8.233958794793315e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.445092230426865e-08</v>
+        <v>7.674359674248991e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.370197194341238e-08</v>
+        <v>7.574554913588096e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>9.49241261476379e-08</v>
+        <v>8.684595603319863e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.431153460369002e-08</v>
+        <v>7.557441029563615e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.023473719401096e-07</v>
+        <v>9.447986947644479e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.493458715637699e-08</v>
+        <v>6.905699739578063e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.160454155736874e-08</v>
+        <v>8.409141772029041e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.051940190630738e-07</v>
+        <v>9.990245570917542e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.690218293845041e-08</v>
+        <v>7.686729744259692e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.488766185204035e-08</v>
+        <v>8.538630757579597e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.577192156866732e-08</v>
+        <v>8.661064724074412e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.175364709531944e-08</v>
+        <v>8.224902275209191e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.431965019401023e-08</v>
+        <v>6.867345487670348e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.297029050338067e-07</v>
+        <v>1.099920326429513e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.510446653883452e-08</v>
+        <v>8.561956505057723e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.89017394619541e-08</v>
+        <v>8.970644461781604e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.072233583040822e-07</v>
+        <v>9.560241593734023e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.096173395660577e-07</v>
+        <v>1.00391775897658e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>9.678025251201367e-08</v>
+        <v>1.217293083750619e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>9.746558857050575e-08</v>
+        <v>9.07629884366248e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.935605732383346e-08</v>
+        <v>1.92460960631254e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.97669914089554e-08</v>
+        <v>8.927127621798318e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.018373002087316e-07</v>
+        <v>9.127639319791572e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.462704303265081e-08</v>
+        <v>8.607511954792224e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.486601433985248e-08</v>
+        <v>8.584031394770186e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>9.608471647891482e-08</v>
+        <v>8.667609954170995e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>9.641558156658711e-08</v>
+        <v>8.747587259665473e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>9.772681470436109e-08</v>
+        <v>8.818264504270915e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.044895181622628e-07</v>
+        <v>9.400005810298861e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.015175714649979e-07</v>
+        <v>9.197970512863412e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.60161096805509e-08</v>
+        <v>9.496541016284265e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.535671903724578e-08</v>
+        <v>8.679788975003741e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.000046610938616e-08</v>
+        <v>8.232642585171591e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.820067428456811e-08</v>
+        <v>8.922770236901204e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.750610079139476e-08</v>
+        <v>9.156183291491044e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.739780901677576e-08</v>
+        <v>1.623099880179424e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.679456391888101e-08</v>
+        <v>1.551909132088092e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.757050137359639e-08</v>
+        <v>1.652606956965352e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.738475561554883e-08</v>
+        <v>1.628405426436024e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.733239774455585e-08</v>
+        <v>1.646133658466947e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.003710606927371e-08</v>
+        <v>1.816497229191384e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.728775807427356e-08</v>
+        <v>1.622602391810149e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.752062414769517e-08</v>
+        <v>1.652631914956007e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.827300186116778e-08</v>
+        <v>1.706942179979348e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.748051120226483e-08</v>
+        <v>1.649929403496419e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.744651391331091e-08</v>
+        <v>1.893648274260694e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.75159587312133e-08</v>
+        <v>1.666349294818728e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74355057043339e-08</v>
+        <v>1.637672940564495e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.812547268251187e-08</v>
+        <v>2.618009245069852e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.760682191673336e-08</v>
+        <v>1.644962989089233e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.735384317897652e-08</v>
+        <v>1.637602336840102e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.723672425839184e-08</v>
+        <v>1.621461351688417e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.74463305955997e-08</v>
+        <v>1.637857149863621e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.735799970273108e-08</v>
+        <v>1.634530003799037e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.552000992242196e-08</v>
+        <v>2.310609914090354e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.735025707458042e-08</v>
+        <v>1.627464763726727e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.663361012847881e-08</v>
+        <v>2.419203091705882e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.782001205627123e-08</v>
+        <v>1.76754625522732e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.769983449278266e-08</v>
+        <v>1.676688436067019e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.830642081639576e-08</v>
+        <v>2.715092073836471e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.745480555818128e-08</v>
+        <v>1.647284737622634e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.754510455262241e-08</v>
+        <v>1.682633776984115e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.489031742373199e-08</v>
+        <v>1.322287260878688e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.360141999083867e-08</v>
+        <v>1.228718652807393e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.61371451654041e-08</v>
+        <v>1.534037166539046e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.479577993894708e-08</v>
+        <v>1.359739370345934e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.443443459924266e-08</v>
+        <v>1.48777194546973e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.365440537435404e-08</v>
+        <v>2.697283787643547e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.411775980948458e-08</v>
+        <v>1.319694358020373e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.578286839777176e-08</v>
+        <v>1.534513780244259e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.111752313840459e-08</v>
+        <v>1.919235681669174e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.548287594782389e-08</v>
+        <v>1.513524227440797e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.524292608043577e-08</v>
+        <v>3.252552776276131e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.601972064201464e-08</v>
+        <v>1.657207612656617e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.516845611214386e-08</v>
+        <v>1.426911380461124e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.273051625030284e-08</v>
+        <v>3.00117013362626e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.637537939014729e-08</v>
+        <v>1.477666844850931e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.458402423620675e-08</v>
+        <v>1.4262676577527e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.375025890689284e-08</v>
+        <v>1.311360027672592e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.523628636918324e-08</v>
+        <v>1.427331713728125e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.461745137975e-08</v>
+        <v>1.404787394942765e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.917175330994633e-08</v>
+        <v>2.593545292561995e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.454634319871085e-08</v>
+        <v>1.352798852869225e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.221834875919695e-08</v>
+        <v>2.951701627773102e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.791849173330318e-08</v>
+        <v>2.355483544631246e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705204352888109e-08</v>
+        <v>1.705064684560638e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.30445915296065e-08</v>
+        <v>3.264516941323636e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.530404424945793e-08</v>
+        <v>1.495319788704762e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.606903014445473e-08</v>
+        <v>1.756803313129576e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.783402854603507e-08</v>
+        <v>5.009034565437582e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.720898356206329e-08</v>
+        <v>5.056844065366433e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.978466815873293e-08</v>
+        <v>5.342330571660488e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.768658437431565e-08</v>
+        <v>5.068963151077751e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.709517813563942e-08</v>
+        <v>5.269211687256695e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.764610289062878e-08</v>
+        <v>7.193546589703676e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.659095252453805e-08</v>
+        <v>5.003415205450664e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.922128194752123e-08</v>
+        <v>5.342612483646276e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.76616557603565e-08</v>
+        <v>5.950504163489027e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.876818777601904e-08</v>
+        <v>5.312086373493509e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.838417275775905e-08</v>
+        <v>8.065003134995721e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.966256868473882e-08</v>
+        <v>5.542227882303549e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.825982997333724e-08</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.811412250494268e-08</v>
+        <v>5.085105315372628e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.019492540174042e-08</v>
+        <v>5.255988438100818e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.733741418280807e-08</v>
+        <v>5.172846484879576e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.601450209743853e-08</v>
+        <v>4.99052663237132e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.838210209988046e-08</v>
+        <v>5.175724715200045e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.738436403071129e-08</v>
+        <v>5.138143069837702e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.929449882671295e-08</v>
+        <v>5.270334195299346e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.690229937520265e-08</v>
+        <v>5.020508891063655e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.210690525643844e-08</v>
+        <v>5.657244473811712e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.26030061001303e-08</v>
+        <v>6.640622820219043e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.09317309623814e-08</v>
+        <v>5.596883286135232e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.814652150586867e-08</v>
+        <v>5.299102656669964e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.847783070091466e-08</v>
+        <v>5.282213655842719e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.968656522721906e-08</v>
+        <v>5.692651333448193e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.048940746447632e-07</v>
+        <v>7.742941797937286e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.786587707589067e-08</v>
+        <v>8.850988184344631e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.46812110067646e-07</v>
+        <v>1.423712099831264e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.015738727827158e-07</v>
+        <v>8.588416319740131e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.750638402533995e-08</v>
+        <v>1.291022537980361e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.944914037002464e-07</v>
+        <v>4.36382360488126e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.958370854214777e-08</v>
+        <v>8.139856069920156e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.377284077899645e-07</v>
+        <v>1.43967905523629e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.697884973330016e-07</v>
+        <v>2.374195426044955e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.226127528277143e-07</v>
+        <v>1.297507802803007e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.172150860163525e-07</v>
+        <v>6.145497848597586e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.46444191313763e-07</v>
+        <v>1.819752325692534e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.354463443443871e-07</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.078685790098677e-07</v>
+        <v>8.909163329321299e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.431920484263463e-07</v>
+        <v>1.17694702143884e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.999378541731244e-08</v>
+        <v>1.088671465855463e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>7.769362930517066e-08</v>
+        <v>7.813090427782991e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.144156188259515e-07</v>
+        <v>1.054659070971023e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.02773642171506e-07</v>
+        <v>1.050464195466275e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.367948274714975e-07</v>
+        <v>1.259700056563454e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.261905530283721e-08</v>
+        <v>8.245046085266156e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.842258199792427e-07</v>
+        <v>1.944362036408601e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.969577651817547e-07</v>
+        <v>3.777939115248615e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.684221669376121e-07</v>
+        <v>1.861112474201751e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.082605406699696e-07</v>
+        <v>1.22547349286797e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.198770854943698e-07</v>
+        <v>1.279428925350575e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.505614158461238e-07</v>
+        <v>2.167843346585768e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.625753459125039e-08</v>
+        <v>5.608160542804622e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.563248960727863e-08</v>
+        <v>4.914931987474156e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.637765725237184e-08</v>
+        <v>5.941456549027527e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.6110090419531e-08</v>
+        <v>5.668089128444793e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.368816722927827e-08</v>
+        <v>5.127299609364418e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.606960893584407e-08</v>
+        <v>7.051634511811393e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.501445856975338e-08</v>
+        <v>4.861503127558389e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.764478799273658e-08</v>
+        <v>5.200700405754001e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.425464485399531e-08</v>
+        <v>6.549630140856069e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.536117686965789e-08</v>
+        <v>5.911212350860554e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.680767880297437e-08</v>
+        <v>8.664129112362762e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.625555777837765e-08</v>
+        <v>5.400315804411274e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.668571036551893e-08</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>5.654000289712435e-08</v>
+        <v>5.699462592625666e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.6978479463224e-08</v>
+        <v>5.870454254421426e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.393040327644691e-08</v>
+        <v>5.77197246224662e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.260749119107739e-08</v>
+        <v>4.848614554479045e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.680560814509579e-08</v>
+        <v>5.774850692567086e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.580787007592663e-08</v>
+        <v>4.996230991945429e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.803181914566324e-08</v>
+        <v>5.145880787413447e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.349528846884148e-08</v>
+        <v>5.619634868430697e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.072978732563481e-08</v>
+        <v>6.271585515864843e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.102651214534565e-08</v>
+        <v>6.498710742326765e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.977294762484929e-08</v>
+        <v>5.481791874877744e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.657002755108398e-08</v>
+        <v>5.898228634037008e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.50708197945535e-08</v>
+        <v>5.88133963320976e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.812136323861964e-08</v>
+        <v>5.55713832925848e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.311413926608363e-08</v>
+        <v>5.533196416124609e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.248909428211186e-08</v>
+        <v>5.581005916053457e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.506477887878152e-08</v>
+        <v>5.866492422347514e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.296669509436418e-08</v>
+        <v>5.593125001764779e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.237528885568798e-08</v>
+        <v>5.79337353794372e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.29262136106773e-08</v>
+        <v>7.717708440390711e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.187106324458659e-08</v>
+        <v>5.527577056137691e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.450139266756978e-08</v>
+        <v>5.866774334333303e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.294176648040501e-08</v>
+        <v>6.474666014176053e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.404829849606759e-08</v>
+        <v>5.836248224180539e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.366428347780759e-08</v>
+        <v>8.589164985682754e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.494267940478735e-08</v>
+        <v>6.066389732990576e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.353994069338581e-08</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>6.339296170136257e-08</v>
+        <v>5.609141147062633e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.547376459816027e-08</v>
+        <v>5.780024269790824e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.261752490285662e-08</v>
+        <v>5.697008335566605e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.129461281748708e-08</v>
+        <v>5.514688483058347e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.366221281992902e-08</v>
+        <v>5.699886565887073e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.266447475075983e-08</v>
+        <v>5.662304920524731e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.488168967444314e-08</v>
+        <v>5.811182412445115e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.21824100952512e-08</v>
+        <v>5.544670741750683e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.738701597648697e-08</v>
+        <v>6.18140632449874e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.78831168201788e-08</v>
+        <v>7.164784670906071e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.652565595616495e-08</v>
+        <v>6.138503806828636e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.342663222591722e-08</v>
+        <v>5.823264507356994e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.375794142096322e-08</v>
+        <v>5.806375506529747e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.496667594726762e-08</v>
+        <v>6.21681318413522e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.250679125699525e-08</v>
+        <v>6.404557654748635e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.444493581499107e-08</v>
+        <v>7.616737886274856e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.702062041166072e-08</v>
+        <v>7.902224392568913e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.823300878692886e-08</v>
+        <v>7.008863904188694e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.372513894770631e-08</v>
+        <v>6.84613012821876e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.174871143367153e-07</v>
+        <v>9.994880266985191e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.382690477746585e-08</v>
+        <v>7.563309026359085e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.645723420044899e-08</v>
+        <v>7.902506304554704e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.489760801328419e-08</v>
+        <v>8.510397984397449e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.600414002894683e-08</v>
+        <v>7.871980194401937e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.562012501068676e-08</v>
+        <v>1.062489695590415e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>8.689852093766497e-08</v>
+        <v>8.102121703211796e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.57572085549322e-08</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>7.828774568976444e-08</v>
+        <v>6.99045442560276e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.971253636720459e-08</v>
+        <v>7.100537587842259e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.954122340761468e-08</v>
+        <v>6.339544149935316e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.32504543503663e-08</v>
+        <v>7.550420453279746e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.561805435280824e-08</v>
+        <v>7.73561853610847e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.462031628363906e-08</v>
+        <v>7.698036890746133e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.070810681812763e-08</v>
+        <v>7.278872018082622e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.069987318148843e-08</v>
+        <v>7.26161020635787e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.934532653525259e-08</v>
+        <v>8.217367126839948e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.595825660959331e-08</v>
+        <v>7.91403737642988e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.009655487815296e-07</v>
+        <v>9.331086276113864e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.258591652074719e-08</v>
+        <v>6.672996961815638e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.571378295384245e-08</v>
+        <v>7.84210747675115e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.000458194735827e-07</v>
+        <v>9.468827746600352e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.991727981536349e-08</v>
+        <v>7.057470139315795e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.680980428995028e-08</v>
+        <v>7.792641402626056e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.938548888661989e-08</v>
+        <v>8.078127908920119e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.555238974393201e-08</v>
+        <v>7.646120967646022e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.936593423442079e-08</v>
+        <v>6.42045125345748e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.172469353308266e-07</v>
+        <v>9.92934492877743e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.619177325242505e-08</v>
+        <v>7.739212542710296e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.88221026754082e-08</v>
+        <v>8.078409820905906e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.726247648824346e-08</v>
+        <v>8.686301500748656e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.836900850390602e-08</v>
+        <v>8.047883710753138e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.798499348564604e-08</v>
+        <v>1.080080047225536e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>8.926338941262579e-08</v>
+        <v>8.278025219563178e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.78606507012242e-08</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.020627150173488e-08</v>
+        <v>8.048694774807505e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.282889300579778e-08</v>
+        <v>8.269118557976767e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.693824662300601e-08</v>
+        <v>7.908644823953324e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.561532282532551e-08</v>
+        <v>7.726323969630943e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.798292282776746e-08</v>
+        <v>7.911522052459672e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.698518475859826e-08</v>
+        <v>7.873940407097327e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.920913382833486e-08</v>
+        <v>8.023590202565352e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.51782491431801e-08</v>
+        <v>8.549508202229717e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.170772598432538e-08</v>
+        <v>8.393041811071341e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.220382682801722e-08</v>
+        <v>9.376420157478672e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.084636596400337e-08</v>
+        <v>8.350139293401241e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.321492098943263e-08</v>
+        <v>7.620482371012731e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.807865142880161e-08</v>
+        <v>8.018010993102347e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.928738595510604e-08</v>
+        <v>8.42844867070782e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.697083615828395e-08</v>
+        <v>1.592077278221432e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.623461188983171e-08</v>
+        <v>1.510640466867518e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.695772599313293e-08</v>
+        <v>1.602554462340782e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.692028086586413e-08</v>
+        <v>1.593906745109854e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.696207589275671e-08</v>
+        <v>1.61718921456688e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.923058742271615e-08</v>
+        <v>1.758413597089218e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.689753906497043e-08</v>
+        <v>1.593762540154885e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.703512642269413e-08</v>
+        <v>1.614097097350832e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.76563875487045e-08</v>
+        <v>1.660513122223515e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.709164035971103e-08</v>
+        <v>1.622796928381159e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.703168821790585e-08</v>
+        <v>1.804761886312324e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.706182173986766e-08</v>
+        <v>1.62691190963933e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.684901035703327e-08</v>
+        <v>1.591153936657832e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.76230696360946e-08</v>
+        <v>2.579285057932273e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.710547033538029e-08</v>
+        <v>1.605761581965109e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.690511854340957e-08</v>
+        <v>1.605801914537146e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.69176339702785e-08</v>
+        <v>1.599950620596176e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.705963412263541e-08</v>
+        <v>1.609181493031778e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.70002191436854e-08</v>
+        <v>1.609017033146748e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.531075568753639e-08</v>
+        <v>2.256578047649931e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.699616923308413e-08</v>
+        <v>1.600880888006341e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.615723236360703e-08</v>
+        <v>2.336543448705333e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.756916772683359e-08</v>
+        <v>1.751733487485596e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.748142047581211e-08</v>
+        <v>1.675182841151897e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.801712500647837e-08</v>
+        <v>2.678975445861005e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.706522293529122e-08</v>
+        <v>1.618690366005232e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.712935411328723e-08</v>
+        <v>1.644145488793933e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.43499705974857e-08</v>
+        <v>1.288894445125767e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.273384745329342e-08</v>
+        <v>1.165577465843937e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.42659778722848e-08</v>
+        <v>1.36425394937553e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.398694816143711e-08</v>
+        <v>1.301446027472439e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.42990599877221e-08</v>
+        <v>1.469099093639961e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.038801448940868e-08</v>
+        <v>2.469472941647969e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.38409234033411e-08</v>
+        <v>1.301906308377904e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.482208880587705e-08</v>
+        <v>1.447096414531686e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.922067214663788e-08</v>
+        <v>1.775451876845456e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.521484980693283e-08</v>
+        <v>1.50780712038013e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.478754628081224e-08</v>
+        <v>2.803123156832046e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.527506735629499e-08</v>
+        <v>1.562548058598478e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.348863762468501e-08</v>
+        <v>1.282758782721868e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.210518429832203e-08</v>
+        <v>2.969532070444958e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.530468542353386e-08</v>
+        <v>1.385973897737474e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.388819926745019e-08</v>
+        <v>1.38711674747415e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.398325253398526e-08</v>
+        <v>1.346108461742205e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.498277333906363e-08</v>
+        <v>1.410557704990405e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.457273978133165e-08</v>
+        <v>1.410812875519906e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.937835560225949e-08</v>
+        <v>2.556674497478911e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.452440886745516e-08</v>
+        <v>1.350898784617938e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.025762608962872e-08</v>
+        <v>2.704923004738949e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.862844063328785e-08</v>
+        <v>2.428754833647599e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.800574470635067e-08</v>
+        <v>1.882965855096902e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.266884738348533e-08</v>
+        <v>3.204334204628857e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.503192824401007e-08</v>
+        <v>1.479325783652315e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.559655138224312e-08</v>
+        <v>1.669084099516258e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.707337854720505e-08</v>
+        <v>4.976823410824618e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.622581925817075e-08</v>
+        <v>4.998338217767077e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.692529320085051e-08</v>
+        <v>5.09516802519548e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.650233326273964e-08</v>
+        <v>4.99748808092567e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.697442731815357e-08</v>
+        <v>5.260474283907911e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.25983086159072e-08</v>
+        <v>6.855668650923358e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.624545415990012e-08</v>
+        <v>4.99585921962176e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.779956665870121e-08</v>
+        <v>5.225547397508443e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.476412155710945e-08</v>
+        <v>5.744729743753872e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.843791757500228e-08</v>
+        <v>5.323815991115988e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.776073055396496e-08</v>
+        <v>7.379193898964766e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.858525964033816e-08</v>
+        <v>5.414530141628376e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.569730007944132e-08</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.743118095092375e-08</v>
+        <v>5.082803761974378e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.859413351228982e-08</v>
+        <v>5.131393916700177e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.633106785560247e-08</v>
+        <v>5.131849491655242e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.647243535946778e-08</v>
+        <v>5.065756434863787e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.807639240363682e-08</v>
+        <v>5.170023385435018e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.740527288415559e-08</v>
+        <v>5.168165735378298e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.939026127846053e-08</v>
+        <v>5.324340163517266e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.69998557562941e-08</v>
+        <v>5.041518192742679e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.858881543421651e-08</v>
+        <v>5.36124316232587e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.38318088600936e-08</v>
+        <v>6.7802137399482e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.257623608576406e-08</v>
+        <v>5.912207310623651e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.725800138774509e-08</v>
+        <v>5.229682328344876e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.813952061356472e-08</v>
+        <v>5.277430479967867e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.903407982793146e-08</v>
+        <v>5.575578866178805e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.778814605136841e-08</v>
+        <v>7.384149031724511e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.729871313619506e-08</v>
+        <v>8.024800911702435e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.001311053831698e-07</v>
+        <v>9.779559060603338e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.654465290661493e-08</v>
+        <v>7.487719794561252e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.020555733742636e-07</v>
+        <v>1.290858745041788e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>5.026432408871875e-07</v>
+        <v>3.720880126066357e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.044040813830869e-08</v>
+        <v>8.230795395989735e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1751161389793e-07</v>
+        <v>1.232500692667601e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.232344881136629e-07</v>
+        <v>2.008064840496965e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.233181612140707e-07</v>
+        <v>1.334768045649195e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.116404726544712e-07</v>
+        <v>4.795041695603107e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.310972082491887e-07</v>
+        <v>1.564608559871409e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.37712545258397e-07</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.030605824204888e-07</v>
+        <v>9.048333166577878e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.214846474698538e-07</v>
+        <v>9.814249209474334e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.842072327951534e-08</v>
+        <v>1.026538587717459e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>9.389048953932074e-08</v>
+        <v>9.486484065066286e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.150343591458555e-07</v>
+        <v>1.058854349778471e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.104269601251166e-07</v>
+        <v>1.129619412443565e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.416699336657277e-07</v>
+        <v>1.324756305963984e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.919091063532758e-08</v>
+        <v>8.679366601014924e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.286112197315406e-07</v>
+        <v>1.440746916593132e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.215445310459016e-07</v>
+        <v>3.948015063532184e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.058596655656821e-07</v>
+        <v>2.447549835992463e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.86079198504484e-08</v>
+        <v>1.107808360772442e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.209534139309753e-07</v>
+        <v>1.295605714973449e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.442687024055194e-07</v>
+        <v>1.94280598155323e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.30072413598795e-08</v>
+        <v>4.833839617379957e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.420259816905697e-08</v>
+        <v>4.855354424322413e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.490207211173672e-08</v>
+        <v>5.671130879018621e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.24361960754141e-08</v>
+        <v>5.573450934748823e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.495120622903978e-08</v>
+        <v>5.117490490463247e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.853217142858166e-08</v>
+        <v>6.712684857478697e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.422223307078634e-08</v>
+        <v>5.571822073444891e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.577634556958741e-08</v>
+        <v>5.082563604063775e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.06979843697839e-08</v>
+        <v>6.320692597577017e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.437178038767666e-08</v>
+        <v>5.899778844939141e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.369459336663942e-08</v>
+        <v>7.236210105520114e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.656203855122436e-08</v>
+        <v>5.271546348183711e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.368259040370503e-08</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.354512198925444e-08</v>
+        <v>4.943390451780937e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.640204418409174e-08</v>
+        <v>5.720883941197237e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.226493066827691e-08</v>
+        <v>5.707812345478384e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.240629817214223e-08</v>
+        <v>5.641719288686934e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.401025521631132e-08</v>
+        <v>5.027039591990352e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.333913569683007e-08</v>
+        <v>5.744128589201457e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.763146739765886e-08</v>
+        <v>5.903634681288702e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.49766346671803e-08</v>
+        <v>4.898534399298018e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.470271545822225e-08</v>
+        <v>5.234734662670741e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.180858777097977e-08</v>
+        <v>6.637229946503532e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.092030415825691e-08</v>
+        <v>5.783222779210334e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.319186420041953e-08</v>
+        <v>5.086698534900209e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.407338342623915e-08</v>
+        <v>5.853393333791001e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.702505440973557e-08</v>
+        <v>5.43574879315437e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.208871989809552e-08</v>
+        <v>5.488929382199109e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.124116060906125e-08</v>
+        <v>5.510444189141567e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.1940634551741e-08</v>
+        <v>5.60727399656997e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.151767461363014e-08</v>
+        <v>5.50959405230016e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.198976866904405e-08</v>
+        <v>5.772580255282403e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.761364996679763e-08</v>
+        <v>7.367774622297846e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.12607955107906e-08</v>
+        <v>5.50796519099625e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.28149080095917e-08</v>
+        <v>5.737653368882931e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.977946290799994e-08</v>
+        <v>6.256835715128364e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.345325892589272e-08</v>
+        <v>5.835921962490481e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.27760719048555e-08</v>
+        <v>7.891299870339267e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.360060099122863e-08</v>
+        <v>5.926636113002867e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.071264143033184e-08</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.244525001634436e-08</v>
+        <v>5.594783545415697e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.360820257771047e-08</v>
+        <v>5.643373700141496e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.134640920649292e-08</v>
+        <v>5.643955463029734e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.148777671035827e-08</v>
+        <v>5.577862406238277e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.309173375452736e-08</v>
+        <v>5.682129356809507e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.242061423504609e-08</v>
+        <v>5.680271706752791e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.466493936614298e-08</v>
+        <v>5.839086985108967e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.201519710718457e-08</v>
+        <v>5.553624164117171e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.360415678510699e-08</v>
+        <v>5.873349133700361e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.884715021098406e-08</v>
+        <v>7.292319711322686e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.785600464496662e-08</v>
+        <v>6.427644945946425e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.227334273863559e-08</v>
+        <v>5.741788299719365e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.315486196445519e-08</v>
+        <v>5.789536451342357e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.404942117882194e-08</v>
+        <v>6.087684837553298e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.143425791060033e-08</v>
+        <v>6.346377400328285e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.300042324399498e-08</v>
+        <v>7.512722853516421e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.369989718667474e-08</v>
+        <v>7.609552660944825e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.66669950689411e-08</v>
+        <v>6.902284167929879e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.326921989503178e-08</v>
+        <v>6.808379508134799e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.119469792701595e-07</v>
+        <v>9.607441379056549e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.302005814572435e-08</v>
+        <v>7.51024385537111e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.457417064452546e-08</v>
+        <v>7.739932033257786e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.153872554293367e-08</v>
+        <v>8.259114379503225e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.52125215608265e-08</v>
+        <v>7.838200626865335e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.453533453978921e-08</v>
+        <v>9.893578534714117e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.535986362616148e-08</v>
+        <v>7.928914777377641e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.284919071153194e-08</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.722747676501931e-08</v>
+        <v>6.953628040368335e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.774222171851183e-08</v>
+        <v>6.942438559476554e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.825236700086963e-08</v>
+        <v>6.276418129654461e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.324703934529205e-08</v>
+        <v>7.580141070613134e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.485099638946111e-08</v>
+        <v>7.684408021184362e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.417987686997983e-08</v>
+        <v>7.68255037112765e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.03673601675684e-08</v>
+        <v>7.282842333475815e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.037833793520279e-08</v>
+        <v>7.242520722715531e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.536585907188581e-08</v>
+        <v>7.875852790012065e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.689085053321228e-08</v>
+        <v>8.029708381455676e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.019528891288593e-07</v>
+        <v>9.56745410698847e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.138828944265991e-08</v>
+        <v>6.577970500799817e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.491412459938893e-08</v>
+        <v>7.791815115717214e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.877585720078215e-08</v>
+        <v>9.285834841110718e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.668403015420905e-08</v>
+        <v>6.825033416826035e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.269142879384563e-08</v>
+        <v>7.477213632991911e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.33909027365254e-08</v>
+        <v>7.57404344042031e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.138585495988852e-08</v>
+        <v>7.330809225511981e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.763747352499488e-08</v>
+        <v>6.285492561481611e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.090639291896763e-07</v>
+        <v>9.33454501956601e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.271106369557501e-08</v>
+        <v>7.474734634846589e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.426517619437606e-08</v>
+        <v>7.704422812733272e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.122973109278431e-08</v>
+        <v>8.223605158978703e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.490352711067713e-08</v>
+        <v>7.802691406340818e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.422634008963986e-08</v>
+        <v>9.858069314189603e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.505086917601306e-08</v>
+        <v>7.893405556853209e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.216290961511622e-08</v>
+        <v>7.435100066972498e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.616852926446369e-08</v>
+        <v>7.770682137409294e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.78255436329454e-08</v>
+        <v>7.864726642741816e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.279668842937157e-08</v>
+        <v>7.610725860297908e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.293804489514264e-08</v>
+        <v>7.544631850088609e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.454200193931179e-08</v>
+        <v>7.648898800659843e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.387088241983047e-08</v>
+        <v>7.64704115060313e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.612029802244751e-08</v>
+        <v>7.806547242690381e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.137595415470342e-08</v>
+        <v>8.248169173333167e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.505442496989135e-08</v>
+        <v>7.840118577550698e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.029741839576845e-08</v>
+        <v>9.259089155173036e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.930627282975099e-08</v>
+        <v>8.39441438979676e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.959068524217913e-08</v>
+        <v>7.328322961355969e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.460513014923957e-08</v>
+        <v>7.756305895192692e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.549968936360631e-08</v>
+        <v>8.054454281403637e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.56185639044199e-08</v>
+        <v>1.519176616295638e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.484211719824066e-08</v>
+        <v>1.435028348059922e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.599679740768793e-08</v>
+        <v>1.558129382866534e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.569736051414052e-08</v>
+        <v>1.527983754440153e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.565506702039164e-08</v>
+        <v>1.524751170465991e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.635617942584401e-08</v>
+        <v>1.571956462567255e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.573400284857644e-08</v>
+        <v>1.531767713270124e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.580690265678224e-08</v>
+        <v>1.540619459063394e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.594925496754746e-08</v>
+        <v>1.548480839850694e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.628935419972188e-08</v>
+        <v>1.587405417308495e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.585611575672558e-08</v>
+        <v>1.609490152296642e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.567406326380569e-08</v>
+        <v>1.533432109273869e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.605388807780244e-08</v>
+        <v>1.563704796558764e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.568577565954864e-08</v>
+        <v>2.485523821949045e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.587205967914801e-08</v>
+        <v>1.544464042313725e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.578877432188919e-08</v>
+        <v>1.53811981990919e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.576290694519248e-08</v>
+        <v>1.536045630281883e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.575235120974726e-08</v>
+        <v>1.533329925963324e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.568582606975059e-08</v>
+        <v>1.527927672998903e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.282118551732556e-08</v>
+        <v>2.17828474540964e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.560669523291589e-08</v>
+        <v>1.518834890518762e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.366611888505191e-08</v>
+        <v>2.258805882483522e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.576589989751811e-08</v>
+        <v>1.540884255241254e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.561462475715145e-08</v>
+        <v>1.520321919222061e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.656413949006925e-08</v>
+        <v>2.601586090977481e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.57698995226155e-08</v>
+        <v>1.538709203538945e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.801364071438486e-08</v>
+        <v>1.766763595040199e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.293645477424377e-08</v>
+        <v>1.250682227993276e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.123867608880283e-08</v>
+        <v>1.076043923432104e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.564936391227545e-08</v>
+        <v>1.529985543824226e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.349596804677152e-08</v>
+        <v>1.313209958390656e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.320589363323259e-08</v>
+        <v>1.291321466878182e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.815883220114818e-08</v>
+        <v>1.624390685290616e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.377597962277641e-08</v>
+        <v>1.342053771218366e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.429338968120218e-08</v>
+        <v>1.404977911399665e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.52840190560403e-08</v>
+        <v>1.458859389050363e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.771386434718828e-08</v>
+        <v>1.736586504918709e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.462213925477468e-08</v>
+        <v>1.891113538653845e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.358213936639461e-08</v>
+        <v>1.376170315926539e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.604666980984137e-08</v>
+        <v>1.568765780272061e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.966120722927237e-08</v>
+        <v>2.859831848171058e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.473901323816873e-08</v>
+        <v>1.430485835301341e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.415435447308114e-08</v>
+        <v>1.386139054680759e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.398136991892438e-08</v>
+        <v>1.372541086838854e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.387983613430831e-08</v>
+        <v>1.350538296832315e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.342355519412327e-08</v>
+        <v>1.313796808991294e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.524365445886115e-08</v>
+        <v>2.386796429995571e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.284797054663879e-08</v>
+        <v>1.247832715418099e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.699964009396594e-08</v>
+        <v>2.568674536507912e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.399629250629568e-08</v>
+        <v>1.406447814370285e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.291327723869951e-08</v>
+        <v>1.259303372010665e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.168055418235594e-08</v>
+        <v>3.119689821935017e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.402155187688803e-08</v>
+        <v>1.390544486006591e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.996701180915236e-08</v>
+        <v>3.010400447730702e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.463614792974038e-08</v>
+        <v>4.982806973141323e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.376494029930353e-08</v>
+        <v>4.907938095035054e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.890846934516135e-08</v>
+        <v>5.42279639071753e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.552619188476646e-08</v>
+        <v>5.082287649967338e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.504846741690481e-08</v>
+        <v>5.045774126917065e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.296785456413048e-08</v>
+        <v>5.578979616708079e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.594008390852709e-08</v>
+        <v>5.12502920565891e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.676352077778056e-08</v>
+        <v>5.225013746398138e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.831451441534333e-08</v>
+        <v>5.308163555722786e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.221303289395812e-08</v>
+        <v>5.753482667380683e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.731940538078477e-08</v>
+        <v>6.002939908551831e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.571211874417391e-08</v>
+        <v>5.186821142897803e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.955333472711064e-08</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.485919259665075e-08</v>
+        <v>5.011976381650166e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.749949931911284e-08</v>
+        <v>5.268440082806313e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.655875289571709e-08</v>
+        <v>5.196779172260575e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.626656897634665e-08</v>
+        <v>5.17335024624577e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.614733708861481e-08</v>
+        <v>5.142675116681947e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.539590502927593e-08</v>
+        <v>5.081654184289693e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.528086155440005e-08</v>
+        <v>5.0509065030993e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.411589143004341e-08</v>
+        <v>4.940644103919471e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.623025016943004e-08</v>
+        <v>5.181784523737964e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.630037574968976e-08</v>
+        <v>5.228004741039315e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.440195040093695e-08</v>
+        <v>4.967260661163927e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.604153203633649e-08</v>
+        <v>5.153728227180711e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.634555335508427e-08</v>
+        <v>5.203436531488528e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.145395680769285e-08</v>
+        <v>7.753814030928968e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.679285923541901e-08</v>
+        <v>7.991376551787122e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.397995756576427e-08</v>
+        <v>6.916013701693257e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.750469503620588e-07</v>
+        <v>1.703113797451849e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.020299846674031e-07</v>
+        <v>9.689232562269763e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.954666504704174e-08</v>
+        <v>9.656555944211627e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.209577203165921e-07</v>
+        <v>1.760422883885753e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.20140966277996e-07</v>
+        <v>1.15193211513347e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.341089877019754e-07</v>
+        <v>1.327010783539094e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.503583988452416e-07</v>
+        <v>1.370567588356658e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.24464207938779e-07</v>
+        <v>2.198034846565734e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.321135306453164e-07</v>
+        <v>2.497698288427716e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.102453924470402e-07</v>
+        <v>1.20644254907727e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.073180003337824e-07</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>9.025405415013984e-08</v>
+        <v>8.458734400343651e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.372324650958706e-07</v>
+        <v>1.301724637090134e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.248690642395242e-07</v>
+        <v>1.218076218390375e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.258137544114474e-07</v>
+        <v>1.240828242039594e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.089898228947526e-07</v>
+        <v>1.037078686430641e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.050774748155199e-07</v>
+        <v>1.022623663577292e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.032352302093811e-07</v>
+        <v>9.860128903758043e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.177128491416536e-08</v>
+        <v>7.651734716512869e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.196837529606413e-07</v>
+        <v>1.200531362939261e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.228723154215902e-07</v>
+        <v>1.309309927013906e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.869692673179246e-08</v>
+        <v>8.484616272877866e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.099219770948107e-07</v>
+        <v>1.08192043116149e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.218989278142243e-07</v>
+        <v>1.241729705409915e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.299151599992423e-07</v>
+        <v>6.404900007820423e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.291470948479946e-08</v>
+        <v>4.82344752366303e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.960393801969133e-08</v>
+        <v>4.748578645556764e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.718703090022042e-08</v>
+        <v>5.986724581492917e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.380475343982554e-08</v>
+        <v>5.646215840742732e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.088746513729258e-08</v>
+        <v>4.886414677438773e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.880685228451826e-08</v>
+        <v>5.419620167229787e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.421864546358617e-08</v>
+        <v>5.68895739643429e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.504208233283965e-08</v>
+        <v>5.788941937173527e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.659307597040241e-08</v>
+        <v>5.148804106244493e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.049159444901719e-08</v>
+        <v>6.31741085815609e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.559796693584385e-08</v>
+        <v>5.843580459073537e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.155111646456171e-08</v>
+        <v>5.750749333673176e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.782977219760066e-08</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>6.088211878257769e-08</v>
+        <v>5.594802012304349e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.560015923365441e-08</v>
+        <v>5.851367414479699e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.239775061610488e-08</v>
+        <v>5.760707363035948e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.454513053140573e-08</v>
+        <v>5.737278437021163e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.442589864367388e-08</v>
+        <v>4.983315667203654e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>6.123490274966372e-08</v>
+        <v>4.922294734811404e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.374912615776874e-08</v>
+        <v>4.920030089017721e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.995488915043123e-08</v>
+        <v>5.50457229469484e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.466806448312379e-08</v>
+        <v>5.764631521279115e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.457893730474885e-08</v>
+        <v>5.068645291561023e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.298358461355632e-08</v>
+        <v>4.84718868506613e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.188052975672429e-08</v>
+        <v>4.994368777702421e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.218455107547207e-08</v>
+        <v>5.767364722263912e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.988657851058659e-08</v>
+        <v>7.611175755370716e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.002226561620927e-08</v>
+        <v>5.50539719197573e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.915105798577242e-08</v>
+        <v>5.430528313869465e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.429458703163025e-08</v>
+        <v>5.945386609551938e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.091230957123533e-08</v>
+        <v>5.604877868801748e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.043458510337369e-08</v>
+        <v>5.568364345751476e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.835397225059935e-08</v>
+        <v>6.10156983554249e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.132620159499598e-08</v>
+        <v>5.647619424493321e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.214963846424946e-08</v>
+        <v>5.74760396523255e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.370063210181222e-08</v>
+        <v>5.830753774557202e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.759915058042697e-08</v>
+        <v>6.276072886215093e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.270552306725364e-08</v>
+        <v>6.525530127386241e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.109823643064279e-08</v>
+        <v>5.709411361732215e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.493945241357952e-08</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>6.024396294229267e-08</v>
+        <v>5.534432794384258e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.288426966475478e-08</v>
+        <v>5.790896495540403e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.194487058218599e-08</v>
+        <v>5.719369391094982e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.165268666281553e-08</v>
+        <v>5.695940465080181e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.153345477508367e-08</v>
+        <v>5.665265335516358e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.078202271574483e-08</v>
+        <v>5.604244403124105e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.085533873467848e-08</v>
+        <v>5.601637696051045e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.95020091165123e-08</v>
+        <v>5.463234322753912e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.161636785589892e-08</v>
+        <v>5.704374742572374e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.168649343615864e-08</v>
+        <v>5.750594959873725e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.997777113571546e-08</v>
+        <v>5.51833391539505e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.142764972280538e-08</v>
+        <v>5.676318446015124e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.173167104155316e-08</v>
+        <v>5.726026750322938e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.684007449416163e-08</v>
+        <v>8.276404249763379e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.929612316231184e-08</v>
+        <v>6.404813846308976e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.082101523669789e-08</v>
+        <v>7.520154043332856e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.596454428255574e-08</v>
+        <v>8.035012339015329e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.598170939120239e-08</v>
+        <v>7.060752374713318e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.163961010677715e-08</v>
+        <v>6.653201663677959e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.259434152848875e-08</v>
+        <v>8.437993170232986e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.299615884592144e-08</v>
+        <v>7.737245153956706e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.38195957151749e-08</v>
+        <v>7.837229694695939e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.537058935273773e-08</v>
+        <v>7.920379504020588e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.926910783135243e-08</v>
+        <v>8.365698615678489e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.437548031817915e-08</v>
+        <v>8.61515585684963e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.276819368156753e-08</v>
+        <v>7.799037091195467e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.700035857052643e-08</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>7.494686711455684e-08</v>
+        <v>6.955122734182228e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.693988654964645e-08</v>
+        <v>7.14943727375075e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.878261160864866e-08</v>
+        <v>6.384882796926455e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.3322643913741e-08</v>
+        <v>7.78556619454357e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.320341202600916e-08</v>
+        <v>7.754891064979741e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.245197996667028e-08</v>
+        <v>7.693870132587493e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.647627165698456e-08</v>
+        <v>7.110518930064904e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.778392864372085e-08</v>
+        <v>7.227379954394072e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.328876129503382e-08</v>
+        <v>7.794234382149155e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.966036163187135e-08</v>
+        <v>6.525193392400009e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.397289318991089e-08</v>
+        <v>8.791081341523173e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.047124335227133e-08</v>
+        <v>6.553626355680326e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.340162829247861e-08</v>
+        <v>7.815652479786326e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.214587944321187e-07</v>
+        <v>1.160930288188316e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.58213760491929e-08</v>
+        <v>7.032939118995482e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.215019730683463e-08</v>
+        <v>7.649823326487625e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.72937263526925e-08</v>
+        <v>8.1646816221701e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.224971883751944e-08</v>
+        <v>7.664519768738318e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.683568047029832e-08</v>
+        <v>6.192978548457424e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.135312098945825e-08</v>
+        <v>8.32086572941584e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.43253409160582e-08</v>
+        <v>7.86691443711148e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.514877778531166e-08</v>
+        <v>7.966898977850712e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.669977142287439e-08</v>
+        <v>8.050048787175357e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>9.05982899014892e-08</v>
+        <v>8.495367898833254e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.570466238831592e-08</v>
+        <v>8.744825140004397e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.409737575170499e-08</v>
+        <v>7.928706374350374e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.793859173464175e-08</v>
+        <v>1.765920085809779e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.563054228890043e-08</v>
+        <v>7.983108853198728e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.878978118362319e-08</v>
+        <v>8.28942970419759e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.494401932104481e-08</v>
+        <v>7.938665284968332e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.465182598387777e-08</v>
+        <v>7.915235477698345e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.453259409614591e-08</v>
+        <v>7.884560348134518e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.378116203680704e-08</v>
+        <v>7.823539415742267e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.385582161024078e-08</v>
+        <v>7.821274769948588e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.080983978217734e-08</v>
+        <v>8.480798714247632e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.461550717696114e-08</v>
+        <v>7.923669755190537e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>8.468563275722088e-08</v>
+        <v>7.969889972491886e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.297691045677769e-08</v>
+        <v>7.737628928013216e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.008581561560851e-08</v>
+        <v>7.478548211038559e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.473081036261542e-08</v>
+        <v>7.9453217629411e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.098392138152239e-07</v>
+        <v>1.049569926238154e-07</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.533959664825775e-08</v>
+        <v>1.488037189537777e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.470506660055386e-08</v>
+        <v>1.41140079955278e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.538231710238076e-08</v>
+        <v>1.490860283853526e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.537737225725153e-08</v>
+        <v>1.491856187429225e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.54839381381624e-08</v>
+        <v>1.502414861883302e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.544425289595087e-08</v>
+        <v>1.498401637302283e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.536397798134726e-08</v>
+        <v>1.490366163065193e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.540413500123142e-08</v>
+        <v>1.495354846066019e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.542853998454659e-08</v>
+        <v>1.496878950277157e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.534166092576885e-08</v>
+        <v>1.488549072558387e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.54240631924476e-08</v>
+        <v>1.496461271239283e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.524466004628386e-08</v>
+        <v>1.478714886926006e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.550605236334681e-08</v>
+        <v>1.50464858235156e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.574064820723677e-08</v>
+        <v>2.473921011610182e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.535912138985207e-08</v>
+        <v>1.490131301524221e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.529804844932538e-08</v>
+        <v>1.483803316712251e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.562283647651841e-08</v>
+        <v>1.516198376996751e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.539884088723242e-08</v>
+        <v>1.493721326513438e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.528543317608936e-08</v>
+        <v>1.483137821737164e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.27063880957054e-08</v>
+        <v>2.121401819912116e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.537218800119553e-08</v>
+        <v>1.49115780010033e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.391488315478313e-08</v>
+        <v>2.23063082751999e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.55887252958986e-08</v>
+        <v>1.512833053681967e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.53419197409643e-08</v>
+        <v>1.488179751547654e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.64742725296959e-08</v>
+        <v>2.577143275054289e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.539583141706123e-08</v>
+        <v>1.49342024915438e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.521395730439967e-08</v>
+        <v>1.475573124112456e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.291115494218169e-08</v>
+        <v>1.2485077755481e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.186359250151749e-08</v>
+        <v>1.122592578822982e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.322179225625879e-08</v>
+        <v>1.269233792079663e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.317815756564433e-08</v>
+        <v>1.275494034362144e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.394938942757825e-08</v>
+        <v>1.351910738767522e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.364821528105686e-08</v>
+        <v>1.321510625406312e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.309834650908404e-08</v>
+        <v>1.266415170099087e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.338099864513073e-08</v>
+        <v>1.301644844033443e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.354229710295137e-08</v>
+        <v>1.311251105744067e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.292950562066947e-08</v>
+        <v>1.252508652066982e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.350402162624351e-08</v>
+        <v>1.307650651203179e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.248859154913912e-08</v>
+        <v>1.206941446859378e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.410131149123319e-08</v>
+        <v>1.367270564245505e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.144696789855551e-08</v>
+        <v>3.013090275711584e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.304910255448284e-08</v>
+        <v>1.263310699560948e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.261671258655159e-08</v>
+        <v>1.218504801491935e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.494812290971218e-08</v>
+        <v>1.451015565024693e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.332631509556731e-08</v>
+        <v>1.288337150412782e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.253152972025433e-08</v>
+        <v>1.214216597639991e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.454643413419498e-08</v>
+        <v>2.242340008982085e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.313594993446153e-08</v>
+        <v>1.270007836749703e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.868525116260796e-08</v>
+        <v>2.630636411117507e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.469048202076729e-08</v>
+        <v>1.425597286237508e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.293347186918573e-08</v>
+        <v>1.250084522970099e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.233456217007881e-08</v>
+        <v>3.151091991603284e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.33179654717279e-08</v>
+        <v>1.287459141727915e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21057938913302e-08</v>
+        <v>1.16834035050699e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.418270463450718e-08</v>
+        <v>4.972107135743719e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.417109488116184e-08</v>
+        <v>4.972262634314278e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.466525181620677e-08</v>
+        <v>5.003995284727661e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.460939751573105e-08</v>
+        <v>5.015244473753456e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.581310816334661e-08</v>
+        <v>5.134509558942473e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.536484509645388e-08</v>
+        <v>5.089178341125336e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.445810300772097e-08</v>
+        <v>4.998413963116639e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49116950204536e-08</v>
+        <v>5.054763432518529e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.513945865069129e-08</v>
+        <v>5.067159508803092e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.420602159861009e-08</v>
+        <v>4.977889089939314e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.513679310766211e-08</v>
+        <v>5.06726101383126e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.356787804703438e-08</v>
+        <v>4.911590607530825e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.606289850985051e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.702585855861056e-08</v>
+        <v>5.257456072119152e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.440324557264037e-08</v>
+        <v>4.995761093969715e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.371339861445072e-08</v>
+        <v>4.924283594501676e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.738202879147005e-08</v>
+        <v>5.290200702879089e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.485189556742273e-08</v>
+        <v>5.036312077716012e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.357090329993759e-08</v>
+        <v>4.916766522615252e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.295976970251176e-08</v>
+        <v>4.86053040959174e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.422520475521944e-08</v>
+        <v>4.974596762084284e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.75232314609169e-08</v>
+        <v>5.294678427060507e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.699672731445097e-08</v>
+        <v>5.252187827913391e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.410012867300104e-08</v>
+        <v>4.971815638252291e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.635534913103778e-08</v>
+        <v>5.190304681409601e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.481790221741465e-08</v>
+        <v>5.032911270443002e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.291600443764369e-08</v>
+        <v>4.84596768364995e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.929133281539291e-08</v>
+        <v>8.4410884340202e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.213003536149585e-08</v>
+        <v>8.741446772320375e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.008002245950788e-07</v>
+        <v>9.304332670625223e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.54887568895111e-08</v>
+        <v>9.064060836812919e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.223056764649501e-07</v>
+        <v>1.172221834716745e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.050811820926391e-07</v>
+        <v>1.000966581964275e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.009928115002575e-07</v>
+        <v>9.572491175375213e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.069680794497644e-07</v>
+        <v>1.037489115009085e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.05120460337632e-07</v>
+        <v>1.001571267027229e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>9.157857902429495e-08</v>
+        <v>8.723456615032893e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.009965397452705e-07</v>
+        <v>9.616069971518403e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.174453658175698e-08</v>
+        <v>7.700249716848819e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.502027108246494e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.323286054393161e-07</v>
+        <v>1.276383937882209e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>9.246570149992956e-08</v>
+        <v>8.785415368081557e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.207356234392534e-08</v>
+        <v>7.70635101599833e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.538942139335765e-07</v>
+        <v>1.485479475132211e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.715284806232565e-08</v>
+        <v>9.193901091853711e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.206822518592715e-08</v>
+        <v>7.812542763015468e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.20259586374284e-08</v>
+        <v>6.744997487946989e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>9.142884749546973e-08</v>
+        <v>8.631747877560794e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46546915188445e-07</v>
+        <v>1.397237326736819e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.397271092152229e-07</v>
+        <v>1.345706419334148e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.272844000504103e-08</v>
+        <v>8.759399544897568e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.216557867373133e-07</v>
+        <v>1.169579659814157e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.033554508625547e-07</v>
+        <v>9.79230975898434e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.129354474283644e-08</v>
+        <v>6.640610531499987e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.265821709142201e-08</v>
+        <v>5.46696816676107e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.264660733807666e-08</v>
+        <v>4.832151026047132e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.314076427312158e-08</v>
+        <v>4.863883676460514e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.96939714306818e-08</v>
+        <v>4.875132865486308e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.089768207829732e-08</v>
+        <v>5.629370589959825e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.384035755336872e-08</v>
+        <v>5.584039372142687e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.29336154646358e-08</v>
+        <v>5.493274994133989e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.338720747736843e-08</v>
+        <v>5.549624463535879e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.361497110760613e-08</v>
+        <v>5.562020539820442e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.268153405552493e-08</v>
+        <v>5.472750120956662e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.022136702261282e-08</v>
+        <v>4.927149405564112e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.865245196198511e-08</v>
+        <v>5.406451638548176e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.453686001095111e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>5.549982005971113e-08</v>
+        <v>5.766075537893885e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.270416379597965e-08</v>
+        <v>4.840780815904826e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.218891107136556e-08</v>
+        <v>5.419144625519028e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.246660270642079e-08</v>
+        <v>5.150089094611941e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.332740802433758e-08</v>
+        <v>5.531173108733365e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.865547721488832e-08</v>
+        <v>4.776654914348104e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.154409852172875e-08</v>
+        <v>4.722320602299333e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.930977867017017e-08</v>
+        <v>4.834485153817139e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.616733578429055e-08</v>
+        <v>5.169588815469589e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.547223977136579e-08</v>
+        <v>5.747048858930742e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.28095639261869e-08</v>
+        <v>4.84453810609761e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.14399230459885e-08</v>
+        <v>5.050193073142455e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.990247613236536e-08</v>
+        <v>5.527772301460354e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.138237313576781e-08</v>
+        <v>4.707870974046292e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.882751817494558e-08</v>
+        <v>5.438112971686775e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.881590842160024e-08</v>
+        <v>5.438268470257332e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.931006535664515e-08</v>
+        <v>5.470001120670715e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.925421105616947e-08</v>
+        <v>5.481250309696513e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0457921703785e-08</v>
+        <v>5.600515394885528e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>6.000965863689226e-08</v>
+        <v>5.555184177068389e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.910291654815936e-08</v>
+        <v>5.464419799059692e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.955650856089198e-08</v>
+        <v>5.520769268461583e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.978427219112971e-08</v>
+        <v>5.533165344746146e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.885083513904848e-08</v>
+        <v>5.443894925882369e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.978160664810048e-08</v>
+        <v>5.533266849774313e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.821269158747277e-08</v>
+        <v>5.377596443473881e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.070771205028887e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>6.166941188992834e-08</v>
+        <v>5.723336378063752e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.904679890395812e-08</v>
+        <v>5.461641399914316e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.835821215488912e-08</v>
+        <v>5.390289430444728e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.202684233190847e-08</v>
+        <v>5.756206538822143e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.949670910786113e-08</v>
+        <v>5.502317913659067e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8215716840376e-08</v>
+        <v>5.382772358558304e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.77143396284105e-08</v>
+        <v>5.32827029624893e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.887001829565783e-08</v>
+        <v>5.44060259802734e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.216804500135531e-08</v>
+        <v>5.760684263003561e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.164154085488937e-08</v>
+        <v>5.718193663856446e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.88537585757416e-08</v>
+        <v>5.439723275170086e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.100016267147618e-08</v>
+        <v>5.656310517352658e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.946271575785305e-08</v>
+        <v>5.498917106386058e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.756081797808208e-08</v>
+        <v>5.311973519593004e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.739581185205979e-08</v>
+        <v>6.251367463651922e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.870222051671507e-08</v>
+        <v>7.325507813783319e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.919637745176001e-08</v>
+        <v>7.357240464196701e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.311401220415056e-08</v>
+        <v>6.796624400322154e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.078943037355622e-08</v>
+        <v>6.581084174756842e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.224283558110488e-08</v>
+        <v>7.665121275933648e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.898922864327427e-08</v>
+        <v>7.351659142585681e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.944282065600685e-08</v>
+        <v>7.40800861198757e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.967058428624459e-08</v>
+        <v>7.420404688272129e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.873714723416336e-08</v>
+        <v>7.331134269408353e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.966791874321539e-08</v>
+        <v>7.420506193300301e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.809900368258657e-08</v>
+        <v>7.26483578699972e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.182066640783282e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>7.519462134059291e-08</v>
+        <v>7.006966474643224e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.198101525075806e-08</v>
+        <v>6.68919121658556e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.470225689124278e-08</v>
+        <v>5.992481386530821e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.191315442702334e-08</v>
+        <v>7.643445882348128e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.938302120297603e-08</v>
+        <v>7.38955725718505e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.810202893549086e-08</v>
+        <v>7.270011702084292e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.207724309612867e-08</v>
+        <v>6.691446998593511e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.566482600593438e-08</v>
+        <v>7.034269599021648e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.205658141093885e-08</v>
+        <v>7.648134675260765e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.902290446843465e-08</v>
+        <v>6.418818465609318e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.999623574408495e-08</v>
+        <v>8.394745337337385e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.935821834537039e-08</v>
+        <v>6.449615189275452e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.934902785296792e-08</v>
+        <v>7.386156449912041e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.926974670850171e-08</v>
+        <v>8.321079845745764e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.0937779207591e-08</v>
+        <v>6.635225979470723e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.683191725073398e-08</v>
+        <v>7.208994356794589e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.732607418577892e-08</v>
+        <v>7.240727007207969e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.590720433293201e-08</v>
+        <v>7.119589352489763e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.48595582370472e-08</v>
+        <v>6.048905906941691e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.802567650127692e-08</v>
+        <v>7.325910933268159e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.71189253772931e-08</v>
+        <v>7.235145685596943e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.757251739002577e-08</v>
+        <v>7.291495154998834e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.780028102026342e-08</v>
+        <v>7.303891231283401e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.686684396818223e-08</v>
+        <v>7.214620812419621e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.779761547723427e-08</v>
+        <v>7.303992736311562e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.62287004166065e-08</v>
+        <v>7.148322330011135e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.872372087942256e-08</v>
+        <v>1.186668090234259e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>8.164385004454397e-08</v>
+        <v>7.684283509403926e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.944688579700291e-08</v>
+        <v>7.463930898594543e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.637423001927376e-08</v>
+        <v>7.161016186644495e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.004285116104219e-08</v>
+        <v>7.526932425359397e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.751271793699485e-08</v>
+        <v>7.27304380019632e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.62317256695097e-08</v>
+        <v>7.153498245095562e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.572940843438605e-08</v>
+        <v>7.099163933046787e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.370114611348556e-08</v>
+        <v>7.873266679216586e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.018405383048904e-08</v>
+        <v>7.531410149540816e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.965754968402306e-08</v>
+        <v>7.488919550393698e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.686976740487532e-08</v>
+        <v>7.21044916170734e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.545553432670989e-08</v>
+        <v>7.081199190982373e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.747872458698678e-08</v>
+        <v>7.269642992923306e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.557682680721577e-08</v>
+        <v>7.082699406130257e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.558700804967521e-08</v>
+        <v>1.5005974058132e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.480581964516212e-08</v>
+        <v>1.407738118581796e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.552704834105677e-08</v>
+        <v>1.49473360468672e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.564878379191172e-08</v>
+        <v>1.506884454911491e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.556907200372285e-08</v>
+        <v>1.498838128586335e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.549440891144527e-08</v>
+        <v>1.491468873465065e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.545233237718722e-08</v>
+        <v>1.487188728391711e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.546473815058549e-08</v>
+        <v>1.488794367967563e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.554601814379325e-08</v>
+        <v>1.496602179487705e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.543639701422438e-08</v>
+        <v>1.48595217885042e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.557539454858039e-08</v>
+        <v>1.499492372140163e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.537676762808978e-08</v>
+        <v>1.480026701330397e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.548878413501647e-08</v>
+        <v>1.491129134376721e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.607112678083021e-08</v>
+        <v>2.478331101676366e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.556132453804327e-08</v>
+        <v>1.498600481118118e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.541963760227615e-08</v>
+        <v>1.484201415566625e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.583121815337238e-08</v>
+        <v>1.524798901978136e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.55309546521099e-08</v>
+        <v>1.495020287668684e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.541364088304283e-08</v>
+        <v>1.483655662619996e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.336280330205201e-08</v>
+        <v>2.111046562147364e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.575201486098141e-08</v>
+        <v>1.517118933034813e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.474561615843916e-08</v>
+        <v>2.230306558797887e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.580620418398106e-08</v>
+        <v>1.52241441494543e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.550091881941878e-08</v>
+        <v>1.491944758709745e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.671093233756936e-08</v>
+        <v>2.568228761336063e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.554445453001551e-08</v>
+        <v>1.495989093722141e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.540230081696343e-08</v>
+        <v>1.482525661380449e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377710279918533e-08</v>
+        <v>1.325033830798911e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.203462926091042e-08</v>
+        <v>1.127512379654335e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.335996970880922e-08</v>
+        <v>1.284232474068837e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.421216465910873e-08</v>
+        <v>1.369315439595143e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.366324382287751e-08</v>
+        <v>1.31385202563192e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.311817770482905e-08</v>
+        <v>1.260078968048455e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.283103991837468e-08</v>
+        <v>1.230795956672465e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2917247858646e-08</v>
+        <v>1.24203830176148e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.348795194244843e-08</v>
+        <v>1.2968461396595e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.271202539269068e-08</v>
+        <v>1.221465480860754e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.36916815338975e-08</v>
+        <v>1.316898097722699e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.25351055640371e-08</v>
+        <v>1.203163920960533e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.308525156221954e-08</v>
+        <v>1.258349717894804e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.199490087820383e-08</v>
+        <v>3.034556296979812e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.359246129327769e-08</v>
+        <v>1.310630019573553e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.259098477326595e-08</v>
+        <v>1.208834501652523e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.554290170818361e-08</v>
+        <v>1.499992795968199e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.337758986363921e-08</v>
+        <v>1.28528775859026e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.255118499145609e-08</v>
+        <v>1.205227546946125e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.573557530797331e-08</v>
+        <v>2.2468677061857e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.494205856752124e-08</v>
+        <v>1.441676771880897e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.053645464056313e-08</v>
+        <v>2.683150370300459e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.534304330361366e-08</v>
+        <v>1.480880427882821e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.317293492935863e-08</v>
+        <v>1.264274018126856e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.213605042979434e-08</v>
+        <v>3.087800521319575e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.348298886843951e-08</v>
+        <v>1.293075160660661e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.254709301277032e-08</v>
+        <v>1.204274706465129e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.585852804059554e-08</v>
+        <v>5.10690786891206e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.490722354580634e-08</v>
+        <v>5.014098781764234e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.518125554892165e-08</v>
+        <v>5.040673537706744e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.655631346740261e-08</v>
+        <v>5.177922980662746e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.565593215057498e-08</v>
+        <v>5.08703602332714e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.481257817658028e-08</v>
+        <v>5.003796896707524e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.433730436597362e-08</v>
+        <v>4.955450689139991e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.447743328344456e-08</v>
+        <v>4.973587126779975e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.535281244824667e-08</v>
+        <v>5.057477024875802e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.415730711067892e-08</v>
+        <v>4.941483293230213e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.57273482032552e-08</v>
+        <v>5.094426005234533e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.393771353597004e-08</v>
+        <v>4.918341901117808e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.474904373929206e-08</v>
+        <v>8.84161393079848e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.775720695600741e-08</v>
+        <v>5.305917557176315e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.556842096171375e-08</v>
+        <v>5.08435168585039e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.396800184301343e-08</v>
+        <v>4.921707616548858e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.86169935040532e-08</v>
+        <v>5.38027490133334e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.522537912925864e-08</v>
+        <v>5.043911753868703e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.390026614064595e-08</v>
+        <v>4.915543085957948e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.393272168741534e-08</v>
+        <v>4.940220407187641e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.743158945062283e-08</v>
+        <v>5.264237811240315e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.923455756065444e-08</v>
+        <v>5.422785601440094e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.833444921278363e-08</v>
+        <v>5.353341023380695e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.480250023116483e-08</v>
+        <v>5.022837620994609e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.58629757629739e-08</v>
+        <v>5.108899761126093e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.537786646045319e-08</v>
+        <v>5.054854863915278e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.390924644230238e-08</v>
+        <v>4.915452293915272e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.083474290557292e-07</v>
+        <v>1.027122242709102e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.671516095060389e-08</v>
+        <v>9.134026791165993e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.019667861751848e-07</v>
+        <v>9.643316677480954e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.176652343522342e-07</v>
+        <v>1.12218136905741e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.120978314564592e-07</v>
+        <v>1.063192325522381e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.086357803455515e-08</v>
+        <v>8.549069302880024e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.927976393258236e-08</v>
+        <v>8.349332417607696e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.05493212120771e-08</v>
+        <v>8.557554821161009e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.018757632019963e-07</v>
+        <v>9.637926174446047e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.335841074096782e-08</v>
+        <v>7.840509547411485e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.047135307494743e-07</v>
+        <v>9.921394834833276e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.052090857109367e-08</v>
+        <v>7.533357838591336e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.981706964249459e-08</v>
+        <v>8.841613930798478e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.365522373071307e-07</v>
+        <v>1.32376510936813e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.025235386931852e-07</v>
+        <v>9.793685089062874e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.927028196917099e-08</v>
+        <v>7.420423900205166e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.689816568901375e-07</v>
+        <v>1.626268142004109e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.743051962582477e-08</v>
+        <v>9.187140007902346e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.962647312686829e-08</v>
+        <v>7.460700379978273e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.908435794129987e-08</v>
+        <v>7.406345838502506e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.344369347705127e-07</v>
+        <v>1.288339247566721e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.688906511488139e-07</v>
+        <v>1.594699662386995e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.529293886731352e-07</v>
+        <v>1.470106322584523e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.646314957503815e-08</v>
+        <v>9.058012627016271e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.056866623463409e-07</v>
+        <v>1.003604080408215e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.048172892241728e-07</v>
+        <v>9.833089321544778e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.101293193791494e-08</v>
+        <v>7.576467225928097e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.072428818798806e-08</v>
+        <v>5.606071450956778e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.977298369319881e-08</v>
+        <v>5.513262363808956e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.004701569631416e-08</v>
+        <v>5.539837119751462e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.142207361479513e-08</v>
+        <v>5.049978771691589e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.052169229796749e-08</v>
+        <v>5.586199605371861e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.967833832397281e-08</v>
+        <v>5.502960478752244e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.24997887899952e-08</v>
+        <v>5.454614271184709e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.263991770746617e-08</v>
+        <v>5.472750708824692e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.351529687226825e-08</v>
+        <v>4.929532815904647e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.902306725807142e-08</v>
+        <v>4.813539084259058e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.05931083506477e-08</v>
+        <v>5.593589587279253e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.880347368336257e-08</v>
+        <v>5.41750548316253e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.290910710817063e-08</v>
+        <v>8.841613930798478e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>6.280856925726995e-08</v>
+        <v>5.180346955695409e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.061989436293066e-08</v>
+        <v>5.59564624544745e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.883376199040594e-08</v>
+        <v>5.420871198593578e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.677947792807477e-08</v>
+        <v>5.879438483378059e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.33878635532802e-08</v>
+        <v>5.543075335913424e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.876602628803848e-08</v>
+        <v>4.787598876986796e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.88820921854898e-08</v>
+        <v>5.425718607701975e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.559407387464443e-08</v>
+        <v>5.136293602269164e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.428585399077059e-08</v>
+        <v>5.933910491125533e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.64969336368052e-08</v>
+        <v>5.225396814409538e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.318057884137551e-08</v>
+        <v>4.893834115326041e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.402546018699547e-08</v>
+        <v>4.980955552154938e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.354035088447478e-08</v>
+        <v>5.554018445959998e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.205737709716227e-08</v>
+        <v>4.786020601107494e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.035046748078116e-08</v>
+        <v>5.574399383559652e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.939916298599194e-08</v>
+        <v>5.48159029641183e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.967319498910726e-08</v>
+        <v>5.508165052354336e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.104825290758827e-08</v>
+        <v>5.645414495310339e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.01478715907606e-08</v>
+        <v>5.554527537974733e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.930451761676591e-08</v>
+        <v>5.471288411355118e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.882924380615924e-08</v>
+        <v>5.422942203787585e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.89693727236302e-08</v>
+        <v>5.441078641427569e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.984475188843228e-08</v>
+        <v>5.524968539523393e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.864924655086455e-08</v>
+        <v>5.408974807877807e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.021928764344081e-08</v>
+        <v>5.561917519882125e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.842965297615566e-08</v>
+        <v>5.385833415765402e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.924098317947767e-08</v>
+        <v>8.841613930798478e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.224788177952408e-08</v>
+        <v>5.773282881830237e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.005909578523041e-08</v>
+        <v>5.55171701050431e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.845994128319903e-08</v>
+        <v>5.38919913119645e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.310893294423878e-08</v>
+        <v>5.847766415980934e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.971731856944423e-08</v>
+        <v>5.5114032685163e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.839220558083157e-08</v>
+        <v>5.383034600605543e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.851173625922031e-08</v>
+        <v>5.394131477935015e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.192352889080844e-08</v>
+        <v>5.73172932588791e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.372649700084005e-08</v>
+        <v>5.890277116087687e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.28263886529692e-08</v>
+        <v>5.820832538028289e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.937805002203242e-08</v>
+        <v>5.476663754111815e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.035491520315953e-08</v>
+        <v>5.576391275773686e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.986980590063882e-08</v>
+        <v>5.522346378562872e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.840118588248798e-08</v>
+        <v>5.382943808562864e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.915248553975865e-08</v>
+        <v>6.383890600746224e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.975631422951711e-08</v>
+        <v>7.363370014854604e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.003034623263246e-08</v>
+        <v>7.389944770797115e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.525263658523751e-08</v>
+        <v>6.956232217350775e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.075004435179869e-08</v>
+        <v>6.531068771515295e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.205770100089398e-08</v>
+        <v>7.575414135850762e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.918639504968441e-08</v>
+        <v>7.304721922230359e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.932652396715536e-08</v>
+        <v>7.322858359870342e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.020190313195749e-08</v>
+        <v>7.406748257966176e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.900639779438973e-08</v>
+        <v>7.29075452632058e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.057643888696602e-08</v>
+        <v>7.4436972383249e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.878680421968097e-08</v>
+        <v>7.267613134208089e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.064097307291581e-08</v>
+        <v>8.841613930798478e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.611064200229298e-08</v>
+        <v>7.052407607471924e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.331848147951669e-08</v>
+        <v>6.77485003458211e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.499111193789984e-08</v>
+        <v>5.987961184055914e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.346608418776401e-08</v>
+        <v>7.729546134423714e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.007446981296942e-08</v>
+        <v>7.393182986959074e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.87493568243568e-08</v>
+        <v>7.264814319048322e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.322918160579284e-08</v>
+        <v>6.752620171640009e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.912653057644635e-08</v>
+        <v>7.320616895415292e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.408591915867865e-08</v>
+        <v>7.772267569879282e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.0416610224372e-08</v>
+        <v>6.517871962677928e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.123047721405069e-08</v>
+        <v>8.42487542656526e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.894229073038591e-08</v>
+        <v>6.36596418349541e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.022695714416396e-08</v>
+        <v>7.40412609700565e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.082863996220264e-08</v>
+        <v>8.384818529892402e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.139303611333471e-08</v>
+        <v>6.665955384377246e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.609077142407935e-08</v>
+        <v>7.11786932558521e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.636480342719471e-08</v>
+        <v>7.144444081527724e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.643609265715062e-08</v>
+        <v>7.155974289972328e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.381689021221335e-08</v>
+        <v>5.935070268145287e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.599613470870567e-08</v>
+        <v>7.107568244669282e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.552085224424667e-08</v>
+        <v>7.059221232960968e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.56609811617176e-08</v>
+        <v>7.077357670600955e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.653636032651973e-08</v>
+        <v>7.16124756869678e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.534085498895197e-08</v>
+        <v>7.045253837051187e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.691089608152824e-08</v>
+        <v>7.19819654905551e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.512126141424309e-08</v>
+        <v>7.022112444938785e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.59325916175651e-08</v>
+        <v>8.841613930798478e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.081285075077652e-08</v>
+        <v>7.590209669972507e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.903121161649919e-08</v>
+        <v>7.407903967783305e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.515155837513891e-08</v>
+        <v>7.025478964510615e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.980054138232622e-08</v>
+        <v>7.484045445154313e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.640892700753164e-08</v>
+        <v>7.147682297689681e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.508381401891898e-08</v>
+        <v>7.019313629778924e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.519987991637036e-08</v>
+        <v>7.030325569478231e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.513402080985264e-08</v>
+        <v>7.996608250378925e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.041810543892747e-08</v>
+        <v>7.526556145261068e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.951799709105672e-08</v>
+        <v>7.45711156720167e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.606965846011983e-08</v>
+        <v>7.112942783285198e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.364065840707809e-08</v>
+        <v>6.884251076825548e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.656141433872625e-08</v>
+        <v>7.158625407736252e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.509279432057545e-08</v>
+        <v>7.019222837736243e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.74094517665206e-08</v>
+        <v>1.651293927063861e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.662293085832421e-08</v>
+        <v>1.568710458575904e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.762518394367865e-08</v>
+        <v>1.678478110293495e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.728663577011296e-08</v>
+        <v>1.644173036113693e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.743048275835095e-08</v>
+        <v>1.667019846569198e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.030953211259075e-08</v>
+        <v>1.861621082691211e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.741121289173132e-08</v>
+        <v>1.657853649900044e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.784585578292441e-08</v>
+        <v>1.703194692251456e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.841492916776871e-08</v>
+        <v>1.738901916514238e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.832895206829813e-08</v>
+        <v>1.750607826179573e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.754151595645075e-08</v>
+        <v>1.935212988306374e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.759214078490443e-08</v>
+        <v>1.700087319392925e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.818863115974924e-08</v>
+        <v>1.730635461192343e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.813282877141947e-08</v>
+        <v>2.669884101523399e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.768044828437293e-08</v>
+        <v>1.679972285738528e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.742747171862633e-08</v>
+        <v>1.662249179380969e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.748971709645149e-08</v>
+        <v>1.668516500073594e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.746318305068613e-08</v>
+        <v>1.663043875500881e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.764678894707516e-08</v>
+        <v>1.681838304879831e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.48368578674504e-08</v>
+        <v>2.330084555927148e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.732531980243142e-08</v>
+        <v>1.648269110108823e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.554843826963376e-08</v>
+        <v>2.396000795021129e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.776128440517372e-08</v>
+        <v>1.749733957495956e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.741354246348522e-08</v>
+        <v>1.664691228601186e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.822927108768518e-08</v>
+        <v>2.736796414401373e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.761776683790447e-08</v>
+        <v>1.68278808487052e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.753390516684143e-08</v>
+        <v>1.697907095701732e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.499124711450516e-08</v>
+        <v>1.387183433480847e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.305069666532737e-08</v>
+        <v>1.219149780594161e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.654962149070558e-08</v>
+        <v>1.582811989634683e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.411520249418772e-08</v>
+        <v>1.33619000920864e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.515604740306519e-08</v>
+        <v>1.500777618104225e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.557913622000464e-08</v>
+        <v>2.880354687585219e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.502314425330803e-08</v>
+        <v>1.435692089401168e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.81299073694502e-08</v>
+        <v>1.759808232378542e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.213574432267428e-08</v>
+        <v>2.010022997888741e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.153838669106836e-08</v>
+        <v>2.094223720639107e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.593691766787088e-08</v>
+        <v>3.409468685497619e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657180940432212e-08</v>
+        <v>1.759826723167075e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.056956025340991e-08</v>
+        <v>1.954898578951577e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.319485605105425e-08</v>
+        <v>3.134354798804722e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.692011023817016e-08</v>
+        <v>1.591228843611271e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.512905048904483e-08</v>
+        <v>1.466064258335106e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.558381372692183e-08</v>
+        <v>1.511921499527639e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.537101591257499e-08</v>
+        <v>1.470466269710398e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.670408723898735e-08</v>
+        <v>1.606847748479061e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.814243270719088e-08</v>
+        <v>2.627336930472855e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.438939978401908e-08</v>
+        <v>1.365284202279779e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.875281072777261e-08</v>
+        <v>2.69329228436891e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.751925105778111e-08</v>
+        <v>2.091980093045109e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.502850669723294e-08</v>
+        <v>1.483356416253999e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.311684934851876e-08</v>
+        <v>3.282894223467795e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.648656006837411e-08</v>
+        <v>1.612588195385992e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.60154986572129e-08</v>
+        <v>1.730430152511735e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.834338432159001e-08</v>
+        <v>5.13322567772676e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.6992193607029e-08</v>
+        <v>5.065665197579082e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.07801785042949e-08</v>
+        <v>5.440283532647582e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.695612114401604e-08</v>
+        <v>5.052791938672914e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8580939049048e-08</v>
+        <v>5.310857172819922e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.110112593332356e-08</v>
+        <v>7.50896765580949e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.836327704100264e-08</v>
+        <v>5.207320764783022e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>6.32727684426369e-08</v>
+        <v>5.719468696052208e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.963492198879828e-08</v>
+        <v>6.116493359360032e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.872956322120404e-08</v>
+        <v>6.25502185488948e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.983511009938e-08</v>
+        <v>8.340222083681904e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.089966861555305e-08</v>
+        <v>5.728412246081761e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.714457400833724e-08</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>5.93893719587032e-08</v>
+        <v>5.269917082522317e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.140441465528955e-08</v>
+        <v>5.457160931653915e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.854692797021168e-08</v>
+        <v>5.256970292313545e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.925001814703551e-08</v>
+        <v>5.327762562646694e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.895030389385159e-08</v>
+        <v>5.265946750566222e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.10242169564511e-08</v>
+        <v>5.478238476266118e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.975770122014521e-08</v>
+        <v>5.334253739123029e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.694687907953355e-08</v>
+        <v>5.056305363774125e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.899871060981599e-08</v>
+        <v>5.290157566944278e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.231749582618705e-08</v>
+        <v>6.245151106108577e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.799990589939853e-08</v>
+        <v>5.241753333654005e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.889163098502941e-08</v>
+        <v>5.348203696721161e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.069639888253808e-08</v>
+        <v>5.488966678181364e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.995269526396513e-08</v>
+        <v>5.67303488855454e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.116461330523646e-07</v>
+        <v>9.271148435913592e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.19475913509542e-08</v>
+        <v>8.452545756977614e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.681114379656683e-07</v>
+        <v>1.597442372541667e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.56935627554199e-08</v>
+        <v>7.655062465310427e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.243138180112501e-07</v>
+        <v>1.338477177548358e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>6.697779480920216e-07</v>
+        <v>4.977329908002795e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.227715180093639e-07</v>
+        <v>1.161291119860971e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.182109218984874e-07</v>
+        <v>2.158289780213133e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.087241379828179e-07</v>
+        <v>2.662801660820089e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.994734368983653e-07</v>
+        <v>2.949870748095659e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.415877633896033e-07</v>
+        <v>6.765117365899635e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.649814632583393e-07</v>
+        <v>2.07879971103916e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.545370726977418e-07</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.284542028463348e-07</v>
+        <v>1.152691880287836e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.666025937082342e-07</v>
+        <v>1.50437820732481e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.206080241237208e-07</v>
+        <v>1.199611471489965e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.397498565014753e-07</v>
+        <v>1.396146569914913e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.210561299665202e-07</v>
+        <v>1.145965281089099e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.728757224527456e-07</v>
+        <v>1.672203908723742e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.475398846357701e-07</v>
+        <v>1.394131050634726e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>9.245668927166141e-08</v>
+        <v>8.409432059005829e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2869476471949e-07</v>
+        <v>1.257752357432733e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.962188506779376e-07</v>
+        <v>3.153290880137988e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.170046506628982e-07</v>
+        <v>1.24415516019925e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.215776399760219e-07</v>
+        <v>1.304245492475863e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.608962055257221e-07</v>
+        <v>1.634750062909993e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.562162519996154e-07</v>
+        <v>2.133779696065087e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.54006847314389e-08</v>
+        <v>4.973808910529193e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.523696527507192e-08</v>
+        <v>4.906248430381513e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.783747891414382e-08</v>
+        <v>5.280866765450019e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.401342155386494e-08</v>
+        <v>5.705005117540747e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.563823945889692e-08</v>
+        <v>5.151440405622351e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.934589760136639e-08</v>
+        <v>8.161180834677314e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.542057745085155e-08</v>
+        <v>5.047903997585448e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.151754011067978e-08</v>
+        <v>5.56005192885464e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.787969365684117e-08</v>
+        <v>5.957076592162464e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.697433488924697e-08</v>
+        <v>6.907235033757311e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.689241050922891e-08</v>
+        <v>8.992435262549721e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.795696902540192e-08</v>
+        <v>5.568995478884196e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.539864768169469e-08</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>5.764344563206067e-08</v>
+        <v>5.94388424764489e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.869198471313239e-08</v>
+        <v>6.131230777591143e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.560422838006055e-08</v>
+        <v>5.097553525115975e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.630731855688443e-08</v>
+        <v>5.979975741514523e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>6.600760430370043e-08</v>
+        <v>5.106529983368653e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.926898862449404e-08</v>
+        <v>5.318821709068546e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.720468635621442e-08</v>
+        <v>6.029267945990882e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.400417948938245e-08</v>
+        <v>4.896888596576558e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.742648521354731e-08</v>
+        <v>5.147839522906978e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.056226749422999e-08</v>
+        <v>6.897364284976408e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.673145193376881e-08</v>
+        <v>5.135132485360513e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.713640265307234e-08</v>
+        <v>6.000416875588991e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.775369929238694e-08</v>
+        <v>6.141179857049191e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.821545522684534e-08</v>
+        <v>5.518157912797842e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.44085256425518e-08</v>
+        <v>5.707572825628629e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.30573349279908e-08</v>
+        <v>5.640012345480948e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.68453198252567e-08</v>
+        <v>6.01463068054945e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.302126246497784e-08</v>
+        <v>5.627139086574781e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.464608037000982e-08</v>
+        <v>5.88520432072179e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.716626725428529e-08</v>
+        <v>8.083314803711358e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.442841836196445e-08</v>
+        <v>5.781667912684889e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.933790976359865e-08</v>
+        <v>6.293815843954076e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.570006330976009e-08</v>
+        <v>6.6908405072619e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.479470454216585e-08</v>
+        <v>6.829369002791354e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.590025142034185e-08</v>
+        <v>8.914569231583782e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.696480993651482e-08</v>
+        <v>6.302759393983631e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.320971532929907e-08</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O7" t="n">
-        <v>6.545315777898715e-08</v>
+        <v>5.844129927242065e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.746820047557343e-08</v>
+        <v>6.031373776373667e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.461206929117346e-08</v>
+        <v>5.831317440215411e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.531515946799732e-08</v>
+        <v>5.902109710548562e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.501544521481338e-08</v>
+        <v>5.84029389846809e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.708935827741291e-08</v>
+        <v>6.052585624167984e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.620442461016681e-08</v>
+        <v>5.950543653001766e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.301202040049532e-08</v>
+        <v>5.630652511675993e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.506385193077778e-08</v>
+        <v>5.864504714846146e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.838263714714891e-08</v>
+        <v>6.819498254010448e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.445473194658067e-08</v>
+        <v>5.858901509555897e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.495677230599122e-08</v>
+        <v>5.922550844623028e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.67615402034999e-08</v>
+        <v>6.063313826083233e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.601783658492694e-08</v>
+        <v>6.247382036456408e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.42760018100452e-08</v>
+        <v>6.653424210384585e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.634651551492086e-08</v>
+        <v>7.853405496278572e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.013450041218679e-08</v>
+        <v>8.228023831347064e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.916378136395204e-08</v>
+        <v>7.165603637088303e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.660450122280239e-08</v>
+        <v>7.028523898505587e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.232385256869174e-07</v>
+        <v>1.055954099697074e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.771759894889446e-08</v>
+        <v>7.995061063482499e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.262709035052875e-08</v>
+        <v>8.507208994751696e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.898924389669014e-08</v>
+        <v>8.904233658059516e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.808388512909591e-08</v>
+        <v>9.042762153588971e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.918943200727191e-08</v>
+        <v>1.112796238238138e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.025399052344413e-08</v>
+        <v>8.516152544781127e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.609482958839242e-08</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>8.11987553023003e-08</v>
+        <v>7.345115631403691e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.251295669786398e-08</v>
+        <v>7.466172236901256e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.184187420444038e-08</v>
+        <v>6.528067937681807e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.860434005492738e-08</v>
+        <v>8.115502861346182e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.830462580174331e-08</v>
+        <v>8.053687049265712e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>9.03785388643429e-08</v>
+        <v>8.265978774965605e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.294552418333085e-08</v>
+        <v>7.545563797111224e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.262707949193738e-08</v>
+        <v>7.496988563447794e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.835567026621925e-08</v>
+        <v>8.078146973816384e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.684256793941188e-08</v>
+        <v>7.632421472937342e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.010798626469149e-07</v>
+        <v>9.331622793367618e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.457493342277029e-08</v>
+        <v>6.844856990277751e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.005072079042992e-08</v>
+        <v>8.276706976880849e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.033271097425776e-07</v>
+        <v>9.784828551992287e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.534121671395453e-08</v>
+        <v>7.613194524370517e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.28919991155242e-08</v>
+        <v>8.362764363240949e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>9.667998401279013e-08</v>
+        <v>8.737382698309447e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>9.080139743977888e-08</v>
+        <v>8.161301603140634e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.395925019398637e-08</v>
+        <v>6.724246505908918e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.270009442758429e-07</v>
+        <v>1.080606791795719e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>9.426308254949788e-08</v>
+        <v>8.504419930444884e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.917257395113213e-08</v>
+        <v>9.016567861714074e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>1.055347274972935e-07</v>
+        <v>9.41359252502189e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.046293687296992e-07</v>
+        <v>9.552121020551347e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.573491560787526e-08</v>
+        <v>1.163732124934378e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>9.679947412404824e-08</v>
+        <v>9.025511411743627e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.030443795168325e-07</v>
+        <v>2.70231843641208e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>9.82392967889484e-08</v>
+        <v>8.83781362582579e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>1.008959370313115e-07</v>
+        <v>9.083951020026994e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.444674631273093e-08</v>
+        <v>8.554070554461238e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>9.514982365553073e-08</v>
+        <v>8.62486172830856e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>9.485010940234677e-08</v>
+        <v>8.563045916228076e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>9.692402246494637e-08</v>
+        <v>8.775337641927982e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>9.604719145486073e-08</v>
+        <v>8.674153932784915e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03119387081186e-07</v>
+        <v>9.296356735511797e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.489851611831122e-08</v>
+        <v>8.587256732606144e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.821730133468227e-08</v>
+        <v>9.542250271770437e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.428939613411418e-08</v>
+        <v>8.581653527315888e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.942434339508193e-08</v>
+        <v>8.152646377480533e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.65962043910333e-08</v>
+        <v>8.786065843843227e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.585250077246037e-08</v>
+        <v>8.970134054216409e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.696391800713371e-08</v>
+        <v>1.59683110053325e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.644016874511644e-08</v>
+        <v>1.526043062534614e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.704334495154306e-08</v>
+        <v>1.604093751429502e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.704515103920801e-08</v>
+        <v>1.604521611228767e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.709825202529627e-08</v>
+        <v>1.609946661971851e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.923716950217093e-08</v>
+        <v>1.762110809163963e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.699598753492084e-08</v>
+        <v>1.599563994214213e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.707016967344464e-08</v>
+        <v>1.608178461416995e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.784127299293753e-08</v>
+        <v>1.667502787792575e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.716335425945793e-08</v>
+        <v>1.617878328540797e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.729049315149969e-08</v>
+        <v>1.70530865884507e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.700520809336845e-08</v>
+        <v>1.602442371146379e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.705109056867023e-08</v>
+        <v>1.605108833262127e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.743067112575615e-08</v>
+        <v>2.568912083200197e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.740052916765458e-08</v>
+        <v>1.635496808371463e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71122084624681e-08</v>
+        <v>1.610479779049447e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.726908945904208e-08</v>
+        <v>1.627153444372098e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.715797151921982e-08</v>
+        <v>1.615359668155837e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.703634831969776e-08</v>
+        <v>1.604905105924361e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.478636767793089e-08</v>
+        <v>2.249910702768812e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.705387937671694e-08</v>
+        <v>1.605478175335406e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.592013513544176e-08</v>
+        <v>2.349491550736166e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.752375331177885e-08</v>
+        <v>1.665163579335134e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.737826917510044e-08</v>
+        <v>1.642992867653365e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.780568805277027e-08</v>
+        <v>2.654973678349595e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.706087587711319e-08</v>
+        <v>1.607710284546504e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.382425573479436e-08</v>
+        <v>3.156446370051326e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.374409452483313e-08</v>
+        <v>1.290065510132747e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.32430373564619e-08</v>
+        <v>1.20854400210045e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.431680733800617e-08</v>
+        <v>1.342461714246312e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.431898070279486e-08</v>
+        <v>1.344461483588274e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.47096244961905e-08</v>
+        <v>1.384329936865777e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.984967474181458e-08</v>
+        <v>2.461084306828622e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.398228916377298e-08</v>
+        <v>1.310448990468684e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.451074016004115e-08</v>
+        <v>1.371875684733135e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.997519101639423e-08</v>
+        <v>1.792244480736236e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.516555781916943e-08</v>
+        <v>1.440053451855224e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.606472456267603e-08</v>
+        <v>2.060340823645364e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.431180075668845e-08</v>
+        <v>1.355665124758057e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.437088613999421e-08</v>
+        <v>1.34958474786019e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.126023038603199e-08</v>
+        <v>2.913973673179853e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.684538538609616e-08</v>
+        <v>1.564710305068069e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.480093466916211e-08</v>
+        <v>1.387356564850788e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.593793069433401e-08</v>
+        <v>1.508024373652075e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.512000840849836e-08</v>
+        <v>1.421449480766394e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.426763712622109e-08</v>
+        <v>1.348341707647871e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.700540341687153e-08</v>
+        <v>2.399062225591407e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.437812795500121e-08</v>
+        <v>1.350998679546928e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.032184751892929e-08</v>
+        <v>2.708330252835059e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.774410436797513e-08</v>
+        <v>1.778189219568281e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.670346739700929e-08</v>
+        <v>1.619711389521626e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.19979021068732e-08</v>
+        <v>3.074962532350836e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.443926270882925e-08</v>
+        <v>1.368015651371831e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.331970737115234e-07</v>
+        <v>1.233889687314847e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.593783223175504e-08</v>
+        <v>4.961258789038845e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.667460236739851e-08</v>
+        <v>5.033079602055469e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.683499610705827e-08</v>
+        <v>5.043293771896504e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.685539669807541e-08</v>
+        <v>5.048126645154442e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.74551967636027e-08</v>
+        <v>5.109405088944197e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.161525361555401e-08</v>
+        <v>6.828169130445143e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.630007230082262e-08</v>
+        <v>4.992128080358559e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.713799368091838e-08</v>
+        <v>5.089432450264676e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.579194971062197e-08</v>
+        <v>5.754135516180027e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.819055644696612e-08</v>
+        <v>5.19899691158734e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.962664871935773e-08</v>
+        <v>6.186562712313142e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.689708953460915e-08</v>
+        <v>5.070754068375027e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.692248641566978e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.643350578388527e-08</v>
+        <v>5.001318195202548e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.08695561408957e-08</v>
+        <v>5.398005746175869e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.76128411417367e-08</v>
+        <v>5.115426891581631e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.93848841668638e-08</v>
+        <v>5.303763611665985e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.81297559197937e-08</v>
+        <v>5.170547483898226e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.675596593175625e-08</v>
+        <v>5.052458394157457e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.63496262415825e-08</v>
+        <v>5.008152087642578e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.657346260290648e-08</v>
+        <v>5.022295237771397e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.962419743996524e-08</v>
+        <v>5.322667555619686e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.2261429534686e-08</v>
+        <v>5.733105571599438e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.033509366833823e-08</v>
+        <v>5.468224770677719e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.668096808476758e-08</v>
+        <v>5.040723458097773e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.703301597599723e-08</v>
+        <v>5.08414417714048e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.438774848146163e-07</v>
+        <v>2.234451428108705e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.773437254157375e-08</v>
+        <v>7.119716690878173e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.297823222684744e-08</v>
+        <v>8.607832910869264e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.662798114379918e-08</v>
+        <v>8.862039819922952e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.143510306841598e-08</v>
+        <v>8.401366712875859e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.08085750188018e-07</v>
+        <v>1.008092595699531e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.703536279312058e-07</v>
+        <v>3.568718189984098e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.896731925566402e-08</v>
+        <v>8.121045688140643e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.032739754795073e-07</v>
+        <v>9.813434453510156e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.370822236409467e-07</v>
+        <v>2.008859323165759e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.165808778316939e-07</v>
+        <v>1.120678061108275e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37715619172246e-07</v>
+        <v>2.675232081413929e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>9.741199224928216e-08</v>
+        <v>9.314067621941051e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>9.030141093091364e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>8.551030248556092e-08</v>
+        <v>7.752113809899404e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.572774927887946e-07</v>
+        <v>1.416321008154028e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.065739223508305e-07</v>
+        <v>9.784120436143112e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.468955001626848e-07</v>
+        <v>1.397906125198259e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.118092695787018e-07</v>
+        <v>1.037807422690166e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.562669500226154e-08</v>
+        <v>9.070417003446681e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.001157637338195e-08</v>
+        <v>8.217816116247822e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>9.116729294834051e-08</v>
+        <v>8.405624475215534e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.446733006803639e-07</v>
+        <v>1.367738104786054e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.918771776553586e-07</v>
+        <v>2.099466370517942e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61615718093912e-07</v>
+        <v>1.643879337219361e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.90795026235575e-08</v>
+        <v>8.339580900812902e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.874988440425052e-08</v>
+        <v>9.451134872797006e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.651158524187251e-06</v>
+        <v>3.376555572204601e-06</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.432361701938147e-08</v>
+        <v>5.631910912946476e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.400748589994528e-08</v>
+        <v>5.703731725963103e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.52207808946847e-08</v>
+        <v>5.713945895804138e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.418828023062218e-08</v>
+        <v>4.9008215381511e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.478808029614946e-08</v>
+        <v>4.962099981940855e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.00010384031804e-08</v>
+        <v>6.680864023441805e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.363295583336939e-08</v>
+        <v>4.844822973355215e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.447087721346518e-08</v>
+        <v>5.760084574172311e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.417773449824839e-08</v>
+        <v>6.42478764008766e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.552343997951286e-08</v>
+        <v>5.051691804583995e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.801243350698416e-08</v>
+        <v>6.857214836220773e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>6.422997306715592e-08</v>
+        <v>4.923448961371683e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.530960379066441e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.482062315887999e-08</v>
+        <v>5.684039708006111e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.906604060910479e-08</v>
+        <v>5.235489898467524e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.494572467428349e-08</v>
+        <v>4.96812178457829e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.671776769941059e-08</v>
+        <v>5.974415735573617e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.651554070742012e-08</v>
+        <v>5.023242376894882e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.514175071938268e-08</v>
+        <v>4.905153287154116e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.501843664576452e-08</v>
+        <v>5.693256624995084e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.390634613545326e-08</v>
+        <v>4.874990130768054e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.819335584412821e-08</v>
+        <v>5.190967307677119e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.064721432231242e-08</v>
+        <v>6.403757695507071e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.91103055587851e-08</v>
+        <v>5.344713105663838e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.506675287239403e-08</v>
+        <v>5.711375582005405e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.436589950854394e-08</v>
+        <v>4.936839070137139e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.432972092625521e-07</v>
+        <v>2.229581314197236e-07</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.102123346938156e-08</v>
+        <v>5.465116307544768e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>6.175800360502502e-08</v>
+        <v>5.536937120561392e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.191839734468478e-08</v>
+        <v>5.547151290402427e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>6.193879793570193e-08</v>
+        <v>5.551984163660365e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>6.25385980012292e-08</v>
+        <v>5.61326260745012e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.669865485318041e-08</v>
+        <v>7.33202664895107e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.138347353844911e-08</v>
+        <v>5.495985598864482e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.222139491854491e-08</v>
+        <v>5.5932899687706e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.087535094824844e-08</v>
+        <v>6.257993034685952e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.327395768459259e-08</v>
+        <v>5.702854430093263e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.471004995698424e-08</v>
+        <v>6.690420230819065e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.198049077223564e-08</v>
+        <v>5.574611586880949e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.200588765329627e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.151564046600131e-08</v>
+        <v>5.505049923763128e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.595169082301176e-08</v>
+        <v>5.901737474736449e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.269624237936323e-08</v>
+        <v>5.619284410087554e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.446828540449031e-08</v>
+        <v>5.807621130171906e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.321315715742019e-08</v>
+        <v>5.67440500240415e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.183936716938275e-08</v>
+        <v>5.556315912663381e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.171038187191984e-08</v>
+        <v>5.525825335065957e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.165686384053298e-08</v>
+        <v>5.526152756277322e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.470759867759173e-08</v>
+        <v>5.826525074125608e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.734483077231251e-08</v>
+        <v>6.236963090105361e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.570152052252031e-08</v>
+        <v>5.986534702628517e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.176436932239409e-08</v>
+        <v>5.544580976603696e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.21164172136237e-08</v>
+        <v>5.588001695646405e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.489608860522428e-07</v>
+        <v>2.284837179959297e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.032866306221902e-08</v>
+        <v>6.328033873335111e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.338351440395043e-08</v>
+        <v>7.541513147922292e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.354390814361022e-08</v>
+        <v>7.551727317763321e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.700529385292144e-08</v>
+        <v>6.948660737042573e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.376504068108565e-08</v>
+        <v>6.654037218665288e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.108784000350891e-07</v>
+        <v>9.573332995538186e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>8.300898433737458e-08</v>
+        <v>7.50056162622538e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.384690571747032e-08</v>
+        <v>7.597865996131498e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.250086174717388e-08</v>
+        <v>8.262569062046848e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.489946848351801e-08</v>
+        <v>7.707430457454158e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.633556075590966e-08</v>
+        <v>8.694996258179963e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>8.360600157115936e-08</v>
+        <v>7.579187614241637e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.408282474692981e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.621787507796938e-08</v>
+        <v>6.867974610174763e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>8.001071204054262e-08</v>
+        <v>7.205048167536278e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.958288786836674e-08</v>
+        <v>6.257840031064383e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.609379620341575e-08</v>
+        <v>7.812197157532807e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.483866795634563e-08</v>
+        <v>7.67898102976505e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.34648779683082e-08</v>
+        <v>7.560891940024277e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.732585935521751e-08</v>
+        <v>6.973413858588602e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.991189230977115e-08</v>
+        <v>7.218259611876226e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.633553033160628e-08</v>
+        <v>7.831325469996321e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.536045287996062e-08</v>
+        <v>6.980153977560475e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.956877956519093e-08</v>
+        <v>9.125558430200164e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.084298423232514e-08</v>
+        <v>6.386291650304561e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.374192801254912e-08</v>
+        <v>7.592577723007301e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.83453662692169e-07</v>
+        <v>2.604550555399337e-07</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.682314791817425e-08</v>
+        <v>6.915708190667966e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.471748243948079e-08</v>
+        <v>7.646963619064517e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.487787617914049e-08</v>
+        <v>7.657177788905549e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.324634551716405e-08</v>
+        <v>7.509816309739564e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.899792825830062e-08</v>
+        <v>6.203111548226287e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.096581407235376e-07</v>
+        <v>9.442053754602511e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>8.434295237290488e-08</v>
+        <v>7.606012097367604e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.518087375300061e-08</v>
+        <v>7.703316467273727e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.383482978270419e-08</v>
+        <v>8.368019533189068e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.623343651904839e-08</v>
+        <v>7.812880928596386e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.766952879144002e-08</v>
+        <v>8.800446729322183e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>8.493996960669146e-08</v>
+        <v>7.684638085384071e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.496536648775201e-08</v>
+        <v>9.001786543939798e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.684840268893602e-08</v>
+        <v>7.833738788649073e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.180032447997384e-08</v>
+        <v>8.277954163496973e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.56557282497204e-08</v>
+        <v>7.729311515738991e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.742776423894606e-08</v>
+        <v>7.91764762867503e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.617263599187599e-08</v>
+        <v>7.784431500907271e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.479884600383852e-08</v>
+        <v>7.666342411166498e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.467553193022037e-08</v>
+        <v>7.636488518096495e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.287602471671907e-08</v>
+        <v>8.397153201905885e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.766707751204754e-08</v>
+        <v>7.936551572628726e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.030430960676825e-08</v>
+        <v>8.346989588608488e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.866099935697614e-08</v>
+        <v>8.096561201131639e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.040847610163227e-08</v>
+        <v>7.257027282338538e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.507589604807952e-08</v>
+        <v>7.69802819414953e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.719203648866982e-07</v>
+        <v>2.495839829809607e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -798,7 +798,7 @@
         <v>6.282999258150731e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>6.541363026133222e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.640446452723438e-08</v>
@@ -974,7 +974,7 @@
         <v>7.077178252243185e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>6.384966001866837e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.484046460676524e-08</v>
@@ -1062,7 +1062,7 @@
         <v>6.976799621257051e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>7.23516338923955e-08</v>
       </c>
       <c r="O7" t="n">
         <v>6.334101238576154e-08</v>
@@ -1150,7 +1150,7 @@
         <v>9.498849284486121e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>8.627462044522447e-08</v>
       </c>
       <c r="O8" t="n">
         <v>8.037010857519501e-08</v>
@@ -1238,7 +1238,7 @@
         <v>1.075928555404428e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>1.101764932202677e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.047654262883863e-07</v>
@@ -1658,7 +1658,7 @@
         <v>4.946517340225624e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>4.939873419343104e-08</v>
       </c>
       <c r="O4" t="n">
         <v>4.933965035594227e-08</v>
@@ -1834,7 +1834,7 @@
         <v>4.814650966254036e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>4.809175273778018e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.442041871330687e-08</v>
@@ -1922,7 +1922,7 @@
         <v>5.417569488098834e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>5.410925567216311e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.404890987952628e-08</v>
@@ -2010,7 +2010,7 @@
         <v>7.308598778921058e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>6.466521250581416e-08</v>
       </c>
       <c r="O8" t="n">
         <v>6.690197276094768e-08</v>
@@ -2098,7 +2098,7 @@
         <v>7.053487951843683e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>7.046844030961164e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.221775741522345e-08</v>
@@ -2518,7 +2518,7 @@
         <v>5.721906738353241e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>5.639921339587798e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.297450085628684e-08</v>
@@ -2694,7 +2694,7 @@
         <v>6.388195874304915e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>5.48706193101221e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.144506733686679e-08</v>
@@ -2782,7 +2782,7 @@
         <v>6.313435649074377e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>6.231450250308936e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.888844474752959e-08</v>
@@ -2870,7 +2870,7 @@
         <v>8.562670378790184e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>7.480587168799888e-08</v>
       </c>
       <c r="O8" t="n">
         <v>7.412951477033949e-08</v>
@@ -2958,7 +2958,7 @@
         <v>9.07629884366248e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>8.994313444897038e-08</v>
       </c>
       <c r="O9" t="n">
         <v>8.927127621798318e-08</v>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.623099880179424e-08</v>
+        <v>1.62309988017943e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.551909132088092e-08</v>
+        <v>1.551909132088095e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.652606956965352e-08</v>
+        <v>1.65260695696535e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.628405426436024e-08</v>
+        <v>1.62840542643603e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.646133658466947e-08</v>
+        <v>1.646133658466953e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.816497229191384e-08</v>
+        <v>1.81649722919139e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.622602391810149e-08</v>
+        <v>1.622602391810154e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.652631914956007e-08</v>
+        <v>1.652631914956013e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.706942179979348e-08</v>
+        <v>1.706942179979354e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.649929403496419e-08</v>
+        <v>1.649929403496423e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.893648274260694e-08</v>
+        <v>1.8936482742607e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.666349294818728e-08</v>
+        <v>1.666349294818731e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.637672940564495e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.618009245069852e-08</v>
+        <v>2.61800924506985e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.644962989089233e-08</v>
+        <v>1.644962989089234e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.637602336840102e-08</v>
+        <v>1.637602336840106e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.621461351688417e-08</v>
+        <v>1.621461351688423e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.637857149863621e-08</v>
+        <v>1.637857149863629e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.634530003799037e-08</v>
+        <v>1.634530003799038e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.310609914090354e-08</v>
+        <v>2.310609914090358e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.627464763726727e-08</v>
+        <v>1.627464763726734e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.419203091705882e-08</v>
+        <v>2.419203091705881e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.76754625522732e-08</v>
+        <v>1.767546255227329e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.676688436067019e-08</v>
+        <v>1.676688436067023e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.715092073836471e-08</v>
+        <v>2.715092073836477e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.647284737622634e-08</v>
+        <v>1.647284737622639e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.682633776984115e-08</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.322287260878688e-08</v>
+        <v>1.322287260878686e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.228718652807393e-08</v>
+        <v>1.228718652807394e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.534037166539046e-08</v>
+        <v>1.534037166539043e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.359739370345934e-08</v>
+        <v>1.359739370345932e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.48777194546973e-08</v>
+        <v>1.487771945469728e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.697283787643547e-08</v>
+        <v>2.697283787643546e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.319694358020373e-08</v>
+        <v>1.319694358020372e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.534513780244259e-08</v>
+        <v>1.534513780244257e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.919235681669174e-08</v>
+        <v>1.91923568166917e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.513524227440797e-08</v>
+        <v>1.513524227440795e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.252552776276131e-08</v>
+        <v>3.252552776276128e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.657207612656617e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.426911380461124e-08</v>
+        <v>1.42691138046112e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.00117013362626e-08</v>
+        <v>3.001170133626261e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.477666844850931e-08</v>
+        <v>1.47766684485093e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.4262676577527e-08</v>
+        <v>1.426267657752698e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.311360027672592e-08</v>
+        <v>1.311360027672591e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.427331713728125e-08</v>
+        <v>1.427331713728123e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.404787394942765e-08</v>
+        <v>1.404787394942763e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.593545292561995e-08</v>
+        <v>2.593545292561999e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352798852869225e-08</v>
+        <v>1.352798852869222e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.951701627773102e-08</v>
+        <v>2.951701627773097e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.355483544631246e-08</v>
+        <v>2.355483544631245e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705064684560638e-08</v>
+        <v>1.70506468456064e-08</v>
       </c>
       <c r="Z3" t="n">
         <v>3.264516941323636e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.495319788704762e-08</v>
+        <v>1.49531978870476e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.756803313129576e-08</v>
+        <v>1.756803313129577e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.009034565437582e-08</v>
+        <v>5.009034565437578e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.056844065366433e-08</v>
+        <v>5.05684406536643e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.342330571660488e-08</v>
+        <v>5.342330571660486e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.068963151077751e-08</v>
+        <v>5.068963151077747e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.269211687256695e-08</v>
+        <v>5.269211687256693e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.193546589703676e-08</v>
+        <v>7.193546589703675e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.003415205450664e-08</v>
+        <v>5.003415205450661e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.342612483646276e-08</v>
+        <v>5.342612483646272e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.950504163489027e-08</v>
+        <v>5.950504163489024e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.312086373493509e-08</v>
+        <v>5.312086373493507e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.065003134995721e-08</v>
+        <v>8.065003134995715e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.542227882303549e-08</v>
+        <v>5.542227882303547e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>5.17364398642589e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.085105315372628e-08</v>
+        <v>5.085105315372624e-08</v>
       </c>
       <c r="P4" t="n">
         <v>5.255988438100818e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.172846484879576e-08</v>
+        <v>5.172846484879574e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.99052663237132e-08</v>
+        <v>4.990526632371316e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.175724715200045e-08</v>
+        <v>5.175724715200042e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.138143069837702e-08</v>
+        <v>5.138143069837701e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.270334195299346e-08</v>
+        <v>5.270334195299348e-08</v>
       </c>
       <c r="V4" t="n">
         <v>5.020508891063655e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.657244473811712e-08</v>
+        <v>5.657244473811711e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.640622820219043e-08</v>
+        <v>6.64062282021904e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.596883286135232e-08</v>
+        <v>5.596883286135231e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.299102656669964e-08</v>
+        <v>5.299102656669961e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.282213655842719e-08</v>
+        <v>5.282213655842716e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.692651333448193e-08</v>
+        <v>5.69265133344819e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.742941797937286e-08</v>
+        <v>7.742941797937234e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.850988184344631e-08</v>
+        <v>8.850988184344627e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.423712099831264e-07</v>
+        <v>1.423712099831263e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.588416319740131e-08</v>
+        <v>8.588416319740119e-08</v>
       </c>
       <c r="F5" t="n">
         <v>1.291022537980361e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.36382360488126e-07</v>
+        <v>4.363823604881264e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.139856069920156e-08</v>
+        <v>8.139856069920166e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.43967905523629e-07</v>
+        <v>1.439679055236288e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.374195426044955e-07</v>
+        <v>2.374195426044954e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.297507802803007e-07</v>
+        <v>1.297507802803005e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.145497848597586e-07</v>
+        <v>6.145497848597577e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.819752325692534e-07</v>
+        <v>1.819752325692529e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>1.097327817513391e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>8.909163329321299e-08</v>
+        <v>8.909163329321313e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.17694702143884e-07</v>
+        <v>1.176947021438841e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.088671465855463e-07</v>
+        <v>1.088671465855461e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>7.813090427782991e-08</v>
+        <v>7.813090427782987e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.054659070971023e-07</v>
+        <v>1.054659070971021e-07</v>
       </c>
       <c r="T5" t="n">
         <v>1.050464195466275e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.259700056563454e-07</v>
+        <v>1.259700056563476e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.245046085266156e-08</v>
+        <v>8.245046085266181e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.944362036408601e-07</v>
+        <v>1.944362036408598e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>3.777939115248615e-07</v>
+        <v>3.77793911524862e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.861112474201751e-07</v>
+        <v>1.861112474201752e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.22547349286797e-07</v>
+        <v>1.225473492867967e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.279428925350575e-07</v>
+        <v>1.279428925350573e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.167843346585768e-07</v>
+        <v>2.167843346585764e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.608160542804622e-08</v>
+        <v>5.608160542804618e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.914931987474156e-08</v>
+        <v>4.914931987474154e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.941456549027527e-08</v>
+        <v>5.941456549027525e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.668089128444793e-08</v>
+        <v>5.66808912844479e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.127299609364418e-08</v>
+        <v>5.127299609364415e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.051634511811393e-08</v>
+        <v>7.051634511811392e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.861503127558389e-08</v>
+        <v>4.861503127558386e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.200700405754001e-08</v>
+        <v>5.200700405753998e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.549630140856069e-08</v>
+        <v>6.549630140856064e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.911212350860554e-08</v>
+        <v>5.911212350860547e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.664129112362762e-08</v>
+        <v>8.664129112362757e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.400315804411274e-08</v>
+        <v>5.400315804411268e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>5.032244659517679e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.699462592625666e-08</v>
+        <v>5.699462592625659e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.870454254421426e-08</v>
+        <v>5.870454254421418e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.77197246224662e-08</v>
+        <v>5.771972462246612e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.848614554479045e-08</v>
+        <v>4.848614554479041e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.774850692567086e-08</v>
+        <v>5.774850692567082e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.996230991945429e-08</v>
+        <v>4.996230991945424e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.145880787413447e-08</v>
+        <v>5.14588078741345e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.619634868430697e-08</v>
+        <v>5.619634868430694e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>6.271585515864843e-08</v>
+        <v>6.271585515864839e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.498710742326765e-08</v>
+        <v>6.498710742326763e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.481791874877744e-08</v>
+        <v>5.481791874877743e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.898228634037008e-08</v>
+        <v>5.898228634037002e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.88133963320976e-08</v>
+        <v>5.881339633209756e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.55713832925848e-08</v>
+        <v>5.557138329258478e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.533196416124609e-08</v>
+        <v>5.533196416124605e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.581005916053457e-08</v>
+        <v>5.581005916053455e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.866492422347514e-08</v>
+        <v>5.866492422347516e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.593125001764779e-08</v>
+        <v>5.593125001764777e-08</v>
       </c>
       <c r="F7" t="n">
         <v>5.79337353794372e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.717708440390711e-08</v>
+        <v>7.717708440390703e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.527577056137691e-08</v>
+        <v>5.527577056137689e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.866774334333303e-08</v>
+        <v>5.866774334333297e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.474666014176053e-08</v>
+        <v>6.474666014176052e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.836248224180539e-08</v>
+        <v>5.836248224180536e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.589164985682754e-08</v>
+        <v>8.58916498568275e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.066389732990576e-08</v>
+        <v>6.066389732990572e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>5.697805837112916e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.609141147062633e-08</v>
+        <v>5.609141147062631e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.780024269790824e-08</v>
+        <v>5.780024269790821e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.697008335566605e-08</v>
+        <v>5.697008335566601e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.514688483058347e-08</v>
+        <v>5.514688483058346e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.699886565887073e-08</v>
+        <v>5.699886565887071e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.662304920524731e-08</v>
+        <v>5.66230492052473e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.811182412445115e-08</v>
+        <v>5.81118241244513e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.544670741750683e-08</v>
+        <v>5.544670741750682e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.18140632449874e-08</v>
+        <v>6.181406324498736e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.164784670906071e-08</v>
+        <v>7.164784670906067e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.138503806828636e-08</v>
+        <v>6.138503806828635e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.823264507356994e-08</v>
+        <v>5.823264507356987e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.806375506529747e-08</v>
+        <v>5.806375506529743e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.21681318413522e-08</v>
+        <v>6.216813184135218e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.404557654748635e-08</v>
+        <v>6.404557654748634e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.616737886274856e-08</v>
+        <v>7.61673788627486e-08</v>
       </c>
       <c r="D8" t="n">
         <v>7.902224392568913e-08</v>
@@ -3709,67 +3709,67 @@
         <v>6.84613012821876e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.994880266985191e-08</v>
+        <v>9.994880266985187e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.563309026359085e-08</v>
+        <v>7.563309026359088e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.902506304554704e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.510397984397449e-08</v>
+        <v>8.510397984397452e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.871980194401937e-08</v>
+        <v>7.87198019440194e-08</v>
       </c>
       <c r="L8" t="n">
         <v>1.062489695590415e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>8.102121703211796e-08</v>
+        <v>8.102121703211793e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>6.830955695316568e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>6.99045442560276e-08</v>
+        <v>6.990454425602761e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.100537587842259e-08</v>
+        <v>7.100537587842255e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.339544149935316e-08</v>
+        <v>6.339544149935315e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.550420453279746e-08</v>
+        <v>7.550420453279745e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.73561853610847e-08</v>
+        <v>7.735618536108472e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.698036890746133e-08</v>
+        <v>7.698036890746131e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.278872018082622e-08</v>
+        <v>7.278872018082616e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.26161020635787e-08</v>
+        <v>7.261610206357879e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.217367126839948e-08</v>
+        <v>8.217367126839947e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.91403737642988e-08</v>
+        <v>7.914037376429881e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.331086276113864e-08</v>
+        <v>9.33108627611386e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.672996961815638e-08</v>
+        <v>6.67299696181564e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.84210747675115e-08</v>
+        <v>7.842107476751151e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>9.468827746600352e-08</v>
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.057470139315795e-08</v>
+        <v>7.057470139315788e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.792641402626056e-08</v>
+        <v>7.792641402626055e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.078127908920119e-08</v>
+        <v>8.078127908920115e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.646120967646022e-08</v>
+        <v>7.646120967646017e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.42045125345748e-08</v>
+        <v>6.420451253457479e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.92934492877743e-08</v>
+        <v>9.929344928777423e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.739212542710296e-08</v>
+        <v>7.739212542710288e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.078409820905906e-08</v>
+        <v>8.078409820905901e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.686301500748656e-08</v>
+        <v>8.686301500748649e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.047883710753138e-08</v>
+        <v>8.047883710753133e-08</v>
       </c>
       <c r="L9" t="n">
         <v>1.080080047225536e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>8.278025219563178e-08</v>
+        <v>8.27802521956317e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>7.909441323685517e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.048694774807505e-08</v>
+        <v>8.048694774807506e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.269118557976767e-08</v>
+        <v>8.269118557976761e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.908644823953324e-08</v>
+        <v>7.908644823953321e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.726323969630943e-08</v>
+        <v>7.726323969630939e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.911522052459672e-08</v>
+        <v>7.91152205245967e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.873940407097327e-08</v>
+        <v>7.873940407097326e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.023590202565352e-08</v>
+        <v>8.023590202565363e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.549508202229717e-08</v>
+        <v>8.549508202229715e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.393041811071341e-08</v>
+        <v>8.393041811071338e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.376420157478672e-08</v>
+        <v>9.376420157478664e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.350139293401241e-08</v>
+        <v>8.350139293401236e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.620482371012731e-08</v>
+        <v>7.620482371012723e-08</v>
       </c>
       <c r="AA9" t="n">
         <v>8.018010993102347e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.42844867070782e-08</v>
+        <v>8.428448670707814e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,43 +4026,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.592077278221432e-08</v>
+        <v>1.59207727822143e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.510640466867518e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.602554462340782e-08</v>
+        <v>1.602554462340783e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.593906745109854e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.61718921456688e-08</v>
+        <v>1.617189214566881e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758413597089218e-08</v>
+        <v>1.758413597089217e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.593762540154885e-08</v>
+        <v>1.593762540154886e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.614097097350832e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.660513122223515e-08</v>
+        <v>1.660513122223513e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.622796928381159e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.804761886312324e-08</v>
+        <v>1.804761886312325e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.62691190963933e-08</v>
+        <v>1.626911909639328e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.591153936657832e-08</v>
+        <v>1.591153936657831e-08</v>
       </c>
       <c r="O2" t="n">
         <v>2.579285057932273e-08</v>
@@ -4074,16 +4074,16 @@
         <v>1.605801914537146e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.599950620596176e-08</v>
+        <v>1.599950620596173e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.609181493031778e-08</v>
+        <v>1.609181493031779e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.609017033146748e-08</v>
+        <v>1.609017033146747e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.256578047649931e-08</v>
+        <v>2.256578047649928e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.600880888006341e-08</v>
@@ -4092,19 +4092,19 @@
         <v>2.336543448705333e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.751733487485596e-08</v>
+        <v>1.751733487485595e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.675182841151897e-08</v>
+        <v>1.675182841151895e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.678975445861005e-08</v>
+        <v>2.678975445861003e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.618690366005232e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.644145488793933e-08</v>
+        <v>1.644145488793932e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.288894445125767e-08</v>
+        <v>1.288894445125766e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.165577465843937e-08</v>
+        <v>1.165577465843936e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.36425394937553e-08</v>
+        <v>1.364253949375523e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.301446027472439e-08</v>
+        <v>1.301446027472437e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.469099093639961e-08</v>
+        <v>1.469099093639958e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.469472941647969e-08</v>
+        <v>2.469472941647968e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.301906308377904e-08</v>
+        <v>1.301906308377902e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.447096414531686e-08</v>
+        <v>1.447096414531683e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.775451876845456e-08</v>
+        <v>1.775451876845452e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.50780712038013e-08</v>
+        <v>1.507807120380127e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.803123156832046e-08</v>
+        <v>2.803123156832045e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.562548058598478e-08</v>
+        <v>1.562548058598476e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.282758782721868e-08</v>
+        <v>1.282758782721865e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.969532070444958e-08</v>
+        <v>2.969532070444956e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.385973897737474e-08</v>
+        <v>1.385973897737472e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.38711674747415e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.346108461742205e-08</v>
+        <v>1.346108461742203e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.410557704990405e-08</v>
+        <v>1.410557704990403e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.410812875519906e-08</v>
+        <v>1.410812875519907e-08</v>
       </c>
       <c r="U3" t="n">
         <v>2.556674497478911e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.350898784617938e-08</v>
+        <v>1.35089878461794e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.704923004738949e-08</v>
+        <v>2.704923004738948e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.428754833647599e-08</v>
+        <v>2.428754833647597e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.882965855096902e-08</v>
+        <v>1.88296585509689e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.204334204628857e-08</v>
+        <v>3.204334204628853e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.479325783652315e-08</v>
+        <v>1.479325783652312e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.669084099516258e-08</v>
+        <v>1.669084099516256e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.976823410824618e-08</v>
+        <v>4.976823410824623e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.998338217767077e-08</v>
+        <v>4.99833821776708e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.09516802519548e-08</v>
+        <v>5.095168025195482e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.99748808092567e-08</v>
+        <v>4.997488080925675e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.260474283907911e-08</v>
+        <v>5.260474283907917e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.855668650923358e-08</v>
+        <v>6.855668650923357e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.99585921962176e-08</v>
+        <v>4.995859219621763e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.225547397508443e-08</v>
+        <v>5.225547397508446e-08</v>
       </c>
       <c r="J4" t="n">
         <v>5.744729743753872e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.323815991115988e-08</v>
+        <v>5.323815991115992e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.379193898964766e-08</v>
+        <v>7.379193898964776e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.414530141628376e-08</v>
+        <v>5.414530141628378e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>4.96639384310563e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.082803761974378e-08</v>
+        <v>5.08280376197438e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.131393916700177e-08</v>
+        <v>5.13139391670018e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.131849491655242e-08</v>
+        <v>5.131849491655246e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.065756434863787e-08</v>
+        <v>5.065756434863788e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.170023385435018e-08</v>
+        <v>5.17002338543502e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.168165735378298e-08</v>
+        <v>5.168165735378303e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.324340163517266e-08</v>
+        <v>5.324340163517271e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.041518192742679e-08</v>
+        <v>5.04151819274267e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.36124316232587e-08</v>
+        <v>5.361243162325872e-08</v>
       </c>
       <c r="X4" t="n">
         <v>6.7802137399482e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.912207310623651e-08</v>
+        <v>5.912207310623654e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.229682328344876e-08</v>
+        <v>5.22968232834488e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.277430479967867e-08</v>
+        <v>5.277430479967869e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.575578866178805e-08</v>
+        <v>5.57557886617881e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,22 +4290,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.384149031724511e-08</v>
+        <v>7.384149031724529e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.024800911702435e-08</v>
+        <v>8.024800911702432e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779559060603338e-08</v>
+        <v>9.779559060603244e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.487719794561252e-08</v>
+        <v>7.487719794561259e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.290858745041788e-07</v>
+        <v>1.290858745041784e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.720880126066357e-07</v>
+        <v>3.720880126066348e-07</v>
       </c>
       <c r="H5" t="n">
         <v>8.230795395989735e-08</v>
@@ -4314,52 +4314,52 @@
         <v>1.232500692667601e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.008064840496965e-07</v>
+        <v>2.008064840496959e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.334768045649195e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>4.795041695603107e-07</v>
+        <v>4.795041695603102e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.564608559871409e-07</v>
+        <v>1.564608559871407e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>7.435100066972496e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>9.048333166577878e-08</v>
+        <v>9.048333166577806e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.814249209474334e-08</v>
+        <v>9.81424920947419e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.026538587717459e-07</v>
+        <v>1.026538587717458e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>9.486484065066286e-08</v>
+        <v>9.486484065066274e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.058854349778471e-07</v>
+        <v>1.05885434977847e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.129619412443565e-07</v>
+        <v>1.129619412443566e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.324756305963984e-07</v>
+        <v>1.324756305963982e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.679366601014924e-08</v>
+        <v>8.679366601014959e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.440746916593132e-07</v>
+        <v>1.440746916593133e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>3.948015063532184e-07</v>
+        <v>3.948015063532172e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.447549835992463e-07</v>
+        <v>2.447549835992451e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>1.107808360772442e-07</v>
@@ -4368,7 +4368,7 @@
         <v>1.295605714973449e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.94280598155323e-07</v>
+        <v>1.942805981553227e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.833839617379957e-08</v>
+        <v>4.833839617379955e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.855354424322413e-08</v>
+        <v>4.855354424322414e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.671130879018621e-08</v>
+        <v>5.671130879018629e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.573450934748823e-08</v>
+        <v>5.573450934748821e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.117490490463247e-08</v>
+        <v>5.117490490463244e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.712684857478697e-08</v>
+        <v>6.712684857478684e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.571822073444891e-08</v>
+        <v>5.571822073444912e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.082563604063775e-08</v>
+        <v>5.082563604063777e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.320692597577017e-08</v>
+        <v>6.320692597577015e-08</v>
       </c>
       <c r="K6" t="n">
         <v>5.899778844939141e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.236210105520114e-08</v>
+        <v>7.236210105520112e-08</v>
       </c>
       <c r="M6" t="n">
         <v>5.271546348183711e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>4.824467428283744e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.943390451780937e-08</v>
+        <v>4.943390451780941e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.720883941197237e-08</v>
+        <v>5.720883941197241e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.707812345478384e-08</v>
+        <v>5.707812345478391e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.641719288686934e-08</v>
+        <v>5.641719288686938e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.027039591990352e-08</v>
+        <v>5.027039591990349e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.744128589201457e-08</v>
+        <v>5.744128589201447e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.903634681288702e-08</v>
+        <v>5.903634681288703e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.898534399298018e-08</v>
+        <v>4.898534399298e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.234734662670741e-08</v>
+        <v>5.234734662670745e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.637229946503532e-08</v>
+        <v>6.637229946503528e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.783222779210334e-08</v>
+        <v>5.783222779210332e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.086698534900209e-08</v>
+        <v>5.086698534900211e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.853393333791001e-08</v>
+        <v>5.853393333791013e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.43574879315437e-08</v>
+        <v>5.435748793154375e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4469,82 +4469,82 @@
         <v>5.488929382199109e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.510444189141567e-08</v>
+        <v>5.51044418914157e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.60727399656997e-08</v>
+        <v>5.607273996569967e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.50959405230016e-08</v>
+        <v>5.509594052300162e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.772580255282403e-08</v>
+        <v>5.772580255282407e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.367774622297846e-08</v>
+        <v>7.36777462229784e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.50796519099625e-08</v>
+        <v>5.507965190996248e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.737653368882931e-08</v>
+        <v>5.737653368882934e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.256835715128364e-08</v>
+        <v>6.256835715128356e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.835921962490481e-08</v>
+        <v>5.83592196249048e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.891299870339267e-08</v>
+        <v>7.89129987033927e-08</v>
       </c>
       <c r="M7" t="n">
         <v>5.926636113002867e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>5.478499814480123e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.594783545415697e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.643373700141496e-08</v>
+        <v>5.643373700141492e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>5.643955463029734e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.577862406238277e-08</v>
+        <v>5.577862406238274e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.682129356809507e-08</v>
+        <v>5.682129356809506e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.680271706752791e-08</v>
+        <v>5.680271706752793e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.839086985108967e-08</v>
+        <v>5.839086985108968e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.553624164117171e-08</v>
+        <v>5.553624164117158e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.873349133700361e-08</v>
+        <v>5.873349133700363e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.292319711322686e-08</v>
+        <v>7.292319711322682e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.427644945946425e-08</v>
+        <v>6.42764494594641e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.741788299719365e-08</v>
+        <v>5.741788299719366e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.789536451342357e-08</v>
+        <v>5.789536451342356e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.087684837553298e-08</v>
+        <v>6.087684837553304e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4557,52 +4557,52 @@
         <v>6.346377400328285e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.512722853516421e-08</v>
+        <v>7.512722853516423e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.609552660944825e-08</v>
+        <v>7.609552660944826e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>6.902284167929879e-08</v>
+        <v>6.902284167929877e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.808379508134799e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.607441379056549e-08</v>
+        <v>9.607441379056537e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.51024385537111e-08</v>
+        <v>7.510243855371102e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.739932033257786e-08</v>
+        <v>7.739932033257783e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.259114379503225e-08</v>
+        <v>8.259114379503217e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.838200626865335e-08</v>
+        <v>7.838200626865334e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.893578534714117e-08</v>
+        <v>9.893578534714119e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.928914777377641e-08</v>
+        <v>7.928914777377637e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>6.59334320197047e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>6.953628040368335e-08</v>
+        <v>6.953628040368332e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.942438559476554e-08</v>
+        <v>6.942438559476555e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.276418129654461e-08</v>
+        <v>6.276418129654466e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.580141070613134e-08</v>
+        <v>7.580141070613132e-08</v>
       </c>
       <c r="S8" t="n">
         <v>7.684408021184362e-08</v>
@@ -4611,28 +4611,28 @@
         <v>7.68255037112765e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.282842333475815e-08</v>
+        <v>7.28284233347581e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.242520722715531e-08</v>
+        <v>7.242520722715535e-08</v>
       </c>
       <c r="W8" t="n">
         <v>7.875852790012065e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>8.029708381455676e-08</v>
+        <v>8.029708381455668e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.56745410698847e-08</v>
+        <v>9.567454106988446e-08</v>
       </c>
       <c r="Z8" t="n">
         <v>6.577970500799817e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.791815115717214e-08</v>
+        <v>7.791815115717207e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.285834841110718e-08</v>
+        <v>9.285834841110711e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4645,82 +4645,82 @@
         <v>6.825033416826035e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.477213632991911e-08</v>
+        <v>7.477213632991906e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.57404344042031e-08</v>
+        <v>7.574043440420313e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.330809225511981e-08</v>
+        <v>7.330809225511975e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.285492561481611e-08</v>
+        <v>6.285492561481613e-08</v>
       </c>
       <c r="G9" t="n">
         <v>9.33454501956601e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.474734634846589e-08</v>
+        <v>7.474734634846587e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.704422812733272e-08</v>
+        <v>7.704422812733269e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.223605158978703e-08</v>
+        <v>8.223605158978692e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.802691406340818e-08</v>
+        <v>7.802691406340817e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.858069314189603e-08</v>
+        <v>9.858069314189599e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.893405556853209e-08</v>
+        <v>7.893405556853201e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.435100066972498e-08</v>
+        <v>7.445269258330459e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.770682137409294e-08</v>
+        <v>7.770682137409288e-08</v>
       </c>
       <c r="P9" t="n">
         <v>7.864726642741816e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.610725860297908e-08</v>
+        <v>7.610725860297907e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.544631850088609e-08</v>
+        <v>7.544631850088607e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.648898800659843e-08</v>
+        <v>7.648898800659844e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.64704115060313e-08</v>
+        <v>7.647041150603136e-08</v>
       </c>
       <c r="U9" t="n">
         <v>7.806547242690381e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.248169173333167e-08</v>
+        <v>8.248169173333152e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.840118577550698e-08</v>
+        <v>7.840118577550701e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.259089155173036e-08</v>
+        <v>9.259089155173026e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.39441438979676e-08</v>
+        <v>8.394414389796771e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.328322961355969e-08</v>
+        <v>7.328322961355968e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.756305895192692e-08</v>
+        <v>7.756305895192693e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.054454281403637e-08</v>
+        <v>8.054454281403641e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>5.186821142897803e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>5.48577325318828e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.011976381650166e-08</v>
@@ -5274,7 +5274,7 @@
         <v>5.750749333673176e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>5.326295750191548e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.594802012304349e-08</v>
@@ -5362,7 +5362,7 @@
         <v>5.709411361732215e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>6.008363472022692e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.534432794384258e-08</v>
@@ -5450,7 +5450,7 @@
         <v>7.799037091195467e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>7.175378050572232e-08</v>
       </c>
       <c r="O8" t="n">
         <v>6.955122734182228e-08</v>
@@ -5538,7 +5538,7 @@
         <v>7.928706374350374e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>8.227658484640851e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.983108853198728e-08</v>
@@ -5958,7 +5958,7 @@
         <v>4.911590607530825e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>5.159740459193632e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.257456072119152e-08</v>
@@ -6134,7 +6134,7 @@
         <v>5.406451638548176e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>5.019565715147587e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.766075537893885e-08</v>
@@ -6222,7 +6222,7 @@
         <v>5.377596443473881e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>5.625746295136686e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.723336378063752e-08</v>
@@ -6261,7 +6261,7 @@
         <v>5.656310517352658e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.498917106386058e-08</v>
+        <v>5.498917106386057e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>5.311973519593004e-08</v>
@@ -6310,7 +6310,7 @@
         <v>7.26483578699972e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>6.680467704908084e-08</v>
       </c>
       <c r="O8" t="n">
         <v>7.006966474643224e-08</v>
@@ -6398,7 +6398,7 @@
         <v>7.148322330011135e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>7.396472181673943e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.684283509403926e-08</v>
@@ -6428,7 +6428,7 @@
         <v>7.531410149540816e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.488919550393698e-08</v>
+        <v>7.488919550393699e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>7.21044916170734e-08</v>
@@ -6818,7 +6818,7 @@
         <v>4.918341901117808e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.84161393079848e-08</v>
+        <v>4.999959387416985e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.305917557176315e-08</v>
@@ -6906,7 +6906,7 @@
         <v>7.533357838591336e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.841613930798478e-08</v>
+        <v>8.84161393079848e-08</v>
       </c>
       <c r="O5" t="n">
         <v>1.32376510936813e-07</v>
@@ -6994,7 +6994,7 @@
         <v>5.41750548316253e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.841613930798478e-08</v>
+        <v>4.8718733718554e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.180346955695409e-08</v>
@@ -7082,7 +7082,7 @@
         <v>5.385833415765402e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>8.841613930798478e-08</v>
+        <v>5.467450902064578e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.773282881830237e-08</v>
@@ -7170,7 +7170,7 @@
         <v>7.267613134208089e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.841613930798478e-08</v>
+        <v>6.518027642031464e-08</v>
       </c>
       <c r="O8" t="n">
         <v>7.052407607471924e-08</v>
@@ -7258,7 +7258,7 @@
         <v>7.022112444938785e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.841613930798478e-08</v>
+        <v>7.103729931237956e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.590209669972507e-08</v>
@@ -7678,7 +7678,7 @@
         <v>5.728412246081761e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>6.029424804616912e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.269917082522317e-08</v>
@@ -7854,7 +7854,7 @@
         <v>5.568995478884196e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>5.8710916889016e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.94388424764489e-08</v>
@@ -7942,7 +7942,7 @@
         <v>6.302759393983631e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>6.603771952518782e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.844129927242065e-08</v>
@@ -8030,7 +8030,7 @@
         <v>8.516152544781127e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>7.834608179461366e-08</v>
       </c>
       <c r="O8" t="n">
         <v>7.345115631403691e-08</v>
@@ -8118,7 +8118,7 @@
         <v>9.025511411743627e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>9.326523970278772e-08</v>
       </c>
       <c r="O9" t="n">
         <v>8.83781362582579e-08</v>
@@ -8538,7 +8538,7 @@
         <v>5.070754068375027e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>5.054759588156707e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.001318195202548e-08</v>
@@ -8714,7 +8714,7 @@
         <v>4.923448961371683e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>4.907688152242205e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.684039708006111e-08</v>
@@ -8802,7 +8802,7 @@
         <v>5.574611586880949e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>5.558617106662632e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.505049923763128e-08</v>
@@ -8890,7 +8890,7 @@
         <v>7.579187614241637e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>6.678216830956927e-08</v>
       </c>
       <c r="O8" t="n">
         <v>6.867974610174763e-08</v>
@@ -8978,7 +8978,7 @@
         <v>7.684638085384071e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>7.668643605165749e-08</v>
       </c>
       <c r="O9" t="n">
         <v>7.833738788649073e-08</v>

--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.777760292998748e-08</v>
+        <v>1.777760292998752e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.697928116501753e-08</v>
+        <v>1.697928116501754e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.833291740186988e-08</v>
+        <v>1.83329174018699e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76258558591763e-08</v>
+        <v>1.762585585917631e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.825087085375678e-08</v>
+        <v>1.82508708537568e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.062882993288248e-08</v>
+        <v>2.062882993288251e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.807066051816932e-08</v>
+        <v>1.807066051816934e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.860127654901627e-08</v>
+        <v>1.860127654901628e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.886405297174167e-08</v>
+        <v>1.88640529717417e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.939486335819077e-08</v>
+        <v>1.939486335819079e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.174876416612552e-08</v>
+        <v>2.174876416612551e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.854622780514137e-08</v>
+        <v>1.854622780514138e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.881467392046555e-08</v>
+        <v>1.881467392046556e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.881425703101803e-08</v>
+        <v>2.881425703101804e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.786640433414131e-08</v>
+        <v>1.786640433414132e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.796795360197904e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.802113209117414e-08</v>
+        <v>1.802113209117415e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78887123427196e-08</v>
+        <v>1.788871234271962e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.840996789987221e-08</v>
+        <v>1.840996789987223e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.52647126076956e-08</v>
+        <v>2.526471260769566e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.776481011466894e-08</v>
+        <v>1.776481011466895e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.588180570904055e-08</v>
+        <v>2.588180570904054e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.84598823396305e-08</v>
+        <v>1.845988233963052e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.786389546733571e-08</v>
+        <v>1.786389546733572e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.887489450297037e-08</v>
+        <v>2.887489450297038e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.863663995279268e-08</v>
+        <v>1.86366399527927e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.829684955710514e-08</v>
+        <v>1.829684955710515e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.540744814826009e-08</v>
+        <v>1.550887322961117e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.368118818925492e-08</v>
+        <v>1.376408449469457e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.939673325727312e-08</v>
+        <v>1.964036555816279e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.432447919144536e-08</v>
+        <v>1.438729137300017e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.881751721686176e-08</v>
+        <v>1.904128337718923e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.570781563268802e-08</v>
+        <v>3.652256309917166e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.753057170874663e-08</v>
+        <v>1.770863738723692e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.132343384213253e-08</v>
+        <v>2.163575021682226e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.315334367893462e-08</v>
+        <v>2.352759474418334e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.699223122181022e-08</v>
+        <v>2.750484171329788e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.375099463345161e-08</v>
+        <v>4.485206813896858e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.11747969770157e-08</v>
+        <v>2.148375845207904e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.282897198213923e-08</v>
+        <v>2.319350557864446e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.492915835980493e-08</v>
+        <v>3.509031171258708e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.603963590011563e-08</v>
+        <v>1.616306953853734e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.677979781139349e-08</v>
+        <v>1.693043114117754e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.717066522852699e-08</v>
+        <v>1.733567381480116e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.620142767456693e-08</v>
+        <v>1.633095498213193e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99498988858574e-08</v>
+        <v>2.021324845495278e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.013619581359911e-08</v>
+        <v>3.034601947959841e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53129735401997e-08</v>
+        <v>1.541113755432912e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.021408252663519e-08</v>
+        <v>3.038138604852415e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.030032706986299e-08</v>
+        <v>2.057595974623026e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.603204412566962e-08</v>
+        <v>1.615598550983505e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.495554372161095e-08</v>
+        <v>3.51132599519932e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.155099524754312e-08</v>
+        <v>2.186976788679702e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.924813081417069e-08</v>
+        <v>1.948649279110233e-08</v>
       </c>
     </row>
     <row r="4">
@@ -768,46 +768,46 @@
         <v>5.28252315329121e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.997196876484644e-08</v>
+        <v>5.99719687648464e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.19853833757429e-08</v>
+        <v>5.198538337574288e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.904521526063211e-08</v>
+        <v>5.904521526063209e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.590535697457851e-08</v>
+        <v>8.590535697457859e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.700965661932165e-08</v>
+        <v>5.700965661932164e-08</v>
       </c>
       <c r="I4" t="n">
         <v>6.300320878317177e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.590248385873116e-08</v>
+        <v>6.590248385873118e-08</v>
       </c>
       <c r="K4" t="n">
         <v>7.196713686076625e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.855552933425913e-08</v>
+        <v>9.855552933425918e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>6.282999258150731e-08</v>
+        <v>6.282999258150725e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.541363026133222e-08</v>
+        <v>6.541363026133224e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.640446452723438e-08</v>
+        <v>5.640446452723431e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.470248905823833e-08</v>
+        <v>5.470248905823826e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.584953475343639e-08</v>
+        <v>5.584953475343634e-08</v>
       </c>
       <c r="R4" t="n">
         <v>5.64502102522089e-08</v>
@@ -816,25 +816,25 @@
         <v>5.495446827732106e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>6.084228958476292e-08</v>
+        <v>6.084228958476293e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.815354941798632e-08</v>
+        <v>5.815354941798627e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.308805384887102e-08</v>
+        <v>5.308805384887103e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.662472008028071e-08</v>
+        <v>5.662472008028067e-08</v>
       </c>
       <c r="X4" t="n">
         <v>6.140609614360958e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.427519412268541e-08</v>
+        <v>5.427519412268537e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.623587115837466e-08</v>
+        <v>5.623587115837464e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>6.340265469679574e-08</v>
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.160248879449678e-07</v>
+        <v>1.160248879449657e-07</v>
       </c>
       <c r="C5" t="n">
         <v>1.051893901112536e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.57780239267764e-07</v>
+        <v>2.577802392677625e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.154169478027623e-08</v>
+        <v>8.154169478027622e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.428940718496277e-07</v>
+        <v>2.428940718496276e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>7.354705526349978e-07</v>
+        <v>7.354705526350005e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.014414646874756e-07</v>
+        <v>2.014414646874755e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>3.256032188998217e-07</v>
+        <v>3.256032188998221e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>3.582412368316834e-07</v>
+        <v>3.582412368316836e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.090468569466533e-07</v>
+        <v>5.090468569466531e-07</v>
       </c>
       <c r="L5" t="n">
         <v>1.020025965946092e-06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.224262860278252e-07</v>
+        <v>3.224262860278242e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.637490207634528e-07</v>
+        <v>3.637490207634524e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.644485650237887e-07</v>
+        <v>1.644485650237874e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.352778310500248e-07</v>
+        <v>1.352778310500246e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.675296857752115e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.863599143551124e-07</v>
+        <v>1.863599143551123e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.418846248683629e-07</v>
+        <v>1.418846248683635e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.772396815897163e-07</v>
+        <v>2.772396815897162e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.145031807900991e-07</v>
+        <v>2.145031807900989e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>1.107630047960236e-07</v>
+        <v>1.107630047960237e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.798739443571468e-07</v>
+        <v>1.798739443571466e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.851381853084972e-07</v>
+        <v>2.851381853084968e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.408373504428537e-07</v>
+        <v>1.408373504428533e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.659154330319847e-07</v>
+        <v>1.659154330319846e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.188901091374535e-07</v>
+        <v>3.18890109137454e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.62529910112338e-07</v>
+        <v>2.625299101123382e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.21129887882083e-08</v>
+        <v>5.211298878820829e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>6.076702147383658e-08</v>
+        <v>6.076702147383661e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>6.791375870577096e-08</v>
+        <v>6.791375870577095e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.992717331666737e-08</v>
+        <v>5.992717331666741e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.745876770118342e-08</v>
+        <v>5.74587677011834e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.384714691550311e-08</v>
+        <v>9.384714691550326e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>6.495144656024619e-08</v>
+        <v>6.49514465602462e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>6.141676122372315e-08</v>
+        <v>6.141676122372311e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.43160362992825e-08</v>
+        <v>6.431603629928251e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.990892680169072e-08</v>
+        <v>7.99089268016908e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.064973192751837e-07</v>
+        <v>1.064973192751838e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.077178252243185e-08</v>
+        <v>7.077178252243176e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>6.384966001866837e-08</v>
+        <v>6.384966001866829e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.484046460676524e-08</v>
+        <v>5.484046460676521e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.285680318539479e-08</v>
+        <v>6.285680318539483e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.379132469436091e-08</v>
+        <v>6.379132469436093e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>6.439200019313338e-08</v>
+        <v>6.439200019313341e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.336802071787241e-08</v>
+        <v>5.336802071787235e-08</v>
       </c>
       <c r="T6" t="n">
         <v>5.925584202531426e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.696605798938567e-08</v>
+        <v>5.696605798938568e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>6.102984378979551e-08</v>
+        <v>6.102984378979555e-08</v>
       </c>
       <c r="W6" t="n">
         <v>6.477899757290672e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.934788608453416e-08</v>
+        <v>6.934788608453417e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.320839124417301e-08</v>
+        <v>5.320839124417305e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.464942359892601e-08</v>
+        <v>5.464942359892598e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.134444463772024e-08</v>
+        <v>7.134444463772023e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.819793101106311e-08</v>
+        <v>5.819793101106312e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,79 +1026,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.063743997872017e-08</v>
+        <v>6.063743997872016e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.976323516397532e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.690997239590968e-08</v>
+        <v>6.69099723959096e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.892338700680611e-08</v>
+        <v>5.892338700680609e-08</v>
       </c>
       <c r="F7" t="n">
         <v>6.598321889169527e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>9.284336060564187e-08</v>
+        <v>9.284336060564194e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>6.394766025038485e-08</v>
+        <v>6.394766025038483e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.994121241423496e-08</v>
+        <v>6.994121241423497e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>7.284048748979437e-08</v>
+        <v>7.284048748979438e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.890514049182944e-08</v>
+        <v>7.890514049182949e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.054935329653224e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>6.976799621257051e-08</v>
+        <v>6.976799621257044e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>7.23516338923955e-08</v>
+        <v>7.235163389239547e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>6.334101238576154e-08</v>
+        <v>6.334101238576142e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.163903691676546e-08</v>
+        <v>6.163903691676538e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.278753838449954e-08</v>
+        <v>6.278753838449959e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>6.338821388327214e-08</v>
+        <v>6.338821388327209e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>6.189247190838424e-08</v>
+        <v>6.189247190838423e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.778029321582616e-08</v>
+        <v>6.778029321582611e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.548037540003444e-08</v>
+        <v>6.54803754000345e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>6.002605747993423e-08</v>
+        <v>6.002605747993425e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.356272371134389e-08</v>
+        <v>6.356272371134387e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.834409977467284e-08</v>
+        <v>6.83440997746728e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.161215388459663e-08</v>
+        <v>6.161215388459659e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.317387478943787e-08</v>
+        <v>6.317387478943783e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>7.034065832785894e-08</v>
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.128365034792817e-08</v>
+        <v>7.128365034792815e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.498373179626769e-08</v>
+        <v>8.498373179626775e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>9.213046902820201e-08</v>
+        <v>9.213046902820208e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.638350611844546e-08</v>
+        <v>7.638350611844551e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.889993272689207e-08</v>
+        <v>7.889993272689213e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.210859304372871e-07</v>
+        <v>1.210859304372873e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.916815688267722e-08</v>
+        <v>8.916815688267737e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>9.516170904652739e-08</v>
+        <v>9.516170904652753e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.806098412208674e-08</v>
+        <v>9.806098412208684e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.041256371241219e-07</v>
+        <v>1.04125637124122e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>1.307140295976147e-07</v>
+        <v>1.307140295976148e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>9.498849284486121e-08</v>
+        <v>9.498849284486125e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>8.627462044522447e-08</v>
+        <v>8.627462044522455e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>8.037010857519501e-08</v>
+        <v>8.037010857519497e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.790710742520204e-08</v>
+        <v>7.790710742520203e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.056956886080485e-08</v>
+        <v>7.056956886080488e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.860871051556451e-08</v>
+        <v>8.860871051556463e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.71129685406767e-08</v>
+        <v>8.711296854067672e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>9.300078984811854e-08</v>
+        <v>9.300078984811858e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>8.359076596462163e-08</v>
+        <v>8.359076596462176e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>8.125576417645823e-08</v>
+        <v>8.125576417645838e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.878608460735931e-08</v>
+        <v>8.878608460735934e-08</v>
       </c>
       <c r="X8" t="n">
         <v>7.74618925460859e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.013120266829454e-07</v>
+        <v>1.013120266829455e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.354936030842796e-08</v>
+        <v>7.3549360308428e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.556115496015132e-08</v>
+        <v>9.556115496015139e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.071179435161942e-07</v>
+        <v>1.071179435161943e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.760503920236649e-08</v>
+        <v>8.760503920236657e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>9.75880944918477e-08</v>
+        <v>9.758809449184776e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.04734831723782e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>9.4242444821764e-08</v>
+        <v>9.424244482176405e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>7.877911376584233e-08</v>
+        <v>7.877911376584236e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.306682327170964e-07</v>
+        <v>1.306682327170965e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.017725195782572e-07</v>
+        <v>1.017725195782573e-07</v>
       </c>
       <c r="I9" t="n">
         <v>1.077660717421073e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.106653468176667e-07</v>
+        <v>1.106653468176668e-07</v>
       </c>
       <c r="K9" t="n">
         <v>1.167299998197018e-07</v>
@@ -1238,22 +1238,22 @@
         <v>1.075928555404428e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.101764932202677e-07</v>
+        <v>1.101764932202679e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.047654262883863e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.038459727956834e-07</v>
+        <v>1.038459727956835e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.006124104959541e-07</v>
+        <v>1.006124104959542e-07</v>
       </c>
       <c r="R9" t="n">
         <v>1.012130732111445e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>9.971733123625662e-08</v>
+        <v>9.971733123625667e-08</v>
       </c>
       <c r="T9" t="n">
         <v>1.056051525436986e-07</v>
@@ -1262,25 +1262,25 @@
         <v>1.033153685077699e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>1.103799767304189e-07</v>
+        <v>1.10379976730419e-07</v>
       </c>
       <c r="W9" t="n">
         <v>1.013875830392163e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.061689591025452e-07</v>
+        <v>1.061689591025453e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.943701321246898e-08</v>
+        <v>9.943701321246903e-08</v>
       </c>
       <c r="Z9" t="n">
         <v>9.445277681591905e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.081655176557312e-07</v>
+        <v>1.081655176557313e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.044982455281144e-07</v>
+        <v>1.044982455281145e-07</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.480204094928746e-08</v>
+        <v>1.480204094928755e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.401762742297641e-08</v>
@@ -1455,13 +1455,13 @@
         <v>1.482808175944911e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.482723712584341e-08</v>
+        <v>1.482723712584349e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.494878295140336e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49792717670154e-08</v>
+        <v>1.497927176701546e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.484517774452389e-08</v>
@@ -1470,16 +1470,16 @@
         <v>1.488649669047692e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.495483647480489e-08</v>
+        <v>1.495483647480488e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.491892222730485e-08</v>
+        <v>1.491892222730476e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.505079718821335e-08</v>
+        <v>1.505079718821334e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.481386156400576e-08</v>
+        <v>1.481386156400575e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.484536233614822e-08</v>
@@ -1488,43 +1488,43 @@
         <v>2.424826369928913e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.491635003420392e-08</v>
+        <v>1.491635003420391e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.484392303820307e-08</v>
+        <v>1.484392303820306e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51416318926115e-08</v>
+        <v>1.514163189261149e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.494249700607935e-08</v>
+        <v>1.494249700607941e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.48698469243444e-08</v>
+        <v>1.486984692434447e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.123743756496554e-08</v>
+        <v>2.12374375649656e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.511497477602927e-08</v>
+        <v>1.511497477602926e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.250259035524714e-08</v>
+        <v>2.250259035524717e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.538341873353302e-08</v>
+        <v>1.538341873353312e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.508823900029773e-08</v>
+        <v>1.508823900029774e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.551278824734141e-08</v>
+        <v>2.551278824734151e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.507908871130573e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.479063966899347e-08</v>
+        <v>1.47906396689935e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.190370028386849e-08</v>
+        <v>1.195650362990347e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.094462304375464e-08</v>
+        <v>1.101324644512526e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.209401814914238e-08</v>
+        <v>1.215384127773556e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.20777965994397e-08</v>
+        <v>1.213629616094092e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.295724833077349e-08</v>
+        <v>1.304803449082604e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.316081028466353e-08</v>
+        <v>1.325796524784732e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.221992046390603e-08</v>
+        <v>1.22843388228937e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.251280762509685e-08</v>
+        <v>1.258755433487311e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.299182833521149e-08</v>
+        <v>1.308323575628666e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.273769869778459e-08</v>
+        <v>1.282051032593598e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.367168832468179e-08</v>
+        <v>1.378724448883247e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.222324388072823e-08</v>
+        <v>1.228909711330171e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22169944487842e-08</v>
+        <v>1.228104814257374e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.770368670888216e-08</v>
+        <v>2.776597506070124e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.271431923488172e-08</v>
+        <v>1.279559514169574e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.220461601585518e-08</v>
+        <v>1.22683673244556e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.434209159879455e-08</v>
+        <v>1.44819828858691e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.290064090795443e-08</v>
+        <v>1.29887513777024e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.239379979371334e-08</v>
+        <v>1.246425644701733e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.310811973804398e-08</v>
+        <v>2.318732007529167e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41194696407566e-08</v>
+        <v>1.425051290855861e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.792630078116228e-08</v>
+        <v>2.813133828449465e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.605075257081359e-08</v>
+        <v>1.625142985889164e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.395129887298218e-08</v>
+        <v>1.407659878026396e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.005704295094464e-08</v>
+        <v>3.013172236686878e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.388517620250221e-08</v>
+        <v>1.400808909087129e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.189300051498642e-08</v>
+        <v>1.194595453132148e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,22 +1622,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.890939920001639e-08</v>
+        <v>4.89093992000164e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.959714427934369e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.920354213015663e-08</v>
+        <v>4.920354213015664e-08</v>
       </c>
       <c r="E4" t="n">
         <v>4.919400160502973e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.056691761857146e-08</v>
+        <v>5.056691761857147e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.091130281645769e-08</v>
+        <v>5.091130281645768e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.939664914611803e-08</v>
@@ -1646,61 +1646,61 @@
         <v>4.986336564831164e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.059197888746107e-08</v>
+        <v>5.059197888746105e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.02296270032661e-08</v>
+        <v>5.022962700326612e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.171921535220791e-08</v>
+        <v>5.171921535220792e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.946517340225624e-08</v>
+        <v>4.946517340225625e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.939873419343104e-08</v>
+        <v>4.939873419343107e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>4.933965035594227e-08</v>
+        <v>4.93396503559423e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.020057289892466e-08</v>
+        <v>5.020057289892468e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.938247666103092e-08</v>
+        <v>4.938247666103093e-08</v>
       </c>
       <c r="R4" t="n">
         <v>5.274523512441343e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.049591497445873e-08</v>
+        <v>5.049591497445876e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.967529888057373e-08</v>
+        <v>4.967529888057374e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.021633115729994e-08</v>
+        <v>5.021633115729992e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.214928007862405e-08</v>
+        <v>5.214928007862406e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.572299196362781e-08</v>
+        <v>5.572299196362784e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.547632872006398e-08</v>
+        <v>5.547632872006399e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.226904407606544e-08</v>
+        <v>5.226904407606542e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.989529631620938e-08</v>
+        <v>4.98952963162094e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.203878112027981e-08</v>
+        <v>5.203878112027984e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.889773938388498e-08</v>
+        <v>4.8897739383885e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.806281490216041e-08</v>
+        <v>6.806281490216037e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.204038034524045e-08</v>
+        <v>8.204038034524057e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.557821277381631e-08</v>
+        <v>7.557821277381634e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.012702340948527e-08</v>
+        <v>7.01270234094853e-08</v>
       </c>
       <c r="F5" t="n">
         <v>1.006140722720556e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>9.943012878891758e-08</v>
+        <v>9.943012878891832e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.100818443422179e-08</v>
+        <v>8.100818443422176e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.822212887752999e-08</v>
+        <v>8.822212887752997e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.73108002427181e-08</v>
+        <v>9.731080024271832e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.131522894582286e-08</v>
+        <v>9.13152289458228e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.139254118656209e-07</v>
+        <v>1.13925411865621e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.087742644684281e-08</v>
+        <v>8.08774264468428e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>7.884599896713191e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.478495559301024e-08</v>
+        <v>7.478495559301027e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.819904600473023e-08</v>
+        <v>8.819904600473019e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.74670289645539e-08</v>
+        <v>7.746702896455388e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.435309691177882e-07</v>
+        <v>1.435309691177883e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.327207810304661e-08</v>
+        <v>9.32720781030466e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.480381044337956e-08</v>
+        <v>8.480381044337959e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>8.73671300211027e-08</v>
+        <v>8.736713002110278e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.211362857910052e-07</v>
+        <v>1.211362857910051e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.895955917928828e-07</v>
+        <v>1.895955917928822e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.830334597753328e-07</v>
+        <v>1.83033459775333e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.278244678661054e-07</v>
+        <v>1.278244678661056e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.261304357683895e-08</v>
+        <v>8.261304357683898e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.255732504622025e-07</v>
+        <v>1.255732504622028e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.150309180398992e-08</v>
+        <v>7.150309180398998e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1801,79 +1801,79 @@
         <v>4.759073546030051e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.453010628128906e-08</v>
+        <v>5.453010628128907e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.788487839044075e-08</v>
+        <v>4.788487839044071e-08</v>
       </c>
       <c r="E6" t="n">
         <v>5.412696360697511e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.549987962051685e-08</v>
+        <v>5.549987962051687e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.959263907674184e-08</v>
+        <v>4.959263907674179e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.807798540640215e-08</v>
+        <v>4.807798540640213e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>4.854470190859578e-08</v>
+        <v>4.854470190859576e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.552494088940646e-08</v>
+        <v>5.552494088940647e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.891096326355023e-08</v>
+        <v>4.891096326355022e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.665217735415326e-08</v>
+        <v>5.66521773541533e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.814650966254036e-08</v>
+        <v>4.814650966254034e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.809175273778018e-08</v>
+        <v>4.809175273778016e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.442041871330687e-08</v>
+        <v>5.44204187133069e-08</v>
       </c>
       <c r="P6" t="n">
         <v>4.874324468964625e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.806381292131505e-08</v>
+        <v>4.806381292131503e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.142657138469757e-08</v>
+        <v>5.142657138469754e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.542887697640411e-08</v>
+        <v>5.542887697640407e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.835663514085787e-08</v>
+        <v>4.835663514085784e-08</v>
       </c>
       <c r="U6" t="n">
         <v>5.502238692696527e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.08306163389082e-08</v>
+        <v>5.083061633890817e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.458040865431952e-08</v>
+        <v>5.458040865431914e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.040929072200938e-08</v>
+        <v>6.040929072200934e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.09607852649851e-08</v>
+        <v>5.096078526498507e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.857663257649352e-08</v>
+        <v>4.857663257649348e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.69717431222252e-08</v>
+        <v>5.697174312222521e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>4.757707332856786e-08</v>
@@ -1886,46 +1886,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.361992067874849e-08</v>
+        <v>5.361992067874848e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.430766575807578e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.391406360888871e-08</v>
+        <v>5.391406360888869e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.390452308376184e-08</v>
+        <v>5.390452308376183e-08</v>
       </c>
       <c r="F7" t="n">
         <v>5.527743909730356e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.562182429518979e-08</v>
+        <v>5.562182429518977e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.41071706248501e-08</v>
+        <v>5.410717062485011e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.457388712704373e-08</v>
+        <v>5.457388712704372e-08</v>
       </c>
       <c r="J7" t="n">
         <v>5.530250036619315e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.49401484819982e-08</v>
+        <v>5.494014848199819e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.642973683093998e-08</v>
+        <v>5.642973683093997e-08</v>
       </c>
       <c r="M7" t="n">
         <v>5.417569488098834e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.410925567216311e-08</v>
+        <v>5.410925567216315e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.404890987952628e-08</v>
+        <v>5.404890987952627e-08</v>
       </c>
       <c r="P7" t="n">
         <v>5.490983242250868e-08</v>
@@ -1937,31 +1937,31 @@
         <v>5.74557566031455e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.520643645319084e-08</v>
+        <v>5.520643645319083e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.438582035930581e-08</v>
+        <v>5.438582035930582e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.480046326043861e-08</v>
+        <v>5.48004632604386e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.685980155735615e-08</v>
+        <v>5.685980155735613e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.04335134423599e-08</v>
+        <v>6.043351344235988e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.018685019879609e-08</v>
+        <v>6.018685019879607e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>5.685265932251748e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.460581779494147e-08</v>
+        <v>5.460581779494148e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.674930259901192e-08</v>
+        <v>5.674930259901194e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>5.360826086261708e-08</v>
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.175275159466828e-08</v>
+        <v>6.17527515946683e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.321795866629966e-08</v>
+        <v>7.321795866629963e-08</v>
       </c>
       <c r="D8" t="n">
         <v>7.282435651711257e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>6.707613539615674e-08</v>
+        <v>6.70761353961568e-08</v>
       </c>
       <c r="F8" t="n">
         <v>6.508927263235975e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.676689415623254e-08</v>
+        <v>7.676689415623248e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.301746353307395e-08</v>
+        <v>7.301746353307399e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.34841800352676e-08</v>
+        <v>7.348418003526761e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.421279327441704e-08</v>
+        <v>7.421279327441706e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.385044139022202e-08</v>
+        <v>7.385044139022207e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.534002973916385e-08</v>
+        <v>7.534002973916387e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.308598778921058e-08</v>
+        <v>7.308598778921056e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.466521250581416e-08</v>
+        <v>6.466521250581417e-08</v>
       </c>
       <c r="O8" t="n">
         <v>6.690197276094768e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.720012844147423e-08</v>
+        <v>6.720012844147424e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.010781179021827e-08</v>
+        <v>6.010781179021828e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.636604951136937e-08</v>
+        <v>7.636604951136944e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.411672936141468e-08</v>
+        <v>7.411672936141474e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.329611326752966e-08</v>
+        <v>7.329611326752965e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>6.845128249380358e-08</v>
+        <v>6.84512824938036e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.282597208263561e-08</v>
+        <v>7.282597208263563e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.93459244300726e-08</v>
+        <v>7.934592443007263e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.718943965582978e-08</v>
+        <v>6.718943965582979e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.648109565238667e-08</v>
+        <v>8.648109565238677e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25384518207896e-08</v>
+        <v>6.253845182078961e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.565959550723572e-08</v>
+        <v>7.565959550723578e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.377651401875791e-08</v>
+        <v>8.377651401875796e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.452226214971618e-08</v>
+        <v>6.452226214971619e-08</v>
       </c>
       <c r="C9" t="n">
         <v>7.066685039552426e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.027324824633719e-08</v>
+        <v>7.02732482463372e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>6.900429650571989e-08</v>
+        <v>6.900429650571987e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.905710086074497e-08</v>
+        <v>5.905710086074498e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.198101664096391e-08</v>
+        <v>7.198101664096389e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.046635526229858e-08</v>
+        <v>7.04663552622986e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.093307176449218e-08</v>
+        <v>7.093307176449222e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.166168500364166e-08</v>
+        <v>7.166168500364164e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.129933311944664e-08</v>
+        <v>7.129933311944667e-08</v>
       </c>
       <c r="L9" t="n">
         <v>7.278892146838849e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.053487951843683e-08</v>
+        <v>7.053487951843684e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.046844030961164e-08</v>
+        <v>7.046844030961165e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.221775741522345e-08</v>
+        <v>7.221775741522344e-08</v>
       </c>
       <c r="P9" t="n">
         <v>7.347197445996628e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.045219048553715e-08</v>
+        <v>7.045219048553711e-08</v>
       </c>
       <c r="R9" t="n">
         <v>7.381494124059398e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.15656210906393e-08</v>
+        <v>7.156562109063928e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.07450049967543e-08</v>
+        <v>7.074500499675431e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.115913104120046e-08</v>
+        <v>7.115913104120048e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.951607776292936e-08</v>
+        <v>7.951607776292935e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.679269807980837e-08</v>
+        <v>7.679269807980838e-08</v>
       </c>
       <c r="X9" t="n">
         <v>7.654603483624455e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.321184395996592e-08</v>
+        <v>7.321184395996594e-08</v>
       </c>
       <c r="Z9" t="n">
         <v>6.767501430531992e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.310848723646038e-08</v>
+        <v>7.310848723646041e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.996744550006556e-08</v>
+        <v>6.996744550006559e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.67285640506783e-08</v>
+        <v>1.672856405067834e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.59986827971712e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.685574968338418e-08</v>
+        <v>1.685574968338414e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.663933761591123e-08</v>
+        <v>1.663933761591119e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.696305838283366e-08</v>
+        <v>1.696305838283364e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.892572948801746e-08</v>
+        <v>1.892572948801743e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.676800804309926e-08</v>
+        <v>1.676800804309922e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.71298241673665e-08</v>
+        <v>1.712982416736647e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.765741915790367e-08</v>
+        <v>1.765741915790364e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.807580877165371e-08</v>
+        <v>1.807580877165374e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.996484493613665e-08</v>
+        <v>1.996484493613672e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.718352166149429e-08</v>
+        <v>1.718352166149432e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.715077858893748e-08</v>
+        <v>1.715077858893744e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.704931374130809e-08</v>
+        <v>2.704931374130815e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.697209691635239e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.680833780614653e-08</v>
+        <v>1.680833780614656e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.678755119554106e-08</v>
+        <v>1.678755119554103e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.686154425047875e-08</v>
+        <v>1.686154425047877e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.693234907412786e-08</v>
+        <v>1.693234907412782e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.376214547269443e-08</v>
+        <v>2.376214547269447e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.669939448760116e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.488355441969427e-08</v>
+        <v>2.488355441969429e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.759540640434003e-08</v>
+        <v>1.759540640434001e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.687232647697351e-08</v>
+        <v>1.687232647697347e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.762891484315836e-08</v>
+        <v>2.76289148431584e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.708744056830628e-08</v>
+        <v>1.708744056830625e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.728316344829476e-08</v>
+        <v>1.728316344829495e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.411693328641942e-08</v>
+        <v>1.419731051754364e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.302654315138086e-08</v>
+        <v>1.311251780152676e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.50381474329409e-08</v>
+        <v>1.515172007297122e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.347853482953636e-08</v>
+        <v>1.353595240365225e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.580781777322252e-08</v>
+        <v>1.594921816580313e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.975233929864184e-08</v>
+        <v>3.038240453106217e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.441519981534203e-08</v>
+        <v>1.450695543724622e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.700331994731703e-08</v>
+        <v>1.718679111766961e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.07356606563419e-08</v>
+        <v>2.104924399909613e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.372651455478557e-08</v>
+        <v>2.414934045036674e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.721511363509726e-08</v>
+        <v>3.811012065788034e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.763301798618321e-08</v>
+        <v>1.784064211353594e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.714209220064743e-08</v>
+        <v>1.732988679412986e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.180056559309551e-08</v>
+        <v>3.191060640501763e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58497171487286e-08</v>
+        <v>1.59907506066244e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.469560392583968e-08</v>
+        <v>1.479693648112954e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.455311048870567e-08</v>
+        <v>1.464965479603213e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.506520812087209e-08</v>
+        <v>1.517911472637002e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.558655270083782e-08</v>
+        <v>1.571964681191526e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.720131644774254e-08</v>
+        <v>2.734894857235572e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.390531734649605e-08</v>
+        <v>1.39783014689611e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.089105161896663e-08</v>
+        <v>3.112373741293545e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.032506408223762e-08</v>
+        <v>2.062619646073749e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51489290263491e-08</v>
+        <v>1.526614939169171e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.315675324152522e-08</v>
+        <v>3.328507273544788e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.66850133907854e-08</v>
+        <v>1.685641667960596e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.818089626624777e-08</v>
+        <v>1.840582481876771e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2485,82 +2485,82 @@
         <v>5.16301059579572e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.184238652270357e-08</v>
+        <v>5.184238652270355e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.306672618765165e-08</v>
+        <v>5.306672618765176e-08</v>
       </c>
       <c r="E4" t="n">
         <v>5.062225233107532e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.427882731237424e-08</v>
+        <v>5.427882731237422e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.644810031874042e-08</v>
+        <v>7.644810031874041e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.207564399748479e-08</v>
+        <v>5.207564399748478e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.616252356472366e-08</v>
+        <v>5.616252356472364e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.205849488424779e-08</v>
+        <v>6.205849488424786e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.684785484456561e-08</v>
+        <v>6.684785484456558e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.818538732196937e-08</v>
+        <v>8.818538732196979e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.721906738353241e-08</v>
+        <v>5.721906738353242e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.639921339587798e-08</v>
+        <v>5.639921339587797e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.297450085628684e-08</v>
+        <v>5.297450085628678e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.438092170639904e-08</v>
+        <v>5.4380921706399e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.253118722371135e-08</v>
+        <v>5.25311872237114e-08</v>
       </c>
       <c r="R4" t="n">
         <v>5.229639289460944e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.313217848861751e-08</v>
+        <v>5.313217848861745e-08</v>
       </c>
       <c r="T4" t="n">
         <v>5.393195154356235e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.420347695056531e-08</v>
+        <v>5.420347695056525e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.08703354920552e-08</v>
+        <v>5.087033549205521e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.843578407554172e-08</v>
+        <v>5.843578407554169e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.142148910975021e-08</v>
+        <v>6.142148910975036e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.281872165789357e-08</v>
+        <v>5.281872165789353e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.379071958955029e-08</v>
+        <v>5.379071958955026e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.568378131591958e-08</v>
+        <v>5.568378131591961e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.801791186181804e-08</v>
+        <v>5.801791186181801e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.572859236471485e-08</v>
+        <v>9.572859236472369e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.046857424696307e-07</v>
+        <v>1.046857424696306e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.303911971037391e-07</v>
+        <v>1.3039119710374e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.579072214624724e-08</v>
+        <v>7.57907221462485e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.554244267417669e-07</v>
+        <v>1.55424426741767e-07</v>
       </c>
       <c r="G5" t="n">
         <v>5.394723501368017e-07</v>
@@ -2591,64 +2591,64 @@
         <v>1.134698842040725e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.939812501667982e-07</v>
+        <v>1.939812501667989e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.881721886967512e-07</v>
+        <v>2.881721886967527e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.802545201849811e-07</v>
+        <v>3.80254520184981e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>7.872918433308304e-07</v>
+        <v>7.872918433308416e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.150478427787266e-07</v>
+        <v>2.150478427787261e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>1.924609606312541e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.180080563747316e-07</v>
+        <v>1.180080563747309e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.447807221443927e-07</v>
+        <v>1.447807221443926e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.179502516754856e-07</v>
+        <v>1.179502516754864e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.167707466569024e-07</v>
+        <v>1.167707466569023e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.236783294367385e-07</v>
+        <v>1.236783294367371e-07</v>
       </c>
       <c r="T5" t="n">
         <v>1.477027043304359e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.533821331850621e-07</v>
+        <v>1.533821331850622e-07</v>
       </c>
       <c r="V5" t="n">
         <v>8.716012765342338e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>2.284131197551736e-07</v>
+        <v>2.28413119755174e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.927835327026079e-07</v>
+        <v>2.927835327026099e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.297449527602629e-07</v>
+        <v>1.297449527602635e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.35109937339441e-07</v>
+        <v>1.351099373394443e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.761349703253029e-07</v>
+        <v>1.761349703253035e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.380542820714801e-07</v>
+        <v>2.380542820714796e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.00898941793932e-08</v>
+        <v>5.008989417939338e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.85052778822203e-08</v>
+        <v>5.850527788222028e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.152651440908772e-08</v>
+        <v>5.152651440908775e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.728514369059206e-08</v>
+        <v>5.728514369059211e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.273861553381031e-08</v>
+        <v>5.273861553381029e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.311099167825715e-08</v>
+        <v>8.311099167825711e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.873853535700153e-08</v>
+        <v>5.873853535700154e-08</v>
       </c>
       <c r="I6" t="n">
         <v>6.282541492424037e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.872138624376451e-08</v>
+        <v>6.872138624376458e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.530764306600169e-08</v>
+        <v>6.53076430660017e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.484827868148599e-08</v>
+        <v>9.484827868148604e-08</v>
       </c>
       <c r="M6" t="n">
         <v>6.388195874304915e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.48706193101221e-08</v>
+        <v>5.487061931012203e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.144506733686679e-08</v>
+        <v>5.144506733686661e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.124730315133143e-08</v>
+        <v>6.124730315133142e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.099097544514741e-08</v>
+        <v>5.099097544514749e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.895928425412618e-08</v>
+        <v>5.89592842541262e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.159196671005357e-08</v>
+        <v>5.159196671005354e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.23917397649984e-08</v>
+        <v>5.239173976499842e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.309851221105274e-08</v>
+        <v>5.309851221105279e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.933012371349126e-08</v>
+        <v>4.933012371349127e-08</v>
       </c>
       <c r="W6" t="n">
         <v>5.71039454026264e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.808438046926692e-08</v>
+        <v>6.808438046926695e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.181779736136816e-08</v>
+        <v>5.181779736136798e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.225050781098636e-08</v>
+        <v>5.225050781098638e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.234667267543632e-08</v>
+        <v>6.234667267543634e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.653021217379349e-08</v>
+        <v>5.653021217379347e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.754539506516854e-08</v>
+        <v>5.754539506516863e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.775767562991495e-08</v>
@@ -2755,7 +2755,7 @@
         <v>5.898201529486305e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.653754143828668e-08</v>
+        <v>5.653754143828679e-08</v>
       </c>
       <c r="F7" t="n">
         <v>6.019411641958563e-08</v>
@@ -2764,31 +2764,31 @@
         <v>8.236338942595175e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.799093310469617e-08</v>
+        <v>5.799093310469618e-08</v>
       </c>
       <c r="I7" t="n">
         <v>6.207781267193499e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.797378399145918e-08</v>
+        <v>6.797378399145923e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>7.276314395177703e-08</v>
+        <v>7.276314395177705e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>9.410067642918095e-08</v>
+        <v>9.410067642918068e-08</v>
       </c>
       <c r="M7" t="n">
         <v>6.313435649074377e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.231450250308936e-08</v>
+        <v>6.231450250308935e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.888844474752959e-08</v>
+        <v>5.888844474752954e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.029486559764176e-08</v>
+        <v>6.029486559764182e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>5.844647633092272e-08</v>
@@ -2797,34 +2797,34 @@
         <v>5.821168200182081e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.904746759582888e-08</v>
+        <v>5.904746759582897e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.984724065077371e-08</v>
+        <v>5.984724065077368e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>6.05454228901423e-08</v>
+        <v>6.054542289014233e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.678562459926656e-08</v>
+        <v>5.678562459926661e-08</v>
       </c>
       <c r="W7" t="n">
         <v>6.435107318275308e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.733677821696158e-08</v>
+        <v>6.733677821696168e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.916925780415632e-08</v>
+        <v>5.916925780415628e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.970600869676166e-08</v>
+        <v>5.970600869676165e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.159907042313098e-08</v>
+        <v>6.159907042313099e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.393320096902939e-08</v>
+        <v>6.393320096902941e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,82 +2834,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.713603951865725e-08</v>
+        <v>6.713603951865742e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>8.025002292707442e-08</v>
+        <v>8.025002292707444e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.147436259202253e-08</v>
+        <v>8.147436259202249e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.216011254750743e-08</v>
+        <v>7.216011254750757e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.179469539025723e-08</v>
+        <v>7.179469539025726e-08</v>
       </c>
       <c r="G8" t="n">
         <v>1.07530988854592e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>8.048328040185561e-08</v>
+        <v>8.048328040185562e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.457015996909445e-08</v>
+        <v>8.457015996909442e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>9.046613128861857e-08</v>
+        <v>9.046613128861873e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>9.525549124893644e-08</v>
+        <v>9.525549124893645e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.165930237263403e-07</v>
+        <v>1.165930237263404e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>8.562670378790184e-08</v>
+        <v>8.562670378790195e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.480587168799888e-08</v>
+        <v>7.48058716879989e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.412951477033949e-08</v>
+        <v>7.412951477033957e-08</v>
       </c>
       <c r="P8" t="n">
         <v>7.48622472479693e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.550164170828902e-08</v>
+        <v>6.550164170828905e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.070402929898031e-08</v>
+        <v>8.07040292989803e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.153981489298835e-08</v>
+        <v>8.153981489298844e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.233958794793315e-08</v>
+        <v>8.233958794793317e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.674359674248991e-08</v>
+        <v>7.674359674248996e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.574554913588096e-08</v>
+        <v>7.574554913588101e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.684595603319863e-08</v>
+        <v>8.684595603319872e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.557441029563615e-08</v>
+        <v>7.557441029563629e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.447986947644479e-08</v>
+        <v>9.447986947644481e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.905699739578063e-08</v>
+        <v>6.905699739578065e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.409141772029041e-08</v>
+        <v>8.409141772029047e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>9.990245570917542e-08</v>
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.686729744259692e-08</v>
+        <v>7.686729744259708e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.538630757579597e-08</v>
+        <v>8.538630757579603e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.661064724074412e-08</v>
+        <v>8.661064724074411e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.224902275209191e-08</v>
+        <v>8.224902275209201e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.867345487670348e-08</v>
+        <v>6.867345487670352e-08</v>
       </c>
       <c r="G9" t="n">
         <v>1.099920326429513e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.561956505057723e-08</v>
+        <v>8.56195650505773e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.970644461781604e-08</v>
+        <v>8.97064446178161e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.560241593734023e-08</v>
+        <v>9.560241593734029e-08</v>
       </c>
       <c r="K9" t="n">
         <v>1.00391775897658e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.217293083750619e-07</v>
+        <v>1.21729308375062e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>9.07629884366248e-08</v>
+        <v>9.076298843662478e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.994313444897038e-08</v>
+        <v>8.994313444897041e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.927127621798318e-08</v>
+        <v>8.927127621798319e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.127639319791572e-08</v>
+        <v>9.127639319791571e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.607511954792224e-08</v>
+        <v>8.607511954792231e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.584031394770186e-08</v>
+        <v>8.584031394770192e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.667609954170995e-08</v>
+        <v>8.667609954171009e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.747587259665473e-08</v>
+        <v>8.747587259665479e-08</v>
       </c>
       <c r="U9" t="n">
         <v>8.818264504270915e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.400005810298861e-08</v>
+        <v>9.40000581029887e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>9.197970512863412e-08</v>
+        <v>9.197970512863418e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.496541016284265e-08</v>
+        <v>9.496541016284277e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.679788975003741e-08</v>
+        <v>8.679788975003745e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.232642585171591e-08</v>
+        <v>8.232642585171597e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.922770236901204e-08</v>
+        <v>8.922770236901211e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.156183291491044e-08</v>
+        <v>9.15618329149105e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.62309988017943e-08</v>
+        <v>1.623099880179421e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.551909132088095e-08</v>
+        <v>1.551909132088094e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.65260695696535e-08</v>
+        <v>1.652606956965342e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.62840542643603e-08</v>
+        <v>1.628405426436026e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.646133658466953e-08</v>
+        <v>1.646133658466945e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.81649722919139e-08</v>
+        <v>1.816497229191384e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.622602391810154e-08</v>
+        <v>1.622602391810145e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.652631914956013e-08</v>
+        <v>1.652631914956004e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.706942179979354e-08</v>
+        <v>1.706942179979345e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.649929403496423e-08</v>
+        <v>1.649929403496414e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8936482742607e-08</v>
+        <v>1.893648274260695e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.666349294818731e-08</v>
+        <v>1.66634929481873e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.637672940564495e-08</v>
+        <v>1.637672940564486e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.61800924506985e-08</v>
+        <v>2.618009245069849e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.644962989089234e-08</v>
+        <v>1.644962989089225e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.637602336840106e-08</v>
+        <v>1.637602336840096e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.621461351688423e-08</v>
+        <v>1.621461351688413e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.637857149863629e-08</v>
+        <v>1.637857149863618e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.634530003799038e-08</v>
+        <v>1.634530003799028e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.310609914090358e-08</v>
+        <v>2.310609914090348e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.627464763726734e-08</v>
+        <v>1.627464763726725e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.419203091705881e-08</v>
+        <v>2.419203091705877e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.767546255227329e-08</v>
+        <v>1.76754625522732e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.676688436067023e-08</v>
+        <v>1.676688436067013e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.715092073836477e-08</v>
+        <v>2.715092073836471e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.647284737622639e-08</v>
+        <v>1.647284737622632e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.682633776984115e-08</v>
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.322287260878686e-08</v>
+        <v>1.328580151795592e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.228718652807394e-08</v>
+        <v>1.236139230592501e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.534037166539043e-08</v>
+        <v>1.547881543177337e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.359739370345932e-08</v>
+        <v>1.36730582076814e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.487771945469728e-08</v>
+        <v>1.500019810840066e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.697283787643546e-08</v>
+        <v>2.751960198460229e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.319694358020372e-08</v>
+        <v>1.325944357144804e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.534513780244257e-08</v>
+        <v>1.548385681260013e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.91923568166917e-08</v>
+        <v>1.946582463602659e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.513524227440795e-08</v>
+        <v>1.526673650392021e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.252552776276128e-08</v>
+        <v>3.326940846113755e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657207612656617e-08</v>
+        <v>1.675606105313621e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.42691138046112e-08</v>
+        <v>1.436931846305356e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.001170133626261e-08</v>
+        <v>3.009140962692319e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.47766684485093e-08</v>
+        <v>1.489407927029306e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.426267657752698e-08</v>
+        <v>1.436282701602577e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.311360027672591e-08</v>
+        <v>1.317308710709523e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.427331713728123e-08</v>
+        <v>1.437337326389481e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.404787394942763e-08</v>
+        <v>1.41404559294938e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.593545292561999e-08</v>
+        <v>2.606061180512171e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352798852869222e-08</v>
+        <v>1.360173101897787e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.951701627773097e-08</v>
+        <v>2.972487396888615e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.355483544631245e-08</v>
+        <v>2.39847653572383e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.70506468456064e-08</v>
+        <v>1.724921145855133e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.264516941323636e-08</v>
+        <v>3.277241807414452e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.49531978870476e-08</v>
+        <v>1.507745830169037e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.756803313129577e-08</v>
+        <v>1.778527778881697e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.009034565437578e-08</v>
+        <v>5.00903456543758e-08</v>
       </c>
       <c r="C4" t="n">
         <v>5.05684406536643e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.342330571660486e-08</v>
+        <v>5.342330571660485e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.068963151077747e-08</v>
+        <v>5.068963151077749e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.269211687256693e-08</v>
+        <v>5.26921168725669e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.193546589703675e-08</v>
+        <v>7.193546589703672e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.003415205450661e-08</v>
+        <v>5.003415205450662e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.342612483646272e-08</v>
+        <v>5.342612483646273e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.950504163489024e-08</v>
+        <v>5.95050416348902e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.312086373493507e-08</v>
+        <v>5.312086373493506e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.065003134995715e-08</v>
+        <v>8.065003134995719e-08</v>
       </c>
       <c r="M4" t="n">
         <v>5.542227882303547e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.17364398642589e-08</v>
+        <v>5.173643986425888e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.085105315372624e-08</v>
+        <v>5.085105315372623e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.255988438100818e-08</v>
+        <v>5.255988438100814e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.172846484879574e-08</v>
+        <v>5.172846484879572e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.990526632371316e-08</v>
+        <v>4.990526632371318e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.175724715200042e-08</v>
+        <v>5.175724715200043e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.138143069837701e-08</v>
+        <v>5.1381430698377e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.270334195299348e-08</v>
+        <v>5.270334195299347e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.020508891063655e-08</v>
+        <v>5.020508891063654e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.657244473811711e-08</v>
+        <v>5.657244473811708e-08</v>
       </c>
       <c r="X4" t="n">
         <v>6.64062282021904e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.596883286135231e-08</v>
+        <v>5.596883286135232e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.299102656669961e-08</v>
+        <v>5.299102656669964e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>5.282213655842716e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.69265133344819e-08</v>
+        <v>5.692651333448188e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,31 +3430,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.742941797937234e-08</v>
+        <v>7.742941797937272e-08</v>
       </c>
       <c r="C5" t="n">
         <v>8.850988184344627e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.423712099831263e-07</v>
+        <v>1.423712099831265e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>8.588416319740119e-08</v>
+        <v>8.588416319740117e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.291022537980361e-07</v>
+        <v>1.29102253798036e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.363823604881264e-07</v>
+        <v>4.363823604881246e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.139856069920166e-08</v>
+        <v>8.139856069920159e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.439679055236288e-07</v>
+        <v>1.43967905523629e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.374195426044954e-07</v>
+        <v>2.374195426044952e-07</v>
       </c>
       <c r="K5" t="n">
         <v>1.297507802803005e-07</v>
@@ -3463,22 +3463,22 @@
         <v>6.145497848597577e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.819752325692529e-07</v>
+        <v>1.819752325692532e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.097327817513391e-07</v>
+        <v>1.097327817513392e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>8.909163329321313e-08</v>
+        <v>8.909163329321292e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.176947021438841e-07</v>
+        <v>1.17694702143884e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.088671465855461e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>7.813090427782987e-08</v>
+        <v>7.813090427782986e-08</v>
       </c>
       <c r="S5" t="n">
         <v>1.054659070971021e-07</v>
@@ -3487,28 +3487,28 @@
         <v>1.050464195466275e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.259700056563476e-07</v>
+        <v>1.259700056563455e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.245046085266181e-08</v>
+        <v>8.24504608526615e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.944362036408598e-07</v>
+        <v>1.9443620364086e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>3.77793911524862e-07</v>
+        <v>3.777939115248618e-07</v>
       </c>
       <c r="Y5" t="n">
         <v>1.861112474201752e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.225473492867967e-07</v>
+        <v>1.225473492867969e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.279428925350573e-07</v>
+        <v>1.279428925350572e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.167843346585764e-07</v>
+        <v>2.167843346585765e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,19 +3518,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.608160542804618e-08</v>
+        <v>5.608160542804616e-08</v>
       </c>
       <c r="C6" t="n">
         <v>4.914931987474154e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.941456549027525e-08</v>
+        <v>5.941456549027523e-08</v>
       </c>
       <c r="E6" t="n">
         <v>5.66808912844479e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.127299609364415e-08</v>
+        <v>5.127299609364416e-08</v>
       </c>
       <c r="G6" t="n">
         <v>7.051634511811392e-08</v>
@@ -3539,43 +3539,43 @@
         <v>4.861503127558386e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.200700405753998e-08</v>
+        <v>5.200700405753999e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.549630140856064e-08</v>
+        <v>6.549630140856062e-08</v>
       </c>
       <c r="K6" t="n">
         <v>5.911212350860547e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.664129112362757e-08</v>
+        <v>8.664129112362763e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.400315804411268e-08</v>
+        <v>5.400315804411271e-08</v>
       </c>
       <c r="N6" t="n">
         <v>5.032244659517679e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.699462592625659e-08</v>
+        <v>5.69946259262566e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.870454254421418e-08</v>
+        <v>5.87045425442142e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.771972462246612e-08</v>
+        <v>5.771972462246615e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.848614554479041e-08</v>
+        <v>4.848614554479042e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.774850692567082e-08</v>
+        <v>5.774850692567083e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.996230991945424e-08</v>
+        <v>4.996230991945427e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.14588078741345e-08</v>
+        <v>5.145880787413447e-08</v>
       </c>
       <c r="V6" t="n">
         <v>5.619634868430694e-08</v>
@@ -3587,16 +3587,16 @@
         <v>6.498710742326763e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.481791874877743e-08</v>
+        <v>5.481791874877742e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>5.898228634037002e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.881339633209756e-08</v>
+        <v>5.881339633209758e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.557138329258478e-08</v>
+        <v>5.557138329258482e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,70 +3606,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.533196416124605e-08</v>
+        <v>5.533196416124607e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.581005916053455e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.866492422347516e-08</v>
+        <v>5.866492422347512e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.593125001764777e-08</v>
+        <v>5.593125001764778e-08</v>
       </c>
       <c r="F7" t="n">
         <v>5.79337353794372e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.717708440390703e-08</v>
+        <v>7.717708440390702e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.527577056137689e-08</v>
+        <v>5.52757705613769e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.866774334333297e-08</v>
+        <v>5.866774334333299e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.474666014176052e-08</v>
+        <v>6.474666014176055e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.836248224180536e-08</v>
+        <v>5.836248224180535e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.58916498568275e-08</v>
+        <v>8.589164985682749e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.066389732990572e-08</v>
+        <v>6.066389732990573e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.697805837112916e-08</v>
+        <v>5.697805837112917e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.609141147062631e-08</v>
+        <v>5.609141147062632e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.780024269790821e-08</v>
+        <v>5.780024269790822e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.697008335566601e-08</v>
+        <v>5.697008335566603e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.514688483058346e-08</v>
+        <v>5.514688483058347e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.699886565887071e-08</v>
+        <v>5.69988656588707e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.66230492052473e-08</v>
+        <v>5.662304920524728e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.81118241244513e-08</v>
+        <v>5.811182412445117e-08</v>
       </c>
       <c r="V7" t="n">
         <v>5.544670741750682e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>6.181406324498736e-08</v>
+        <v>6.181406324498738e-08</v>
       </c>
       <c r="X7" t="n">
         <v>7.164784670906067e-08</v>
@@ -3678,13 +3678,13 @@
         <v>6.138503806828635e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.823264507356987e-08</v>
+        <v>5.823264507356993e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.806375506529743e-08</v>
+        <v>5.806375506529744e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.216813184135218e-08</v>
+        <v>6.21681318413522e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3697,34 +3697,34 @@
         <v>6.404557654748634e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.61673788627486e-08</v>
+        <v>7.616737886274856e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.902224392568913e-08</v>
+        <v>7.90222439256891e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.008863904188694e-08</v>
+        <v>7.008863904188692e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.84613012821876e-08</v>
+        <v>6.846130128218758e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.994880266985187e-08</v>
+        <v>9.994880266985176e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.563309026359088e-08</v>
+        <v>7.563309026359086e-08</v>
       </c>
       <c r="I8" t="n">
         <v>7.902506304554704e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.510397984397452e-08</v>
+        <v>8.510397984397447e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.87198019440194e-08</v>
+        <v>7.871980194401936e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.062489695590415e-07</v>
+        <v>1.062489695590416e-07</v>
       </c>
       <c r="M8" t="n">
         <v>8.102121703211793e-08</v>
@@ -3736,7 +3736,7 @@
         <v>6.990454425602761e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.100537587842255e-08</v>
+        <v>7.10053758784226e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>6.339544149935315e-08</v>
@@ -3748,31 +3748,31 @@
         <v>7.735618536108472e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.698036890746131e-08</v>
+        <v>7.698036890746127e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.278872018082616e-08</v>
+        <v>7.278872018082619e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.261610206357879e-08</v>
+        <v>7.261610206357872e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.217367126839947e-08</v>
+        <v>8.217367126839943e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.914037376429881e-08</v>
+        <v>7.914037376429875e-08</v>
       </c>
       <c r="Y8" t="n">
         <v>9.33108627611386e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.67299696181564e-08</v>
+        <v>6.672996961815638e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.842107476751151e-08</v>
+        <v>7.842107476751147e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.468827746600352e-08</v>
+        <v>9.468827746600349e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,64 +3782,64 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.057470139315788e-08</v>
+        <v>7.057470139315792e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.792641402626055e-08</v>
+        <v>7.792641402626053e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.078127908920115e-08</v>
+        <v>8.078127908920113e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.646120967646017e-08</v>
+        <v>7.646120967646019e-08</v>
       </c>
       <c r="F9" t="n">
         <v>6.420451253457479e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.929344928777423e-08</v>
+        <v>9.929344928777417e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.739212542710288e-08</v>
+        <v>7.739212542710286e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>8.078409820905901e-08</v>
+        <v>8.0784098209059e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.686301500748649e-08</v>
+        <v>8.686301500748645e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>8.047883710753133e-08</v>
+        <v>8.04788371075313e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.080080047225536e-07</v>
+        <v>1.080080047225535e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>8.27802521956317e-08</v>
+        <v>8.278025219563173e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.909441323685517e-08</v>
+        <v>7.909441323685514e-08</v>
       </c>
       <c r="O9" t="n">
         <v>8.048694774807506e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.269118557976761e-08</v>
+        <v>8.269118557976763e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.908644823953321e-08</v>
+        <v>7.908644823953324e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.726323969630939e-08</v>
+        <v>7.726323969630942e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.91152205245967e-08</v>
+        <v>7.911522052459668e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.873940407097326e-08</v>
+        <v>7.873940407097325e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.023590202565363e-08</v>
+        <v>8.023590202565346e-08</v>
       </c>
       <c r="V9" t="n">
         <v>8.549508202229715e-08</v>
@@ -3848,16 +3848,16 @@
         <v>8.393041811071338e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.376420157478664e-08</v>
+        <v>9.376420157478666e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>8.350139293401236e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.620482371012723e-08</v>
+        <v>7.620482371012728e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.018010993102347e-08</v>
+        <v>8.018010993102344e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>8.428448670707814e-08</v>
@@ -4029,82 +4029,82 @@
         <v>1.59207727822143e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.510640466867518e-08</v>
+        <v>1.510640466867516e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.602554462340783e-08</v>
+        <v>1.602554462340779e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.593906745109854e-08</v>
+        <v>1.593906745109852e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.617189214566881e-08</v>
+        <v>1.617189214566878e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758413597089217e-08</v>
+        <v>1.758413597089215e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.593762540154886e-08</v>
+        <v>1.593762540154883e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.614097097350832e-08</v>
+        <v>1.614097097350829e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.660513122223513e-08</v>
+        <v>1.660513122223512e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.622796928381159e-08</v>
+        <v>1.622796928381157e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.804761886312325e-08</v>
+        <v>1.804761886312322e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.626911909639328e-08</v>
+        <v>1.626911909639326e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.591153936657831e-08</v>
+        <v>1.591153936657829e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.579285057932273e-08</v>
+        <v>2.579285057932268e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.605761581965109e-08</v>
+        <v>1.605761581965106e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.605801914537146e-08</v>
+        <v>1.605801914537144e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.599950620596173e-08</v>
+        <v>1.599950620596174e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.609181493031779e-08</v>
+        <v>1.609181493031775e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.609017033146747e-08</v>
+        <v>1.609017033146745e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.256578047649928e-08</v>
+        <v>2.256578047649925e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.600880888006341e-08</v>
+        <v>1.600880888006339e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.336543448705333e-08</v>
+        <v>2.336543448705328e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.751733487485595e-08</v>
+        <v>1.751733487485593e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.675182841151895e-08</v>
+        <v>1.675182841151894e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.678975445861003e-08</v>
+        <v>2.678975445861001e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.618690366005232e-08</v>
+        <v>1.61869036600523e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.644145488793932e-08</v>
+        <v>1.644145488793931e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.288894445125766e-08</v>
+        <v>1.294898539102793e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.165577465843936e-08</v>
+        <v>1.172112556009011e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.364253949375523e-08</v>
+        <v>1.372970365800272e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.301446027472437e-08</v>
+        <v>1.307847138045096e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.469099093639958e-08</v>
+        <v>1.481579590606104e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.469472941647968e-08</v>
+        <v>2.51709056678632e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.301906308377902e-08</v>
+        <v>1.308415849532114e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.447096414531683e-08</v>
+        <v>1.458760740257027e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.775451876845452e-08</v>
+        <v>1.798653625911545e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.507807120380127e-08</v>
+        <v>1.521648081936951e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.803123156832045e-08</v>
+        <v>2.862660841012341e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.562548058598476e-08</v>
+        <v>1.578494492281194e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.282758782721865e-08</v>
+        <v>1.288566999204696e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.969532070444956e-08</v>
+        <v>2.977875905039138e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.385973897737472e-08</v>
+        <v>1.395386149288778e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.38711674747415e-08</v>
+        <v>1.396640356631398e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.346108461742203e-08</v>
+        <v>1.354184865116134e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.410557704990403e-08</v>
+        <v>1.420861803546203e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.410812875519907e-08</v>
+        <v>1.421175257051319e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.556674497478911e-08</v>
+        <v>2.57050350337598e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35089878461794e-08</v>
+        <v>1.359095342322362e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.704923004738948e-08</v>
+        <v>2.719530797892061e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.428754833647597e-08</v>
+        <v>2.475311361444189e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.88296585509689e-08</v>
+        <v>1.909980469674243e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.204334204628853e-08</v>
+        <v>3.215945251379801e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.479325783652312e-08</v>
+        <v>1.492071706423343e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.669084099516256e-08</v>
+        <v>1.688604686167788e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.976823410824623e-08</v>
+        <v>4.976823410824619e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.99833821776708e-08</v>
+        <v>4.998338217767076e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.095168025195482e-08</v>
+        <v>5.095168025195473e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.997488080925675e-08</v>
+        <v>4.997488080925671e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.260474283907917e-08</v>
+        <v>5.260474283907911e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.855668650923357e-08</v>
+        <v>6.855668650923352e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.995859219621763e-08</v>
+        <v>4.995859219621759e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.225547397508446e-08</v>
+        <v>5.225547397508441e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.744729743753872e-08</v>
+        <v>5.744729743753866e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.323815991115992e-08</v>
+        <v>5.323815991115988e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>7.379193898964776e-08</v>
+        <v>7.379193898964769e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.414530141628378e-08</v>
+        <v>5.414530141628376e-08</v>
       </c>
       <c r="N4" t="n">
         <v>4.96639384310563e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.08280376197438e-08</v>
+        <v>5.082803761974372e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.13139391670018e-08</v>
+        <v>5.131393916700175e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.131849491655246e-08</v>
+        <v>5.131849491655242e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.065756434863788e-08</v>
+        <v>5.065756434863787e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.17002338543502e-08</v>
+        <v>5.170023385435014e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.168165735378303e-08</v>
+        <v>5.1681657353783e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.324340163517271e-08</v>
+        <v>5.324340163517265e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.04151819274267e-08</v>
+        <v>5.041518192742667e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.361243162325872e-08</v>
+        <v>5.361243162325871e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.7802137399482e-08</v>
+        <v>6.780213739948197e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.912207310623654e-08</v>
+        <v>5.912207310623646e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.22968232834488e-08</v>
+        <v>5.229682328344876e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.277430479967869e-08</v>
+        <v>5.277430479967863e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.57557886617881e-08</v>
+        <v>5.575578866178805e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,76 +4290,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.384149031724529e-08</v>
+        <v>7.384149031724527e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.024800911702432e-08</v>
+        <v>8.024800911702427e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.779559060603244e-08</v>
+        <v>9.779559060603202e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.487719794561259e-08</v>
+        <v>7.487719794561255e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.290858745041784e-07</v>
+        <v>1.290858745041786e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.720880126066348e-07</v>
+        <v>3.720880126066344e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.230795395989735e-08</v>
+        <v>8.230795395989733e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.232500692667601e-07</v>
+        <v>1.2325006926676e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.008064840496959e-07</v>
+        <v>2.008064840496961e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.334768045649195e-07</v>
+        <v>1.334768045649194e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>4.795041695603102e-07</v>
+        <v>4.795041695603103e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.564608559871407e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>7.435100066972496e-08</v>
+        <v>7.435100066972484e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>9.048333166577806e-08</v>
+        <v>9.048333166577807e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.81424920947419e-08</v>
+        <v>9.814249209474294e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.026538587717458e-07</v>
+        <v>1.026538587717459e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>9.486484065066274e-08</v>
+        <v>9.486484065066269e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05885434977847e-07</v>
+        <v>1.058854349778467e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.129619412443566e-07</v>
+        <v>1.129619412443564e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.324756305963982e-07</v>
+        <v>1.324756305963983e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.679366601014959e-08</v>
+        <v>8.679366601014909e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.440746916593133e-07</v>
+        <v>1.440746916593132e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>3.948015063532172e-07</v>
+        <v>3.948015063532174e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.447549835992451e-07</v>
+        <v>2.447549835992455e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>1.107808360772442e-07</v>
@@ -4368,7 +4368,7 @@
         <v>1.295605714973449e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.942805981553227e-07</v>
+        <v>1.942805981553229e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.833839617379955e-08</v>
+        <v>4.833839617379949e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.855354424322414e-08</v>
+        <v>4.855354424322408e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.671130879018629e-08</v>
+        <v>5.671130879018617e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.573450934748821e-08</v>
+        <v>5.573450934748813e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.117490490463244e-08</v>
+        <v>5.117490490463243e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.712684857478684e-08</v>
+        <v>6.712684857478673e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.571822073444912e-08</v>
+        <v>5.571822073444905e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.082563604063777e-08</v>
+        <v>5.082563604063771e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.320692597577015e-08</v>
+        <v>6.320692597577011e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.899778844939141e-08</v>
+        <v>5.899778844939133e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.236210105520112e-08</v>
+        <v>7.236210105520106e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.271546348183711e-08</v>
+        <v>5.271546348183705e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.824467428283744e-08</v>
+        <v>4.824467428283756e-08</v>
       </c>
       <c r="O6" t="n">
         <v>4.943390451780941e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.720883941197241e-08</v>
+        <v>5.720883941197235e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.707812345478391e-08</v>
+        <v>5.707812345478387e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.641719288686938e-08</v>
+        <v>5.641719288686929e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.027039591990349e-08</v>
+        <v>5.027039591990345e-08</v>
       </c>
       <c r="T6" t="n">
         <v>5.744128589201447e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.903634681288703e-08</v>
+        <v>5.903634681288695e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.898534399298e-08</v>
+        <v>4.898534399297997e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.234734662670745e-08</v>
+        <v>5.234734662670737e-08</v>
       </c>
       <c r="X6" t="n">
         <v>6.637229946503528e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.783222779210332e-08</v>
+        <v>5.78322277921033e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.086698534900211e-08</v>
+        <v>5.086698534900206e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.853393333791013e-08</v>
+        <v>5.85339333379101e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.435748793154375e-08</v>
+        <v>5.435748793154368e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.488929382199109e-08</v>
+        <v>5.488929382199106e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.51044418914157e-08</v>
+        <v>5.510444189141565e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.607273996569967e-08</v>
+        <v>5.60727399656996e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.509594052300162e-08</v>
+        <v>5.509594052300159e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.772580255282407e-08</v>
+        <v>5.772580255282403e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.36777462229784e-08</v>
+        <v>7.367774622297835e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.507965190996248e-08</v>
+        <v>5.507965190996244e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.737653368882934e-08</v>
+        <v>5.737653368882929e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.256835715128356e-08</v>
+        <v>6.256835715128354e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.83592196249048e-08</v>
+        <v>5.835921962490478e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>7.89129987033927e-08</v>
+        <v>7.891299870339264e-08</v>
       </c>
       <c r="M7" t="n">
         <v>5.926636113002867e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.478499814480123e-08</v>
+        <v>5.478499814480119e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.594783545415697e-08</v>
+        <v>5.594783545415687e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.643373700141492e-08</v>
+        <v>5.643373700141489e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.643955463029734e-08</v>
+        <v>5.643955463029732e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.577862406238274e-08</v>
+        <v>5.577862406238273e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.682129356809506e-08</v>
+        <v>5.682129356809502e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.680271706752793e-08</v>
+        <v>5.68027170675279e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.839086985108968e-08</v>
+        <v>5.839086985108964e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.553624164117158e-08</v>
+        <v>5.553624164117153e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.873349133700363e-08</v>
+        <v>5.873349133700355e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>7.292319711322682e-08</v>
+        <v>7.292319711322684e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.42764494594641e-08</v>
+        <v>6.427644945946418e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.741788299719366e-08</v>
+        <v>5.741788299719363e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.789536451342356e-08</v>
+        <v>5.789536451342354e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.087684837553304e-08</v>
+        <v>6.087684837553296e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.346377400328285e-08</v>
+        <v>6.346377400328279e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.512722853516423e-08</v>
+        <v>7.512722853516411e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.609552660944826e-08</v>
+        <v>7.60955266094481e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>6.902284167929877e-08</v>
+        <v>6.902284167929869e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.808379508134799e-08</v>
+        <v>6.808379508134792e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.607441379056537e-08</v>
+        <v>9.607441379056528e-08</v>
       </c>
       <c r="H8" t="n">
         <v>7.510243855371102e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.739932033257783e-08</v>
+        <v>7.739932033257777e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.259114379503217e-08</v>
+        <v>8.25911437950321e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.838200626865334e-08</v>
+        <v>7.838200626865327e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>9.893578534714119e-08</v>
+        <v>9.893578534714106e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.928914777377637e-08</v>
+        <v>7.928914777377629e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.59334320197047e-08</v>
+        <v>6.593343201970462e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>6.953628040368332e-08</v>
+        <v>6.953628040368323e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.942438559476555e-08</v>
+        <v>6.942438559476547e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.276418129654466e-08</v>
+        <v>6.276418129654457e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.580141070613132e-08</v>
+        <v>7.580141070613122e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.684408021184362e-08</v>
+        <v>7.684408021184348e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.68255037112765e-08</v>
+        <v>7.682550371127642e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.28284233347581e-08</v>
+        <v>7.282842333475804e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.242520722715535e-08</v>
+        <v>7.242520722715528e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.875852790012065e-08</v>
+        <v>7.875852790012055e-08</v>
       </c>
       <c r="X8" t="n">
         <v>8.029708381455668e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.567454106988446e-08</v>
+        <v>9.567454106988444e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.577970500799817e-08</v>
+        <v>6.577970500799812e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.791815115717207e-08</v>
+        <v>7.791815115717199e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.285834841110711e-08</v>
+        <v>9.285834841110701e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.825033416826035e-08</v>
+        <v>6.825033416826037e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.477213632991906e-08</v>
+        <v>7.477213632991905e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.574043440420313e-08</v>
+        <v>7.574043440420295e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.330809225511975e-08</v>
+        <v>7.330809225511968e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.285492561481613e-08</v>
+        <v>6.285492561481609e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.33454501956601e-08</v>
+        <v>9.334545019566002e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.474734634846587e-08</v>
+        <v>7.474734634846582e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.704422812733269e-08</v>
+        <v>7.704422812733268e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.223605158978692e-08</v>
+        <v>8.223605158978687e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.802691406340817e-08</v>
+        <v>7.802691406340811e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>9.858069314189599e-08</v>
+        <v>9.858069314189592e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.893405556853201e-08</v>
+        <v>7.893405556853199e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.445269258330459e-08</v>
+        <v>7.445269258330451e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.770682137409288e-08</v>
+        <v>7.770682137409278e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.864726642741816e-08</v>
+        <v>7.864726642741807e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.610725860297907e-08</v>
+        <v>7.610725860297899e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.544631850088607e-08</v>
+        <v>7.544631850088608e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.648898800659844e-08</v>
+        <v>7.648898800659833e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.647041150603136e-08</v>
+        <v>7.647041150603125e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.806547242690381e-08</v>
+        <v>7.806547242690373e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.248169173333152e-08</v>
+        <v>8.248169173333147e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.840118577550701e-08</v>
+        <v>7.840118577550696e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.259089155173026e-08</v>
+        <v>9.259089155173022e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.394414389796771e-08</v>
+        <v>8.39441438979675e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.328322961355968e-08</v>
+        <v>7.328322961355961e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.756305895192693e-08</v>
+        <v>7.756305895192688e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.054454281403641e-08</v>
+        <v>8.054454281403628e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4889,7 +4889,7 @@
         <v>1.519176616295638e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.435028348059922e-08</v>
+        <v>1.435028348059921e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.558129382866534e-08</v>
@@ -4898,25 +4898,25 @@
         <v>1.527983754440153e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.524751170465991e-08</v>
+        <v>1.52475117046599e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.571956462567255e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.531767713270124e-08</v>
+        <v>1.531767713270123e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.540619459063394e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.548480839850694e-08</v>
+        <v>1.548480839850693e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.587405417308495e-08</v>
+        <v>1.587405417308494e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.609490152296642e-08</v>
+        <v>1.609490152296643e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.533432109273869e-08</v>
@@ -4928,10 +4928,10 @@
         <v>2.485523821949045e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.544464042313725e-08</v>
+        <v>1.544464042313726e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53811981990919e-08</v>
+        <v>1.538119819909189e-08</v>
       </c>
       <c r="R2" t="n">
         <v>1.536045630281883e-08</v>
@@ -4943,28 +4943,28 @@
         <v>1.527927672998903e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.17828474540964e-08</v>
+        <v>2.178284745409639e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.518834890518762e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.258805882483522e-08</v>
+        <v>2.258805882483523e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.540884255241254e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.520321919222061e-08</v>
+        <v>1.520321919222062e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.601586090977481e-08</v>
+        <v>2.60158609097748e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.538709203538945e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.766763595040199e-08</v>
+        <v>1.766763595040198e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.250682227993276e-08</v>
+        <v>1.256811365819271e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.076043923432104e-08</v>
+        <v>1.080548028459424e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.529985543824226e-08</v>
+        <v>1.546067038304478e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.313209958390656e-08</v>
+        <v>1.321497354786959e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.291321466878182e-08</v>
+        <v>1.298953227513095e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.624390685290616e-08</v>
+        <v>1.643725707335447e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.342053771218366e-08</v>
+        <v>1.351489515025361e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.404977911399665e-08</v>
+        <v>1.416630567580983e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.458859389050363e-08</v>
+        <v>1.472369401161941e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.736586504918709e-08</v>
+        <v>1.760072205664213e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.891113538653845e-08</v>
+        <v>1.919990612148505e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.376170315926539e-08</v>
+        <v>1.386979232000459e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.568765780272061e-08</v>
+        <v>1.586198839860698e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.859831848171058e-08</v>
+        <v>2.866601728205118e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.430485835301341e-08</v>
+        <v>1.442917362079273e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.386139054680759e-08</v>
+        <v>1.397117020257788e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.372541086838854e-08</v>
+        <v>1.383047210354527e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.350538296832315e-08</v>
+        <v>1.360229126987905e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.313796808991294e-08</v>
+        <v>1.322212841248515e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.386796429995571e-08</v>
+        <v>2.395095417853971e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.247832715418099e-08</v>
+        <v>1.253864746301807e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.568674536507912e-08</v>
+        <v>2.5792743452506e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.406447814370285e-08</v>
+        <v>1.418141011917916e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.259303372010665e-08</v>
+        <v>1.265759000682395e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.119689821935017e-08</v>
+        <v>3.129610833974847e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.390544486006591e-08</v>
+        <v>1.401634591273429e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.010400447730702e-08</v>
+        <v>3.078901783918044e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.982806973141323e-08</v>
+        <v>4.982806973141322e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.907938095035054e-08</v>
+        <v>4.907938095035055e-08</v>
       </c>
       <c r="D4" t="n">
         <v>5.42279639071753e-08</v>
@@ -5077,70 +5077,70 @@
         <v>5.045774126917065e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.578979616708079e-08</v>
+        <v>5.57897961670808e-08</v>
       </c>
       <c r="H4" t="n">
         <v>5.12502920565891e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.225013746398138e-08</v>
+        <v>5.22501374639814e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.308163555722786e-08</v>
+        <v>5.308163555722798e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.753482667380683e-08</v>
+        <v>5.753482667380682e-08</v>
       </c>
       <c r="L4" t="n">
         <v>6.002939908551831e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.186821142897803e-08</v>
+        <v>5.186821142897801e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.48577325318828e-08</v>
+        <v>5.485773253188279e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.011976381650166e-08</v>
+        <v>5.011976381650165e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.268440082806313e-08</v>
+        <v>5.268440082806311e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.196779172260575e-08</v>
+        <v>5.196779172260572e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.17335024624577e-08</v>
+        <v>5.173350246245771e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.142675116681947e-08</v>
+        <v>5.142675116681948e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.081654184289693e-08</v>
+        <v>5.081654184289695e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.0509065030993e-08</v>
+        <v>5.050906503099301e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>4.940644103919471e-08</v>
+        <v>4.940644103919503e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.181784523737964e-08</v>
+        <v>5.181784523737962e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.228004741039315e-08</v>
+        <v>5.228004741039313e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.967260661163927e-08</v>
+        <v>4.967260661163929e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.153728227180711e-08</v>
+        <v>5.153728227180712e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.203436531488528e-08</v>
+        <v>5.203436531488527e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.753814030928968e-08</v>
+        <v>7.753814030928967e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,55 +5150,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.991376551787122e-08</v>
+        <v>7.991376551787128e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>6.916013701693257e-08</v>
+        <v>6.916013701693258e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.703113797451849e-07</v>
+        <v>1.703113797451845e-07</v>
       </c>
       <c r="E5" t="n">
         <v>9.689232562269763e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.656555944211627e-08</v>
+        <v>9.656555944211615e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.760422883885753e-07</v>
+        <v>1.76042288388576e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.15193211513347e-07</v>
+        <v>1.151932115133469e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.327010783539094e-07</v>
+        <v>1.327010783539093e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.370567588356658e-07</v>
+        <v>1.370567588356661e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.198034846565734e-07</v>
+        <v>2.198034846565735e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.497698288427716e-07</v>
+        <v>2.497698288427715e-07</v>
       </c>
       <c r="M5" t="n">
         <v>1.20644254907727e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>1.765920085809781e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>8.458734400343651e-08</v>
+        <v>8.458734400343646e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.301724637090134e-07</v>
+        <v>1.301724637090136e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.218076218390375e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.240828242039594e-07</v>
+        <v>1.240828242039596e-07</v>
       </c>
       <c r="S5" t="n">
         <v>1.037078686430641e-07</v>
@@ -5207,28 +5207,28 @@
         <v>1.022623663577292e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>9.860128903758043e-08</v>
+        <v>9.860128903758031e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.651734716512869e-08</v>
+        <v>7.65173471651289e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.200531362939261e-07</v>
+        <v>1.200531362939262e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.309309927013906e-07</v>
+        <v>1.309309927013907e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.484616272877866e-08</v>
+        <v>8.484616272877865e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.08192043116149e-07</v>
+        <v>1.081920431161489e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.241729705409915e-07</v>
+        <v>1.241729705409914e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.404900007820423e-07</v>
+        <v>6.404900007820427e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.82344752366303e-08</v>
+        <v>4.823447523663028e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.748578645556764e-08</v>
+        <v>4.748578645556763e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.986724581492917e-08</v>
+        <v>5.986724581492925e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.646215840742732e-08</v>
+        <v>5.646215840742735e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.886414677438773e-08</v>
+        <v>4.886414677438774e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.419620167229787e-08</v>
+        <v>5.419620167229788e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.68895739643429e-08</v>
+        <v>5.688957396434306e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.788941937173527e-08</v>
+        <v>5.788941937173536e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.148804106244493e-08</v>
+        <v>5.148804106244504e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.31741085815609e-08</v>
+        <v>6.317410858156079e-08</v>
       </c>
       <c r="L6" t="n">
         <v>5.843580459073537e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.750749333673176e-08</v>
+        <v>5.750749333673201e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.326295750191548e-08</v>
+        <v>5.326295750191554e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.594802012304349e-08</v>
+        <v>5.594802012304374e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.851367414479699e-08</v>
+        <v>5.851367414479706e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.760707363035948e-08</v>
+        <v>5.76070736303597e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.737278437021163e-08</v>
+        <v>5.737278437021168e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>4.983315667203654e-08</v>
+        <v>4.983315667203655e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.922294734811404e-08</v>
+        <v>4.922294734811403e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.920030089017721e-08</v>
+        <v>4.920030089017723e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.50457229469484e-08</v>
+        <v>5.5045722946949e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.764631521279115e-08</v>
+        <v>5.764631521279106e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.068645291561023e-08</v>
+        <v>5.068645291561021e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.84718868506613e-08</v>
+        <v>4.847188685066129e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>4.994368777702421e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.767364722263912e-08</v>
+        <v>5.767364722263926e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.611175755370716e-08</v>
+        <v>7.611175755370714e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,55 +5326,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.50539719197573e-08</v>
+        <v>5.505397191975731e-08</v>
       </c>
       <c r="C7" t="n">
         <v>5.430528313869465e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.945386609551938e-08</v>
+        <v>5.945386609551936e-08</v>
       </c>
       <c r="E7" t="n">
         <v>5.604877868801748e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.568364345751476e-08</v>
+        <v>5.568364345751474e-08</v>
       </c>
       <c r="G7" t="n">
         <v>6.10156983554249e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.647619424493321e-08</v>
+        <v>5.647619424493319e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.74760396523255e-08</v>
+        <v>5.747603965232549e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.830753774557202e-08</v>
+        <v>5.830753774557208e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.276072886215093e-08</v>
+        <v>6.276072886215092e-08</v>
       </c>
       <c r="L7" t="n">
         <v>6.525530127386241e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.709411361732215e-08</v>
+        <v>5.709411361732212e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.008363472022692e-08</v>
+        <v>6.008363472022691e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.534432794384258e-08</v>
+        <v>5.534432794384256e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.790896495540403e-08</v>
+        <v>5.790896495540404e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>5.719369391094982e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.695940465080181e-08</v>
+        <v>5.695940465080182e-08</v>
       </c>
       <c r="S7" t="n">
         <v>5.665265335516358e-08</v>
@@ -5386,22 +5386,22 @@
         <v>5.601637696051045e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.463234322753912e-08</v>
+        <v>5.463234322753913e-08</v>
       </c>
       <c r="W7" t="n">
         <v>5.704374742572374e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>5.750594959873725e-08</v>
+        <v>5.750594959873724e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.51833391539505e-08</v>
+        <v>5.518333915395051e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.676318446015124e-08</v>
+        <v>5.676318446015123e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.726026750322938e-08</v>
+        <v>5.726026750322939e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>8.276404249763379e-08</v>
@@ -5414,82 +5414,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.404813846308976e-08</v>
+        <v>6.404813846308982e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.520154043332856e-08</v>
+        <v>7.520154043332861e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.035012339015329e-08</v>
+        <v>8.035012339015335e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.060752374713318e-08</v>
+        <v>7.060752374713323e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.653201663677959e-08</v>
+        <v>6.653201663677964e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>8.437993170232986e-08</v>
+        <v>8.437993170232993e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.737245153956706e-08</v>
+        <v>7.737245153956714e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.837229694695939e-08</v>
+        <v>7.837229694695941e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.920379504020588e-08</v>
+        <v>7.920379504020606e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>8.365698615678489e-08</v>
+        <v>8.365698615678491e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.61515585684963e-08</v>
+        <v>8.615155856849634e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.799037091195467e-08</v>
+        <v>7.799037091195471e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>7.175378050572232e-08</v>
+        <v>7.17537805057224e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>6.955122734182228e-08</v>
+        <v>6.95512273418223e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.14943727375075e-08</v>
+        <v>7.149437273750753e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.384882796926455e-08</v>
+        <v>6.384882796926461e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.78556619454357e-08</v>
+        <v>7.785566194543571e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.754891064979741e-08</v>
+        <v>7.754891064979747e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.693870132587493e-08</v>
+        <v>7.693870132587499e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.110518930064904e-08</v>
+        <v>7.110518930064913e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.227379954394072e-08</v>
+        <v>7.227379954394104e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.794234382149155e-08</v>
+        <v>7.794234382149162e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.525193392400009e-08</v>
+        <v>6.525193392400011e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.791081341523173e-08</v>
+        <v>8.791081341523181e-08</v>
       </c>
       <c r="Z8" t="n">
         <v>6.553626355680326e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.815652479786326e-08</v>
+        <v>7.81565247978633e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>1.160930288188316e-07</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.032939118995482e-08</v>
+        <v>7.032939118995484e-08</v>
       </c>
       <c r="C9" t="n">
         <v>7.649823326487625e-08</v>
@@ -5511,7 +5511,7 @@
         <v>8.1646816221701e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.664519768738318e-08</v>
+        <v>7.664519768738317e-08</v>
       </c>
       <c r="F9" t="n">
         <v>6.192978548457424e-08</v>
@@ -5526,7 +5526,7 @@
         <v>7.966898977850712e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.050048787175357e-08</v>
+        <v>8.050048787175366e-08</v>
       </c>
       <c r="K9" t="n">
         <v>8.495367898833254e-08</v>
@@ -5535,49 +5535,49 @@
         <v>8.744825140004397e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.928706374350374e-08</v>
+        <v>7.928706374350373e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.227658484640851e-08</v>
+        <v>8.227658484640853e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.983108853198728e-08</v>
+        <v>7.983108853198726e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.28942970419759e-08</v>
+        <v>8.289429704197585e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.938665284968332e-08</v>
+        <v>7.938665284968333e-08</v>
       </c>
       <c r="R9" t="n">
         <v>7.915235477698345e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.884560348134518e-08</v>
+        <v>7.884560348134521e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.823539415742267e-08</v>
+        <v>7.823539415742265e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.821274769948588e-08</v>
+        <v>7.821274769948585e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.480798714247632e-08</v>
+        <v>8.480798714247652e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.923669755190537e-08</v>
+        <v>7.923669755190536e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.969889972491886e-08</v>
+        <v>7.969889972491885e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.737628928013216e-08</v>
+        <v>7.737628928013213e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.478548211038559e-08</v>
+        <v>7.478548211038558e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.9453217629411e-08</v>
+        <v>7.945321762941099e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>1.049569926238154e-07</v>
@@ -5752,13 +5752,13 @@
         <v>1.41140079955278e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490860283853526e-08</v>
+        <v>1.490860283853525e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.491856187429225e-08</v>
+        <v>1.491856187429227e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.502414861883302e-08</v>
+        <v>1.502414861883303e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.498401637302283e-08</v>
@@ -5767,25 +5767,25 @@
         <v>1.490366163065193e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.495354846066019e-08</v>
+        <v>1.495354846066018e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.496878950277157e-08</v>
+        <v>1.496878950277156e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.488549072558387e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496461271239283e-08</v>
+        <v>1.496461271239281e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.478714886926006e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.50464858235156e-08</v>
+        <v>1.504648582351559e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.473921011610182e-08</v>
+        <v>2.473921011610181e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.490131301524221e-08</v>
@@ -5803,19 +5803,19 @@
         <v>1.483137821737164e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.121401819912116e-08</v>
+        <v>2.121401819912115e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49115780010033e-08</v>
+        <v>1.491157800100331e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.23063082751999e-08</v>
+        <v>2.230630827519991e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.512833053681967e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.488179751547654e-08</v>
+        <v>1.488179751547653e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>2.577143275054289e-08</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.2485077755481e-08</v>
+        <v>1.255833177483185e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.122592578822982e-08</v>
+        <v>1.129991285319393e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.269233792079663e-08</v>
+        <v>1.27735157264953e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.275494034362144e-08</v>
+        <v>1.283730296348853e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.351910738767522e-08</v>
+        <v>1.363004610469407e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.321510625406312e-08</v>
+        <v>1.331431545807274e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.266415170099087e-08</v>
+        <v>1.274444773675346e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.301644844033443e-08</v>
+        <v>1.310916642736264e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.311251105744067e-08</v>
+        <v>1.320824579291439e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.252508652066982e-08</v>
+        <v>1.260032407583671e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.307650651203179e-08</v>
+        <v>1.317126071015915e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.206941446859378e-08</v>
+        <v>1.212995318241374e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.367270564245505e-08</v>
+        <v>1.378851312604815e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.013090275711584e-08</v>
+        <v>3.026719804165533e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.263310699560948e-08</v>
+        <v>1.271149126526892e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.218504801491935e-08</v>
+        <v>1.224820787724387e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.451015565024693e-08</v>
+        <v>1.465615341616071e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.288337150412782e-08</v>
+        <v>1.297103083623273e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.214216597639991e-08</v>
+        <v>1.220375670782013e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.242340008982085e-08</v>
+        <v>2.247250471110261e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.270007836749703e-08</v>
+        <v>1.278105047245924e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.630636411117507e-08</v>
+        <v>2.645197665237571e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.425597286237508e-08</v>
+        <v>1.439284035011051e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.250084522970099e-08</v>
+        <v>1.257492360934368e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.151091991603284e-08</v>
+        <v>3.163257941785276e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.287459141727915e-08</v>
+        <v>1.296184863611966e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16834035050699e-08</v>
+        <v>1.172905889658614e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,22 +5922,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.972107135743719e-08</v>
+        <v>4.972107135743721e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.972262634314278e-08</v>
+        <v>4.97226263431428e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.003995284727661e-08</v>
+        <v>5.00399528472766e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.015244473753456e-08</v>
+        <v>5.015244473753457e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.134509558942473e-08</v>
+        <v>5.134509558942475e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.089178341125336e-08</v>
+        <v>5.089178341125337e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.998413963116639e-08</v>
@@ -5949,31 +5949,31 @@
         <v>5.067159508803092e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.977889089939314e-08</v>
+        <v>4.977889089939315e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.06726101383126e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.911590607530825e-08</v>
+        <v>4.911590607530826e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.159740459193632e-08</v>
+        <v>5.15974045919363e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.257456072119152e-08</v>
+        <v>5.257456072119155e-08</v>
       </c>
       <c r="P4" t="n">
         <v>4.995761093969715e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.924283594501676e-08</v>
+        <v>4.924283594501678e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.290200702879089e-08</v>
+        <v>5.290200702879087e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.036312077716012e-08</v>
+        <v>5.036312077716014e-08</v>
       </c>
       <c r="T4" t="n">
         <v>4.916766522615252e-08</v>
@@ -5982,25 +5982,25 @@
         <v>4.86053040959174e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>4.974596762084284e-08</v>
+        <v>4.974596762084283e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.294678427060507e-08</v>
+        <v>5.294678427060508e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.252187827913391e-08</v>
+        <v>5.252187827913389e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.971815638252291e-08</v>
+        <v>4.97181563825229e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.190304681409601e-08</v>
+        <v>5.190304681409602e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.032911270443002e-08</v>
+        <v>5.032911270443004e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.84596768364995e-08</v>
+        <v>4.845967683649951e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6010,82 +6010,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.4410884340202e-08</v>
+        <v>8.441088434020209e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.741446772320375e-08</v>
+        <v>8.741446772320393e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.304332670625223e-08</v>
+        <v>9.304332670625221e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.064060836812919e-08</v>
+        <v>9.064060836812914e-08</v>
       </c>
       <c r="F5" t="n">
         <v>1.172221834716745e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.000966581964275e-07</v>
+        <v>1.000966581964278e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>9.572491175375213e-08</v>
+        <v>9.572491175375227e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.037489115009085e-07</v>
+        <v>1.037489115009086e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.001571267027229e-07</v>
+        <v>1.001571267027231e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>8.723456615032893e-08</v>
+        <v>8.723456615032896e-08</v>
       </c>
       <c r="L5" t="n">
         <v>9.616069971518403e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.700249716848819e-08</v>
+        <v>7.700249716848815e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.186668090234259e-07</v>
+        <v>1.186668090234261e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.276383937882209e-07</v>
+        <v>1.276383937882211e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>8.785415368081557e-08</v>
+        <v>8.785415368081563e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.70635101599833e-08</v>
+        <v>7.706351015998331e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.485479475132211e-07</v>
+        <v>1.485479475132213e-07</v>
       </c>
       <c r="S5" t="n">
         <v>9.193901091853711e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.812542763015468e-08</v>
+        <v>7.812542763015471e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.744997487946989e-08</v>
+        <v>6.744997487946985e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.631747877560794e-08</v>
+        <v>8.631747877560801e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.397237326736819e-07</v>
+        <v>1.397237326736817e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.345706419334148e-07</v>
+        <v>1.34570641933415e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.759399544897568e-08</v>
+        <v>8.759399544897559e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>1.169579659814157e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.79230975898434e-08</v>
+        <v>9.792309758984337e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>6.640610531499987e-08</v>
@@ -6098,22 +6098,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.46696816676107e-08</v>
+        <v>5.466968166761072e-08</v>
       </c>
       <c r="C6" t="n">
         <v>4.832151026047132e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.863883676460514e-08</v>
+        <v>4.863883676460515e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.875132865486308e-08</v>
+        <v>4.87513286548631e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.629370589959825e-08</v>
+        <v>5.629370589959827e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.584039372142687e-08</v>
+        <v>5.584039372142689e-08</v>
       </c>
       <c r="H6" t="n">
         <v>5.493274994133989e-08</v>
@@ -6122,22 +6122,22 @@
         <v>5.549624463535879e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.562020539820442e-08</v>
+        <v>5.562020539820444e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.472750120956662e-08</v>
+        <v>5.472750120956666e-08</v>
       </c>
       <c r="L6" t="n">
         <v>4.927149405564112e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.406451638548176e-08</v>
+        <v>5.406451638548178e-08</v>
       </c>
       <c r="N6" t="n">
         <v>5.019565715147587e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.766075537893885e-08</v>
+        <v>5.766075537893883e-08</v>
       </c>
       <c r="P6" t="n">
         <v>4.840780815904826e-08</v>
@@ -6149,22 +6149,22 @@
         <v>5.150089094611941e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.531173108733365e-08</v>
+        <v>5.531173108733367e-08</v>
       </c>
       <c r="T6" t="n">
         <v>4.776654914348104e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.722320602299333e-08</v>
+        <v>4.722320602299334e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.834485153817139e-08</v>
+        <v>4.834485153817137e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.169588815469589e-08</v>
+        <v>5.169588815469588e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.747048858930742e-08</v>
+        <v>5.747048858930741e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>4.84453810609761e-08</v>
@@ -6186,31 +6186,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.438112971686775e-08</v>
+        <v>5.438112971686777e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.438268470257332e-08</v>
+        <v>5.438268470257335e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.470001120670715e-08</v>
+        <v>5.470001120670718e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.481250309696513e-08</v>
+        <v>5.481250309696512e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.600515394885528e-08</v>
+        <v>5.600515394885532e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.555184177068389e-08</v>
+        <v>5.55518417706839e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.464419799059692e-08</v>
+        <v>5.464419799059693e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.520769268461583e-08</v>
+        <v>5.520769268461584e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.533165344746146e-08</v>
+        <v>5.53316534474615e-08</v>
       </c>
       <c r="K7" t="n">
         <v>5.443894925882369e-08</v>
@@ -6219,52 +6219,52 @@
         <v>5.533266849774313e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.377596443473881e-08</v>
+        <v>5.377596443473883e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.625746295136686e-08</v>
+        <v>5.625746295136689e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.723336378063752e-08</v>
+        <v>5.723336378063755e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.461641399914316e-08</v>
+        <v>5.461641399914317e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.390289430444728e-08</v>
+        <v>5.390289430444729e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.756206538822143e-08</v>
+        <v>5.756206538822144e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.502317913659067e-08</v>
+        <v>5.50231791365907e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.382772358558304e-08</v>
+        <v>5.382772358558307e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.32827029624893e-08</v>
+        <v>5.328270296248929e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.44060259802734e-08</v>
+        <v>5.440602598027342e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.760684263003561e-08</v>
+        <v>5.760684263003564e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>5.718193663856446e-08</v>
+        <v>5.71819366385645e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.439723275170086e-08</v>
+        <v>5.439723275170088e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.656310517352658e-08</v>
+        <v>5.65631051735266e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.498917106386057e-08</v>
+        <v>5.498917106386058e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.311973519593004e-08</v>
+        <v>5.311973519593005e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.251367463651922e-08</v>
+        <v>6.251367463651925e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.325507813783319e-08</v>
+        <v>7.325507813783322e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.357240464196701e-08</v>
+        <v>7.3572404641967e-08</v>
       </c>
       <c r="E8" t="n">
         <v>6.796624400322154e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.581084174756842e-08</v>
+        <v>6.581084174756845e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.665121275933648e-08</v>
+        <v>7.665121275933649e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.351659142585681e-08</v>
+        <v>7.351659142585679e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.40800861198757e-08</v>
+        <v>7.408008611987567e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.420404688272129e-08</v>
+        <v>7.420404688272132e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.331134269408353e-08</v>
+        <v>7.331134269408354e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.420506193300301e-08</v>
+        <v>7.420506193300294e-08</v>
       </c>
       <c r="M8" t="n">
         <v>7.26483578699972e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.680467704908084e-08</v>
+        <v>6.680467704908086e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.006966474643224e-08</v>
+        <v>7.006966474643225e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.68919121658556e-08</v>
+        <v>6.689191216585562e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.992481386530821e-08</v>
+        <v>5.992481386530824e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.643445882348128e-08</v>
+        <v>7.643445882348126e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.38955725718505e-08</v>
+        <v>7.389557257185052e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.270011702084292e-08</v>
+        <v>7.27001170208429e-08</v>
       </c>
       <c r="U8" t="n">
         <v>6.691446998593511e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.034269599021648e-08</v>
+        <v>7.034269599021646e-08</v>
       </c>
       <c r="W8" t="n">
         <v>7.648134675260765e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.418818465609318e-08</v>
+        <v>6.418818465609314e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.394745337337385e-08</v>
+        <v>8.394745337337388e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.449615189275452e-08</v>
+        <v>6.44961518927545e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.386156449912041e-08</v>
+        <v>7.386156449912043e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.321079845745764e-08</v>
+        <v>8.321079845745762e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.635225979470723e-08</v>
+        <v>6.635225979470725e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.208994356794589e-08</v>
+        <v>7.208994356794586e-08</v>
       </c>
       <c r="D9" t="n">
         <v>7.240727007207969e-08</v>
@@ -6374,73 +6374,73 @@
         <v>7.119589352489763e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.048905906941691e-08</v>
+        <v>6.048905906941693e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.325910933268159e-08</v>
+        <v>7.325910933268161e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.235145685596943e-08</v>
+        <v>7.235145685596949e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.291495154998834e-08</v>
+        <v>7.291495154998836e-08</v>
       </c>
       <c r="J9" t="n">
         <v>7.303891231283401e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.214620812419621e-08</v>
+        <v>7.214620812419622e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.303992736311562e-08</v>
+        <v>7.303992736311568e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.148322330011135e-08</v>
+        <v>7.148322330011139e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.396472181673943e-08</v>
+        <v>7.396472181673947e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.684283509403926e-08</v>
+        <v>7.68428350940393e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.463930898594543e-08</v>
+        <v>7.463930898594547e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.161016186644495e-08</v>
+        <v>7.161016186644498e-08</v>
       </c>
       <c r="R9" t="n">
         <v>7.526932425359397e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.27304380019632e-08</v>
+        <v>7.273043800196321e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.153498245095562e-08</v>
+        <v>7.153498245095568e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.099163933046787e-08</v>
+        <v>7.099163933046788e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.873266679216586e-08</v>
+        <v>7.873266679216589e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.531410149540816e-08</v>
+        <v>7.531410149540819e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.488919550393699e-08</v>
+        <v>7.488919550393693e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>7.21044916170734e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.081199190982373e-08</v>
+        <v>7.081199190982377e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.269642992923306e-08</v>
+        <v>7.26964299292331e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.082699406130257e-08</v>
+        <v>7.082699406130259e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,64 +6606,64 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.5005974058132e-08</v>
+        <v>1.500597405813199e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.407738118581796e-08</v>
+        <v>1.407738118581797e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49473360468672e-08</v>
+        <v>1.494733604686725e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.506884454911491e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.498838128586335e-08</v>
+        <v>1.498838128586336e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.491468873465065e-08</v>
+        <v>1.491468873465064e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.487188728391711e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.488794367967563e-08</v>
+        <v>1.488794367967565e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.496602179487705e-08</v>
+        <v>1.496602179487708e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.48595217885042e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.499492372140163e-08</v>
+        <v>1.499492372140164e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.480026701330397e-08</v>
+        <v>1.480026701330398e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.491129134376721e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.478331101676366e-08</v>
+        <v>2.478331101676365e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.498600481118118e-08</v>
+        <v>1.498600481118119e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.484201415566625e-08</v>
+        <v>1.484201415566626e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.524798901978136e-08</v>
+        <v>1.524798901978139e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.495020287668684e-08</v>
+        <v>1.495020287668687e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483655662619996e-08</v>
+        <v>1.483655662619998e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.111046562147364e-08</v>
+        <v>2.111046562147366e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.517118933034813e-08</v>
@@ -6672,16 +6672,16 @@
         <v>2.230306558797887e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.52241441494543e-08</v>
+        <v>1.522414414945432e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.491944758709745e-08</v>
+        <v>1.491944758709744e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.568228761336063e-08</v>
+        <v>2.568228761336067e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.495989093722141e-08</v>
+        <v>1.495989093722142e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.482525661380449e-08</v>
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.325033830798911e-08</v>
+        <v>1.335035237470968e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.127512379654335e-08</v>
+        <v>1.135535829113849e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.284232474068837e-08</v>
+        <v>1.292859571108398e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.369315439595143e-08</v>
+        <v>1.380865371765231e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.31385202563192e-08</v>
+        <v>1.323555757782156e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.260078968048455e-08</v>
+        <v>1.267800808087243e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.230795956672465e-08</v>
+        <v>1.237534584038368e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.24203830176148e-08</v>
+        <v>1.249165544969865e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2968461396595e-08</v>
+        <v>1.305887969704329e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.221465480860754e-08</v>
+        <v>1.227857357331619e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.316898097722699e-08</v>
+        <v>1.326667784125491e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.203163920960533e-08</v>
+        <v>1.209053046720369e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.258349717894804e-08</v>
+        <v>1.266040252861515e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.034556296979812e-08</v>
+        <v>3.048950046295698e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.310630019573553e-08</v>
+        <v>1.320118648348334e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.208834501652523e-08</v>
+        <v>1.21477868960933e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.499992795968199e-08</v>
+        <v>1.516308410609557e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28528775859026e-08</v>
+        <v>1.293913129349784e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.205227546946125e-08</v>
+        <v>1.211043526596145e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2468677061857e-08</v>
+        <v>2.252894721073665e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.441676771880897e-08</v>
+        <v>1.455810456268119e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.683150370300459e-08</v>
+        <v>2.700258343905129e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.480880427882821e-08</v>
+        <v>1.496524262964772e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.264274018126856e-08</v>
+        <v>1.27216180369945e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.087800521319575e-08</v>
+        <v>3.09785420249728e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.293075160660661e-08</v>
+        <v>1.301978869365189e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.204274706465129e-08</v>
+        <v>1.210087344309873e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6782,82 +6782,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.10690786891206e-08</v>
+        <v>5.106907868912061e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.014098781764234e-08</v>
+        <v>5.014098781764238e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.040673537706744e-08</v>
+        <v>5.040673537706746e-08</v>
       </c>
       <c r="E4" t="n">
         <v>5.177922980662746e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.08703602332714e-08</v>
+        <v>5.087036023327142e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.003796896707524e-08</v>
+        <v>5.003796896707525e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.955450689139991e-08</v>
+        <v>4.955450689139993e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.973587126779975e-08</v>
+        <v>4.973587126779977e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.057477024875802e-08</v>
+        <v>5.057477024875804e-08</v>
       </c>
       <c r="K4" t="n">
         <v>4.941483293230213e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.094426005234533e-08</v>
+        <v>5.094426005234536e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.918341901117808e-08</v>
+        <v>4.918341901117811e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.999959387416985e-08</v>
+        <v>4.999959387416987e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.305917557176315e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.08435168585039e-08</v>
+        <v>5.084351685850391e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.921707616548858e-08</v>
+        <v>4.92170761654886e-08</v>
       </c>
       <c r="R4" t="n">
         <v>5.38027490133334e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.043911753868703e-08</v>
+        <v>5.043911753868705e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.915543085957948e-08</v>
+        <v>4.915543085957951e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>4.940220407187641e-08</v>
+        <v>4.940220407187642e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.264237811240315e-08</v>
+        <v>5.264237811240317e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.422785601440094e-08</v>
+        <v>5.422785601440093e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.353341023380695e-08</v>
+        <v>5.353341023380697e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.022837620994609e-08</v>
+        <v>5.02283762099461e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.108899761126093e-08</v>
+        <v>5.108899761126096e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.054854863915278e-08</v>
+        <v>5.054854863915283e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>4.915452293915272e-08</v>
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.027122242709102e-07</v>
+        <v>1.027122242709103e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.134026791165993e-08</v>
+        <v>9.134026791165994e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.643316677480954e-08</v>
+        <v>9.643316677480951e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.12218136905741e-07</v>
+        <v>1.122181369057409e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.063192325522381e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>8.549069302880024e-08</v>
+        <v>8.549069302880037e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.349332417607696e-08</v>
+        <v>8.3493324176077e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.557554821161009e-08</v>
+        <v>8.557554821161012e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.637926174446047e-08</v>
+        <v>9.637926174446055e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.840509547411485e-08</v>
+        <v>7.840509547411496e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.921394834833276e-08</v>
+        <v>9.921394834833273e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.533357838591336e-08</v>
+        <v>7.533357838591341e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.84161393079848e-08</v>
+        <v>8.841613930798488e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.32376510936813e-07</v>
+        <v>1.323765109368131e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>9.793685089062874e-08</v>
+        <v>9.793685089062907e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.420423900205166e-08</v>
+        <v>7.420423900205165e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.626268142004109e-07</v>
+        <v>1.626268142004111e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>9.187140007902346e-08</v>
+        <v>9.187140007902349e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.460700379978273e-08</v>
+        <v>7.460700379978288e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.406345838502506e-08</v>
+        <v>7.406345838502514e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.288339247566721e-07</v>
+        <v>1.28833924756672e-07</v>
       </c>
       <c r="W5" t="n">
         <v>1.594699662386995e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.470106322584523e-07</v>
+        <v>1.470106322584526e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.058012627016271e-08</v>
+        <v>9.058012627016264e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.003604080408215e-07</v>
+        <v>1.003604080408216e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.833089321544778e-08</v>
+        <v>9.833089321544854e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.576467225928097e-08</v>
+        <v>7.576467225928099e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.606071450956778e-08</v>
+        <v>5.606071450956783e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>5.513262363808956e-08</v>
+        <v>5.51326236380896e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.539837119751462e-08</v>
+        <v>5.539837119751466e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.049978771691589e-08</v>
+        <v>5.049978771691592e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.586199605371861e-08</v>
+        <v>5.586199605371862e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>5.502960478752244e-08</v>
+        <v>5.502960478752248e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.454614271184709e-08</v>
+        <v>5.454614271184713e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.472750708824692e-08</v>
+        <v>5.472750708824697e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.929532815904647e-08</v>
+        <v>4.929532815904649e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.813539084259058e-08</v>
+        <v>4.81353908425906e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>5.593589587279253e-08</v>
+        <v>5.593589587279256e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.41750548316253e-08</v>
+        <v>5.417505483162532e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8718733718554e-08</v>
+        <v>4.871873371855402e-08</v>
       </c>
       <c r="O6" t="n">
         <v>5.180346955695409e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.59564624544745e-08</v>
+        <v>5.59564624544746e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.420871198593578e-08</v>
+        <v>5.420871198593581e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.879438483378059e-08</v>
+        <v>5.879438483378064e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.543075335913424e-08</v>
+        <v>5.543075335913427e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.787598876986796e-08</v>
+        <v>4.787598876986798e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.425718607701975e-08</v>
+        <v>5.425718607701977e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>5.136293602269164e-08</v>
+        <v>5.136293602269168e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.933910491125533e-08</v>
+        <v>5.93391049112554e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>5.225396814409538e-08</v>
+        <v>5.22539681440954e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.893834115326041e-08</v>
+        <v>4.893834115326037e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.980955552154938e-08</v>
+        <v>4.980955552154941e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.554018445959998e-08</v>
+        <v>5.554018445960006e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.786020601107494e-08</v>
+        <v>4.786020601107496e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.574399383559652e-08</v>
+        <v>5.574399383559654e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.48159029641183e-08</v>
+        <v>5.481590296411831e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>5.508165052354336e-08</v>
+        <v>5.508165052354337e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.645414495310339e-08</v>
+        <v>5.645414495310343e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.554527537974733e-08</v>
+        <v>5.554527537974735e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>5.471288411355118e-08</v>
+        <v>5.47128841135512e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.422942203787585e-08</v>
+        <v>5.422942203787587e-08</v>
       </c>
       <c r="I7" t="n">
         <v>5.441078641427569e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>5.524968539523393e-08</v>
+        <v>5.524968539523395e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.408974807877807e-08</v>
+        <v>5.408974807877808e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>5.561917519882125e-08</v>
+        <v>5.561917519882127e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.385833415765402e-08</v>
+        <v>5.385833415765404e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.467450902064578e-08</v>
+        <v>5.46745090206458e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.773282881830237e-08</v>
+        <v>5.773282881830238e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>5.55171701050431e-08</v>
+        <v>5.551717010504312e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.38919913119645e-08</v>
+        <v>5.389199131196452e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.847766415980934e-08</v>
+        <v>5.847766415980936e-08</v>
       </c>
       <c r="S7" t="n">
         <v>5.5114032685163e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>5.383034600605543e-08</v>
+        <v>5.383034600605546e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.394131477935015e-08</v>
+        <v>5.394131477935018e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.73172932588791e-08</v>
+        <v>5.731729325887912e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.890277116087687e-08</v>
+        <v>5.890277116087689e-08</v>
       </c>
       <c r="X7" t="n">
         <v>5.820832538028289e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.476663754111815e-08</v>
+        <v>5.476663754111817e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.576391275773686e-08</v>
+        <v>5.576391275773687e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.522346378562872e-08</v>
+        <v>5.522346378562878e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.382943808562864e-08</v>
+        <v>5.382943808562865e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.383890600746224e-08</v>
+        <v>6.383890600746226e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.363370014854604e-08</v>
+        <v>7.363370014854611e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.389944770797115e-08</v>
+        <v>7.389944770797119e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>6.956232217350775e-08</v>
+        <v>6.956232217350778e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.531068771515295e-08</v>
+        <v>6.531068771515297e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>7.575414135850762e-08</v>
+        <v>7.575414135850767e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.304721922230359e-08</v>
+        <v>7.304721922230366e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.322858359870342e-08</v>
+        <v>7.32285835987035e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>7.406748257966176e-08</v>
+        <v>7.406748257966177e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.29075452632058e-08</v>
+        <v>7.290754526320582e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4436972383249e-08</v>
+        <v>7.443697238324904e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>7.267613134208089e-08</v>
+        <v>7.267613134208093e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.518027642031464e-08</v>
+        <v>6.518027642031466e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>7.052407607471924e-08</v>
+        <v>7.052407607471927e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>6.77485003458211e-08</v>
+        <v>6.774850034582111e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.987961184055914e-08</v>
+        <v>5.987961184055915e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.729546134423714e-08</v>
+        <v>7.729546134423715e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.393182986959074e-08</v>
+        <v>7.393182986959078e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.264814319048322e-08</v>
+        <v>7.264814319048328e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>6.752620171640009e-08</v>
+        <v>6.752620171640012e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.320616895415292e-08</v>
+        <v>7.320616895415297e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>7.772267569879282e-08</v>
+        <v>7.77226756987929e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.517871962677928e-08</v>
+        <v>6.51787196267793e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.42487542656526e-08</v>
+        <v>8.424875426565266e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.36596418349541e-08</v>
+        <v>6.365964183495412e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.40412609700565e-08</v>
+        <v>7.404126097005655e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.384818529892402e-08</v>
+        <v>8.384818529892404e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.665955384377246e-08</v>
+        <v>6.665955384377249e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.11786932558521e-08</v>
+        <v>7.117869325585217e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.144444081527724e-08</v>
+        <v>7.144444081527727e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>7.155974289972328e-08</v>
+        <v>7.155974289972335e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>5.935070268145287e-08</v>
+        <v>5.935070268145289e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>7.107568244669282e-08</v>
+        <v>7.107568244669288e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.059221232960968e-08</v>
+        <v>7.059221232960973e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>7.077357670600955e-08</v>
+        <v>7.077357670600958e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>7.16124756869678e-08</v>
+        <v>7.161247568696783e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>7.045253837051187e-08</v>
+        <v>7.045253837051196e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>7.19819654905551e-08</v>
+        <v>7.198196549055516e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.022112444938785e-08</v>
+        <v>7.022112444938791e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.103729931237956e-08</v>
+        <v>7.103729931237967e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.590209669972507e-08</v>
+        <v>7.590209669972512e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>7.407903967783305e-08</v>
+        <v>7.407903967783313e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.025478964510615e-08</v>
+        <v>7.025478964510621e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.484045445154313e-08</v>
+        <v>7.484045445154321e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>7.147682297689681e-08</v>
+        <v>7.147682297689688e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.019313629778924e-08</v>
+        <v>7.019313629778931e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.030325569478231e-08</v>
+        <v>7.030325569478236e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>7.996608250378925e-08</v>
+        <v>7.996608250378933e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.526556145261068e-08</v>
+        <v>7.526556145261075e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>7.45711156720167e-08</v>
+        <v>7.457111567201678e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.112942783285198e-08</v>
+        <v>7.112942783285203e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.884251076825548e-08</v>
+        <v>6.884251076825553e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.158625407736252e-08</v>
+        <v>7.158625407736263e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.019222837736243e-08</v>
+        <v>7.019222837736251e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7472,79 +7472,79 @@
         <v>1.568710458575904e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.678478110293495e-08</v>
+        <v>1.678478110293494e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.644173036113693e-08</v>
+        <v>1.64417303611369e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.667019846569198e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.861621082691211e-08</v>
+        <v>1.861621082691209e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.657853649900044e-08</v>
+        <v>1.657853649900042e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.703194692251456e-08</v>
+        <v>1.703194692251454e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.738901916514238e-08</v>
+        <v>1.738901916514235e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.750607826179573e-08</v>
+        <v>1.750607826179572e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.935212988306374e-08</v>
+        <v>1.935212988306359e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.700087319392925e-08</v>
+        <v>1.700087319392927e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.730635461192343e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.669884101523399e-08</v>
+        <v>2.669884101523396e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.679972285738528e-08</v>
+        <v>1.679972285738529e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.662249179380969e-08</v>
+        <v>1.662249179380967e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.668516500073594e-08</v>
+        <v>1.668516500073593e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.663043875500881e-08</v>
+        <v>1.663043875500879e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.681838304879831e-08</v>
+        <v>1.68183830487983e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.330084555927148e-08</v>
+        <v>2.330084555927144e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.648269110108823e-08</v>
+        <v>1.648269110108821e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.396000795021129e-08</v>
+        <v>2.396000795021124e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.749733957495956e-08</v>
+        <v>1.749733957495951e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.664691228601186e-08</v>
+        <v>1.664691228601185e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.736796414401373e-08</v>
+        <v>2.736796414401371e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.68278808487052e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.697907095701732e-08</v>
+        <v>1.697907095701733e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.387183433480847e-08</v>
+        <v>1.394856475392621e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.219149780594161e-08</v>
+        <v>1.225383716330397e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.582811989634683e-08</v>
+        <v>1.59747247736913e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.33619000920864e-08</v>
+        <v>1.342018896610121e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.500777618104225e-08</v>
+        <v>1.512574842882301e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.880354687585219e-08</v>
+        <v>2.94064742949555e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.435692089401168e-08</v>
+        <v>1.445163723427992e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.759808232378542e-08</v>
+        <v>1.780780199363997e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.010022997888741e-08</v>
+        <v>2.039692209951966e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.094223720639107e-08</v>
+        <v>2.127157276105683e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.409468685497619e-08</v>
+        <v>3.48861147207804e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.759826723167075e-08</v>
+        <v>1.781036596535849e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.954898578951577e-08</v>
+        <v>1.982695890224187e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.134354798804722e-08</v>
+        <v>3.145044371727558e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.591228843611271e-08</v>
+        <v>1.606047448483725e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.466064258335106e-08</v>
+        <v>1.476582533756598e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.511921499527639e-08</v>
+        <v>1.524091308847881e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.470466269710398e-08</v>
+        <v>1.481102907067172e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.606847748479061e-08</v>
+        <v>1.622369926427585e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.627336930472855e-08</v>
+        <v>2.640464468916777e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.365284202279779e-08</v>
+        <v>1.372190485348659e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.69329228436891e-08</v>
+        <v>2.70450992302872e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.091980093045109e-08</v>
+        <v>2.124705897635968e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.483356416253999e-08</v>
+        <v>1.494463284708582e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.282894223467795e-08</v>
+        <v>3.295337096990499e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.612588195385992e-08</v>
+        <v>1.628252580789558e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.730430152511735e-08</v>
+        <v>1.750327239438286e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.13322567772676e-08</v>
+        <v>5.133225677726726e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.065665197579082e-08</v>
+        <v>5.065665197579084e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.440283532647582e-08</v>
+        <v>5.440283532647586e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>5.052791938672914e-08</v>
+        <v>5.05279193867291e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.310857172819922e-08</v>
+        <v>5.310857172819924e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.50896765580949e-08</v>
+        <v>7.508967655809497e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>5.207320764783022e-08</v>
+        <v>5.207320764783015e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.719468696052208e-08</v>
+        <v>5.71946869605221e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>6.116493359360032e-08</v>
+        <v>6.116493359360028e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25502185488948e-08</v>
+        <v>6.255021854889482e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>8.340222083681904e-08</v>
+        <v>8.340222083681831e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>5.728412246081761e-08</v>
+        <v>5.728412246081768e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>6.029424804616912e-08</v>
+        <v>6.029424804616914e-08</v>
       </c>
       <c r="O4" t="n">
         <v>5.269917082522317e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>5.457160931653915e-08</v>
+        <v>5.457160931653914e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.256970292313545e-08</v>
+        <v>5.256970292313541e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.327762562646694e-08</v>
+        <v>5.3277625626467e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.265946750566222e-08</v>
+        <v>5.265946750566216e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.478238476266118e-08</v>
+        <v>5.478238476266116e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.334253739123029e-08</v>
+        <v>5.334253739123027e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>5.056305363774125e-08</v>
+        <v>5.056305363774127e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.290157566944278e-08</v>
+        <v>5.290157566944279e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.245151106108577e-08</v>
+        <v>6.245151106108556e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.241753333654005e-08</v>
+        <v>5.241753333654003e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.348203696721161e-08</v>
+        <v>5.348203696721152e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.488966678181364e-08</v>
+        <v>5.488966678181362e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.67303488855454e-08</v>
+        <v>5.673034888554542e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.271148435913592e-08</v>
+        <v>9.271148435913254e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.452545756977614e-08</v>
+        <v>8.452545756977621e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.597442372541667e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>7.655062465310427e-08</v>
+        <v>7.655062465310333e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.338477177548358e-07</v>
+        <v>1.338477177548357e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>4.977329908002795e-07</v>
+        <v>4.977329908002802e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.161291119860971e-07</v>
+        <v>1.161291119860972e-07</v>
       </c>
       <c r="I5" t="n">
         <v>2.158289780213133e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.662801660820089e-07</v>
+        <v>2.662801660820086e-07</v>
       </c>
       <c r="K5" t="n">
         <v>2.949870748095659e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>6.765117365899635e-07</v>
+        <v>6.765117365899517e-07</v>
       </c>
       <c r="M5" t="n">
         <v>2.07879971103916e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.70231843641208e-07</v>
+        <v>2.702318436412084e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.152691880287836e-07</v>
+        <v>1.152691880287837e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.50437820732481e-07</v>
+        <v>1.504378207324808e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.199611471489965e-07</v>
+        <v>1.199611471489953e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>1.396146569914913e-07</v>
+        <v>1.396146569914916e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.145965281089099e-07</v>
+        <v>1.145965281089085e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>1.672203908723742e-07</v>
+        <v>1.672203908723738e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.394131050634726e-07</v>
+        <v>1.394131050634725e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>8.409432059005829e-08</v>
+        <v>8.409432059005842e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.257752357432733e-07</v>
+        <v>1.257752357432725e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>3.153290880137988e-07</v>
+        <v>3.153290880137979e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24415516019925e-07</v>
+        <v>1.244155160199249e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.304245492475863e-07</v>
+        <v>1.304245492475836e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.634750062909993e-07</v>
+        <v>1.634750062909987e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.133779696065087e-07</v>
+        <v>2.133779696065085e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.973808910529193e-08</v>
+        <v>4.973808910529175e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>4.906248430381513e-08</v>
+        <v>4.906248430381516e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.280866765450019e-08</v>
+        <v>5.280866765450018e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>5.705005117540747e-08</v>
+        <v>5.705005117540739e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.151440405622351e-08</v>
+        <v>5.151440405622357e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.161180834677314e-08</v>
+        <v>8.161180834677323e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>5.047903997585448e-08</v>
+        <v>5.047903997585449e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.56005192885464e-08</v>
+        <v>5.560051928854641e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>5.957076592162464e-08</v>
+        <v>5.957076592162462e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>6.907235033757311e-08</v>
+        <v>6.907235033757309e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.992435262549721e-08</v>
+        <v>8.992435262549602e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>5.568995478884196e-08</v>
+        <v>5.568995478884199e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>5.8710916889016e-08</v>
+        <v>5.871091688901588e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.94388424764489e-08</v>
+        <v>5.943884247644888e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>6.131230777591143e-08</v>
+        <v>6.131230777591142e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.097553525115975e-08</v>
+        <v>5.097553525115969e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.979975741514523e-08</v>
+        <v>5.979975741514531e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.106529983368653e-08</v>
+        <v>5.10652998336865e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>5.318821709068546e-08</v>
+        <v>5.31882170906855e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>6.029267945990882e-08</v>
+        <v>6.02926794599088e-08</v>
       </c>
       <c r="V6" t="n">
         <v>4.896888596576558e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.147839522906978e-08</v>
+        <v>5.147839522906972e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.897364284976408e-08</v>
+        <v>6.897364284976381e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.135132485360513e-08</v>
+        <v>5.135132485360515e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.000416875588991e-08</v>
+        <v>6.000416875588979e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.141179857049191e-08</v>
+        <v>6.141179857049189e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.518157912797842e-08</v>
+        <v>5.518157912797841e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.707572825628629e-08</v>
+        <v>5.707572825628606e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.640012345480948e-08</v>
+        <v>5.640012345480955e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>6.01463068054945e-08</v>
+        <v>6.014630680549454e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.627139086574781e-08</v>
+        <v>5.627139086574777e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.88520432072179e-08</v>
+        <v>5.885204320721794e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>8.083314803711358e-08</v>
+        <v>8.083314803711364e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.781667912684889e-08</v>
+        <v>5.781667912684885e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>6.293815843954076e-08</v>
+        <v>6.29381584395408e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6908405072619e-08</v>
+        <v>6.690840507261897e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>6.829369002791354e-08</v>
+        <v>6.829369002791351e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>8.914569231583782e-08</v>
+        <v>8.914569231583663e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>6.302759393983631e-08</v>
+        <v>6.302759393983636e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>6.603771952518782e-08</v>
+        <v>6.603771952518786e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.844129927242065e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>6.031373776373667e-08</v>
+        <v>6.031373776373663e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.831317440215411e-08</v>
+        <v>5.831317440215403e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.902109710548562e-08</v>
+        <v>5.90210971054857e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.84029389846809e-08</v>
+        <v>5.840293898468087e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>6.052585624167984e-08</v>
+        <v>6.052585624167981e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>5.950543653001766e-08</v>
+        <v>5.950543653001769e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.630652511675993e-08</v>
+        <v>5.630652511675992e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.864504714846146e-08</v>
+        <v>5.86450471484615e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.819498254010448e-08</v>
+        <v>6.819498254010426e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.858901509555897e-08</v>
+        <v>5.858901509555903e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.922550844623028e-08</v>
+        <v>5.922550844623022e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.063313826083233e-08</v>
+        <v>6.063313826083234e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.247382036456408e-08</v>
+        <v>6.247382036456416e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,40 +7994,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.653424210384585e-08</v>
+        <v>6.653424210384559e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.853405496278572e-08</v>
+        <v>7.853405496278576e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>8.228023831347064e-08</v>
+        <v>8.228023831347074e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>7.165603637088303e-08</v>
+        <v>7.165603637088295e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>7.028523898505587e-08</v>
+        <v>7.028523898505584e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.055954099697074e-07</v>
+        <v>1.055954099697076e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>7.995061063482499e-08</v>
+        <v>7.995061063482495e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>8.507208994751696e-08</v>
+        <v>8.507208994751698e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>8.904233658059516e-08</v>
+        <v>8.904233658059519e-08</v>
       </c>
       <c r="K8" t="n">
         <v>9.042762153588971e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>1.112796238238138e-07</v>
+        <v>1.112796238238133e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>8.516152544781127e-08</v>
+        <v>8.516152544781131e-08</v>
       </c>
       <c r="N8" t="n">
         <v>7.834608179461366e-08</v>
@@ -8036,43 +8036,43 @@
         <v>7.345115631403691e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.466172236901256e-08</v>
+        <v>7.466172236901264e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.528067937681807e-08</v>
+        <v>6.528067937681809e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>8.115502861346182e-08</v>
+        <v>8.115502861346188e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>8.053687049265712e-08</v>
+        <v>8.053687049265713e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>8.265978774965605e-08</v>
+        <v>8.265978774965601e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>7.545563797111224e-08</v>
+        <v>7.545563797111232e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.496988563447794e-08</v>
+        <v>7.496988563447799e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>8.078146973816384e-08</v>
+        <v>8.078146973816389e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>7.632421472937342e-08</v>
+        <v>7.632421472937327e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.331622793367618e-08</v>
+        <v>9.331622793367631e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.844856990277751e-08</v>
+        <v>6.844856990277737e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.276706976880849e-08</v>
+        <v>8.276706976880846e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.784828551992287e-08</v>
+        <v>9.784828551992283e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.613194524370517e-08</v>
+        <v>7.613194524370482e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>8.362764363240949e-08</v>
+        <v>8.362764363240944e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.737382698309447e-08</v>
+        <v>8.737382698309454e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>8.161301603140634e-08</v>
+        <v>8.161301603140623e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.724246505908918e-08</v>
+        <v>6.724246505908916e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.080606791795719e-07</v>
+        <v>1.08060679179572e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>8.504419930444884e-08</v>
+        <v>8.504419930444888e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>9.016567861714074e-08</v>
+        <v>9.016567861714071e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>9.41359252502189e-08</v>
+        <v>9.413592525021892e-08</v>
       </c>
       <c r="K9" t="n">
         <v>9.552121020551347e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>1.163732124934378e-07</v>
+        <v>1.163732124934364e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>9.025511411743627e-08</v>
+        <v>9.025511411743622e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>9.326523970278772e-08</v>
+        <v>9.326523970278767e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>8.83781362582579e-08</v>
+        <v>8.837813625825782e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>9.083951020026994e-08</v>
+        <v>9.083951020026987e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.554070554461238e-08</v>
+        <v>8.55407055446123e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>8.62486172830856e-08</v>
+        <v>8.624861728308558e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>8.563045916228076e-08</v>
+        <v>8.563045916228069e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>8.775337641927982e-08</v>
+        <v>8.775337641927979e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>8.674153932784915e-08</v>
+        <v>8.674153932784918e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>9.296356735511797e-08</v>
+        <v>9.296356735511805e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>8.587256732606144e-08</v>
+        <v>8.587256732606138e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>9.542250271770437e-08</v>
+        <v>9.542250271770409e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.581653527315888e-08</v>
+        <v>8.58165352731589e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.152646377480533e-08</v>
+        <v>8.152646377480517e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.786065843843227e-08</v>
+        <v>8.786065843843226e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.970134054216409e-08</v>
+        <v>8.970134054216404e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,82 +8326,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.59683110053325e-08</v>
+        <v>1.596831100533248e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.526043062534614e-08</v>
+        <v>1.526043062534612e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.604093751429502e-08</v>
+        <v>1.604093751429499e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.604521611228767e-08</v>
+        <v>1.604521611228764e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.609946661971851e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.762110809163963e-08</v>
+        <v>1.762110809163956e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.599563994214213e-08</v>
+        <v>1.599563994214212e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.608178461416995e-08</v>
+        <v>1.608178461416989e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.667502787792575e-08</v>
+        <v>1.667502787792573e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.617878328540797e-08</v>
+        <v>1.617878328540795e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.70530865884507e-08</v>
+        <v>1.705308658845064e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.602442371146379e-08</v>
+        <v>1.602442371146381e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.605108833262127e-08</v>
+        <v>1.605108833262125e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.568912083200197e-08</v>
+        <v>2.568912083200203e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.635496808371463e-08</v>
+        <v>1.63549680837146e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.610479779049447e-08</v>
+        <v>1.610479779049441e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.627153444372098e-08</v>
+        <v>1.627153444372102e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.615359668155837e-08</v>
+        <v>1.615359668155835e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.604905105924361e-08</v>
+        <v>1.604905105924359e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.249910702768812e-08</v>
+        <v>2.249910702768819e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.605478175335406e-08</v>
+        <v>1.605478175335402e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.349491550736166e-08</v>
+        <v>2.349491550736172e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.665163579335134e-08</v>
+        <v>1.665163579335132e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.642992867653365e-08</v>
+        <v>1.64299286765336e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>2.654973678349595e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.607710284546504e-08</v>
+        <v>1.607710284546511e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>3.156446370051326e-08</v>
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.290065510132747e-08</v>
+        <v>1.295525148277822e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.20854400210045e-08</v>
+        <v>1.215658663198016e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.342461714246312e-08</v>
+        <v>1.349811307570582e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.344461483588274e-08</v>
+        <v>1.351790502656187e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.384329936865777e-08</v>
+        <v>1.393196690552576e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.461084306828622e-08</v>
+        <v>2.507892932294e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.310448990468684e-08</v>
+        <v>1.316673166294488e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.371875684733135e-08</v>
+        <v>1.380273510106207e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.792244480736236e-08</v>
+        <v>1.815468946001391e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.440053451855224e-08</v>
+        <v>1.450891718444378e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.060340823645364e-08</v>
+        <v>2.09311249432804e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.355665124758057e-08</v>
+        <v>1.363652741357841e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.34958474786019e-08</v>
+        <v>1.3571707610065e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.913973673179853e-08</v>
+        <v>2.92031589008765e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.564710305068069e-08</v>
+        <v>1.579812558837557e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.387356564850788e-08</v>
+        <v>1.396311411138069e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.508024373652075e-08</v>
+        <v>1.521271907874239e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.421449480766394e-08</v>
+        <v>1.431565150754757e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.348341707647871e-08</v>
+        <v>1.355900523216254e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.399062225591407e-08</v>
+        <v>2.405902485250326e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.350998679546928e-08</v>
+        <v>1.358610916841286e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.708330252835059e-08</v>
+        <v>2.721877060521237e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.778189219568281e-08</v>
+        <v>1.801027266464562e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.619711389521626e-08</v>
+        <v>1.636851940021829e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.074962532350836e-08</v>
+        <v>3.082186325487384e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.368015651371831e-08</v>
+        <v>1.376245111604205e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.233889687314847e-07</v>
+        <v>1.273529344972917e-07</v>
       </c>
     </row>
     <row r="4">
@@ -8505,34 +8505,34 @@
         <v>4.961258789038845e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>5.033079602055469e-08</v>
+        <v>5.033079602055471e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.043293771896504e-08</v>
+        <v>5.043293771896503e-08</v>
       </c>
       <c r="E4" t="n">
         <v>5.048126645154442e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.109405088944197e-08</v>
+        <v>5.109405088944198e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>6.828169130445143e-08</v>
+        <v>6.828169130445137e-08</v>
       </c>
       <c r="H4" t="n">
         <v>4.992128080358559e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.089432450264676e-08</v>
+        <v>5.089432450264678e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.754135516180027e-08</v>
+        <v>5.754135516180026e-08</v>
       </c>
       <c r="K4" t="n">
         <v>5.19899691158734e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.186562712313142e-08</v>
+        <v>6.186562712313144e-08</v>
       </c>
       <c r="M4" t="n">
         <v>5.070754068375027e-08</v>
@@ -8541,46 +8541,46 @@
         <v>5.054759588156707e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.001318195202548e-08</v>
+        <v>5.001318195202551e-08</v>
       </c>
       <c r="P4" t="n">
         <v>5.398005746175869e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.115426891581631e-08</v>
+        <v>5.115426891581633e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>5.303763611665985e-08</v>
+        <v>5.303763611665986e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>5.170547483898226e-08</v>
+        <v>5.170547483898227e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>5.052458394157457e-08</v>
+        <v>5.05245839415746e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>5.008152087642578e-08</v>
+        <v>5.00815208764258e-08</v>
       </c>
       <c r="V4" t="n">
         <v>5.022295237771397e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.322667555619686e-08</v>
+        <v>5.322667555619685e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.733105571599438e-08</v>
+        <v>5.733105571599441e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.468224770677719e-08</v>
+        <v>5.468224770677718e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.040723458097773e-08</v>
+        <v>5.040723458097772e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.08414417714048e-08</v>
+        <v>5.084144177140481e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.234451428108705e-07</v>
+        <v>2.234451428108706e-07</v>
       </c>
     </row>
     <row r="5">
@@ -8590,13 +8590,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.119716690878173e-08</v>
+        <v>7.119716690878169e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.607832910869264e-08</v>
+        <v>8.607832910869267e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.862039819922952e-08</v>
+        <v>8.862039819922953e-08</v>
       </c>
       <c r="E5" t="n">
         <v>8.401366712875859e-08</v>
@@ -8605,70 +8605,70 @@
         <v>1.008092595699531e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>3.568718189984098e-07</v>
+        <v>3.568718189984088e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.121045688140643e-08</v>
+        <v>8.121045688140641e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.813434453510156e-08</v>
+        <v>9.813434453510154e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.008859323165759e-07</v>
+        <v>2.008859323165754e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.120678061108275e-07</v>
+        <v>1.120678061108274e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.675232081413929e-07</v>
+        <v>2.675232081413932e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>9.314067621941051e-08</v>
+        <v>9.314067621941053e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>9.001786543939798e-08</v>
+        <v>9.001786543939788e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.752113809899404e-08</v>
+        <v>7.75211380989941e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.416321008154028e-07</v>
+        <v>1.416321008154027e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.784120436143112e-08</v>
+        <v>9.784120436143116e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.397906125198259e-07</v>
+        <v>1.39790612519826e-07</v>
       </c>
       <c r="S5" t="n">
         <v>1.037807422690166e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>9.070417003446681e-08</v>
+        <v>9.07041700344671e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>8.217816116247822e-08</v>
+        <v>8.217816116247829e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.405624475215534e-08</v>
+        <v>8.405624475215528e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.367738104786054e-07</v>
+        <v>1.367738104786052e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>2.099466370517942e-07</v>
+        <v>2.099466370517944e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.643879337219361e-07</v>
+        <v>1.643879337219359e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.339580900812902e-08</v>
+        <v>8.339580900812906e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.451134872797006e-08</v>
+        <v>9.451134872796986e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.376555572204601e-06</v>
+        <v>3.376555572204607e-06</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.631910912946476e-08</v>
+        <v>5.631910912946479e-08</v>
       </c>
       <c r="C6" t="n">
         <v>5.703731725963103e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>5.713945895804138e-08</v>
+        <v>5.713945895804139e-08</v>
       </c>
       <c r="E6" t="n">
         <v>4.9008215381511e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>4.962099981940855e-08</v>
+        <v>4.962099981940856e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>6.680864023441805e-08</v>
+        <v>6.680864023441799e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.844822973355215e-08</v>
+        <v>4.844822973355217e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.760084574172311e-08</v>
+        <v>5.76008457417231e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>6.42478764008766e-08</v>
+        <v>6.424787640087661e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>5.051691804583995e-08</v>
+        <v>5.051691804583997e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>6.857214836220773e-08</v>
+        <v>6.857214836220776e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.923448961371683e-08</v>
+        <v>4.923448961371685e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.907688152242205e-08</v>
+        <v>4.907688152242206e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>5.684039708006111e-08</v>
+        <v>5.684039708006113e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>5.235489898467524e-08</v>
+        <v>5.235489898467526e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>4.96812178457829e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>5.974415735573617e-08</v>
+        <v>5.974415735573618e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>5.023242376894882e-08</v>
+        <v>5.023242376894886e-08</v>
       </c>
       <c r="T6" t="n">
         <v>4.905153287154116e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>5.693256624995084e-08</v>
+        <v>5.693256624995086e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.874990130768054e-08</v>
+        <v>4.874990130768055e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>5.190967307677119e-08</v>
+        <v>5.190967307677106e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>6.403757695507071e-08</v>
+        <v>6.403757695507072e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.344713105663838e-08</v>
+        <v>5.344713105663839e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.711375582005405e-08</v>
+        <v>5.711375582005406e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.936839070137139e-08</v>
+        <v>4.93683907013714e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.229581314197236e-07</v>
+        <v>2.229581314197234e-07</v>
       </c>
     </row>
     <row r="7">
@@ -8766,58 +8766,58 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.465116307544768e-08</v>
+        <v>5.465116307544771e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>5.536937120561392e-08</v>
+        <v>5.536937120561393e-08</v>
       </c>
       <c r="D7" t="n">
         <v>5.547151290402427e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>5.551984163660365e-08</v>
+        <v>5.551984163660369e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>5.61326260745012e-08</v>
+        <v>5.613262607450122e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>7.33202664895107e-08</v>
+        <v>7.332026648951063e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>5.495985598864482e-08</v>
+        <v>5.495985598864483e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5932899687706e-08</v>
+        <v>5.593289968770602e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>6.257993034685952e-08</v>
+        <v>6.257993034685953e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>5.702854430093263e-08</v>
+        <v>5.702854430093266e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>6.690420230819065e-08</v>
+        <v>6.690420230819069e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>5.574611586880949e-08</v>
+        <v>5.574611586880951e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>5.558617106662632e-08</v>
+        <v>5.558617106662633e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>5.505049923763128e-08</v>
+        <v>5.505049923763129e-08</v>
       </c>
       <c r="P7" t="n">
         <v>5.901737474736449e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.619284410087554e-08</v>
+        <v>5.619284410087556e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>5.807621130171906e-08</v>
+        <v>5.807621130171909e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>5.67440500240415e-08</v>
+        <v>5.674405002404152e-08</v>
       </c>
       <c r="T7" t="n">
         <v>5.556315912663381e-08</v>
@@ -8826,25 +8826,25 @@
         <v>5.525825335065957e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>5.526152756277322e-08</v>
+        <v>5.526152756277323e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>5.826525074125608e-08</v>
+        <v>5.826525074125609e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>6.236963090105361e-08</v>
+        <v>6.236963090105365e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.986534702628517e-08</v>
+        <v>5.986534702628518e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.544580976603696e-08</v>
+        <v>5.544580976603698e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>5.588001695646405e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.284837179959297e-07</v>
+        <v>2.284837179959298e-07</v>
       </c>
     </row>
     <row r="8">
@@ -8854,76 +8854,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.328033873335111e-08</v>
+        <v>6.328033873335112e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>7.541513147922292e-08</v>
+        <v>7.541513147922286e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>7.551727317763321e-08</v>
+        <v>7.55172731776332e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>6.948660737042573e-08</v>
+        <v>6.948660737042574e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>6.654037218665288e-08</v>
+        <v>6.654037218665285e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>9.573332995538186e-08</v>
+        <v>9.573332995538169e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>7.50056162622538e-08</v>
+        <v>7.500561626225378e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>7.597865996131498e-08</v>
+        <v>7.597865996131493e-08</v>
       </c>
       <c r="J8" t="n">
         <v>8.262569062046848e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>7.707430457454158e-08</v>
+        <v>7.707430457454161e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>8.694996258179963e-08</v>
+        <v>8.69499625817996e-08</v>
       </c>
       <c r="M8" t="n">
         <v>7.579187614241637e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>6.678216830956927e-08</v>
+        <v>6.67821683095693e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>6.867974610174763e-08</v>
+        <v>6.867974610174764e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>7.205048167536278e-08</v>
+        <v>7.205048167536279e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.257840031064383e-08</v>
+        <v>6.257840031064384e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>7.812197157532807e-08</v>
+        <v>7.812197157532802e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>7.67898102976505e-08</v>
+        <v>7.678981029765048e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>7.560891940024277e-08</v>
+        <v>7.560891940024273e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>6.973413858588602e-08</v>
+        <v>6.973413858588601e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>7.218259611876226e-08</v>
+        <v>7.218259611876231e-08</v>
       </c>
       <c r="W8" t="n">
         <v>7.831325469996321e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>6.980153977560475e-08</v>
+        <v>6.980153977560478e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.125558430200164e-08</v>
+        <v>9.125558430200166e-08</v>
       </c>
       <c r="Z8" t="n">
         <v>6.386291650304561e-08</v>
@@ -8932,7 +8932,7 @@
         <v>7.592577723007301e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.604550555399337e-07</v>
+        <v>2.604550555399335e-07</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.915708190667966e-08</v>
+        <v>6.915708190667973e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>7.646963619064517e-08</v>
+        <v>7.646963619064519e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>7.657177788905549e-08</v>
+        <v>7.657177788905554e-08</v>
       </c>
       <c r="E9" t="n">
         <v>7.509816309739564e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>6.203111548226287e-08</v>
+        <v>6.20311154822629e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>9.442053754602511e-08</v>
+        <v>9.442053754602503e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>7.606012097367604e-08</v>
+        <v>7.606012097367608e-08</v>
       </c>
       <c r="I9" t="n">
         <v>7.703316467273727e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>8.368019533189068e-08</v>
+        <v>8.368019533189073e-08</v>
       </c>
       <c r="K9" t="n">
         <v>7.812880928596386e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>8.800446729322183e-08</v>
+        <v>8.800446729322193e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>7.684638085384071e-08</v>
+        <v>7.684638085384076e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>7.668643605165749e-08</v>
+        <v>7.668643605165758e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>7.833738788649073e-08</v>
+        <v>7.833738788649087e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>8.277954163496973e-08</v>
+        <v>8.277954163496981e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.729311515738991e-08</v>
+        <v>7.729311515738997e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>7.91764762867503e-08</v>
+        <v>7.917647628675033e-08</v>
       </c>
       <c r="S9" t="n">
         <v>7.784431500907271e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>7.666342411166498e-08</v>
+        <v>7.666342411166505e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>7.636488518096495e-08</v>
+        <v>7.6364885180965e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>8.397153201905885e-08</v>
+        <v>8.397153201905893e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>7.936551572628726e-08</v>
+        <v>7.93655157262873e-08</v>
       </c>
       <c r="X9" t="n">
         <v>8.346989588608488e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.096561201131639e-08</v>
+        <v>8.096561201131642e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.257027282338538e-08</v>
+        <v>7.257027282338543e-08</v>
       </c>
       <c r="AA9" t="n">
         <v>7.69802819414953e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.495839829809607e-07</v>
+        <v>2.495839829809608e-07</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -589,82 +589,82 @@
         <v>1.777760292998752e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.697928116501752e-08</v>
+        <v>1.697928116501751e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.83329174018699e-08</v>
+        <v>1.833291740186987e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76258558591763e-08</v>
+        <v>1.762585585917629e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.82508708537568e-08</v>
+        <v>1.825087085375682e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.062882993288251e-08</v>
+        <v>2.062882993288252e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.807066051816932e-08</v>
+        <v>1.807066051816934e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.860127654901627e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.88640529717417e-08</v>
+        <v>1.886405297174169e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.939486335819079e-08</v>
+        <v>1.939486335819078e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.174876416612552e-08</v>
+        <v>2.17487641661255e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.854622780514138e-08</v>
+        <v>1.854622780514136e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.881467392046556e-08</v>
+        <v>1.881467392046552e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.881425703101803e-08</v>
+        <v>2.881425703101801e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.786640433414131e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.796795360197904e-08</v>
+        <v>1.796795360197903e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.802113209117415e-08</v>
+        <v>1.80211320911742e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.788871234271962e-08</v>
+        <v>1.788871234271956e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.840996789987223e-08</v>
+        <v>1.84099678998722e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.526471260769565e-08</v>
+        <v>2.526471260769563e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.776481011466895e-08</v>
+        <v>1.776481011466897e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.588180570904054e-08</v>
+        <v>2.588180570904051e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.845988233963052e-08</v>
+        <v>1.845988233963051e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.786389546733572e-08</v>
+        <v>1.786389546733574e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.887489450297037e-08</v>
+        <v>2.887489450297032e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86366399527927e-08</v>
+        <v>1.863663995279273e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.829684955710516e-08</v>
+        <v>1.829684955710513e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.874002514178394e-08</v>
+        <v>1.83274227781741e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.630359320819005e-08</v>
+        <v>1.707613553408287e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.180245155543517e-08</v>
+        <v>2.296903629669624e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.842970020683657e-08</v>
+        <v>2.03487743512755e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.996261167135911e-08</v>
+        <v>2.236280989229567e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>9.445089558617992e-08</v>
+        <v>4.074170537696744e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.576256846434705e-08</v>
+        <v>2.091562365423406e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.811111985791273e-08</v>
+        <v>2.520332058123906e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.386039429418671e-08</v>
+        <v>2.695010359724295e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.654151597846544e-08</v>
+        <v>3.158629908697877e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.20759386583182e-07</v>
+        <v>5.008488834520288e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7751666709042e-08</v>
+        <v>2.504579799563674e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>5.293362488796255e-08</v>
+        <v>2.677359093570432e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>4.503738584435785e-08</v>
+        <v>3.096065012070269e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.077200793564293e-08</v>
+        <v>1.902467851815606e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.325475192216962e-08</v>
+        <v>1.995660631956578e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.456734403245981e-08</v>
+        <v>2.046975065969426e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.132487941027166e-08</v>
+        <v>1.92234499137504e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>4.361353835846197e-08</v>
+        <v>2.36103568343508e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>4.577145481118854e-08</v>
+        <v>2.882980677086517e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.843696327865454e-08</v>
+        <v>1.820088595803298e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>4.26424418459769e-08</v>
+        <v>2.830761612996001e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>4.474465583666057e-08</v>
+        <v>2.396461460402896e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.080372556494333e-08</v>
+        <v>1.908510270296284e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.479755268206376e-08</v>
+        <v>3.097979822571718e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.873497830238681e-08</v>
+        <v>2.529276809939645e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.131811544758046e-08</v>
+        <v>2.290858761627093e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.160248879449677e-07</v>
+        <v>1.160248879449656e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.051893901112536e-07</v>
+        <v>1.051893901112537e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.577802392677625e-07</v>
+        <v>2.577802392677626e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.154169478027622e-08</v>
+        <v>8.154169478027789e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.428940718496276e-07</v>
+        <v>2.428940718496273e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.354705526349996e-07</v>
+        <v>7.35470552634999e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.014414646874753e-07</v>
+        <v>2.01441464687475e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.256032188998219e-07</v>
+        <v>3.25603218899822e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.582412368316838e-07</v>
+        <v>3.58241236831684e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.090468569466545e-07</v>
+        <v>5.090468569466532e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.020025965946093e-06</v>
+        <v>1.020025965946085e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.224262860278246e-07</v>
+        <v>3.224262860278247e-07</v>
       </c>
       <c r="N4" t="n">
         <v>3.63749020763453e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.644485650237868e-07</v>
+        <v>1.644485650237867e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.352778310500241e-07</v>
+        <v>1.35277831050024e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.675296857752116e-07</v>
+        <v>1.675296857752112e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.863599143551124e-07</v>
+        <v>1.863599143551125e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.418846248683634e-07</v>
+        <v>1.418846248683638e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.772396815897163e-07</v>
+        <v>2.772396815897153e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.145031807900985e-07</v>
+        <v>2.145031807900981e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.107630047960237e-07</v>
+        <v>1.107630047960235e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.798739443571467e-07</v>
+        <v>1.798739443571466e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.851381853084971e-07</v>
+        <v>2.851381853084939e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.408373504428526e-07</v>
+        <v>1.408373504428525e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.659154330319846e-07</v>
+        <v>1.659154330319844e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.18890109137454e-07</v>
+        <v>3.188901091374534e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.625299101123382e-07</v>
+        <v>2.625299101123381e-07</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.128365034792815e-08</v>
+        <v>7.128365034792783e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.498373179626773e-08</v>
+        <v>8.498373179626761e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.213046902820201e-08</v>
+        <v>9.213046902820203e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.638350611844546e-08</v>
+        <v>7.638350611844535e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.889993272689206e-08</v>
+        <v>7.889993272689194e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.210859304372872e-07</v>
+        <v>1.21085930437287e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.916815688267726e-08</v>
+        <v>8.91681568826771e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.516170904652739e-08</v>
+        <v>9.51617090465273e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.806098412208676e-08</v>
+        <v>9.806098412208674e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.041256371241219e-07</v>
+        <v>1.04125637124122e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.307140295976148e-07</v>
+        <v>1.307140295976146e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>9.498849284486114e-08</v>
+        <v>9.498849284486118e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.63749020763453e-07</v>
+        <v>8.627462044522444e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>8.0370108575195e-08</v>
+        <v>8.037010857519484e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.790710742520198e-08</v>
+        <v>7.790710742520179e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.056956886080488e-08</v>
+        <v>7.05695688608048e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>8.860871051556454e-08</v>
+        <v>8.860871051556446e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>8.711296854067668e-08</v>
+        <v>8.711296854067664e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>9.300078984811857e-08</v>
+        <v>9.300078984811866e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>8.359076596462167e-08</v>
+        <v>8.359076596462153e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>8.125576417645826e-08</v>
+        <v>8.125576417645823e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>8.87860846073593e-08</v>
+        <v>8.878608460735911e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.746189254608586e-08</v>
+        <v>7.746189254608564e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.013120266829454e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.3549360308428e-08</v>
+        <v>7.354936030842804e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.556115496015136e-08</v>
+        <v>9.556115496015141e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.071179435161942e-07</v>
+        <v>1.071179435161941e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,43 +938,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.760503920236661e-08</v>
+        <v>8.760503920236639e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.758809449184776e-08</v>
+        <v>9.758809449184765e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.047348317237821e-07</v>
+        <v>1.047348317237819e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>9.424244482176408e-08</v>
+        <v>9.42424448217641e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>7.877911376584238e-08</v>
+        <v>7.877911376584232e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.306682327170965e-07</v>
+        <v>1.306682327170964e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.017725195782573e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.077660717421074e-07</v>
+        <v>1.077660717421075e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.106653468176668e-07</v>
+        <v>1.106653468176666e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.167299998197019e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.433183922931947e-07</v>
+        <v>1.433183922931945e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.075928555404429e-07</v>
+        <v>1.075928555404428e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.63749020763453e-07</v>
+        <v>1.101764932202677e-07</v>
       </c>
       <c r="O6" t="n">
         <v>1.047654262883863e-07</v>
@@ -983,19 +983,19 @@
         <v>1.038459727956834e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.006124104959542e-07</v>
+        <v>1.006124104959539e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.012130732111446e-07</v>
+        <v>1.012130732111443e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>9.971733123625667e-08</v>
+        <v>9.971733123625662e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.056051525436986e-07</v>
+        <v>1.056051525436985e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.033153685077699e-07</v>
+        <v>1.0331536850777e-07</v>
       </c>
       <c r="V6" t="n">
         <v>1.103799767304189e-07</v>
@@ -1004,16 +1004,16 @@
         <v>1.013875830392163e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.061689591025453e-07</v>
+        <v>1.061689591025452e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.943701321246896e-08</v>
+        <v>9.94370132124688e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.44527768159191e-08</v>
+        <v>9.445277681591885e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.081655176557313e-07</v>
+        <v>1.081655176557312e-07</v>
       </c>
       <c r="AB6" t="n">
         <v>1.044982455281144e-07</v>
@@ -1185,7 +1185,7 @@
         <v>1.480204094928746e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.40176274229764e-08</v>
+        <v>1.401762742297641e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.482808175944911e-08</v>
@@ -1194,73 +1194,73 @@
         <v>1.482723712584342e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.494878295140336e-08</v>
+        <v>1.494878295140334e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49792717670154e-08</v>
+        <v>1.497927176701539e-08</v>
       </c>
       <c r="H2" t="n">
         <v>1.48451777445239e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.488649669047693e-08</v>
+        <v>1.488649669047698e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.495483647480498e-08</v>
+        <v>1.495483647480489e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.491892222730477e-08</v>
+        <v>1.49189222273048e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.505079718821335e-08</v>
+        <v>1.505079718821336e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.481386156400574e-08</v>
+        <v>1.481386156400575e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.484536233614827e-08</v>
+        <v>1.484536233614816e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.424826369928913e-08</v>
+        <v>2.424826369928909e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.491635003420405e-08</v>
+        <v>1.491635003420391e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.484392303820308e-08</v>
+        <v>1.484392303820304e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51416318926115e-08</v>
+        <v>1.514163189261149e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.494249700607934e-08</v>
+        <v>1.494249700607936e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.486984692434437e-08</v>
+        <v>1.486984692434436e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.123743756496561e-08</v>
+        <v>2.12374375649655e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.511497477602927e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.250259035524717e-08</v>
+        <v>2.250259035524706e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.538341873353302e-08</v>
+        <v>1.538341873353305e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.508823900029774e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.551278824734144e-08</v>
+        <v>2.551278824734145e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.507908871130573e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.479063966899349e-08</v>
+        <v>1.47906396689935e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.187366911314919e-08</v>
+        <v>1.457396916277824e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.247698149245074e-08</v>
+        <v>1.424292213500572e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.251397568663946e-08</v>
+        <v>1.481694233099262e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.592578308661135e-08</v>
+        <v>1.8249805096639e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.535303792718935e-08</v>
+        <v>1.579641117647626e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.595438727832666e-08</v>
+        <v>1.593100596758831e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.293436978595896e-08</v>
+        <v>1.498373786747396e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.388470957252611e-08</v>
+        <v>1.529863795171838e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.54216718116292e-08</v>
+        <v>1.577759049631691e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.462272550415562e-08</v>
+        <v>1.550788875070045e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.763971973290849e-08</v>
+        <v>1.650649246413665e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.302835757869787e-08</v>
+        <v>1.497494329936114e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.290570113623505e-08</v>
+        <v>1.495219231406866e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.215548863093444e-08</v>
+        <v>2.427339793831646e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.449609171674112e-08</v>
+        <v>1.544761555117246e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.287442775534136e-08</v>
+        <v>1.492471212595586e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.986921338751771e-08</v>
+        <v>1.740370096345942e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.51193078836405e-08</v>
+        <v>1.565483572101637e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.349182827821038e-08</v>
+        <v>1.516401608556495e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.062922318146611e-08</v>
+        <v>2.171719944526995e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.906979849490276e-08</v>
+        <v>1.694027101025908e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>4.29775741416056e-08</v>
+        <v>2.650954622945959e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.544935516824347e-08</v>
+        <v>1.920703701846644e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.854193772317051e-08</v>
+        <v>1.69008311888974e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.450724506975104e-08</v>
+        <v>2.585258698644e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.832325472779622e-08</v>
+        <v>1.682131501935561e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.187476425492673e-08</v>
+        <v>1.460967656736311e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.806281490216044e-08</v>
+        <v>6.806281490216037e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.204038034524047e-08</v>
+        <v>8.204038034524051e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.557821277381631e-08</v>
+        <v>7.557821277381634e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.012702340948531e-08</v>
+        <v>7.012702340948527e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.006140722720556e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.943012878891768e-08</v>
+        <v>9.943012878891755e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.100818443422178e-08</v>
+        <v>8.10081844342218e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.822212887753002e-08</v>
+        <v>8.822212887752991e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.731080024271814e-08</v>
+        <v>9.731080024271805e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.131522894582293e-08</v>
+        <v>9.131522894582286e-08</v>
       </c>
       <c r="L4" t="n">
         <v>1.139254118656209e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>8.087742644684286e-08</v>
+        <v>8.087742644684281e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>7.884599896713185e-08</v>
       </c>
       <c r="O4" t="n">
         <v>7.478495559301029e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>8.819904600473024e-08</v>
+        <v>8.819904600473023e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.746702896455394e-08</v>
+        <v>7.746702896455387e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.435309691177882e-07</v>
+        <v>1.435309691177881e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.327207810304663e-08</v>
+        <v>9.327207810304656e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.480381044337964e-08</v>
+        <v>8.480381044337963e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>8.736713002110312e-08</v>
+        <v>8.736713002110269e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.211362857910052e-07</v>
+        <v>1.211362857910049e-07</v>
       </c>
       <c r="W4" t="n">
         <v>1.895955917928824e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.830334597753329e-07</v>
+        <v>1.83033459775333e-07</v>
       </c>
       <c r="Y4" t="n">
         <v>1.278244678661055e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.261304357683891e-08</v>
+        <v>8.261304357683896e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.255732504622027e-07</v>
+        <v>1.255732504622025e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.150309180398994e-08</v>
+        <v>7.150309180398992e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1446,31 +1446,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.175275159466828e-08</v>
+        <v>6.175275159466825e-08</v>
       </c>
       <c r="C5" t="n">
         <v>7.321795866629956e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.282435651711251e-08</v>
+        <v>7.28243565171125e-08</v>
       </c>
       <c r="E5" t="n">
         <v>6.707613539615673e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.508927263235974e-08</v>
+        <v>6.508927263235973e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.676689415623245e-08</v>
+        <v>7.676689415623244e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.301746353307396e-08</v>
+        <v>7.301746353307391e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.348418003526761e-08</v>
+        <v>7.348418003526753e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.421279327441699e-08</v>
+        <v>7.421279327441692e-08</v>
       </c>
       <c r="K5" t="n">
         <v>7.385044139022198e-08</v>
@@ -1482,49 +1482,49 @@
         <v>7.30859877892105e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>6.466521250581411e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.690197276094767e-08</v>
+        <v>6.690197276094763e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.720012844147423e-08</v>
+        <v>6.720012844147416e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.010781179021824e-08</v>
+        <v>6.010781179021823e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.636604951136934e-08</v>
+        <v>7.636604951136933e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.411672936141466e-08</v>
+        <v>7.411672936141465e-08</v>
       </c>
       <c r="T5" t="n">
         <v>7.329611326752961e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.84512824938036e-08</v>
+        <v>6.845128249380354e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.282597208263558e-08</v>
+        <v>7.282597208263527e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.934592443007262e-08</v>
+        <v>7.934592443007259e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.718943965582976e-08</v>
+        <v>6.718943965582974e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.648109565238663e-08</v>
+        <v>8.648109565238662e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.253845182078961e-08</v>
+        <v>6.253845182078955e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.565959550723573e-08</v>
+        <v>7.565959550723571e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.377651401875791e-08</v>
+        <v>8.377651401875786e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.452226214971621e-08</v>
+        <v>6.452226214971618e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.066685039552428e-08</v>
+        <v>7.066685039552426e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.027324824633725e-08</v>
+        <v>7.02732482463372e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>6.900429650571987e-08</v>
+        <v>6.90042965057199e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>5.905710086074498e-08</v>
+        <v>5.905710086074496e-08</v>
       </c>
       <c r="G6" t="n">
         <v>7.198101664096395e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.046635526229861e-08</v>
+        <v>7.046635526229858e-08</v>
       </c>
       <c r="I6" t="n">
         <v>7.093307176449222e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.166168500364163e-08</v>
+        <v>7.166168500364161e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.129933311944667e-08</v>
+        <v>7.129933311944664e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.278892146838852e-08</v>
+        <v>7.278892146838848e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.053487951843685e-08</v>
+        <v>7.053487951843681e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.884599896713189e-08</v>
+        <v>7.046844030961167e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.221775741522349e-08</v>
+        <v>7.221775741522348e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.347197445996632e-08</v>
+        <v>7.347197445996631e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>7.045219048553717e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.381494124059402e-08</v>
+        <v>7.381494124059398e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.156562109063928e-08</v>
+        <v>7.15656210906393e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.074500499675435e-08</v>
+        <v>7.074500499675431e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.115913104120054e-08</v>
+        <v>7.115913104120047e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>7.951607776292936e-08</v>
+        <v>7.951607776292916e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.679269807980839e-08</v>
+        <v>7.679269807980837e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.654603483624457e-08</v>
+        <v>7.654603483624456e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.321184395996594e-08</v>
+        <v>7.321184395996595e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.767501430531997e-08</v>
+        <v>6.767501430531993e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.310848723646043e-08</v>
+        <v>7.310848723646037e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>6.99674455000656e-08</v>
+        <v>6.996744550006556e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.672856405067831e-08</v>
+        <v>1.672856405067828e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.599868279717121e-08</v>
+        <v>1.599868279717125e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.685574968338418e-08</v>
+        <v>1.685574968338415e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.663933761591124e-08</v>
+        <v>1.663933761591121e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.696305838283367e-08</v>
+        <v>1.696305838283363e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.892572948801747e-08</v>
+        <v>1.892572948801741e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.676800804309926e-08</v>
+        <v>1.67680080430993e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.712982416736651e-08</v>
+        <v>1.712982416736647e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.765741915790368e-08</v>
+        <v>1.765741915790362e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.807580877165372e-08</v>
+        <v>1.807580877165368e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.996484493613667e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.71835216614943e-08</v>
+        <v>1.718352166149431e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.715077858893749e-08</v>
+        <v>1.715077858893745e-08</v>
       </c>
       <c r="O2" t="n">
         <v>2.70493137413081e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69720969163524e-08</v>
+        <v>1.697209691635231e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.680833780614655e-08</v>
+        <v>1.68083378061465e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.678755119554107e-08</v>
+        <v>1.678755119554104e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.686154425047876e-08</v>
+        <v>1.686154425047878e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.693234907412786e-08</v>
+        <v>1.693234907412783e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.376214547269443e-08</v>
+        <v>2.376214547269441e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.669939448760117e-08</v>
+        <v>1.669939448760113e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.488355441969429e-08</v>
+        <v>2.488355441969426e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.759540640434004e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.687232647697351e-08</v>
+        <v>1.687232647697347e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.762891484315836e-08</v>
+        <v>2.762891484315835e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.70874405683063e-08</v>
+        <v>1.708744056830624e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.728316344829495e-08</v>
+        <v>1.728316344829497e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.617305117466145e-08</v>
+        <v>1.691652661768862e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.59290637580974e-08</v>
+        <v>1.638727761755544e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.921596530984305e-08</v>
+        <v>1.803807496220882e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.740863048112099e-08</v>
+        <v>1.952982204658349e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.176319905374133e-08</v>
+        <v>1.892627954681569e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.680192115410827e-08</v>
+        <v>3.412704197819417e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.720496328527097e-08</v>
+        <v>1.736196395544061e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.563909294844099e-08</v>
+        <v>2.030000914762989e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.764284925494949e-08</v>
+        <v>2.426100195687229e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.761624529382496e-08</v>
+        <v>2.76486245480036e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.011615109117936e-07</v>
+        <v>4.279501772804085e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.78108080122649e-08</v>
+        <v>2.102387936117269e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.604744178752236e-08</v>
+        <v>2.038379093274034e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.910629098188683e-08</v>
+        <v>2.802625522687477e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.176556815649839e-08</v>
+        <v>1.882189205913423e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.809188376768933e-08</v>
+        <v>1.762679021727915e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.76471044652177e-08</v>
+        <v>1.750602489994453e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.925742144396538e-08</v>
+        <v>1.797356833715044e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.100931690964982e-08</v>
+        <v>1.866390461835364e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.912792879329789e-08</v>
+        <v>2.582405452838453e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.548953699887917e-08</v>
+        <v>1.66570653043888e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>4.773859416830474e-08</v>
+        <v>2.934189370157863e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>4.645846811297714e-08</v>
+        <v>2.401426697684021e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.955588942860875e-08</v>
+        <v>1.811234506423859e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.129707421225761e-08</v>
+        <v>2.913433720541134e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.454353022033118e-08</v>
+        <v>1.983832191768161e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.945793272484271e-08</v>
+        <v>2.172582211060197e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1954,49 +1954,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.572859236471473e-08</v>
+        <v>9.57285923647159e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>1.046857424696306e-07</v>
+        <v>1.046857424696307e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.303911971037393e-07</v>
+        <v>1.30391197103739e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.579072214624755e-08</v>
+        <v>7.579072214625166e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.554244267417667e-07</v>
+        <v>1.554244267417669e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.394723501368019e-07</v>
+        <v>5.394723501368004e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.134698842040725e-07</v>
+        <v>1.134698842040727e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.939812501667981e-07</v>
+        <v>1.939812501667983e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.881721886967518e-07</v>
+        <v>2.88172188696752e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>3.802545201849812e-07</v>
+        <v>3.802545201849818e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.872918433308282e-07</v>
+        <v>7.872918433308614e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.150478427787262e-07</v>
+        <v>2.15047842778727e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>1.924609606312541e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.180080563747316e-07</v>
+        <v>1.180080563747318e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.447807221443927e-07</v>
+        <v>1.44780722144393e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.179502516754856e-07</v>
@@ -2005,34 +2005,34 @@
         <v>1.167707466569025e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.236783294367384e-07</v>
+        <v>1.236783294367389e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.477027043304359e-07</v>
+        <v>1.477027043304364e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.533821331850621e-07</v>
+        <v>1.533821331850622e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>8.716012765342348e-08</v>
+        <v>8.716012765342338e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>2.284131197551734e-07</v>
+        <v>2.284131197551735e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.927835327026077e-07</v>
+        <v>2.92783532702608e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.297449527602629e-07</v>
+        <v>1.297449527602632e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.351099373394408e-07</v>
+        <v>1.351099373394447e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.761349703253032e-07</v>
+        <v>1.761349703253039e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.380542820714792e-07</v>
+        <v>2.380542820714808e-07</v>
       </c>
     </row>
     <row r="5">
@@ -2042,25 +2042,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.713603951865725e-08</v>
+        <v>6.713603951865718e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.025002292707447e-08</v>
+        <v>8.025002292707452e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.147436259202254e-08</v>
+        <v>8.147436259202264e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.216011254750747e-08</v>
+        <v>7.216011254750783e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.17946953902573e-08</v>
+        <v>7.179469539025731e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.075309888545921e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>8.048328040185569e-08</v>
+        <v>8.048328040185575e-08</v>
       </c>
       <c r="I5" t="n">
         <v>8.457015996909453e-08</v>
@@ -2069,58 +2069,58 @@
         <v>9.04661312886187e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.525549124893651e-08</v>
+        <v>9.525549124893655e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.165930237263403e-07</v>
+        <v>1.165930237263416e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.562670378790197e-08</v>
+        <v>8.562670378790195e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>7.480587168799899e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.412951477033961e-08</v>
+        <v>7.412951477033958e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.486224724796927e-08</v>
+        <v>7.486224724796943e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.550164170828905e-08</v>
+        <v>6.550164170828914e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>8.070402929898036e-08</v>
+        <v>8.070402929898037e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>8.15398148929884e-08</v>
+        <v>8.15398148929885e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.233958794793313e-08</v>
+        <v>8.233958794793326e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.674359674248994e-08</v>
+        <v>7.674359674249e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.574554913588103e-08</v>
+        <v>7.574554913588105e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>8.684595603319874e-08</v>
+        <v>8.684595603319876e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.557441029563617e-08</v>
+        <v>7.557441029563635e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.447986947644482e-08</v>
+        <v>9.447986947644489e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.905699739578065e-08</v>
+        <v>6.905699739578075e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.409141772029048e-08</v>
+        <v>8.409141772029059e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.990245570917556e-08</v>
+        <v>9.990245570917565e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2130,58 +2130,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.686729744259692e-08</v>
+        <v>7.686729744259708e-08</v>
       </c>
       <c r="C6" t="n">
         <v>8.5386307575796e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.661064724074412e-08</v>
+        <v>8.661064724074411e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.224902275209193e-08</v>
+        <v>8.224902275209213e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.867345487670351e-08</v>
+        <v>6.867345487670349e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.099920326429513e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>8.561956505057724e-08</v>
+        <v>8.561956505057719e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.970644461781607e-08</v>
+        <v>8.970644461781612e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.560241593734026e-08</v>
+        <v>9.560241593734023e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.003917758976581e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.217293083750618e-07</v>
+        <v>1.217293083750617e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>9.076298843662481e-08</v>
+        <v>9.076298843662478e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.92460960631254e-07</v>
+        <v>8.994313444897046e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>8.92712762179832e-08</v>
+        <v>8.927127621798315e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.127639319791576e-08</v>
+        <v>9.127639319791577e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.607511954792227e-08</v>
+        <v>8.607511954792219e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>8.584031394770189e-08</v>
+        <v>8.584031394770192e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>8.667609954170997e-08</v>
+        <v>8.667609954170991e-08</v>
       </c>
       <c r="T6" t="n">
         <v>8.747587259665478e-08</v>
@@ -2193,22 +2193,22 @@
         <v>9.400005810298865e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>9.197970512863416e-08</v>
+        <v>9.197970512863414e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>9.496541016284265e-08</v>
+        <v>9.496541016284314e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.679788975003741e-08</v>
+        <v>8.679788975003743e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.232642585171594e-08</v>
+        <v>8.232642585171593e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.922770236901209e-08</v>
+        <v>8.92277023690121e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.156183291491048e-08</v>
+        <v>9.156183291491058e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2374,82 +2374,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.623099880179427e-08</v>
+        <v>1.623099880179433e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.551909132088094e-08</v>
+        <v>1.551909132088095e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.652606956965346e-08</v>
+        <v>1.652606956965352e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.628405426436027e-08</v>
+        <v>1.628405426436033e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.646133658466951e-08</v>
+        <v>1.646133658466957e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.816497229191387e-08</v>
+        <v>1.816497229191394e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.622602391810151e-08</v>
+        <v>1.622602391810158e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.65263191495601e-08</v>
+        <v>1.652631914956016e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.706942179979353e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.649929403496419e-08</v>
+        <v>1.649929403496426e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.893648274260697e-08</v>
+        <v>1.893648274260703e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.66634929481873e-08</v>
+        <v>1.666349294818731e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.637672940564492e-08</v>
+        <v>1.637672940564498e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.618009245069848e-08</v>
+        <v>2.618009245069855e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.644962989089231e-08</v>
+        <v>1.644962989089237e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.637602336840102e-08</v>
+        <v>1.637602336840109e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.621461351688419e-08</v>
+        <v>1.621461351688424e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.637857149863625e-08</v>
+        <v>1.637857149863631e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.634530003799034e-08</v>
+        <v>1.634530003799041e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.310609914090352e-08</v>
+        <v>2.310609914090356e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62746476372673e-08</v>
+        <v>1.627464763726737e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.419203091705877e-08</v>
+        <v>2.419203091705885e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.767546255227325e-08</v>
+        <v>1.767546255227332e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.67668843606702e-08</v>
+        <v>1.676688436067026e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.715092073836476e-08</v>
+        <v>2.71509207383648e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.647284737622636e-08</v>
+        <v>1.647284737622642e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.682633776984114e-08</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.397319215550128e-08</v>
+        <v>1.594711770773001e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.424804478054474e-08</v>
+        <v>1.557089085978274e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.090842037804046e-08</v>
+        <v>1.839631588917244e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.855584537231875e-08</v>
+        <v>1.973942388283249e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9430836604494e-08</v>
+        <v>1.787435343379425e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.852436134857476e-08</v>
+        <v>3.100049481493377e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.392497696628761e-08</v>
+        <v>1.598170525450221e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.093201800761771e-08</v>
+        <v>1.842141773837037e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.335048008815791e-08</v>
+        <v>2.253958244945469e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.025933735151079e-08</v>
+        <v>1.807487673945541e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>8.665069757338572e-08</v>
+        <v>3.752697280622141e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.504689909959065e-08</v>
+        <v>1.983572782827203e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.739744846800429e-08</v>
+        <v>1.71600865487602e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.539989077150816e-08</v>
+        <v>2.634062676785885e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.89940040012104e-08</v>
+        <v>1.764391321677034e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.738831279602519e-08</v>
+        <v>1.714396931381996e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.364883936627571e-08</v>
+        <v>1.587571338531223e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.738844670013072e-08</v>
+        <v>1.710561622565579e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.669242455396543e-08</v>
+        <v>1.693271605511877e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.632596176534086e-08</v>
+        <v>2.453738760988962e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.496545997673349e-08</v>
+        <v>1.624691871260482e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>4.469521598267717e-08</v>
+        <v>2.795771091412026e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>5.770319505374724e-08</v>
+        <v>2.767420291687631e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.644523604325271e-08</v>
+        <v>2.025646133043573e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.055208354540121e-08</v>
+        <v>2.857173204732844e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.961298668861202e-08</v>
+        <v>1.791370064031964e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.815975821858544e-08</v>
+        <v>2.105044369509242e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.742941797937268e-08</v>
+        <v>7.742941797937297e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.850988184344623e-08</v>
+        <v>8.850988184344626e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.423712099831261e-07</v>
+        <v>1.423712099831264e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.588416319740117e-08</v>
+        <v>8.588416319740119e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.291022537980359e-07</v>
+        <v>1.291022537980361e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.363823604881262e-07</v>
+        <v>4.36382360488127e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.13985606992016e-08</v>
+        <v>8.139856069920168e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.439679055236289e-07</v>
+        <v>1.43967905523629e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.374195426044954e-07</v>
+        <v>2.374195426044956e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.297507802803006e-07</v>
+        <v>1.297507802803008e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.145497848597583e-07</v>
+        <v>6.145497848597575e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.819752325692534e-07</v>
+        <v>1.819752325692532e-07</v>
       </c>
       <c r="N4" t="n">
         <v>1.097327817513392e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>8.909163329321281e-08</v>
+        <v>8.909163329321301e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.176947021438839e-07</v>
+        <v>1.17694702143884e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.08867146585546e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>7.813090427782983e-08</v>
+        <v>7.813090427782982e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.054659070971019e-07</v>
+        <v>1.054659070971021e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.050464195466274e-07</v>
+        <v>1.050464195466276e-07</v>
       </c>
       <c r="U4" t="n">
         <v>1.259700056563453e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>8.24504608526614e-08</v>
+        <v>8.245046085266144e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.944362036408599e-07</v>
+        <v>1.944362036408597e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.777939115248613e-07</v>
+        <v>3.777939115248616e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.861112474201748e-07</v>
+        <v>1.861112474201751e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.225473492867969e-07</v>
+        <v>1.225473492867968e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.279428925350574e-07</v>
+        <v>1.279428925350576e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.167843346585769e-07</v>
+        <v>2.167843346585771e-07</v>
       </c>
     </row>
     <row r="5">
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.404557654748628e-08</v>
+        <v>6.404557654748634e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.616737886274852e-08</v>
+        <v>7.616737886274858e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.902224392568902e-08</v>
+        <v>7.902224392568909e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.008863904188687e-08</v>
+        <v>7.008863904188693e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.846130128218753e-08</v>
+        <v>6.846130128218758e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.99488026698518e-08</v>
+        <v>9.994880266985192e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.563309026359085e-08</v>
+        <v>7.563309026359088e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.902506304554698e-08</v>
+        <v>7.902506304554704e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.510397984397443e-08</v>
+        <v>8.510397984397449e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.871980194401933e-08</v>
+        <v>7.871980194401937e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.062489695590415e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.102121703211785e-08</v>
+        <v>8.10212170321179e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>6.830955695316566e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.990454425602756e-08</v>
+        <v>6.990454425602758e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.100537587842252e-08</v>
+        <v>7.100537587842256e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.339544149935311e-08</v>
+        <v>6.339544149935315e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.550420453279741e-08</v>
+        <v>7.550420453279747e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.735618536108463e-08</v>
+        <v>7.735618536108471e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.698036890746125e-08</v>
+        <v>7.698036890746129e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.278872018082612e-08</v>
+        <v>7.278872018082619e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.261610206357866e-08</v>
+        <v>7.261610206357872e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>8.217367126839939e-08</v>
+        <v>8.217367126839943e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.914037376429875e-08</v>
+        <v>7.914037376429879e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.331086276113846e-08</v>
+        <v>9.331086276113858e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.672996961815637e-08</v>
+        <v>6.67299696181564e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.842107476751143e-08</v>
+        <v>7.842107476751148e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.468827746600344e-08</v>
+        <v>9.468827746600349e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.057470139315788e-08</v>
+        <v>7.057470139315797e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.792641402626053e-08</v>
+        <v>7.792641402626059e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.078127908920109e-08</v>
+        <v>8.078127908920115e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.646120967646017e-08</v>
+        <v>7.646120967646022e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.42045125345748e-08</v>
+        <v>6.420451253457482e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.929344928777417e-08</v>
+        <v>9.929344928777431e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.739212542710289e-08</v>
+        <v>7.739212542710292e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>8.078409820905902e-08</v>
+        <v>8.078409820905906e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.686301500748649e-08</v>
+        <v>8.686301500748653e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.047883710753133e-08</v>
+        <v>8.047883710753138e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.080080047225535e-07</v>
+        <v>1.080080047225536e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>8.278025219563169e-08</v>
+        <v>8.278025219563178e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.097327817513392e-07</v>
+        <v>7.90944132368552e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>8.048694774807506e-08</v>
+        <v>8.048694774807512e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>8.269118557976761e-08</v>
+        <v>8.269118557976768e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.908644823953321e-08</v>
+        <v>7.90864482395333e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.726323969630939e-08</v>
+        <v>7.726323969630946e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.911522052459666e-08</v>
+        <v>7.911522052459675e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.873940407097323e-08</v>
+        <v>7.87394040709733e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>8.023590202565348e-08</v>
+        <v>8.023590202565352e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.549508202229709e-08</v>
+        <v>8.549508202229726e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>8.393041811071335e-08</v>
+        <v>8.393041811071341e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>9.376420157478664e-08</v>
+        <v>9.37642015747867e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.350139293401233e-08</v>
+        <v>8.350139293401241e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.620482371012726e-08</v>
+        <v>7.620482371012732e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.018010993102344e-08</v>
+        <v>8.018010993102351e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.428448670707814e-08</v>
+        <v>8.428448670707819e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.592077278221434e-08</v>
+        <v>1.592077278221431e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.510640466867518e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.602554462340784e-08</v>
+        <v>1.602554462340781e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.593906745109857e-08</v>
+        <v>1.593906745109853e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.617189214566884e-08</v>
+        <v>1.61718921456688e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.758413597089219e-08</v>
+        <v>1.758413597089216e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.593762540154888e-08</v>
+        <v>1.593762540154884e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.614097097350835e-08</v>
+        <v>1.61409709735083e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.660513122223517e-08</v>
+        <v>1.660513122223514e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.622796928381162e-08</v>
+        <v>1.622796928381159e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.804761886312327e-08</v>
+        <v>1.804761886312324e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.626911909639329e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.591153936657836e-08</v>
+        <v>1.59115393665783e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.579285057932277e-08</v>
+        <v>2.579285057932271e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.605761581965112e-08</v>
+        <v>1.605761581965108e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.605801914537147e-08</v>
+        <v>1.605801914537145e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.599950620596179e-08</v>
+        <v>1.599950620596175e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.60918149303178e-08</v>
+        <v>1.609181493031776e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.60901703314675e-08</v>
+        <v>1.609017033146747e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.256578047649933e-08</v>
+        <v>2.25657804764993e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.600880888006345e-08</v>
+        <v>1.600880888006341e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.336543448705335e-08</v>
+        <v>2.336543448705333e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.751733487485598e-08</v>
+        <v>1.751733487485595e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.675182841151899e-08</v>
+        <v>1.675182841151896e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.678975445861007e-08</v>
+        <v>2.678975445861003e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.618690366005233e-08</v>
+        <v>1.61869036600523e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.644145488793933e-08</v>
+        <v>1.644145488793932e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.332639554098995e-08</v>
+        <v>1.556641050410698e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.297515008857928e-08</v>
+        <v>1.4924380396229e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.581227362662699e-08</v>
+        <v>1.644971978026106e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.714822473598353e-08</v>
+        <v>1.912041799780345e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.926327631973067e-08</v>
+        <v>1.765122237057969e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.162359375802448e-08</v>
+        <v>2.835916699530581e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.378344174231764e-08</v>
+        <v>1.577749806420969e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.852105143375377e-08</v>
+        <v>1.740844817480412e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.914476471984713e-08</v>
+        <v>2.089437331488344e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.051382040502498e-08</v>
+        <v>1.799845534750203e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>7.256832378100957e-08</v>
+        <v>3.228679671162116e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.24073258403039e-08</v>
+        <v>1.870484259872154e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.314250368270526e-08</v>
+        <v>1.5527824114785e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.525924989084568e-08</v>
+        <v>2.606347632239571e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.646589030169616e-08</v>
+        <v>1.661514917044276e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.655444037995437e-08</v>
+        <v>1.668519603039628e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.522408632195277e-08</v>
+        <v>1.627522728331751e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.728171237650022e-08</v>
+        <v>1.690245767146117e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73274849498823e-08</v>
+        <v>1.699989419474641e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.685573188215583e-08</v>
+        <v>2.433382397022674e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.534104706880001e-08</v>
+        <v>1.62067385335444e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.834665675316706e-08</v>
+        <v>2.54251981838138e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>6.057835070467471e-08</v>
+        <v>2.836572626170414e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.265597590167452e-08</v>
+        <v>2.228387106211038e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.91238448747441e-08</v>
+        <v>2.788621274540821e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.952773799504927e-08</v>
+        <v>1.77323035117001e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.574832276864839e-08</v>
+        <v>2.001168223946304e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3146,85 +3146,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.384149031724527e-08</v>
+        <v>7.384149031724528e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.02480091170242e-08</v>
+        <v>8.024800911702432e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.77955906060331e-08</v>
+        <v>9.779559060603342e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>7.487719794561254e-08</v>
+        <v>7.487719794561255e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.290858745041787e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.720880126066356e-07</v>
+        <v>3.720880126066338e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.230795395989744e-08</v>
+        <v>8.230795395989741e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2325006926676e-07</v>
+        <v>1.232500692667602e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.008064840496962e-07</v>
+        <v>2.00806484049696e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.334768045649198e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.795041695603105e-07</v>
+        <v>4.795041695603104e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.564608559871409e-07</v>
+        <v>1.564608559871408e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>7.435100066972497e-08</v>
+        <v>7.435100066972502e-08</v>
       </c>
       <c r="O4" t="n">
         <v>9.048333166577878e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>9.814249209474322e-08</v>
+        <v>9.814249209474337e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.026538587717459e-07</v>
+        <v>1.026538587717458e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>9.486484065066289e-08</v>
+        <v>9.486484065066285e-08</v>
       </c>
       <c r="S4" t="n">
         <v>1.058854349778471e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.129619412443564e-07</v>
+        <v>1.129619412443566e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.324756305963987e-07</v>
+        <v>1.324756305963984e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>8.679366601014986e-08</v>
+        <v>8.679366601014977e-08</v>
       </c>
       <c r="W4" t="n">
         <v>1.440746916593133e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.948015063532181e-07</v>
+        <v>3.948015063532183e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.447549835992465e-07</v>
+        <v>2.447549835992464e-07</v>
       </c>
       <c r="Z4" t="n">
         <v>1.107808360772442e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.295605714973447e-07</v>
+        <v>1.29560571497345e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.942805981553228e-07</v>
+        <v>1.942805981553229e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.346377400328273e-08</v>
+        <v>6.346377400328287e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.512722853516423e-08</v>
+        <v>7.512722853516427e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.60955266094482e-08</v>
+        <v>7.609552660944831e-08</v>
       </c>
       <c r="E5" t="n">
         <v>6.90228416792988e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.808379508134793e-08</v>
+        <v>6.808379508134801e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.607441379056538e-08</v>
+        <v>9.607441379056542e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.510243855371108e-08</v>
+        <v>7.51024385537111e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.73993203325779e-08</v>
+        <v>7.739932033257788e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.259114379503216e-08</v>
+        <v>8.259114379503221e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.838200626865339e-08</v>
+        <v>7.838200626865342e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.89357853471412e-08</v>
+        <v>9.893578534714124e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.928914777377638e-08</v>
+        <v>7.928914777377641e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>7.435100066972497e-08</v>
+        <v>6.593343201970473e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.953628040368347e-08</v>
+        <v>6.953628040368339e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.942438559476561e-08</v>
+        <v>6.942438559476553e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.276418129654471e-08</v>
+        <v>6.276418129654465e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.58014107061313e-08</v>
+        <v>7.580141070613136e-08</v>
       </c>
       <c r="S5" t="n">
         <v>7.684408021184364e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.68255037112765e-08</v>
+        <v>7.682550371127655e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.282842333475802e-08</v>
+        <v>7.282842333475814e-08</v>
       </c>
       <c r="V5" t="n">
         <v>7.242520722715541e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.87585279001207e-08</v>
+        <v>7.875852790012066e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.029708381455672e-08</v>
+        <v>8.02970838145568e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.567454106988455e-08</v>
+        <v>9.567454106988471e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.577970500799821e-08</v>
+        <v>6.577970500799819e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.791815115717205e-08</v>
+        <v>7.791815115717213e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.285834841110715e-08</v>
+        <v>9.285834841110718e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.825033416826046e-08</v>
+        <v>6.825033416826041e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.477213632991909e-08</v>
+        <v>7.47721363299191e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.574043440420309e-08</v>
+        <v>7.574043440420308e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.330809225511967e-08</v>
+        <v>7.330809225511975e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.28549256148162e-08</v>
+        <v>6.285492561481613e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.334545019566002e-08</v>
+        <v>9.33454501956601e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.474734634846582e-08</v>
+        <v>7.474734634846587e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.704422812733268e-08</v>
+        <v>7.704422812733273e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.223605158978691e-08</v>
+        <v>8.223605158978693e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.802691406340809e-08</v>
+        <v>7.802691406340818e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.858069314189591e-08</v>
+        <v>9.858069314189602e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.893405556853198e-08</v>
+        <v>7.893405556853203e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>7.435100066972497e-08</v>
+        <v>7.445269258330459e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.770682137409297e-08</v>
+        <v>7.770682137409292e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.864726642741824e-08</v>
+        <v>7.864726642741817e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.6107258602979e-08</v>
+        <v>7.610725860297908e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.544631850088608e-08</v>
+        <v>7.544631850088612e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.648898800659829e-08</v>
+        <v>7.648898800659844e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.647041150603125e-08</v>
+        <v>7.64704115060313e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.806547242690375e-08</v>
+        <v>7.806547242690378e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.248169173333159e-08</v>
+        <v>8.248169173333156e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.840118577550696e-08</v>
+        <v>7.840118577550699e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>9.259089155173025e-08</v>
+        <v>9.259089155173034e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.394414389796756e-08</v>
+        <v>8.394414389796762e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.328322961355973e-08</v>
+        <v>7.32832296135597e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.756305895192688e-08</v>
+        <v>7.756305895192694e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.054454281403644e-08</v>
+        <v>8.054454281403637e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3566,43 +3566,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.519176616295639e-08</v>
+        <v>1.51917661629564e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.435028348059923e-08</v>
+        <v>1.435028348059922e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.558129382866535e-08</v>
+        <v>1.558129382866536e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.527983754440154e-08</v>
+        <v>1.527983754440155e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.524751170465991e-08</v>
+        <v>1.524751170465993e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.571956462567256e-08</v>
+        <v>1.571956462567257e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.531767713270124e-08</v>
+        <v>1.531767713270125e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.540619459063394e-08</v>
+        <v>1.540619459063396e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.548480839850695e-08</v>
+        <v>1.548480839850697e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.587405417308495e-08</v>
+        <v>1.587405417308497e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.609490152296643e-08</v>
+        <v>1.609490152296644e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.533432109273869e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.563704796558765e-08</v>
+        <v>1.563704796558766e-08</v>
       </c>
       <c r="O2" t="n">
         <v>2.485523821949046e-08</v>
@@ -3614,7 +3614,7 @@
         <v>1.53811981990919e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.536045630281883e-08</v>
+        <v>1.536045630281884e-08</v>
       </c>
       <c r="S2" t="n">
         <v>1.533329925963325e-08</v>
@@ -3623,28 +3623,28 @@
         <v>1.527927672998905e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.17828474540964e-08</v>
+        <v>2.178284745409641e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.518834890518763e-08</v>
+        <v>1.518834890518764e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.258805882483524e-08</v>
+        <v>2.258805882483522e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.540884255241254e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.520321919222062e-08</v>
+        <v>1.520321919222064e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.601586090977483e-08</v>
+        <v>2.601586090977484e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.538709203538946e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7667635950402e-08</v>
+        <v>1.766763595040199e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.331077444116396e-08</v>
+        <v>1.522025117768835e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.103602187221646e-08</v>
+        <v>1.396249820709783e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.245226335579033e-08</v>
+        <v>1.843558357043552e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.881450356957913e-08</v>
+        <v>1.94055892970258e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.468038644959642e-08</v>
+        <v>1.573259333870471e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.545495236779159e-08</v>
+        <v>1.921096797241302e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.633912170850946e-08</v>
+        <v>1.634410654875746e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.83798049326783e-08</v>
+        <v>1.703244020324449e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.009428831470714e-08</v>
+        <v>1.748923209315879e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.923673798327445e-08</v>
+        <v>2.059788818357914e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.420594586868536e-08</v>
+        <v>2.212491219013856e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.7554547775654e-08</v>
+        <v>1.665784287728378e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.369781372229044e-08</v>
+        <v>1.880331839908475e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.353878774580722e-08</v>
+        <v>2.50526627764987e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.911945846490778e-08</v>
+        <v>1.718950791873042e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.775887035917246e-08</v>
+        <v>1.675568333375752e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.732541086369635e-08</v>
+        <v>1.668262747865469e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.657800348445805e-08</v>
+        <v>1.626350463816647e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.540376881067566e-08</v>
+        <v>1.597138985469094e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.181059598771482e-08</v>
+        <v>2.241554054473514e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.321941957242338e-08</v>
+        <v>1.516143124628133e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.464263598089987e-08</v>
+        <v>2.388382071153273e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.841873112894016e-08</v>
+        <v>1.702115943254887e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.360728989194259e-08</v>
+        <v>1.534652371787681e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.747042297892227e-08</v>
+        <v>2.704710290952788e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.787214050751292e-08</v>
+        <v>1.681741261865663e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.067565476806428e-08</v>
+        <v>3.536804108879372e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.991376551787128e-08</v>
+        <v>7.991376551787124e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>6.916013701693256e-08</v>
+        <v>6.916013701693261e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.703113797451846e-07</v>
+        <v>1.703113797451847e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>9.689232562269756e-08</v>
+        <v>9.689232562269748e-08</v>
       </c>
       <c r="F4" t="n">
         <v>9.65655594421162e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.760422883885755e-07</v>
+        <v>1.760422883885753e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15193211513347e-07</v>
+        <v>1.151932115133469e-07</v>
       </c>
       <c r="I4" t="n">
         <v>1.327010783539093e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.37056758835666e-07</v>
+        <v>1.370567588356659e-07</v>
       </c>
       <c r="K4" t="n">
         <v>2.198034846565733e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.497698288427715e-07</v>
+        <v>2.497698288427714e-07</v>
       </c>
       <c r="M4" t="n">
         <v>1.206442549077269e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>1.765920085809778e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>8.458734400343644e-08</v>
+        <v>8.458734400343643e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.301724637090134e-07</v>
+        <v>1.301724637090136e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.218076218390375e-07</v>
+        <v>1.218076218390373e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.240828242039595e-07</v>
+        <v>1.240828242039594e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.03707868643064e-07</v>
+        <v>1.037078686430642e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.022623663577292e-07</v>
+        <v>1.022623663577291e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>9.860128903758038e-08</v>
+        <v>9.860128903758055e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>7.65173471651289e-08</v>
+        <v>7.651734716512857e-08</v>
       </c>
       <c r="W4" t="n">
         <v>1.200531362939261e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.309309927013904e-07</v>
+        <v>1.309309927013907e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.484616272877871e-08</v>
+        <v>8.484616272877866e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.08192043116149e-07</v>
+        <v>1.081920431161489e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.241729705409915e-07</v>
+        <v>1.241729705409914e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.404900007820431e-07</v>
+        <v>6.40490000782043e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.40481384630898e-08</v>
+        <v>6.404813846308979e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.520154043332857e-08</v>
+        <v>7.520154043332854e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.035012339015335e-08</v>
+        <v>8.035012339015326e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.060752374713324e-08</v>
+        <v>7.06075237471332e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.653201663677962e-08</v>
+        <v>6.653201663677963e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.437993170232992e-08</v>
+        <v>8.437993170232984e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.737245153956716e-08</v>
+        <v>7.7372451539567e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.837229694695946e-08</v>
+        <v>7.837229694695934e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.9203795040206e-08</v>
+        <v>7.920379504020599e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.365698615678488e-08</v>
+        <v>8.365698615678492e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.615155856849633e-08</v>
+        <v>8.615155856849626e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.799037091195469e-08</v>
+        <v>7.799037091195461e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>7.175378050572232e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.955122734182232e-08</v>
+        <v>6.955122734182226e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.149437273750752e-08</v>
+        <v>7.149437273750753e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.384882796926459e-08</v>
+        <v>6.384882796926457e-08</v>
       </c>
       <c r="R5" t="n">
         <v>7.78556619454357e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.754891064979747e-08</v>
+        <v>7.754891064979741e-08</v>
       </c>
       <c r="T5" t="n">
         <v>7.693870132587492e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.110518930064914e-08</v>
+        <v>7.110518930064906e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.2273799543941e-08</v>
+        <v>7.227379954394098e-08</v>
       </c>
       <c r="W5" t="n">
         <v>7.794234382149153e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.525193392400009e-08</v>
+        <v>6.525193392400007e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.791081341523176e-08</v>
+        <v>8.791081341523173e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.553626355680328e-08</v>
+        <v>6.553626355680325e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.815652479786336e-08</v>
+        <v>7.815652479786326e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.160930288188317e-07</v>
+        <v>1.160930288188316e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3918,79 +3918,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.032939118995488e-08</v>
+        <v>7.032939118995484e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.649823326487623e-08</v>
+        <v>7.649823326487624e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.164681622170098e-08</v>
+        <v>8.1646816221701e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.664519768738315e-08</v>
+        <v>7.664519768738317e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.192978548457426e-08</v>
+        <v>6.192978548457424e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>8.320865729415834e-08</v>
+        <v>8.320865729415837e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.866914437111481e-08</v>
+        <v>7.866914437111483e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.966898977850709e-08</v>
+        <v>7.966898977850708e-08</v>
       </c>
       <c r="J6" t="n">
         <v>8.050048787175366e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>8.495367898833258e-08</v>
+        <v>8.495367898833257e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.744825140004396e-08</v>
+        <v>8.744825140004397e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.928706374350373e-08</v>
+        <v>7.92870637435037e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.765920085809779e-07</v>
+        <v>8.227658484640851e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.983108853198727e-08</v>
+        <v>7.983108853198726e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>8.289429704197585e-08</v>
+        <v>8.289429704197588e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.938665284968329e-08</v>
+        <v>7.938665284968334e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.915235477698344e-08</v>
+        <v>7.915235477698345e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.884560348134515e-08</v>
+        <v>7.884560348134519e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.823539415742265e-08</v>
+        <v>7.823539415742266e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.821274769948587e-08</v>
+        <v>7.821274769948584e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.480798714247653e-08</v>
+        <v>8.480798714247655e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.923669755190533e-08</v>
+        <v>7.923669755190534e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.969889972491884e-08</v>
+        <v>7.969889972491886e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.737628928013216e-08</v>
+        <v>7.737628928013215e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.478548211038551e-08</v>
+        <v>7.478548211038559e-08</v>
       </c>
       <c r="AA6" t="n">
         <v>7.9453217629411e-08</v>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.488037189537777e-08</v>
+        <v>1.488037189537773e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.41140079955278e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.490860283853526e-08</v>
+        <v>1.490860283853524e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.491856187429227e-08</v>
+        <v>1.491856187429223e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.502414861883302e-08</v>
+        <v>1.502414861883303e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.498401637302284e-08</v>
+        <v>1.49840163730228e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.490366163065193e-08</v>
+        <v>1.490366163065189e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.49535484606602e-08</v>
+        <v>1.495354846066018e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.496878950277157e-08</v>
+        <v>1.49687895027716e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.488549072558388e-08</v>
+        <v>1.488549072558384e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.496461271239283e-08</v>
+        <v>1.496461271239279e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.478714886926006e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.504648582351559e-08</v>
+        <v>1.504648582351556e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.473921011610181e-08</v>
+        <v>2.473921011610179e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.490131301524222e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.483803316712252e-08</v>
+        <v>1.48380331671225e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.516198376996752e-08</v>
+        <v>1.516198376996749e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.493721326513439e-08</v>
+        <v>1.493721326513435e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483137821737164e-08</v>
+        <v>1.483137821737162e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.121401819912117e-08</v>
+        <v>2.121401819912113e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.491157800100331e-08</v>
+        <v>1.491157800100328e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.230630827519992e-08</v>
+        <v>2.230630827519987e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.512833053681968e-08</v>
+        <v>1.512833053681964e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.488179751547654e-08</v>
+        <v>1.488179751547651e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.57714327505429e-08</v>
+        <v>2.577143275054289e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.49342024915438e-08</v>
+        <v>1.493420249154377e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.475573124112457e-08</v>
+        <v>1.475573124112456e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.388036511994227e-08</v>
+        <v>1.522600979001594e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.317138490481426e-08</v>
+        <v>1.450552149438423e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.459735414168061e-08</v>
+        <v>1.549705135257828e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.825161898352238e-08</v>
+        <v>1.903420417499457e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.732396759127068e-08</v>
+        <v>1.643800040436277e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.626295464797253e-08</v>
+        <v>1.598050553919092e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.451521482321951e-08</v>
+        <v>1.551212763105946e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56579365167764e-08</v>
+        <v>1.588215306317538e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.59411472444638e-08</v>
+        <v>1.590571794043737e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.405097149043282e-08</v>
+        <v>1.529454250363187e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.584311762425791e-08</v>
+        <v>1.582517764499259e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.265928850662545e-08</v>
+        <v>1.480775673984981e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.778308609605854e-08</v>
+        <v>1.657096559593212e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.928783657419288e-08</v>
+        <v>2.674441708553593e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.435431870070762e-08</v>
+        <v>1.538230814660775e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.294080238497086e-08</v>
+        <v>1.490476471160354e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.05504295313877e-08</v>
+        <v>1.759631524788161e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.519684348263332e-08</v>
+        <v>1.562424764560947e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27986183265282e-08</v>
+        <v>1.488693296270616e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8086342638705e-08</v>
+        <v>2.091682422342725e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.458592025571088e-08</v>
+        <v>1.541639050164036e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.766753039292185e-08</v>
+        <v>2.462462398240232e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.97106354242388e-08</v>
+        <v>1.721943513489294e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.395148940862434e-08</v>
+        <v>1.528080821216297e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.902710435999897e-08</v>
+        <v>2.737893290153572e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.51646251305442e-08</v>
+        <v>1.569768827965237e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.132355472598152e-08</v>
+        <v>1.438442863088061e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4338,58 +4338,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.4410884340202e-08</v>
+        <v>8.441088434020203e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.741446772320391e-08</v>
+        <v>8.741446772320386e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.304332670625223e-08</v>
+        <v>9.304332670625218e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.064060836812914e-08</v>
+        <v>9.064060836812917e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.172221834716746e-07</v>
+        <v>1.172221834716745e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.000966581964278e-07</v>
+        <v>1.000966581964279e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.572491175375216e-08</v>
+        <v>9.572491175375215e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>1.037489115009086e-07</v>
+        <v>1.037489115009084e-07</v>
       </c>
       <c r="J4" t="n">
         <v>1.00157126702723e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>8.7234566150329e-08</v>
+        <v>8.723456615032897e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.616069971518403e-08</v>
+        <v>9.616069971518397e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>7.700249716848816e-08</v>
+        <v>7.700249716848813e-08</v>
       </c>
       <c r="N4" t="n">
         <v>1.18666809023426e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27638393788221e-07</v>
+        <v>1.276383937882209e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>8.785415368081567e-08</v>
+        <v>8.785415368081569e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.706351015998331e-08</v>
+        <v>7.706351015998333e-08</v>
       </c>
       <c r="R4" t="n">
         <v>1.485479475132212e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.193901091853716e-08</v>
+        <v>9.193901091853712e-08</v>
       </c>
       <c r="T4" t="n">
         <v>7.812542763015471e-08</v>
@@ -4398,25 +4398,25 @@
         <v>6.744997487946986e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.631747877560789e-08</v>
+        <v>8.631747877560785e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.397237326736818e-07</v>
+        <v>1.397237326736817e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.345706419334145e-07</v>
+        <v>1.345706419334149e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.759399544897573e-08</v>
+        <v>8.759399544897572e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.169579659814158e-07</v>
+        <v>1.169579659814156e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>9.792309758984331e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.640610531499991e-08</v>
+        <v>6.640610531499988e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.25136746365193e-08</v>
+        <v>6.251367463651925e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.325507813783333e-08</v>
+        <v>7.325507813783322e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.357240464196712e-08</v>
+        <v>7.357240464196704e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.796624400322162e-08</v>
+        <v>6.796624400322154e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.581084174756851e-08</v>
+        <v>6.581084174756842e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.66512127593366e-08</v>
+        <v>7.665121275933647e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.351659142585691e-08</v>
+        <v>7.351659142585679e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.40800861198758e-08</v>
+        <v>7.40800861198757e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.420404688272139e-08</v>
+        <v>7.420404688272132e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.331134269408368e-08</v>
+        <v>7.331134269408356e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.42050619330031e-08</v>
+        <v>7.420506193300298e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.264835786999731e-08</v>
+        <v>7.264835786999719e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.18666809023426e-07</v>
+        <v>6.680467704908086e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.006966474643233e-08</v>
+        <v>7.006966474643224e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.689191216585569e-08</v>
+        <v>6.689191216585565e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.99248138653083e-08</v>
+        <v>5.992481386530824e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.643445882348138e-08</v>
+        <v>7.643445882348128e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.389557257185062e-08</v>
+        <v>7.389557257185054e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.270011702084302e-08</v>
+        <v>7.270011702084292e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.69144699859352e-08</v>
+        <v>6.691446998593512e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.034269599021654e-08</v>
+        <v>7.034269599021648e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>7.648134675260779e-08</v>
+        <v>7.648134675260768e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.418818465609323e-08</v>
+        <v>6.418818465609318e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.394745337337401e-08</v>
+        <v>8.394745337337393e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.44961518927546e-08</v>
+        <v>6.44961518927545e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.386156449912055e-08</v>
+        <v>7.386156449912043e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.32107984574578e-08</v>
+        <v>8.321079845745765e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.635225979470725e-08</v>
+        <v>6.635225979470722e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.208994356794587e-08</v>
+        <v>7.208994356794585e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.240727007207971e-08</v>
+        <v>7.240727007207967e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.119589352489763e-08</v>
+        <v>7.119589352489758e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.048905906941691e-08</v>
+        <v>6.04890590694169e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.325910933268169e-08</v>
+        <v>7.325910933268157e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.235145685596947e-08</v>
+        <v>7.235145685596943e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.291495154998836e-08</v>
+        <v>7.291495154998832e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.303891231283399e-08</v>
+        <v>7.303891231283397e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.214620812419626e-08</v>
+        <v>7.214620812419621e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.303992736311568e-08</v>
+        <v>7.30399273631156e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.148322330011134e-08</v>
+        <v>7.14832233001113e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.18666809023426e-07</v>
+        <v>7.396472181673939e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.684283509403927e-08</v>
+        <v>7.684283509403922e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.463930898594545e-08</v>
+        <v>7.463930898594543e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.161016186644494e-08</v>
+        <v>7.161016186644492e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.526932425359398e-08</v>
+        <v>7.526932425359394e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.273043800196323e-08</v>
+        <v>7.273043800196316e-08</v>
       </c>
       <c r="T6" t="n">
         <v>7.153498245095559e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.099163933046787e-08</v>
+        <v>7.099163933046786e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>7.873266679216583e-08</v>
+        <v>7.873266679216581e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.531410149540815e-08</v>
+        <v>7.531410149540813e-08</v>
       </c>
       <c r="X6" t="n">
         <v>7.488919550393698e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.210449161707344e-08</v>
+        <v>7.210449161707339e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.081199190982377e-08</v>
+        <v>7.081199190982373e-08</v>
       </c>
       <c r="AA6" t="n">
         <v>7.269642992923306e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.082699406130257e-08</v>
+        <v>7.082699406130255e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.500597405813202e-08</v>
+        <v>1.500597405813198e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.407738118581796e-08</v>
+        <v>1.407738118581797e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.494733604686727e-08</v>
+        <v>1.494733604686723e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.506884454911494e-08</v>
+        <v>1.506884454911491e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.49883812858634e-08</v>
+        <v>1.498838128586336e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.491468873465066e-08</v>
+        <v>1.491468873465064e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.487188728391713e-08</v>
+        <v>1.487188728391711e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.488794367967568e-08</v>
+        <v>1.488794367967564e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.496602179487708e-08</v>
+        <v>1.496602179487705e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.485952178850424e-08</v>
+        <v>1.48595217885042e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.499492372140167e-08</v>
+        <v>1.499492372140164e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.480026701330398e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.491129134376722e-08</v>
+        <v>1.491129134376719e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.478331101676369e-08</v>
+        <v>2.478331101676364e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.498600481118117e-08</v>
+        <v>1.498600481118118e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.484201415566628e-08</v>
+        <v>1.484201415566624e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.524798901978142e-08</v>
+        <v>1.52479890197814e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.495020287668689e-08</v>
+        <v>1.495020287668687e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.483655662620001e-08</v>
+        <v>1.483655662619997e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.111046562147365e-08</v>
+        <v>2.111046562147364e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.517118933034811e-08</v>
+        <v>1.517118933034812e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.230306558797888e-08</v>
+        <v>2.230306558797885e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.522414414945436e-08</v>
+        <v>1.522414414945431e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.491944758709747e-08</v>
+        <v>1.491944758709746e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.56822876133607e-08</v>
+        <v>2.568228761336065e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.495989093722144e-08</v>
+        <v>1.49598909372214e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.48252566138045e-08</v>
+        <v>1.482525661380445e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.62358285208553e-08</v>
+        <v>1.604395900946345e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.355813385116992e-08</v>
+        <v>1.461630323655899e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.495862749915416e-08</v>
+        <v>1.565678478718702e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>3.122326919844662e-08</v>
+        <v>2.006141972948005e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.594327522102344e-08</v>
+        <v>1.601043798444587e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.413544917707414e-08</v>
+        <v>1.532938980993294e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.322200011450208e-08</v>
+        <v>1.508516345939469e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.358101296396062e-08</v>
+        <v>1.519671624635513e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.534553935202962e-08</v>
+        <v>1.575018055341612e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.290565172660595e-08</v>
+        <v>1.494720607156815e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.600970978011533e-08</v>
+        <v>1.593734483139912e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.240298783262386e-08</v>
+        <v>1.475988828492686e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.410143985229317e-08</v>
+        <v>1.535614169812767e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.987897757757846e-08</v>
+        <v>2.697153340362824e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.57645425604581e-08</v>
+        <v>1.587258002625734e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.249374588883228e-08</v>
+        <v>1.479677437571635e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.202103348773782e-08</v>
+        <v>1.815256822523591e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.496356215469933e-08</v>
+        <v>1.560295237266115e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.237657084955533e-08</v>
+        <v>1.477526753301979e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.883782646649957e-08</v>
+        <v>2.108015276518563e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>3.003270301912087e-08</v>
+        <v>1.726735375609383e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.978171773517731e-08</v>
+        <v>2.531129106843878e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.139762351859365e-08</v>
+        <v>1.780104044029623e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.428583483450038e-08</v>
+        <v>1.542909140394683e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.69513611606962e-08</v>
+        <v>2.669292242891059e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.522083993142258e-08</v>
+        <v>1.574755020392874e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.236449111312211e-08</v>
+        <v>1.478066377575336e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4934,85 +4934,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.027122242709104e-07</v>
+        <v>1.027122242709103e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>9.134026791165992e-08</v>
+        <v>9.134026791165993e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>9.64331667748096e-08</v>
+        <v>9.643316677480955e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.12218136905741e-07</v>
+        <v>1.122181369057409e-07</v>
       </c>
       <c r="F4" t="n">
         <v>1.063192325522381e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.54906930287995e-08</v>
+        <v>8.549069302880025e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.349332417607702e-08</v>
+        <v>8.349332417607703e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.557554821161012e-08</v>
+        <v>8.557554821161016e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.637926174446058e-08</v>
+        <v>9.637926174446051e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>7.840509547411496e-08</v>
+        <v>7.840509547411493e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.921394834833276e-08</v>
+        <v>9.921394834833282e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>7.533357838591341e-08</v>
+        <v>7.533357838591342e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.84161393079848e-08</v>
+        <v>8.841613930798484e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32376510936813e-07</v>
+        <v>1.323765109368129e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>9.79368508906288e-08</v>
+        <v>9.793685089062875e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.420423900205163e-08</v>
+        <v>7.420423900205166e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.626268142004112e-07</v>
+        <v>1.626268142004109e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>9.187140007902347e-08</v>
+        <v>9.187140007902357e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>7.460700379978281e-08</v>
+        <v>7.460700379978279e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>7.406345838502514e-08</v>
+        <v>7.406345838502513e-08</v>
       </c>
       <c r="V4" t="n">
         <v>1.288339247566721e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.594699662386993e-07</v>
+        <v>1.594699662386995e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>1.470106322584526e-07</v>
+        <v>1.470106322584525e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.058012627016263e-08</v>
+        <v>9.058012627016274e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>1.003604080408215e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.833089321544773e-08</v>
+        <v>9.833089321544774e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.576467225928101e-08</v>
+        <v>7.576467225928103e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5028,19 +5028,19 @@
         <v>7.363370014854609e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.389944770797119e-08</v>
+        <v>7.389944770797118e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.956232217350779e-08</v>
+        <v>6.956232217350777e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.531068771515299e-08</v>
+        <v>6.531068771515297e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.575414135850765e-08</v>
+        <v>7.575414135850769e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.304721922230366e-08</v>
+        <v>7.304721922230364e-08</v>
       </c>
       <c r="I5" t="n">
         <v>7.32285835987035e-08</v>
@@ -5055,31 +5055,31 @@
         <v>7.443697238324905e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.267613134208093e-08</v>
+        <v>7.267613134208095e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>8.84161393079848e-08</v>
+        <v>6.518027642031466e-08</v>
       </c>
       <c r="O5" t="n">
         <v>7.052407607471927e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.774850034582111e-08</v>
+        <v>6.77485003458211e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.987961184055916e-08</v>
+        <v>5.987961184055918e-08</v>
       </c>
       <c r="R5" t="n">
         <v>7.729546134423715e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.393182986959078e-08</v>
+        <v>7.393182986959076e-08</v>
       </c>
       <c r="T5" t="n">
         <v>7.264814319048325e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.752620171640013e-08</v>
+        <v>6.752620171640009e-08</v>
       </c>
       <c r="V5" t="n">
         <v>7.320616895415297e-08</v>
@@ -5091,13 +5091,13 @@
         <v>6.517871962677928e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.424875426565266e-08</v>
+        <v>8.424875426565265e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>6.365964183495412e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.404126097005654e-08</v>
+        <v>7.40412609700565e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>8.384818529892404e-08</v>
@@ -5110,85 +5110,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.665955384377248e-08</v>
+        <v>6.665955384377245e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.117869325585219e-08</v>
+        <v>7.117869325585215e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.144444081527729e-08</v>
+        <v>7.144444081527725e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.155974289972338e-08</v>
+        <v>7.155974289972334e-08</v>
       </c>
       <c r="F6" t="n">
         <v>5.935070268145291e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>7.107568244669281e-08</v>
+        <v>7.107568244669285e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.059221232960977e-08</v>
+        <v>7.059221232960973e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>7.07735767060096e-08</v>
+        <v>7.077357670600956e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>7.161247568696787e-08</v>
+        <v>7.161247568696784e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.045253837051198e-08</v>
+        <v>7.045253837051194e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>7.198196549055518e-08</v>
+        <v>7.198196549055516e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.022112444938796e-08</v>
+        <v>7.022112444938791e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>8.84161393079848e-08</v>
+        <v>7.103729931237964e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.590209669972511e-08</v>
+        <v>7.590209669972509e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>7.407903967783313e-08</v>
+        <v>7.407903967783309e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.025478964510619e-08</v>
+        <v>7.025478964510616e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.484045445154323e-08</v>
+        <v>7.48404544515432e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.147682297689688e-08</v>
+        <v>7.147682297689686e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>7.01931362977893e-08</v>
+        <v>7.019313629778927e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>7.030325569478238e-08</v>
+        <v>7.030325569478234e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>7.996608250378931e-08</v>
+        <v>7.996608250378929e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.526556145261075e-08</v>
+        <v>7.526556145261071e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>7.457111567201681e-08</v>
+        <v>7.457111567201674e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>7.112942783285206e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.884251076825556e-08</v>
+        <v>6.884251076825552e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.158625407736263e-08</v>
+        <v>7.15862540773626e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.019222837736253e-08</v>
+        <v>7.019222837736249e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.651293927063863e-08</v>
+        <v>1.651293927063856e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.568710458575885e-08</v>
+        <v>1.568710458575906e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.678478110293479e-08</v>
+        <v>1.678478110293489e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.644173036113698e-08</v>
+        <v>1.644173036113687e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.66701984656919e-08</v>
+        <v>1.667019846569192e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.861621082691191e-08</v>
+        <v>1.861621082691206e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.657853649900035e-08</v>
+        <v>1.657853649900048e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.703194692251455e-08</v>
+        <v>1.703194692251463e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.738901916514242e-08</v>
+        <v>1.738901916514231e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.750607826179589e-08</v>
+        <v>1.750607826179577e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.935212988306375e-08</v>
+        <v>1.935212988306386e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.700087319392944e-08</v>
+        <v>1.700087319392927e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.730635461192309e-08</v>
+        <v>1.73063546119235e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.669884101523405e-08</v>
+        <v>2.669884101523406e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.679972285738525e-08</v>
+        <v>1.679972285738526e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.662249179380946e-08</v>
+        <v>1.662249179380975e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.668516500073613e-08</v>
+        <v>1.668516500073605e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6630438755009e-08</v>
+        <v>1.663043875500884e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.681838304879824e-08</v>
+        <v>1.681838304879841e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.330084555927142e-08</v>
+        <v>2.330084555927163e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.648269110108816e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.39600079502115e-08</v>
+        <v>2.396000795021141e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.749733957495938e-08</v>
+        <v>1.74973395749596e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.664691228601202e-08</v>
+        <v>1.66469122860118e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.736796414401357e-08</v>
+        <v>2.736796414401368e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.682788084870524e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.697907095701725e-08</v>
+        <v>1.697907095701733e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.566643529065657e-08</v>
+        <v>1.662521565638726e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.356897503261436e-08</v>
+        <v>1.544499695766909e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.208243222634563e-08</v>
+        <v>1.892391449505282e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.736063684035151e-08</v>
+        <v>1.942402372703743e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.943953101528742e-08</v>
+        <v>1.798864064828069e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>7.409616026762176e-08</v>
+        <v>3.282920197209486e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.730620238724302e-08</v>
+        <v>1.728102423633626e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.78781760556248e-08</v>
+        <v>2.094658373154029e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.590250430656922e-08</v>
+        <v>2.344352018340422e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.884326447634411e-08</v>
+        <v>2.443435853815805e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>9.141421466520839e-08</v>
+        <v>3.901420978186e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.803206860676334e-08</v>
+        <v>2.083926154078788e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>4.417167272366128e-08</v>
+        <v>2.308145576485856e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85087554450968e-08</v>
+        <v>2.761201716937985e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.225398718889198e-08</v>
+        <v>1.88684991957192e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.827295711998518e-08</v>
+        <v>1.755528379870639e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.978804490868566e-08</v>
+        <v>1.814349036052472e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.838737657405833e-08</v>
+        <v>1.752065875557867e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.287263960001202e-08</v>
+        <v>1.919691461087054e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.725586666633188e-08</v>
+        <v>2.493158293470157e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.495807563065083e-08</v>
+        <v>1.635958072660197e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.623297889600906e-08</v>
+        <v>2.509135740583944e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>4.868924221086472e-08</v>
+        <v>2.466933565331243e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.881920364085149e-08</v>
+        <v>1.773966659663335e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.072106076598902e-08</v>
+        <v>2.877091258435283e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.30147034940146e-08</v>
+        <v>1.919211760162864e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.689709337585191e-08</v>
+        <v>2.06923477491011e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5530,37 +5530,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.271148435913437e-08</v>
+        <v>9.271148435913596e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.452545756977623e-08</v>
+        <v>8.452545756977629e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.597442372541666e-07</v>
+        <v>1.597442372541668e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>7.655062465310278e-08</v>
+        <v>7.655062465310418e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.338477177548358e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.977329908002792e-07</v>
+        <v>4.977329908002788e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.161291119860972e-07</v>
+        <v>1.161291119860971e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.158289780213131e-07</v>
+        <v>2.158289780213132e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.662801660820082e-07</v>
+        <v>2.662801660820086e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.949870748095659e-07</v>
+        <v>2.949870748095662e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.76511736589957e-07</v>
+        <v>6.76511736589964e-07</v>
       </c>
       <c r="M4" t="n">
         <v>2.07879971103916e-07</v>
@@ -5572,43 +5572,43 @@
         <v>1.152691880287835e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.504378207324809e-07</v>
+        <v>1.504378207324811e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.199611471489969e-07</v>
+        <v>1.199611471489966e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.396146569914914e-07</v>
+        <v>1.396146569914912e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.145965281089095e-07</v>
+        <v>1.145965281089099e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67220390872374e-07</v>
+        <v>1.672203908723742e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.394131050634726e-07</v>
+        <v>1.394131050634772e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>8.409432059005843e-08</v>
+        <v>8.409432059005817e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.257752357432733e-07</v>
+        <v>1.257752357432735e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.153290880137994e-07</v>
+        <v>3.153290880137988e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.244155160199248e-07</v>
+        <v>1.24415516019925e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.304245492475866e-07</v>
+        <v>1.304245492475862e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.63475006290999e-07</v>
+        <v>1.634750062909996e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.133779696065089e-07</v>
+        <v>2.133779696065087e-07</v>
       </c>
     </row>
     <row r="5">
@@ -5618,52 +5618,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.65342421038459e-08</v>
+        <v>6.653424210384588e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.853405496278575e-08</v>
+        <v>7.853405496278576e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.228023831347073e-08</v>
+        <v>8.228023831347076e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.165603637088303e-08</v>
+        <v>7.165603637088312e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.028523898505588e-08</v>
+        <v>7.028523898505593e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.055954099697075e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9950610634825e-08</v>
+        <v>7.995061063482502e-08</v>
       </c>
       <c r="I5" t="n">
         <v>8.507208994751698e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.904233658059517e-08</v>
+        <v>8.90423365805952e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.042762153588968e-08</v>
+        <v>9.04276215358898e-08</v>
       </c>
       <c r="L5" t="n">
         <v>1.112796238238139e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>8.516152544781126e-08</v>
+        <v>8.516152544781122e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.702318436412085e-07</v>
+        <v>7.83460817946137e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.345115631403687e-08</v>
+        <v>7.345115631403691e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.46617223690126e-08</v>
+        <v>7.466172236901264e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.528067937681811e-08</v>
+        <v>6.528067937681812e-08</v>
       </c>
       <c r="R5" t="n">
         <v>8.115502861346184e-08</v>
@@ -5672,28 +5672,28 @@
         <v>8.053687049265709e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>8.265978774965606e-08</v>
+        <v>8.265978774965608e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.545563797111228e-08</v>
+        <v>7.545563797111241e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.496988563447795e-08</v>
+        <v>7.496988563447794e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>8.07814697381639e-08</v>
+        <v>8.078146973816386e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.632421472937331e-08</v>
+        <v>7.632421472937345e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.331622793367621e-08</v>
+        <v>9.331622793367624e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.844856990277747e-08</v>
+        <v>6.844856990277754e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.276706976880853e-08</v>
+        <v>8.276706976880857e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>9.78482855199229e-08</v>
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.613194524370519e-08</v>
+        <v>7.613194524370526e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>8.362764363240945e-08</v>
+        <v>8.362764363240949e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>8.737382698309446e-08</v>
+        <v>8.737382698309449e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>8.161301603140634e-08</v>
+        <v>8.161301603140632e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.724246505908921e-08</v>
+        <v>6.724246505908922e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.080606791795719e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>8.504419930444881e-08</v>
+        <v>8.504419930444889e-08</v>
       </c>
       <c r="I6" t="n">
         <v>9.016567861714077e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>9.413592525021897e-08</v>
+        <v>9.413592525021902e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.552121020551347e-08</v>
+        <v>9.552121020551351e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.163732124934377e-07</v>
+        <v>1.163732124934378e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>9.025511411743626e-08</v>
+        <v>9.025511411743631e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.702318436412085e-07</v>
+        <v>9.326523970278774e-08</v>
       </c>
       <c r="O6" t="n">
         <v>8.837813625825791e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.083951020026995e-08</v>
+        <v>9.083951020026994e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.554070554461237e-08</v>
+        <v>8.554070554461239e-08</v>
       </c>
       <c r="R6" t="n">
         <v>8.624861728308562e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>8.563045916228086e-08</v>
+        <v>8.56304591622809e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>8.775337641927991e-08</v>
+        <v>8.775337641927985e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>8.674153932784916e-08</v>
+        <v>8.674153932784924e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>9.296356735511805e-08</v>
+        <v>9.296356735511797e-08</v>
       </c>
       <c r="W6" t="n">
         <v>8.587256732606144e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>9.542250271770445e-08</v>
+        <v>9.54225027177044e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.581653527315888e-08</v>
+        <v>8.581653527315893e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.152646377480532e-08</v>
+        <v>8.152646377480535e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.786065843843227e-08</v>
+        <v>8.786065843843234e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.970134054216409e-08</v>
+        <v>8.970134054216413e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.596831100533249e-08</v>
+        <v>1.59683110053325e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.526043062534614e-08</v>
@@ -5959,37 +5959,37 @@
         <v>1.604093751429503e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.604521611228767e-08</v>
+        <v>1.604521611228768e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.60994666197185e-08</v>
+        <v>1.609946661971851e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.762110809163962e-08</v>
+        <v>1.762110809163963e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.599563994214212e-08</v>
+        <v>1.599563994214213e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.608178461416994e-08</v>
+        <v>1.608178461416995e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.667502787792574e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.617878328540796e-08</v>
+        <v>1.617878328540797e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.705308658845071e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.602442371146379e-08</v>
+        <v>1.602442371146378e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.605108833262126e-08</v>
+        <v>1.605108833262127e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.568912083200196e-08</v>
+        <v>2.568912083200197e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.635496808371463e-08</v>
@@ -6010,25 +6010,25 @@
         <v>2.249910702768812e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.605478175335405e-08</v>
+        <v>1.605478175335406e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.349491550736165e-08</v>
+        <v>2.349491550736166e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.665163579335135e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.642992867653365e-08</v>
+        <v>1.642992867653366e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>2.654973678349594e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.607710284546504e-08</v>
+        <v>1.607710284546505e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.156446370051322e-08</v>
+        <v>3.156446370051324e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.308172587553163e-08</v>
+        <v>1.556128117094854e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.382563489865664e-08</v>
+        <v>1.533108303365577e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.481333160715872e-08</v>
+        <v>1.61857848681996e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.826742508943585e-08</v>
+        <v>1.959261432895528e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.620109775906217e-08</v>
+        <v>1.666170359639581e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>6.111490039896668e-08</v>
+        <v>2.811558313537506e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.377724133415402e-08</v>
+        <v>1.584801184153487e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.577639940234759e-08</v>
+        <v>1.653258979847018e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.94178548775707e-08</v>
+        <v>2.104244547059162e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.801261634489713e-08</v>
+        <v>1.722789504299323e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.818207914204751e-08</v>
+        <v>2.393373614782743e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.535317385402081e-08</v>
+        <v>1.633477634735006e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.503398892850161e-08</v>
+        <v>1.625735623016004e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.358028246073052e-08</v>
+        <v>2.551879471388237e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.196480790423283e-08</v>
+        <v>1.855082135233631e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.628465793573482e-08</v>
+        <v>1.664422484123963e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.023153987535208e-08</v>
+        <v>1.810593001751421e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.736087866476862e-08</v>
+        <v>1.697721528731343e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.500570704562407e-08</v>
+        <v>1.625754331877391e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.082633438158367e-08</v>
+        <v>2.247410461755471e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.506026358084111e-08</v>
+        <v>1.619259886894475e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.772852722492279e-08</v>
+        <v>2.535081941778036e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.904353909153373e-08</v>
+        <v>2.106001166236901e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.382243165129476e-08</v>
+        <v>1.926703638889728e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.521447053892793e-08</v>
+        <v>2.660736610536848e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.56274646029968e-08</v>
+        <v>1.64547975604092e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.828065793213999e-07</v>
+        <v>1.422582905072817e-07</v>
       </c>
     </row>
     <row r="4">
@@ -6126,67 +6126,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.119716690878168e-08</v>
+        <v>7.119716690878171e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.607832910869259e-08</v>
+        <v>8.607832910869264e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.862039819922943e-08</v>
+        <v>8.862039819922946e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.401366712875847e-08</v>
+        <v>8.401366712875853e-08</v>
       </c>
       <c r="F4" t="n">
         <v>1.008092595699531e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>3.568718189984087e-07</v>
+        <v>3.568718189984089e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.12104568814064e-08</v>
+        <v>8.121045688140643e-08</v>
       </c>
       <c r="I4" t="n">
         <v>9.813434453510148e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>2.008859323165755e-07</v>
+        <v>2.008859323165756e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.120678061108274e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.675232081413933e-07</v>
+        <v>2.675232081413932e-07</v>
       </c>
       <c r="M4" t="n">
         <v>9.314067621941049e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.00178654393979e-08</v>
+        <v>9.001786543939788e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.752113809899403e-08</v>
+        <v>7.752113809899414e-08</v>
       </c>
       <c r="P4" t="n">
         <v>1.416321008154028e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.784120436143107e-08</v>
+        <v>9.784120436143104e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39790612519826e-07</v>
+        <v>1.397906125198261e-07</v>
       </c>
       <c r="S4" t="n">
         <v>1.037807422690166e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>9.070417003446704e-08</v>
+        <v>9.070417003446699e-08</v>
       </c>
       <c r="U4" t="n">
         <v>8.217816116247822e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.405624475215531e-08</v>
+        <v>8.40562447521553e-08</v>
       </c>
       <c r="W4" t="n">
         <v>1.367738104786051e-07</v>
@@ -6195,13 +6195,13 @@
         <v>2.099466370517946e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.643879337219362e-07</v>
+        <v>1.64387933721936e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.3395809008129e-08</v>
+        <v>8.339580900812898e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.45113487279699e-08</v>
+        <v>9.451134872796986e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>3.376555572204601e-06</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.328033873335106e-08</v>
+        <v>6.32803387333511e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.541513147922286e-08</v>
+        <v>7.541513147922288e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.551727317763313e-08</v>
+        <v>7.55172731776332e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>6.94866073704257e-08</v>
+        <v>6.948660737042571e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.654037218665281e-08</v>
+        <v>6.654037218665284e-08</v>
       </c>
       <c r="G5" t="n">
         <v>9.573332995538165e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.500561626225375e-08</v>
+        <v>7.500561626225378e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.597865996131493e-08</v>
+        <v>7.597865996131495e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.262569062046838e-08</v>
+        <v>8.262569062046844e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.707430457454154e-08</v>
+        <v>7.707430457454157e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.694996258179958e-08</v>
+        <v>8.694996258179962e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>7.57918761424163e-08</v>
+        <v>7.579187614241633e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>9.00178654393979e-08</v>
+        <v>6.678216830956927e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.867974610174758e-08</v>
+        <v>6.867974610174763e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.205048167536275e-08</v>
+        <v>7.205048167536278e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.257840031064379e-08</v>
+        <v>6.257840031064382e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.812197157532798e-08</v>
+        <v>7.812197157532802e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.678981029765045e-08</v>
+        <v>7.678981029765048e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>7.560891940024272e-08</v>
+        <v>7.560891940024276e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.9734138585886e-08</v>
+        <v>6.973413858588601e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>7.218259611876222e-08</v>
+        <v>7.218259611876227e-08</v>
       </c>
       <c r="W5" t="n">
         <v>7.831325469996316e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.980153977560474e-08</v>
+        <v>6.980153977560475e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.125558430200156e-08</v>
+        <v>9.125558430200162e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.386291650304556e-08</v>
+        <v>6.386291650304557e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.592577723007295e-08</v>
+        <v>7.592577723007299e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.604550555399337e-07</v>
+        <v>2.604550555399336e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.915708190667964e-08</v>
+        <v>6.915708190667962e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>7.646963619064508e-08</v>
+        <v>7.646963619064511e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>7.657177788905545e-08</v>
+        <v>7.657177788905542e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>7.509816309739556e-08</v>
+        <v>7.509816309739559e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>6.203111548226284e-08</v>
+        <v>6.203111548226286e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>9.442053754602498e-08</v>
+        <v>9.4420537546025e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>7.606012097367596e-08</v>
+        <v>7.6060120973676e-08</v>
       </c>
       <c r="I6" t="n">
         <v>7.703316467273718e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>8.368019533189064e-08</v>
+        <v>8.368019533189065e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7.81288092859638e-08</v>
+        <v>7.812880928596378e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>8.800446729322183e-08</v>
+        <v>8.80044672932218e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>7.684638085384063e-08</v>
+        <v>7.684638085384064e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>9.00178654393979e-08</v>
+        <v>7.668643605165748e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>7.833738788649076e-08</v>
+        <v>7.833738788649078e-08</v>
       </c>
       <c r="P6" t="n">
         <v>8.277954163496971e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.729311515738986e-08</v>
+        <v>7.729311515738987e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>7.917647628675023e-08</v>
+        <v>7.917647628675025e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>7.784431500907263e-08</v>
+        <v>7.784431500907262e-08</v>
       </c>
       <c r="T6" t="n">
         <v>7.666342411166497e-08</v>
@@ -6362,22 +6362,22 @@
         <v>7.636488518096491e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>8.397153201905885e-08</v>
+        <v>8.397153201905887e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>7.936551572628723e-08</v>
+        <v>7.936551572628722e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>8.346989588608481e-08</v>
+        <v>8.346989588608483e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.096561201131634e-08</v>
+        <v>8.096561201131633e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.257027282338534e-08</v>
+        <v>7.257027282338532e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.698028194149522e-08</v>
+        <v>7.698028194149519e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>2.495839829809606e-07</v>

--- a/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia particulate matter results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.83274227781741e-08</v>
+        <v>1.757255901383333e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.707613553408287e-08</v>
+        <v>1.643237620544662e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.296903629669624e-08</v>
+        <v>2.070304921598433e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.03487743512755e-08</v>
+        <v>1.995940498838534e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.236280989229567e-08</v>
+        <v>2.025252075187311e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.074170537696744e-08</v>
+        <v>3.343699509539514e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.091562365423406e-08</v>
+        <v>1.924497713096044e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.520332058123906e-08</v>
+        <v>2.221467132661137e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.695010359724295e-08</v>
+        <v>2.3629759828929e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.158629908697877e-08</v>
+        <v>2.665157017370536e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.008488834520288e-08</v>
+        <v>3.974745145841062e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.504579799563674e-08</v>
+        <v>2.209065104287269e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.677359093570432e-08</v>
+        <v>2.338636297599737e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.096065012070269e-08</v>
+        <v>2.969585810935098e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.902467851815606e-08</v>
+        <v>1.806626248704762e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.995660631956578e-08</v>
+        <v>1.865125919744392e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.046975065969426e-08</v>
+        <v>1.896107810538528e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.92234499137504e-08</v>
+        <v>1.819415472180276e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36103568343508e-08</v>
+        <v>2.113703383341307e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.882980677086517e-08</v>
+        <v>2.703068322811357e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.820088595803298e-08</v>
+        <v>1.749789209145498e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.830761612996001e-08</v>
+        <v>2.687323200900844e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.396461460402896e-08</v>
+        <v>2.1409483208592e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.908510270296284e-08</v>
+        <v>1.806436184809393e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.097979822571718e-08</v>
+        <v>2.969676490642796e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.529276809939645e-08</v>
+        <v>2.238344955849171e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.290858761627093e-08</v>
+        <v>2.058698574000194e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.457396916277824e-08</v>
+        <v>1.427627204132994e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.424292213500572e-08</v>
+        <v>1.377522116312792e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.481694233099262e-08</v>
+        <v>1.442687066185371e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8249805096639e-08</v>
+        <v>1.792934319121617e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.579641117647626e-08</v>
+        <v>1.510352025765982e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.593100596758831e-08</v>
+        <v>1.525766548311818e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.498373786747396e-08</v>
+        <v>1.452667604125502e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.529863795171838e-08</v>
+        <v>1.47552653479028e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.577759049631691e-08</v>
+        <v>1.51272757343427e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.550788875070045e-08</v>
+        <v>1.492963432996941e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.650649246413665e-08</v>
+        <v>1.565806265336049e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.497494329936114e-08</v>
+        <v>1.452043069862402e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.495219231406866e-08</v>
+        <v>1.452281591253939e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.427339793831646e-08</v>
+        <v>2.389521474420976e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.544761555117246e-08</v>
+        <v>1.490885179131227e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.492471212595586e-08</v>
+        <v>1.451276759036733e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.740370096345942e-08</v>
+        <v>1.618968070209002e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.565483572101637e-08</v>
+        <v>1.505495558201785e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.516401608556495e-08</v>
+        <v>1.466196497490094e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.171719944526995e-08</v>
+        <v>2.118765577519017e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.694027101025908e-08</v>
+        <v>1.600510084925242e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.650954622945959e-08</v>
+        <v>2.474435726192632e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.920703701846644e-08</v>
+        <v>1.752263575004862e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.69008311888974e-08</v>
+        <v>1.588001420337321e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.585258698644e-08</v>
+        <v>2.538137445768529e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.682131501935561e-08</v>
+        <v>1.582797354334616e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.460967656736311e-08</v>
+        <v>1.42678221497716e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.691652661768862e-08</v>
+        <v>1.633368154616393e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.638727761755544e-08</v>
+        <v>1.570019663360274e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.803807496220882e-08</v>
+        <v>1.705918729728254e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.952982204658349e-08</v>
+        <v>1.917261642486812e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.892627954681569e-08</v>
+        <v>1.766345201815085e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.412704197819417e-08</v>
+        <v>2.855074228871731e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.736196395544061e-08</v>
+        <v>1.657295929855294e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.030000914762989e-08</v>
+        <v>1.860005024097578e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.426100195687229e-08</v>
+        <v>2.150859664976614e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.76486245480036e-08</v>
+        <v>2.385571629297338e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.279501772804085e-08</v>
+        <v>3.440469730820702e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.102387936117269e-08</v>
+        <v>1.908540738304308e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.038379093274034e-08</v>
+        <v>1.870477463095459e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.802625522687477e-08</v>
+        <v>2.719387115187206e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.882189205913423e-08</v>
+        <v>1.768715085096743e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.762679021727915e-08</v>
+        <v>1.678981100506715e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.750602489994453e-08</v>
+        <v>1.668030632235331e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.797356833715044e-08</v>
+        <v>1.707547597321111e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.866390461835364e-08</v>
+        <v>1.748898278859803e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.582405452838453e-08</v>
+        <v>2.458986030176158e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.66570653043888e-08</v>
+        <v>1.616729724971378e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.934189370157863e-08</v>
+        <v>2.725861495873774e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.401426697684021e-08</v>
+        <v>2.119930310032554e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.811234506423859e-08</v>
+        <v>1.714339228309716e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.913433720541134e-08</v>
+        <v>2.810783349781837e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.983832191768161e-08</v>
+        <v>1.834537823512947e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.172582211060197e-08</v>
+        <v>1.952264304934409e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.594711770773001e-08</v>
+        <v>1.554149277750714e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.557089085978274e-08</v>
+        <v>1.502964005341159e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.839631588917244e-08</v>
+        <v>1.72025886096439e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.973942388283249e-08</v>
+        <v>1.923331163962745e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.787435343379425e-08</v>
+        <v>1.684100971592633e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.100049481493377e-08</v>
+        <v>2.628257474252431e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.598170525450221e-08</v>
+        <v>1.552458808022397e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.842141773837037e-08</v>
+        <v>1.720730153550038e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.253958244945469e-08</v>
+        <v>2.020779132969655e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.807487673945541e-08</v>
+        <v>1.703872159294468e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.752697280622141e-08</v>
+        <v>3.064140579096534e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.983572782827203e-08</v>
+        <v>1.816095543058847e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.71600865487602e-08</v>
+        <v>1.63622927459298e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.634062676785885e-08</v>
+        <v>2.579554936550131e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.764391321677034e-08</v>
+        <v>1.675480377897521e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.714396931381996e-08</v>
+        <v>1.635714672985672e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.587571338531223e-08</v>
+        <v>1.545874747631887e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.710561622565579e-08</v>
+        <v>1.63626706013261e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.693271605511877e-08</v>
+        <v>1.619032907299897e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.453738760988962e-08</v>
+        <v>2.354648863147545e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.624691871260482e-08</v>
+        <v>1.577853222478179e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.795771091412026e-08</v>
+        <v>2.6138250298279e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.767420291687631e-08</v>
+        <v>2.363501814483159e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.025646133043573e-08</v>
+        <v>1.853800574276356e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.857173204732844e-08</v>
+        <v>2.762606256230563e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.791370064031964e-08</v>
+        <v>1.689685072898733e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.105044369509242e-08</v>
+        <v>1.89496342576813e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.556641050410698e-08</v>
+        <v>1.520317396386628e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4924380396229e-08</v>
+        <v>1.448194362342023e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.644971978026106e-08</v>
+        <v>1.579520022975331e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.912041799780345e-08</v>
+        <v>1.874657608096367e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.765122237057969e-08</v>
+        <v>1.661758244063871e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.835916699530581e-08</v>
+        <v>2.442109297688473e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.577749806420969e-08</v>
+        <v>1.530839329006158e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.740844817480412e-08</v>
+        <v>1.644499221149882e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.089437331488344e-08</v>
+        <v>1.900522694926136e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.799845534750203e-08</v>
+        <v>1.691674917899448e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.228679671162116e-08</v>
+        <v>2.704162096229913e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.870484259872154e-08</v>
+        <v>1.734072782055899e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5527824114785e-08</v>
+        <v>1.515673574618208e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.606347632239571e-08</v>
+        <v>2.550091380502897e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.661514917044276e-08</v>
+        <v>1.596082607267389e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.668519603039628e-08</v>
+        <v>1.597322164842236e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.627522728331751e-08</v>
+        <v>1.565443564851922e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.690245767146117e-08</v>
+        <v>1.61540280707222e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.699989419474641e-08</v>
+        <v>1.616070404521861e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.433382397022674e-08</v>
+        <v>2.326541809435078e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.62067385335444e-08</v>
+        <v>1.56860930847039e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.54251981838138e-08</v>
+        <v>2.421271116705333e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.836572626170414e-08</v>
+        <v>2.41274482120455e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.228387106211038e-08</v>
+        <v>1.985438391849488e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.788621274540821e-08</v>
+        <v>2.708279259429165e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.77323035117001e-08</v>
+        <v>1.669476028366949e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.001168223946304e-08</v>
+        <v>1.818437739630696e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.522025117768835e-08</v>
+        <v>1.480785916675722e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.396249820709783e-08</v>
+        <v>1.366936172258679e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.843558357043552e-08</v>
+        <v>1.69981275748309e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.94055892970258e-08</v>
+        <v>1.880267630628967e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.573259333870471e-08</v>
+        <v>1.512922300176013e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.921096797241302e-08</v>
+        <v>1.772381798436883e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.634410654875746e-08</v>
+        <v>1.552814778530483e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.703244020324449e-08</v>
+        <v>1.601971136008257e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.748923209315879e-08</v>
+        <v>1.643449617771962e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.059788818357914e-08</v>
+        <v>1.860991958929595e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.212491219013856e-08</v>
+        <v>1.980948928864447e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.665784287728378e-08</v>
+        <v>1.578427489622128e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.880331839908475e-08</v>
+        <v>1.729850604471463e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.50526627764987e-08</v>
+        <v>2.458804017292814e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.718950791873042e-08</v>
+        <v>1.621209558786863e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.675568333375752e-08</v>
+        <v>1.586943537270239e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.668262747865469e-08</v>
+        <v>1.576646721895771e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.626350463816647e-08</v>
+        <v>1.558655064367111e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.597138985469094e-08</v>
+        <v>1.530439227218977e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.241554054473514e-08</v>
+        <v>2.179191183800582e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.516143124628133e-08</v>
+        <v>1.478449773054234e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.388382071153273e-08</v>
+        <v>2.30166983180078e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.702115943254887e-08</v>
+        <v>1.602988593331848e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.534652371787681e-08</v>
+        <v>1.487688120026383e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.704710290952788e-08</v>
+        <v>2.631801655273552e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.681741261865663e-08</v>
+        <v>1.590376402916184e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.536804108879372e-08</v>
+        <v>2.860406308530863e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.522600979001594e-08</v>
+        <v>1.472967860048451e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.450552149438423e-08</v>
+        <v>1.397078825180241e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.549705135257828e-08</v>
+        <v>1.489437279934653e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.903420417499457e-08</v>
+        <v>1.846370027964087e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.643800040436277e-08</v>
+        <v>1.554272049527022e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.598050553919092e-08</v>
+        <v>1.529849716756891e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.551212763105946e-08</v>
+        <v>1.487443218277307e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.588215306317538e-08</v>
+        <v>1.51490225713393e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.590571794043737e-08</v>
+        <v>1.522011939676174e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.529454250363187e-08</v>
+        <v>1.476283030649634e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.582517764499259e-08</v>
+        <v>1.519071452073556e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.480775673984981e-08</v>
+        <v>1.439845260447709e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.657096559593212e-08</v>
+        <v>1.566043353152421e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.674441708553593e-08</v>
+        <v>2.573162000829664e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.538230814660775e-08</v>
+        <v>1.484495635700157e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.490476471160354e-08</v>
+        <v>1.449630378725986e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.759631524788161e-08</v>
+        <v>1.632023112724064e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.562424764560947e-08</v>
+        <v>1.503982951439811e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.488693296270616e-08</v>
+        <v>1.446392636617707e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.091682422342725e-08</v>
+        <v>2.062342793034557e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.541639050164036e-08</v>
+        <v>1.489598856278122e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.462462398240232e-08</v>
+        <v>2.346199232101138e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.721943513489294e-08</v>
+        <v>1.611728657943095e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.528080821216297e-08</v>
+        <v>1.47439645437436e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.737893290153572e-08</v>
+        <v>2.649417020361801e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.569768827965237e-08</v>
+        <v>1.503628646839622e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.438442863088061e-08</v>
+        <v>1.410227940596852e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.604395900946345e-08</v>
+        <v>1.533081036078929e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.461630323655899e-08</v>
+        <v>1.403675288324871e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.565678478718702e-08</v>
+        <v>1.501548534428957e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.006141972948005e-08</v>
+        <v>1.923575538951165e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.601043798444587e-08</v>
+        <v>1.524860634523508e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.532938980993294e-08</v>
+        <v>1.482334960389775e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.508516345939469e-08</v>
+        <v>1.459848920220191e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.519671624635513e-08</v>
+        <v>1.468572612541598e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.575018055341612e-08</v>
+        <v>1.511172017356677e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.494720607156815e-08</v>
+        <v>1.452383390103433e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.593734483139912e-08</v>
+        <v>1.526734956720639e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.475988828492686e-08</v>
+        <v>1.437284681419218e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.535614169812767e-08</v>
+        <v>1.481218818465495e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.697153340362824e-08</v>
+        <v>2.590437554400173e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.587258002625734e-08</v>
+        <v>1.521763272726295e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.479677437571635e-08</v>
+        <v>1.442460999768226e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.815256822523591e-08</v>
+        <v>1.670795923790192e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.560295237266115e-08</v>
+        <v>1.502042144384651e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.477526753301979e-08</v>
+        <v>1.439716240457401e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.108015276518563e-08</v>
+        <v>2.071040934004705e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.726735375609383e-08</v>
+        <v>1.624018109593706e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.531129106843878e-08</v>
+        <v>2.391250257521758e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.780104044029623e-08</v>
+        <v>1.655274881152244e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.542909140394683e-08</v>
+        <v>1.485863460427502e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.669292242891059e-08</v>
+        <v>2.601011309988427e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.574755020392874e-08</v>
+        <v>1.508378905777242e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.478066377575336e-08</v>
+        <v>1.438773809742707e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.662521565638726e-08</v>
+        <v>1.607540530799654e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.544499695766909e-08</v>
+        <v>1.49847083208408e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.892391449505282e-08</v>
+        <v>1.761169647743549e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.942402372703743e-08</v>
+        <v>1.905725797501519e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.798864064828069e-08</v>
+        <v>1.696967327092186e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.282920197209486e-08</v>
+        <v>2.7734851563216e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.728102423633626e-08</v>
+        <v>1.64609155053706e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.094658373154029e-08</v>
+        <v>1.899913234661054e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.344352018340422e-08</v>
+        <v>2.094203156350347e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.443435853815805e-08</v>
+        <v>2.160720532488251e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.901420978186e-08</v>
+        <v>3.188795941483988e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.083926154078788e-08</v>
+        <v>1.898762569387831e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.308145576485856e-08</v>
+        <v>2.052248619385045e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.761201716937985e-08</v>
+        <v>2.680961971478471e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.88684991957192e-08</v>
+        <v>1.766922227160625e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.755528379870639e-08</v>
+        <v>1.669541655081541e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.814349036052472e-08</v>
+        <v>1.705779806711846e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.752065875557867e-08</v>
+        <v>1.672580593140472e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.919691461087054e-08</v>
+        <v>1.780010745116771e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.493158293470157e-08</v>
+        <v>2.385416853816706e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.635958072660197e-08</v>
+        <v>1.590331543719267e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.509135740583944e-08</v>
+        <v>2.416614398343827e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.466933565331243e-08</v>
+        <v>2.15985359039472e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.773966659663335e-08</v>
+        <v>1.682999269408731e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.877091258435283e-08</v>
+        <v>2.77971998080922e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.919211760162864e-08</v>
+        <v>1.78412329358568e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.06923477491011e-08</v>
+        <v>1.876857680841514e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.556128117094854e-08</v>
+        <v>1.523016304245056e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.533108303365577e-08</v>
+        <v>1.481879189759179e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.61857848681996e-08</v>
+        <v>1.564228209495194e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.959261432895528e-08</v>
+        <v>1.910865924475364e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.666170359639581e-08</v>
+        <v>1.597073746193004e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.811558313537506e-08</v>
+        <v>2.436892061888112e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.584801184153487e-08</v>
+        <v>1.539275216546042e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.653258979847018e-08</v>
+        <v>1.587328636441659e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.104244547059162e-08</v>
+        <v>1.915376915508216e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.722789504299323e-08</v>
+        <v>1.640436980194764e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.393373614782743e-08</v>
+        <v>2.124794969097137e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.633477634735006e-08</v>
+        <v>1.573696274917519e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.625735623016004e-08</v>
+        <v>1.569744371798564e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.551879471388237e-08</v>
+        <v>2.511190453641444e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.855082135233631e-08</v>
+        <v>1.737456589182887e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.664422484123963e-08</v>
+        <v>1.599199648471169e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.810593001751421e-08</v>
+        <v>1.69411754531206e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.697721528731343e-08</v>
+        <v>1.625605919815472e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.625754331877391e-08</v>
+        <v>1.568855720448654e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.247410461755471e-08</v>
+        <v>2.201036458869426e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.619259886894475e-08</v>
+        <v>1.570479476754867e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.535081941778036e-08</v>
+        <v>2.422707409058322e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.106001166236901e-08</v>
+        <v>1.90527403346635e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.926703638889728e-08</v>
+        <v>1.781051871210912e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.660736610536848e-08</v>
+        <v>2.613036766572219e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.64547975604092e-08</v>
+        <v>1.584116313863399e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.422582905072817e-07</v>
+        <v>1.018685833450772e-07</v>
       </c>
     </row>
     <row r="4">
